--- a/InputData/bldgs/BDESC/BAU Distribued Electricity Source Capacities.xlsx
+++ b/InputData/bldgs/BDESC/BAU Distribued Electricity Source Capacities.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Olivia Ashmoore\Documents\EPS_Models by Region\United States\us-eps\InputData\bldgs\BDESC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEF52A99-7564-4EF3-AEB4-281A3673C0EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F76CAA9-DCF1-437A-8271-E84E3059A6C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{78C42925-BD2F-4DDC-9C55-3AA1D702B622}"/>
+    <workbookView xWindow="6665" yWindow="0" windowWidth="12615" windowHeight="10155" xr2:uid="{78C42925-BD2F-4DDC-9C55-3AA1D702B622}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1971" uniqueCount="835">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1972" uniqueCount="836">
   <si>
     <t>Energy Information Administration</t>
   </si>
@@ -2700,6 +2700,9 @@
   </si>
   <si>
     <t>https://www.eia.gov/outlooks/aeo/tables_side_xls.php</t>
+  </si>
+  <si>
+    <t>Scenario: High zero-carbon technology cost</t>
   </si>
 </sst>
 </file>
@@ -3493,7 +3496,7 @@
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -3626,7 +3629,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="54">
     <cellStyle name="20% - Accent1" xfId="28" builtinId="30" customBuiltin="1"/>
@@ -12861,20 +12863,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F29"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
-    <col min="1" max="1" width="51.85546875" customWidth="1"/>
+    <col min="1" max="1" width="51.86328125" customWidth="1"/>
     <col min="2" max="2" width="51" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.40625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.86328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A1" s="1" t="s">
         <v>337</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A3" s="1" t="s">
         <v>53</v>
       </c>
@@ -12882,97 +12884,102 @@
         <v>301</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.75">
       <c r="B4" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.75">
       <c r="B5" s="2" t="s">
         <v>831</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B6" s="66" t="s">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="B6" t="s">
         <v>833</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.75">
       <c r="B7" t="s">
         <v>832</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.75">
       <c r="B8" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="B9" t="s">
         <v>834</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B9" t="s">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="B10" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.75">
       <c r="B12" s="3" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.75">
       <c r="B13" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.75">
       <c r="B14" s="2">
         <v>2020</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.75">
       <c r="B15" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.75">
       <c r="B16" s="18" t="s">
         <v>273</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.75">
       <c r="B17" s="18" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.75">
       <c r="B18" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A20" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A21" t="s">
         <v>326</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A22" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A23" t="s">
         <v>583</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A24" s="1" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A25" s="8">
         <f>'RECS HC2.1'!B24/SUM('RECS HC2.1'!B24,'RECS HC2.1'!B27)</f>
         <v>0.81308184246741677</v>
@@ -12981,7 +12988,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A26" s="8">
         <f>'RECS HC2.1'!B27/SUM('RECS HC2.1'!B24,'RECS HC2.1'!B27)</f>
         <v>0.18691815753258317</v>
@@ -12990,7 +12997,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="28" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A28" s="10" t="s">
         <v>165</v>
       </c>
@@ -13002,7 +13009,7 @@
       <c r="D28" s="12"/>
       <c r="E28" s="13"/>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A29" t="s">
         <v>173</v>
       </c>
@@ -13028,16 +13035,16 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:AL79"/>
-  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.7"/>
   <cols>
-    <col min="1" max="1" width="50.5703125" style="34" customWidth="1"/>
-    <col min="2" max="2" width="16.42578125" style="34" customWidth="1"/>
-    <col min="3" max="3" width="15.28515625" style="34" customWidth="1"/>
-    <col min="4" max="4" width="15.42578125" style="34" customWidth="1"/>
-    <col min="5" max="16384" width="12.5703125" style="34"/>
+    <col min="1" max="1" width="50.54296875" style="34" customWidth="1"/>
+    <col min="2" max="2" width="16.40625" style="34" customWidth="1"/>
+    <col min="3" max="3" width="15.26953125" style="34" customWidth="1"/>
+    <col min="4" max="4" width="15.40625" style="34" customWidth="1"/>
+    <col min="5" max="16384" width="12.54296875" style="34"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:38" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:38" ht="14.25" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A1" s="32" t="s">
         <v>302</v>
       </c>
@@ -13079,59 +13086,59 @@
       <c r="AK1" s="33"/>
       <c r="AL1" s="33"/>
     </row>
-    <row r="2" spans="1:38" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:38" ht="13.5" x14ac:dyDescent="0.7">
       <c r="A2" s="35" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="3" spans="1:38" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:38" ht="13.5" x14ac:dyDescent="0.7">
       <c r="A3" s="35"/>
     </row>
-    <row r="4" spans="1:38" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:38" ht="13.5" x14ac:dyDescent="0.7">
       <c r="A4" s="35" t="s">
         <v>310</v>
       </c>
     </row>
-    <row r="5" spans="1:38" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:38" ht="13.5" x14ac:dyDescent="0.7">
       <c r="A5" s="35" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="6" spans="1:38" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:38" ht="13.5" x14ac:dyDescent="0.7">
       <c r="A6" s="35" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="7" spans="1:38" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:38" ht="13.5" x14ac:dyDescent="0.7">
       <c r="A7" s="35"/>
     </row>
-    <row r="8" spans="1:38" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:38" ht="13.5" x14ac:dyDescent="0.7">
       <c r="A8" s="35" t="s">
         <v>313</v>
       </c>
     </row>
-    <row r="9" spans="1:38" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:38" ht="13.5" x14ac:dyDescent="0.7">
       <c r="A9" s="35" t="s">
         <v>314</v>
       </c>
     </row>
-    <row r="10" spans="1:38" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:38" ht="13.5" x14ac:dyDescent="0.7">
       <c r="A10" s="35"/>
     </row>
-    <row r="11" spans="1:38" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:38" ht="13.5" x14ac:dyDescent="0.7">
       <c r="A11" s="35" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="12" spans="1:38" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:38" ht="13.5" x14ac:dyDescent="0.7">
       <c r="A12" s="35" t="s">
         <v>316</v>
       </c>
     </row>
-    <row r="13" spans="1:38" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:38" ht="13.5" x14ac:dyDescent="0.7">
       <c r="A13" s="35"/>
     </row>
-    <row r="14" spans="1:38" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:38" ht="14.25" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A14" s="32" t="s">
         <v>303</v>
       </c>
@@ -13173,27 +13180,27 @@
       <c r="AK14" s="33"/>
       <c r="AL14" s="33"/>
     </row>
-    <row r="15" spans="1:38" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:38" ht="13.5" x14ac:dyDescent="0.7">
       <c r="A15" s="36"/>
       <c r="B15" s="37"/>
     </row>
-    <row r="16" spans="1:38" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:38" ht="13.5" x14ac:dyDescent="0.7">
       <c r="A16" s="35" t="s">
         <v>304</v>
       </c>
       <c r="B16" s="37"/>
     </row>
-    <row r="17" spans="1:31" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:31" ht="13.5" x14ac:dyDescent="0.7">
       <c r="A17" s="35" t="s">
         <v>305</v>
       </c>
       <c r="B17" s="37"/>
     </row>
-    <row r="18" spans="1:31" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:31" ht="13.5" x14ac:dyDescent="0.7">
       <c r="A18" s="35"/>
       <c r="B18" s="37"/>
     </row>
-    <row r="19" spans="1:31" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:31" ht="13.5" x14ac:dyDescent="0.7">
       <c r="A19" s="35" t="s">
         <v>317</v>
       </c>
@@ -13201,7 +13208,7 @@
         <v>3.3</v>
       </c>
     </row>
-    <row r="20" spans="1:31" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:31" ht="13.5" x14ac:dyDescent="0.7">
       <c r="A20" s="35" t="s">
         <v>318</v>
       </c>
@@ -13209,15 +13216,15 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="21" spans="1:31" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:31" ht="13.5" x14ac:dyDescent="0.7">
       <c r="A21" s="35"/>
       <c r="B21" s="37"/>
     </row>
-    <row r="22" spans="1:31" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:31" ht="13.5" x14ac:dyDescent="0.7">
       <c r="A22" s="35"/>
       <c r="B22" s="37"/>
     </row>
-    <row r="23" spans="1:31" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:31" ht="27" x14ac:dyDescent="0.7">
       <c r="A23" s="40" t="s">
         <v>306</v>
       </c>
@@ -13225,7 +13232,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:31" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:31" ht="13.5" x14ac:dyDescent="0.7">
       <c r="A24" s="35" t="s">
         <v>307</v>
       </c>
@@ -13233,21 +13240,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:31" ht="15" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:31" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A25" s="39"/>
       <c r="C25" s="38"/>
     </row>
-    <row r="26" spans="1:31" s="44" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:31" s="44" customFormat="1" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A26" s="43" t="s">
         <v>338</v>
       </c>
     </row>
-    <row r="27" spans="1:31" s="44" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:31" s="44" customFormat="1" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A27" s="45" t="s">
         <v>338</v>
       </c>
     </row>
-    <row r="28" spans="1:31" s="44" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:31" s="44" customFormat="1" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A28" s="44" t="s">
         <v>581</v>
       </c>
@@ -13258,13 +13265,13 @@
         <v>582</v>
       </c>
     </row>
-    <row r="29" spans="1:31" s="44" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:31" s="44" customFormat="1" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A29" s="44" t="s">
         <v>339</v>
       </c>
     </row>
-    <row r="30" spans="1:31" s="44" customFormat="1" ht="15" x14ac:dyDescent="0.25"/>
-    <row r="31" spans="1:31" s="44" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:31" s="44" customFormat="1" ht="14.75" x14ac:dyDescent="0.75"/>
+    <row r="31" spans="1:31" s="44" customFormat="1" ht="14.75" x14ac:dyDescent="0.75">
       <c r="B31" s="44">
         <v>2021</v>
       </c>
@@ -13356,7 +13363,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="32" spans="1:31" s="44" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:31" s="44" customFormat="1" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A32" s="44" t="s">
         <v>340</v>
       </c>
@@ -13451,15 +13458,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:31" s="44" customFormat="1" ht="15" x14ac:dyDescent="0.25"/>
-    <row r="34" spans="1:31" s="44" customFormat="1" ht="15" x14ac:dyDescent="0.25"/>
-    <row r="35" spans="1:31" s="44" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:31" s="44" customFormat="1" ht="14.75" x14ac:dyDescent="0.75"/>
+    <row r="34" spans="1:31" s="44" customFormat="1" ht="14.75" x14ac:dyDescent="0.75"/>
+    <row r="35" spans="1:31" s="44" customFormat="1" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A35" s="43" t="s">
         <v>341</v>
       </c>
     </row>
-    <row r="36" spans="1:31" s="44" customFormat="1" ht="15" x14ac:dyDescent="0.25"/>
-    <row r="37" spans="1:31" s="44" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:31" s="44" customFormat="1" ht="14.75" x14ac:dyDescent="0.75"/>
+    <row r="37" spans="1:31" s="44" customFormat="1" ht="29.5" x14ac:dyDescent="0.75">
       <c r="A37" s="45" t="s">
         <v>342</v>
       </c>
@@ -13467,7 +13474,7 @@
         <v>2.4805304788796994</v>
       </c>
     </row>
-    <row r="38" spans="1:31" s="44" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:31" s="44" customFormat="1" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A38" s="45" t="s">
         <v>343</v>
       </c>
@@ -13475,7 +13482,7 @@
         <v>9.9221219155187974</v>
       </c>
     </row>
-    <row r="39" spans="1:31" s="44" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:31" s="44" customFormat="1" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A39" s="44" t="s">
         <v>344</v>
       </c>
@@ -13483,8 +13490,8 @@
         <v>7</v>
       </c>
     </row>
-    <row r="40" spans="1:31" s="44" customFormat="1" ht="15" x14ac:dyDescent="0.25"/>
-    <row r="41" spans="1:31" s="44" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:31" s="44" customFormat="1" ht="14.75" x14ac:dyDescent="0.75"/>
+    <row r="41" spans="1:31" s="44" customFormat="1" ht="14.75" x14ac:dyDescent="0.75">
       <c r="B41" s="44">
         <v>2021</v>
       </c>
@@ -13576,7 +13583,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="42" spans="1:31" s="44" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:31" s="44" customFormat="1" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A42" s="44" t="s">
         <v>340</v>
       </c>
@@ -13671,14 +13678,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:31" s="46" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="44" spans="1:31" s="44" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:31" s="46" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.7"/>
+    <row r="44" spans="1:31" s="44" customFormat="1" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A44" s="43" t="s">
         <v>345</v>
       </c>
     </row>
-    <row r="45" spans="1:31" s="44" customFormat="1" ht="15" x14ac:dyDescent="0.25"/>
-    <row r="46" spans="1:31" s="44" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:31" s="44" customFormat="1" ht="14.75" x14ac:dyDescent="0.75"/>
+    <row r="46" spans="1:31" s="44" customFormat="1" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A46" s="44" t="s">
         <v>346</v>
       </c>
@@ -13686,8 +13693,8 @@
         <v>281</v>
       </c>
     </row>
-    <row r="47" spans="1:31" s="44" customFormat="1" ht="15" x14ac:dyDescent="0.25"/>
-    <row r="48" spans="1:31" s="44" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:31" s="44" customFormat="1" ht="14.75" x14ac:dyDescent="0.75"/>
+    <row r="48" spans="1:31" s="44" customFormat="1" ht="14.75" x14ac:dyDescent="0.75">
       <c r="B48" s="44">
         <v>2021</v>
       </c>
@@ -13779,7 +13786,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="49" spans="1:31" s="44" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:31" s="44" customFormat="1" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A49" s="44" t="s">
         <v>340</v>
       </c>
@@ -13874,7 +13881,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.7">
       <c r="B56" s="34">
         <v>2023</v>
       </c>
@@ -13960,7 +13967,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="57" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A57" s="34" t="s">
         <v>324</v>
       </c>
@@ -14077,7 +14084,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A58" s="34" t="s">
         <v>325</v>
       </c>
@@ -14194,7 +14201,7 @@
         <v>14203.121915518801</v>
       </c>
     </row>
-    <row r="59" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A59" s="34" t="s">
         <v>320</v>
       </c>
@@ -14311,7 +14318,7 @@
         <v>11548.300535859373</v>
       </c>
     </row>
-    <row r="60" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A60" s="34" t="s">
         <v>321</v>
       </c>
@@ -14428,7 +14435,7 @@
         <v>2654.8213796594277</v>
       </c>
     </row>
-    <row r="61" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A61" s="34" t="s">
         <v>322</v>
       </c>
@@ -14545,7 +14552,7 @@
         <v>16135327.368901607</v>
       </c>
     </row>
-    <row r="62" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A62" s="34" t="s">
         <v>323</v>
       </c>
@@ -14662,13 +14669,13 @@
         <v>3709326.0548380939</v>
       </c>
     </row>
-    <row r="65" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:3" ht="14.75" x14ac:dyDescent="0.75">
       <c r="C65" s="38"/>
     </row>
-    <row r="66" spans="1:3" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="67" spans="1:3" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="68" spans="1:3" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="79" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:3" ht="13.5" x14ac:dyDescent="0.7"/>
+    <row r="67" spans="1:3" ht="13.5" x14ac:dyDescent="0.7"/>
+    <row r="68" spans="1:3" ht="13.5" x14ac:dyDescent="0.7"/>
+    <row r="79" spans="1:3" ht="13.5" x14ac:dyDescent="0.7">
       <c r="A79" s="35" t="s">
         <v>308</v>
       </c>
@@ -14685,13 +14692,13 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AC25"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
-    <col min="1" max="1" width="31.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="29" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="31.1328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="29" width="9.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:29" x14ac:dyDescent="0.75">
       <c r="A1" t="s">
         <v>161</v>
       </c>
@@ -14780,7 +14787,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:29" x14ac:dyDescent="0.75">
       <c r="A2" t="s">
         <v>58</v>
       </c>
@@ -14869,7 +14876,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:29" x14ac:dyDescent="0.75">
       <c r="A3" t="s">
         <v>328</v>
       </c>
@@ -14958,7 +14965,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:29" x14ac:dyDescent="0.75">
       <c r="A4" t="s">
         <v>329</v>
       </c>
@@ -15075,7 +15082,7 @@
         <v>3.4027475107261393</v>
       </c>
     </row>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.75">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -15164,7 +15171,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.75">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -15253,7 +15260,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.75">
       <c r="A7" t="s">
         <v>59</v>
       </c>
@@ -15370,7 +15377,7 @@
         <v>1792.7397620011334</v>
       </c>
     </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:29" x14ac:dyDescent="0.75">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -15487,7 +15494,7 @@
         <v>172476.23879252005</v>
       </c>
     </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:29" x14ac:dyDescent="0.75">
       <c r="A9" t="s">
         <v>11</v>
       </c>
@@ -15576,7 +15583,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:29" x14ac:dyDescent="0.75">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -15665,7 +15672,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:29" x14ac:dyDescent="0.75">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -15754,7 +15761,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:29" x14ac:dyDescent="0.75">
       <c r="A12" t="s">
         <v>14</v>
       </c>
@@ -15843,7 +15850,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:29" x14ac:dyDescent="0.75">
       <c r="A13" t="s">
         <v>15</v>
       </c>
@@ -15932,7 +15939,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:29" x14ac:dyDescent="0.75">
       <c r="A14" t="s">
         <v>57</v>
       </c>
@@ -16021,7 +16028,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:29" x14ac:dyDescent="0.75">
       <c r="A15" t="s">
         <v>60</v>
       </c>
@@ -16110,7 +16117,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:29" x14ac:dyDescent="0.75">
       <c r="A16" t="s">
         <v>158</v>
       </c>
@@ -16199,7 +16206,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:29" x14ac:dyDescent="0.75">
       <c r="A17" t="s">
         <v>159</v>
       </c>
@@ -16288,7 +16295,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:29" x14ac:dyDescent="0.75">
       <c r="A18" t="s">
         <v>160</v>
       </c>
@@ -16377,7 +16384,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:29" x14ac:dyDescent="0.75">
       <c r="A19" s="55" t="s">
         <v>330</v>
       </c>
@@ -16466,7 +16473,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:29" x14ac:dyDescent="0.75">
       <c r="A20" s="55" t="s">
         <v>331</v>
       </c>
@@ -16555,7 +16562,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:29" x14ac:dyDescent="0.75">
       <c r="A21" s="55" t="s">
         <v>332</v>
       </c>
@@ -16644,7 +16651,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:29" x14ac:dyDescent="0.75">
       <c r="A22" s="55" t="s">
         <v>333</v>
       </c>
@@ -16733,7 +16740,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:29" x14ac:dyDescent="0.75">
       <c r="A23" s="55" t="s">
         <v>334</v>
       </c>
@@ -16822,7 +16829,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:29" x14ac:dyDescent="0.75">
       <c r="A24" s="56" t="s">
         <v>335</v>
       </c>
@@ -16911,7 +16918,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:29" x14ac:dyDescent="0.75">
       <c r="A25" s="56" t="s">
         <v>336</v>
       </c>
@@ -17011,13 +17018,13 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AC25"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
-    <col min="1" max="1" width="23.42578125" customWidth="1"/>
-    <col min="2" max="29" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.40625" customWidth="1"/>
+    <col min="2" max="29" width="9.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:29" x14ac:dyDescent="0.75">
       <c r="A1" t="s">
         <v>161</v>
       </c>
@@ -17106,7 +17113,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:29" x14ac:dyDescent="0.75">
       <c r="A2" t="s">
         <v>58</v>
       </c>
@@ -17222,7 +17229,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:29" x14ac:dyDescent="0.75">
       <c r="A3" t="s">
         <v>328</v>
       </c>
@@ -17311,7 +17318,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:29" x14ac:dyDescent="0.75">
       <c r="A4" t="s">
         <v>329</v>
       </c>
@@ -17428,7 +17435,7 @@
         <v>0.78225248927386071</v>
       </c>
     </row>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.75">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -17545,7 +17552,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.75">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -17662,7 +17669,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.75">
       <c r="A7" t="s">
         <v>59</v>
       </c>
@@ -17779,7 +17786,7 @@
         <v>412.13023799886668</v>
       </c>
     </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:29" x14ac:dyDescent="0.75">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -17896,7 +17903,7 @@
         <v>39650.302207479966</v>
       </c>
     </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:29" x14ac:dyDescent="0.75">
       <c r="A9" t="s">
         <v>11</v>
       </c>
@@ -18013,7 +18020,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:29" x14ac:dyDescent="0.75">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -18130,7 +18137,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:29" x14ac:dyDescent="0.75">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -18247,7 +18254,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:29" x14ac:dyDescent="0.75">
       <c r="A12" t="s">
         <v>14</v>
       </c>
@@ -18364,7 +18371,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:29" x14ac:dyDescent="0.75">
       <c r="A13" t="s">
         <v>15</v>
       </c>
@@ -18481,7 +18488,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:29" x14ac:dyDescent="0.75">
       <c r="A14" t="s">
         <v>57</v>
       </c>
@@ -18598,7 +18605,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:29" x14ac:dyDescent="0.75">
       <c r="A15" t="s">
         <v>60</v>
       </c>
@@ -18715,7 +18722,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:29" x14ac:dyDescent="0.75">
       <c r="A16" t="s">
         <v>158</v>
       </c>
@@ -18832,7 +18839,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:29" x14ac:dyDescent="0.75">
       <c r="A17" t="s">
         <v>159</v>
       </c>
@@ -18949,7 +18956,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:29" x14ac:dyDescent="0.75">
       <c r="A18" t="s">
         <v>160</v>
       </c>
@@ -19066,7 +19073,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:29" x14ac:dyDescent="0.75">
       <c r="A19" s="55" t="s">
         <v>330</v>
       </c>
@@ -19155,7 +19162,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:29" x14ac:dyDescent="0.75">
       <c r="A20" s="55" t="s">
         <v>331</v>
       </c>
@@ -19244,7 +19251,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:29" x14ac:dyDescent="0.75">
       <c r="A21" s="55" t="s">
         <v>332</v>
       </c>
@@ -19333,7 +19340,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:29" x14ac:dyDescent="0.75">
       <c r="A22" s="55" t="s">
         <v>333</v>
       </c>
@@ -19422,7 +19429,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:29" x14ac:dyDescent="0.75">
       <c r="A23" s="55" t="s">
         <v>334</v>
       </c>
@@ -19511,7 +19518,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:29" x14ac:dyDescent="0.75">
       <c r="A24" s="56" t="s">
         <v>335</v>
       </c>
@@ -19600,7 +19607,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:29" x14ac:dyDescent="0.75">
       <c r="A25" s="56" t="s">
         <v>336</v>
       </c>
@@ -19700,13 +19707,13 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AC25"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
-    <col min="1" max="1" width="23.42578125" customWidth="1"/>
-    <col min="2" max="29" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.40625" customWidth="1"/>
+    <col min="2" max="29" width="9.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:29" x14ac:dyDescent="0.75">
       <c r="A1" t="s">
         <v>161</v>
       </c>
@@ -19795,7 +19802,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:29" x14ac:dyDescent="0.75">
       <c r="A2" t="s">
         <v>58</v>
       </c>
@@ -19912,7 +19919,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:29" x14ac:dyDescent="0.75">
       <c r="A3" t="s">
         <v>328</v>
       </c>
@@ -20001,7 +20008,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:29" x14ac:dyDescent="0.75">
       <c r="A4" t="s">
         <v>329</v>
       </c>
@@ -20118,7 +20125,7 @@
         <v>2128.86</v>
       </c>
     </row>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.75">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -20235,7 +20242,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.75">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -20352,7 +20359,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.75">
       <c r="A7" t="s">
         <v>59</v>
       </c>
@@ -20469,7 +20476,7 @@
         <v>613.52099999999996</v>
       </c>
     </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:29" x14ac:dyDescent="0.75">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -20586,7 +20593,7 @@
         <v>86847.686999999991</v>
       </c>
     </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:29" x14ac:dyDescent="0.75">
       <c r="A9" t="s">
         <v>11</v>
       </c>
@@ -20703,7 +20710,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:29" x14ac:dyDescent="0.75">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -20820,7 +20827,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:29" x14ac:dyDescent="0.75">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -20937,7 +20944,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:29" x14ac:dyDescent="0.75">
       <c r="A12" t="s">
         <v>14</v>
       </c>
@@ -21054,7 +21061,7 @@
         <v>20.507000000000001</v>
       </c>
     </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:29" x14ac:dyDescent="0.75">
       <c r="A13" t="s">
         <v>15</v>
       </c>
@@ -21171,7 +21178,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:29" x14ac:dyDescent="0.75">
       <c r="A14" t="s">
         <v>57</v>
       </c>
@@ -21288,7 +21295,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:29" x14ac:dyDescent="0.75">
       <c r="A15" t="s">
         <v>60</v>
       </c>
@@ -21405,7 +21412,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:29" x14ac:dyDescent="0.75">
       <c r="A16" t="s">
         <v>158</v>
       </c>
@@ -21522,7 +21529,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:29" x14ac:dyDescent="0.75">
       <c r="A17" t="s">
         <v>159</v>
       </c>
@@ -21639,7 +21646,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:29" x14ac:dyDescent="0.75">
       <c r="A18" t="s">
         <v>160</v>
       </c>
@@ -21756,7 +21763,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:29" x14ac:dyDescent="0.75">
       <c r="A19" s="55" t="s">
         <v>330</v>
       </c>
@@ -21845,7 +21852,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:29" x14ac:dyDescent="0.75">
       <c r="A20" s="55" t="s">
         <v>331</v>
       </c>
@@ -21934,7 +21941,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:29" x14ac:dyDescent="0.75">
       <c r="A21" s="55" t="s">
         <v>332</v>
       </c>
@@ -22023,7 +22030,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:29" x14ac:dyDescent="0.75">
       <c r="A22" s="55" t="s">
         <v>333</v>
       </c>
@@ -22112,7 +22119,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:29" x14ac:dyDescent="0.75">
       <c r="A23" s="55" t="s">
         <v>334</v>
       </c>
@@ -22201,7 +22208,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:29" x14ac:dyDescent="0.75">
       <c r="A24" s="56" t="s">
         <v>335</v>
       </c>
@@ -22290,7 +22297,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:29" x14ac:dyDescent="0.75">
       <c r="A25" s="56" t="s">
         <v>336</v>
       </c>
@@ -22390,7 +22397,7 @@
     <tabColor theme="0" tint="-0.34998626667073579"/>
   </sheetPr>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -22399,33 +22406,33 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9D8ACAE-8802-46BC-8EDF-731327A79C5C}">
   <dimension ref="A1:AI93"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
-    <col min="1" max="1" width="27.42578125" customWidth="1"/>
+    <col min="1" max="1" width="27.40625" customWidth="1"/>
     <col min="2" max="2" width="102" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A1" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="2" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A2" t="s">
         <v>347</v>
       </c>
     </row>
-    <row r="3" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A3" t="s">
         <v>348</v>
       </c>
     </row>
-    <row r="4" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A4" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.75">
       <c r="B5" t="s">
         <v>178</v>
       </c>
@@ -22529,17 +22536,17 @@
         <v>349</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A6" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A7" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A8" t="s">
         <v>182</v>
       </c>
@@ -22643,7 +22650,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A9" t="s">
         <v>184</v>
       </c>
@@ -22747,7 +22754,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A10" t="s">
         <v>185</v>
       </c>
@@ -22851,7 +22858,7 @@
         <v>-1E-3</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A11" t="s">
         <v>186</v>
       </c>
@@ -22955,7 +22962,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A12" t="s">
         <v>187</v>
       </c>
@@ -23059,7 +23066,7 @@
         <v>-7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A13" t="s">
         <v>149</v>
       </c>
@@ -23163,7 +23170,7 @@
         <v>-1E-3</v>
       </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A14" t="s">
         <v>188</v>
       </c>
@@ -23267,7 +23274,7 @@
         <v>0.104</v>
       </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A15" t="s">
         <v>189</v>
       </c>
@@ -23371,7 +23378,7 @@
         <v>-8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A16" t="s">
         <v>190</v>
       </c>
@@ -23475,7 +23482,7 @@
         <v>4.1000000000000002E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A17" t="s">
         <v>191</v>
       </c>
@@ -23579,12 +23586,12 @@
         <v>8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="18" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A18" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="19" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A19" t="s">
         <v>182</v>
       </c>
@@ -23688,7 +23695,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A20" t="s">
         <v>185</v>
       </c>
@@ -23792,7 +23799,7 @@
         <v>-1E-3</v>
       </c>
     </row>
-    <row r="21" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A21" t="s">
         <v>190</v>
       </c>
@@ -23896,7 +23903,7 @@
         <v>4.1000000000000002E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A22" t="s">
         <v>193</v>
       </c>
@@ -24000,7 +24007,7 @@
         <v>1.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A23" t="s">
         <v>194</v>
       </c>
@@ -24104,7 +24111,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A24" t="s">
         <v>191</v>
       </c>
@@ -24208,12 +24215,12 @@
         <v>1.0999999999999999E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A25" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="26" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A26" t="s">
         <v>196</v>
       </c>
@@ -24317,7 +24324,7 @@
         <v>6.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="27" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A27" t="s">
         <v>197</v>
       </c>
@@ -24421,7 +24428,7 @@
         <v>8.9999999999999993E-3</v>
       </c>
     </row>
-    <row r="28" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A28" t="s">
         <v>187</v>
       </c>
@@ -24525,7 +24532,7 @@
         <v>-1.4E-2</v>
       </c>
     </row>
-    <row r="29" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A29" t="s">
         <v>149</v>
       </c>
@@ -24629,7 +24636,7 @@
         <v>-1.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="30" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A30" t="s">
         <v>198</v>
       </c>
@@ -24733,7 +24740,7 @@
         <v>3.4000000000000002E-2</v>
       </c>
     </row>
-    <row r="31" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A31" t="s">
         <v>191</v>
       </c>
@@ -24837,12 +24844,12 @@
         <v>8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="32" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A32" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="33" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A33" t="s">
         <v>196</v>
       </c>
@@ -24946,7 +24953,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="34" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A34" t="s">
         <v>197</v>
       </c>
@@ -25050,7 +25057,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="35" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A35" t="s">
         <v>149</v>
       </c>
@@ -25154,7 +25161,7 @@
         <v>-4.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="36" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A36" t="s">
         <v>191</v>
       </c>
@@ -25258,12 +25265,12 @@
         <v>6.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="37" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A37" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="38" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A38" t="s">
         <v>196</v>
       </c>
@@ -25367,7 +25374,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="39" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A39" t="s">
         <v>197</v>
       </c>
@@ -25471,7 +25478,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="40" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A40" t="s">
         <v>191</v>
       </c>
@@ -25575,12 +25582,12 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="41" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A41" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="42" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A42" t="s">
         <v>202</v>
       </c>
@@ -25684,7 +25691,7 @@
         <v>8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="43" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A43" t="s">
         <v>203</v>
       </c>
@@ -25788,17 +25795,17 @@
         <v>7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="44" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A44" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="45" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A45" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="46" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A46" t="s">
         <v>204</v>
       </c>
@@ -25902,7 +25909,7 @@
         <v>4.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="47" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A47" t="s">
         <v>206</v>
       </c>
@@ -26006,7 +26013,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A48" t="s">
         <v>208</v>
       </c>
@@ -26110,7 +26117,7 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="49" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A49" t="s">
         <v>210</v>
       </c>
@@ -26214,7 +26221,7 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="50" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A50" t="s">
         <v>212</v>
       </c>
@@ -26318,12 +26325,12 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="51" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A51" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="52" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A52" t="s">
         <v>214</v>
       </c>
@@ -26427,7 +26434,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="53" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A53" t="s">
         <v>206</v>
       </c>
@@ -26531,7 +26538,7 @@
         <v>4.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="54" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A54" t="s">
         <v>216</v>
       </c>
@@ -26635,7 +26642,7 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="55" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A55" t="s">
         <v>218</v>
       </c>
@@ -26739,7 +26746,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="56" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A56" t="s">
         <v>219</v>
       </c>
@@ -26843,12 +26850,12 @@
         <v>3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="57" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A57" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="58" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A58" t="s">
         <v>221</v>
       </c>
@@ -26952,7 +26959,7 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="59" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A59" t="s">
         <v>223</v>
       </c>
@@ -27056,7 +27063,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A60" t="s">
         <v>224</v>
       </c>
@@ -27160,7 +27167,7 @@
         <v>3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="61" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A61" t="s">
         <v>225</v>
       </c>
@@ -27264,12 +27271,12 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="62" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A62" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="63" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A63" t="s">
         <v>202</v>
       </c>
@@ -27373,7 +27380,7 @@
         <v>-6.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="64" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A64" t="s">
         <v>203</v>
       </c>
@@ -27477,17 +27484,17 @@
         <v>-6.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="65" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A65" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="66" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A66" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="67" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A67" t="s">
         <v>230</v>
       </c>
@@ -27591,7 +27598,7 @@
         <v>-8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="68" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A68" t="s">
         <v>232</v>
       </c>
@@ -27695,7 +27702,7 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="69" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A69" t="s">
         <v>233</v>
       </c>
@@ -27799,12 +27806,12 @@
         <v>-6.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="70" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A70" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="71" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A71" t="s">
         <v>230</v>
       </c>
@@ -27908,7 +27915,7 @@
         <v>-3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="72" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A72" t="s">
         <v>232</v>
       </c>
@@ -28012,7 +28019,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="73" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A73" t="s">
         <v>233</v>
       </c>
@@ -28116,22 +28123,22 @@
         <v>-2E-3</v>
       </c>
     </row>
-    <row r="74" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A74" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="75" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A75" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="76" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A76" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="77" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A77" t="s">
         <v>236</v>
       </c>
@@ -28235,7 +28242,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="78" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A78" t="s">
         <v>238</v>
       </c>
@@ -28339,7 +28346,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="79" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A79" t="s">
         <v>239</v>
       </c>
@@ -28443,7 +28450,7 @@
         <v>2.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="80" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A80" t="s">
         <v>191</v>
       </c>
@@ -28547,12 +28554,12 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="81" spans="1:35" s="49" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:35" s="49" customFormat="1" x14ac:dyDescent="0.75">
       <c r="A81" s="49" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="82" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A82" t="s">
         <v>236</v>
       </c>
@@ -28656,7 +28663,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="83" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A83" t="s">
         <v>238</v>
       </c>
@@ -28760,7 +28767,7 @@
         <v>6.6000000000000003E-2</v>
       </c>
     </row>
-    <row r="84" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.75">
       <c r="A84" s="1" t="s">
         <v>239</v>
       </c>
@@ -28864,7 +28871,7 @@
         <v>2.7E-2</v>
       </c>
     </row>
-    <row r="85" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A85" t="s">
         <v>191</v>
       </c>
@@ -28968,12 +28975,12 @@
         <v>6.6000000000000003E-2</v>
       </c>
     </row>
-    <row r="86" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A86" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="87" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A87" t="s">
         <v>242</v>
       </c>
@@ -29077,7 +29084,7 @@
         <v>7.6999999999999999E-2</v>
       </c>
     </row>
-    <row r="88" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A88" t="s">
         <v>243</v>
       </c>
@@ -29181,12 +29188,12 @@
         <v>6.4000000000000001E-2</v>
       </c>
     </row>
-    <row r="89" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A89" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="90" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A90" t="s">
         <v>236</v>
       </c>
@@ -29290,7 +29297,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="91" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A91" t="s">
         <v>238</v>
       </c>
@@ -29394,7 +29401,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="92" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A92" t="s">
         <v>239</v>
       </c>
@@ -29498,7 +29505,7 @@
         <v>2.7E-2</v>
       </c>
     </row>
-    <row r="93" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A93" t="s">
         <v>191</v>
       </c>
@@ -29610,34 +29617,34 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F854BB1-F435-4277-98CC-C79FDF16BDAB}">
   <dimension ref="A1:AG93"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
-    <col min="1" max="1" width="27.42578125" customWidth="1"/>
-    <col min="2" max="2" width="42.5703125" customWidth="1"/>
-    <col min="3" max="3" width="34.5703125" customWidth="1"/>
+    <col min="1" max="1" width="27.40625" customWidth="1"/>
+    <col min="2" max="2" width="42.54296875" customWidth="1"/>
+    <col min="3" max="3" width="34.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A1" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="2" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A2" t="s">
         <v>721</v>
       </c>
     </row>
-    <row r="3" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A3" t="s">
         <v>720</v>
       </c>
     </row>
-    <row r="4" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A4" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.75">
       <c r="B5" t="s">
         <v>178</v>
       </c>
@@ -29735,17 +29742,17 @@
         <v>719</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A6" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A7" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A8" t="s">
         <v>182</v>
       </c>
@@ -29843,7 +29850,7 @@
         <v>1.4E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A9" t="s">
         <v>184</v>
       </c>
@@ -29941,7 +29948,7 @@
         <v>6.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A10" t="s">
         <v>185</v>
       </c>
@@ -30039,7 +30046,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A11" t="s">
         <v>186</v>
       </c>
@@ -30137,7 +30144,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A12" t="s">
         <v>187</v>
       </c>
@@ -30235,7 +30242,7 @@
         <v>-8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A13" t="s">
         <v>149</v>
       </c>
@@ -30333,7 +30340,7 @@
         <v>-2E-3</v>
       </c>
     </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A14" t="s">
         <v>188</v>
       </c>
@@ -30431,7 +30438,7 @@
         <v>0.109</v>
       </c>
     </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A15" t="s">
         <v>189</v>
       </c>
@@ -30529,7 +30536,7 @@
         <v>-4.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A16" t="s">
         <v>190</v>
       </c>
@@ -30627,7 +30634,7 @@
         <v>2.3E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A17" t="s">
         <v>191</v>
       </c>
@@ -30725,12 +30732,12 @@
         <v>8.9999999999999993E-3</v>
       </c>
     </row>
-    <row r="18" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A18" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="19" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A19" t="s">
         <v>182</v>
       </c>
@@ -30828,7 +30835,7 @@
         <v>1.4E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A20" t="s">
         <v>185</v>
       </c>
@@ -30926,7 +30933,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A21" t="s">
         <v>190</v>
       </c>
@@ -31024,7 +31031,7 @@
         <v>2.3E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A22" t="s">
         <v>193</v>
       </c>
@@ -31122,7 +31129,7 @@
         <v>1.2E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A23" t="s">
         <v>194</v>
       </c>
@@ -31220,7 +31227,7 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="24" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A24" t="s">
         <v>191</v>
       </c>
@@ -31318,12 +31325,12 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="25" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A25" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="26" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A26" t="s">
         <v>196</v>
       </c>
@@ -31421,7 +31428,7 @@
         <v>8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="27" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A27" t="s">
         <v>197</v>
       </c>
@@ -31519,7 +31526,7 @@
         <v>8.9999999999999993E-3</v>
       </c>
     </row>
-    <row r="28" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A28" t="s">
         <v>187</v>
       </c>
@@ -31617,7 +31624,7 @@
         <v>-2.3E-2</v>
       </c>
     </row>
-    <row r="29" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A29" t="s">
         <v>149</v>
       </c>
@@ -31715,7 +31722,7 @@
         <v>-1.6E-2</v>
       </c>
     </row>
-    <row r="30" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A30" t="s">
         <v>198</v>
       </c>
@@ -31813,7 +31820,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="31" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A31" t="s">
         <v>191</v>
       </c>
@@ -31911,12 +31918,12 @@
         <v>8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="32" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A32" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="33" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A33" t="s">
         <v>196</v>
       </c>
@@ -32014,7 +32021,7 @@
         <v>6.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="34" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A34" t="s">
         <v>197</v>
       </c>
@@ -32112,7 +32119,7 @@
         <v>8.9999999999999993E-3</v>
       </c>
     </row>
-    <row r="35" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A35" t="s">
         <v>149</v>
       </c>
@@ -32210,7 +32217,7 @@
         <v>-2E-3</v>
       </c>
     </row>
-    <row r="36" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A36" t="s">
         <v>191</v>
       </c>
@@ -32308,12 +32315,12 @@
         <v>7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="37" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A37" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="38" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A38" t="s">
         <v>196</v>
       </c>
@@ -32411,7 +32418,7 @@
         <v>2.1000000000000001E-2</v>
       </c>
     </row>
-    <row r="39" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A39" t="s">
         <v>197</v>
       </c>
@@ -32509,7 +32516,7 @@
         <v>1.7000000000000001E-2</v>
       </c>
     </row>
-    <row r="40" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A40" t="s">
         <v>191</v>
       </c>
@@ -32607,12 +32614,12 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="41" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A41" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="42" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A42" t="s">
         <v>202</v>
       </c>
@@ -32710,7 +32717,7 @@
         <v>8.9999999999999993E-3</v>
       </c>
     </row>
-    <row r="43" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A43" t="s">
         <v>203</v>
       </c>
@@ -32808,17 +32815,17 @@
         <v>8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="44" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A44" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="45" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A45" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="46" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A46" t="s">
         <v>204</v>
       </c>
@@ -32916,7 +32923,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="47" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A47" t="s">
         <v>206</v>
       </c>
@@ -33014,7 +33021,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A48" t="s">
         <v>208</v>
       </c>
@@ -33112,7 +33119,7 @@
         <v>4.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="49" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A49" t="s">
         <v>210</v>
       </c>
@@ -33210,7 +33217,7 @@
         <v>6.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="50" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A50" t="s">
         <v>212</v>
       </c>
@@ -33308,12 +33315,12 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="51" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A51" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="52" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A52" t="s">
         <v>214</v>
       </c>
@@ -33411,7 +33418,7 @@
         <v>7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="53" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A53" t="s">
         <v>206</v>
       </c>
@@ -33509,7 +33516,7 @@
         <v>4.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="54" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A54" t="s">
         <v>216</v>
       </c>
@@ -33607,7 +33614,7 @@
         <v>6.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="55" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A55" t="s">
         <v>218</v>
       </c>
@@ -33705,7 +33712,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="56" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A56" t="s">
         <v>219</v>
       </c>
@@ -33803,12 +33810,12 @@
         <v>1.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="57" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A57" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="58" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A58" t="s">
         <v>221</v>
       </c>
@@ -33906,7 +33913,7 @@
         <v>3.1E-2</v>
       </c>
     </row>
-    <row r="59" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A59" t="s">
         <v>223</v>
       </c>
@@ -34004,7 +34011,7 @@
         <v>4.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="60" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A60" t="s">
         <v>224</v>
       </c>
@@ -34102,7 +34109,7 @@
         <v>7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="61" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A61" t="s">
         <v>225</v>
       </c>
@@ -34200,12 +34207,12 @@
         <v>3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="62" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A62" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="63" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A63" t="s">
         <v>202</v>
       </c>
@@ -34303,7 +34310,7 @@
         <v>-1.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="64" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A64" t="s">
         <v>203</v>
       </c>
@@ -34401,17 +34408,17 @@
         <v>-1.0999999999999999E-2</v>
       </c>
     </row>
-    <row r="65" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A65" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="66" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A66" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="67" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A67" t="s">
         <v>618</v>
       </c>
@@ -34509,7 +34516,7 @@
         <v>-7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="68" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A68" t="s">
         <v>232</v>
       </c>
@@ -34607,7 +34614,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="69" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A69" t="s">
         <v>233</v>
       </c>
@@ -34705,12 +34712,12 @@
         <v>-6.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="70" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A70" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="71" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A71" t="s">
         <v>618</v>
       </c>
@@ -34808,7 +34815,7 @@
         <v>-2E-3</v>
       </c>
     </row>
-    <row r="72" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A72" t="s">
         <v>232</v>
       </c>
@@ -34906,7 +34913,7 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="73" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A73" t="s">
         <v>233</v>
       </c>
@@ -35004,22 +35011,22 @@
         <v>-2E-3</v>
       </c>
     </row>
-    <row r="74" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A74" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="75" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A75" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="76" spans="1:33" s="49" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:33" s="49" customFormat="1" x14ac:dyDescent="0.75">
       <c r="A76" s="49" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="77" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A77" t="s">
         <v>236</v>
       </c>
@@ -35117,7 +35124,7 @@
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
-    <row r="78" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A78" t="s">
         <v>238</v>
       </c>
@@ -35215,7 +35222,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="79" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A79" t="s">
         <v>239</v>
       </c>
@@ -35313,7 +35320,7 @@
         <v>7.9000000000000001E-2</v>
       </c>
     </row>
-    <row r="80" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A80" t="s">
         <v>191</v>
       </c>
@@ -35411,12 +35418,12 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="81" spans="1:33" s="49" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:33" s="49" customFormat="1" x14ac:dyDescent="0.75">
       <c r="A81" s="49" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="82" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A82" t="s">
         <v>236</v>
       </c>
@@ -35514,7 +35521,7 @@
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
-    <row r="83" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A83" t="s">
         <v>238</v>
       </c>
@@ -35612,7 +35619,7 @@
         <v>6.2E-2</v>
       </c>
     </row>
-    <row r="84" spans="1:33" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:33" s="1" customFormat="1" x14ac:dyDescent="0.75">
       <c r="A84" s="1" t="s">
         <v>239</v>
       </c>
@@ -35710,7 +35717,7 @@
         <v>7.5999999999999998E-2</v>
       </c>
     </row>
-    <row r="85" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A85" t="s">
         <v>191</v>
       </c>
@@ -35808,12 +35815,12 @@
         <v>6.2E-2</v>
       </c>
     </row>
-    <row r="86" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A86" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="87" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A87" t="s">
         <v>242</v>
       </c>
@@ -35911,7 +35918,7 @@
         <v>6.6000000000000003E-2</v>
       </c>
     </row>
-    <row r="88" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A88" t="s">
         <v>243</v>
       </c>
@@ -36009,12 +36016,12 @@
         <v>6.0999999999999999E-2</v>
       </c>
     </row>
-    <row r="89" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A89" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="90" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A90" t="s">
         <v>236</v>
       </c>
@@ -36112,7 +36119,7 @@
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
-    <row r="91" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A91" t="s">
         <v>238</v>
       </c>
@@ -36210,7 +36217,7 @@
         <v>6.2E-2</v>
       </c>
     </row>
-    <row r="92" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A92" t="s">
         <v>239</v>
       </c>
@@ -36308,7 +36315,7 @@
         <v>7.5999999999999998E-2</v>
       </c>
     </row>
-    <row r="93" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A93" t="s">
         <v>191</v>
       </c>
@@ -36414,33 +36421,33 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{071732F1-1795-4BD1-B6BF-8C27C4F5084F}">
   <dimension ref="A1:AI81"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
-    <col min="1" max="1" width="25.7109375" customWidth="1"/>
-    <col min="7" max="7" width="9.140625" style="1"/>
+    <col min="1" max="1" width="25.7265625" customWidth="1"/>
+    <col min="7" max="7" width="9.1328125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A1" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="2" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A2" t="s">
         <v>484</v>
       </c>
     </row>
-    <row r="3" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A3" t="s">
         <v>485</v>
       </c>
     </row>
-    <row r="4" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A4" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.75">
       <c r="B5" t="s">
         <v>178</v>
       </c>
@@ -36544,17 +36551,17 @@
         <v>349</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A6" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A7" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A8" t="s">
         <v>248</v>
       </c>
@@ -36658,7 +36665,7 @@
         <v>-4.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A9" t="s">
         <v>250</v>
       </c>
@@ -36762,7 +36769,7 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A10" t="s">
         <v>251</v>
       </c>
@@ -36866,7 +36873,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A11" t="s">
         <v>252</v>
       </c>
@@ -36970,7 +36977,7 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A12" t="s">
         <v>253</v>
       </c>
@@ -37074,7 +37081,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A13" t="s">
         <v>254</v>
       </c>
@@ -37178,7 +37185,7 @@
         <v>6.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A14" t="s">
         <v>255</v>
       </c>
@@ -37282,7 +37289,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A15" t="s">
         <v>256</v>
       </c>
@@ -37386,7 +37393,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A16" t="s">
         <v>257</v>
       </c>
@@ -37490,7 +37497,7 @@
         <v>-1E-3</v>
       </c>
     </row>
-    <row r="17" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A17" t="s">
         <v>258</v>
       </c>
@@ -37594,7 +37601,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="18" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A18" t="s">
         <v>259</v>
       </c>
@@ -37698,7 +37705,7 @@
         <v>4.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="19" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A19" t="s">
         <v>191</v>
       </c>
@@ -37802,17 +37809,17 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="20" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A20" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="21" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A21" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="22" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A22" t="s">
         <v>248</v>
       </c>
@@ -37916,7 +37923,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="23" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A23" t="s">
         <v>250</v>
       </c>
@@ -38020,7 +38027,7 @@
         <v>8.9999999999999993E-3</v>
       </c>
     </row>
-    <row r="24" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A24" t="s">
         <v>251</v>
       </c>
@@ -38124,7 +38131,7 @@
         <v>6.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="25" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A25" t="s">
         <v>252</v>
       </c>
@@ -38228,7 +38235,7 @@
         <v>6.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="26" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A26" t="s">
         <v>253</v>
       </c>
@@ -38332,7 +38339,7 @@
         <v>1.2E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A27" t="s">
         <v>254</v>
       </c>
@@ -38436,7 +38443,7 @@
         <v>1.2E-2</v>
       </c>
     </row>
-    <row r="28" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A28" t="s">
         <v>255</v>
       </c>
@@ -38540,7 +38547,7 @@
         <v>6.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="29" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A29" t="s">
         <v>256</v>
       </c>
@@ -38644,7 +38651,7 @@
         <v>7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="30" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A30" t="s">
         <v>257</v>
       </c>
@@ -38748,7 +38755,7 @@
         <v>7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="31" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A31" t="s">
         <v>258</v>
       </c>
@@ -38852,7 +38859,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="32" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A32" t="s">
         <v>259</v>
       </c>
@@ -38956,7 +38963,7 @@
         <v>1.0999999999999999E-2</v>
       </c>
     </row>
-    <row r="33" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A33" t="s">
         <v>191</v>
       </c>
@@ -39060,17 +39067,17 @@
         <v>8.9999999999999993E-3</v>
       </c>
     </row>
-    <row r="34" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A34" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="35" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A35" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="36" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A36" t="s">
         <v>147</v>
       </c>
@@ -39174,7 +39181,7 @@
         <v>-4.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="37" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A37" t="s">
         <v>197</v>
       </c>
@@ -39278,7 +39285,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A38" t="s">
         <v>187</v>
       </c>
@@ -39382,12 +39389,12 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="39" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A39" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="40" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A40" t="s">
         <v>147</v>
       </c>
@@ -39491,7 +39498,7 @@
         <v>6.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="41" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A41" t="s">
         <v>197</v>
       </c>
@@ -39595,12 +39602,12 @@
         <v>8.9999999999999993E-3</v>
       </c>
     </row>
-    <row r="42" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A42" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="43" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A43" t="s">
         <v>147</v>
       </c>
@@ -39704,7 +39711,7 @@
         <v>7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="44" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A44" t="s">
         <v>197</v>
       </c>
@@ -39808,7 +39815,7 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="45" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A45" t="s">
         <v>187</v>
       </c>
@@ -39912,12 +39919,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A46" t="s">
         <v>264</v>
       </c>
     </row>
-    <row r="47" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A47" t="s">
         <v>147</v>
       </c>
@@ -40021,12 +40028,12 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="48" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A48" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="49" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A49" t="s">
         <v>147</v>
       </c>
@@ -40130,7 +40137,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A50" t="s">
         <v>197</v>
       </c>
@@ -40234,17 +40241,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A51" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="52" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A52" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="53" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A53" t="s">
         <v>147</v>
       </c>
@@ -40348,12 +40355,12 @@
         <v>1.2E-2</v>
       </c>
     </row>
-    <row r="54" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A54" t="s">
         <v>270</v>
       </c>
     </row>
-    <row r="55" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A55" t="s">
         <v>147</v>
       </c>
@@ -40457,22 +40464,22 @@
         <v>3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="56" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A56" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="57" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A57" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="58" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A58" s="1" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="59" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A59" t="s">
         <v>271</v>
       </c>
@@ -40576,7 +40583,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A60" t="s">
         <v>197</v>
       </c>
@@ -40680,7 +40687,7 @@
         <v>1.0999999999999999E-2</v>
       </c>
     </row>
-    <row r="61" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A61" t="s">
         <v>238</v>
       </c>
@@ -40784,7 +40791,7 @@
         <v>4.3999999999999997E-2</v>
       </c>
     </row>
-    <row r="62" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A62" t="s">
         <v>239</v>
       </c>
@@ -40888,7 +40895,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="63" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A63" t="s">
         <v>259</v>
       </c>
@@ -40992,7 +40999,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A64" t="s">
         <v>191</v>
       </c>
@@ -41096,12 +41103,12 @@
         <v>4.2000000000000003E-2</v>
       </c>
     </row>
-    <row r="65" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A65" s="1" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="66" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A66" t="s">
         <v>271</v>
       </c>
@@ -41205,7 +41212,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A67" t="s">
         <v>197</v>
       </c>
@@ -41309,7 +41316,7 @@
         <v>1.0999999999999999E-2</v>
       </c>
     </row>
-    <row r="68" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A68" t="s">
         <v>238</v>
       </c>
@@ -41413,7 +41420,7 @@
         <v>4.2000000000000003E-2</v>
       </c>
     </row>
-    <row r="69" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A69" t="s">
         <v>239</v>
       </c>
@@ -41517,7 +41524,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="70" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A70" t="s">
         <v>259</v>
       </c>
@@ -41621,7 +41628,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A71" t="s">
         <v>191</v>
       </c>
@@ -41725,12 +41732,12 @@
         <v>3.5999999999999997E-2</v>
       </c>
     </row>
-    <row r="72" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A72" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="73" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A73" t="s">
         <v>242</v>
       </c>
@@ -41834,7 +41841,7 @@
         <v>1.0999999999999999E-2</v>
       </c>
     </row>
-    <row r="74" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A74" t="s">
         <v>243</v>
       </c>
@@ -41938,12 +41945,12 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="75" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A75" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="76" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A76" t="s">
         <v>271</v>
       </c>
@@ -42047,7 +42054,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A77" t="s">
         <v>197</v>
       </c>
@@ -42151,7 +42158,7 @@
         <v>1.0999999999999999E-2</v>
       </c>
     </row>
-    <row r="78" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A78" t="s">
         <v>238</v>
       </c>
@@ -42255,7 +42262,7 @@
         <v>4.2000000000000003E-2</v>
       </c>
     </row>
-    <row r="79" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A79" t="s">
         <v>239</v>
       </c>
@@ -42359,7 +42366,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A80" t="s">
         <v>259</v>
       </c>
@@ -42463,7 +42470,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:35" x14ac:dyDescent="0.75">
       <c r="A81" t="s">
         <v>191</v>
       </c>
@@ -42575,33 +42582,33 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3FF5D7AE-769E-4749-8258-C6193598C5A3}">
   <dimension ref="A1:AG81"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
-    <col min="1" max="1" width="37.42578125" customWidth="1"/>
-    <col min="2" max="2" width="107.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="37.40625" customWidth="1"/>
+    <col min="2" max="2" width="107.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A1" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="2" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A2" t="s">
         <v>829</v>
       </c>
     </row>
-    <row r="3" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A3" t="s">
         <v>828</v>
       </c>
     </row>
-    <row r="4" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A4" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.75">
       <c r="B5" t="s">
         <v>178</v>
       </c>
@@ -42699,17 +42706,17 @@
         <v>719</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A6" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A7" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A8" t="s">
         <v>248</v>
       </c>
@@ -42807,7 +42814,7 @@
         <v>8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A9" t="s">
         <v>250</v>
       </c>
@@ -42905,7 +42912,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A10" t="s">
         <v>251</v>
       </c>
@@ -43003,7 +43010,7 @@
         <v>3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A11" t="s">
         <v>252</v>
       </c>
@@ -43101,7 +43108,7 @@
         <v>6.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A12" t="s">
         <v>253</v>
       </c>
@@ -43199,7 +43206,7 @@
         <v>1.0999999999999999E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A13" t="s">
         <v>254</v>
       </c>
@@ -43297,7 +43304,7 @@
         <v>1.4E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A14" t="s">
         <v>255</v>
       </c>
@@ -43395,7 +43402,7 @@
         <v>6.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A15" t="s">
         <v>256</v>
       </c>
@@ -43493,7 +43500,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A16" t="s">
         <v>257</v>
       </c>
@@ -43591,7 +43598,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="17" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A17" t="s">
         <v>258</v>
       </c>
@@ -43689,7 +43696,7 @@
         <v>1.7000000000000001E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A18" t="s">
         <v>259</v>
       </c>
@@ -43787,7 +43794,7 @@
         <v>3.1E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A19" t="s">
         <v>191</v>
       </c>
@@ -43885,17 +43892,17 @@
         <v>1.0999999999999999E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A20" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="21" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A21" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="22" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A22" t="s">
         <v>248</v>
       </c>
@@ -43993,7 +44000,7 @@
         <v>8.9999999999999993E-3</v>
       </c>
     </row>
-    <row r="23" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A23" t="s">
         <v>250</v>
       </c>
@@ -44091,7 +44098,7 @@
         <v>1.2E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A24" t="s">
         <v>251</v>
       </c>
@@ -44189,7 +44196,7 @@
         <v>8.9999999999999993E-3</v>
       </c>
     </row>
-    <row r="25" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A25" t="s">
         <v>252</v>
       </c>
@@ -44287,7 +44294,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="26" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A26" t="s">
         <v>253</v>
       </c>
@@ -44385,7 +44392,7 @@
         <v>1.6E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A27" t="s">
         <v>254</v>
       </c>
@@ -44483,7 +44490,7 @@
         <v>1.6E-2</v>
       </c>
     </row>
-    <row r="28" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A28" t="s">
         <v>255</v>
       </c>
@@ -44581,7 +44588,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="29" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A29" t="s">
         <v>256</v>
       </c>
@@ -44679,7 +44686,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="30" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A30" t="s">
         <v>257</v>
       </c>
@@ -44777,7 +44784,7 @@
         <v>1.0999999999999999E-2</v>
       </c>
     </row>
-    <row r="31" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A31" t="s">
         <v>258</v>
       </c>
@@ -44875,7 +44882,7 @@
         <v>1.7000000000000001E-2</v>
       </c>
     </row>
-    <row r="32" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A32" t="s">
         <v>259</v>
       </c>
@@ -44973,7 +44980,7 @@
         <v>1.4E-2</v>
       </c>
     </row>
-    <row r="33" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A33" t="s">
         <v>191</v>
       </c>
@@ -45071,17 +45078,17 @@
         <v>1.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="34" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A34" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="35" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A35" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="36" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A36" t="s">
         <v>147</v>
       </c>
@@ -45179,7 +45186,7 @@
         <v>-8.9999999999999993E-3</v>
       </c>
     </row>
-    <row r="37" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A37" t="s">
         <v>197</v>
       </c>
@@ -45277,7 +45284,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A38" t="s">
         <v>187</v>
       </c>
@@ -45375,12 +45382,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A39" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="40" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A40" t="s">
         <v>147</v>
       </c>
@@ -45478,7 +45485,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="41" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A41" t="s">
         <v>197</v>
       </c>
@@ -45576,12 +45583,12 @@
         <v>6.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="42" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A42" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="43" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A43" t="s">
         <v>147</v>
       </c>
@@ -45679,7 +45686,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="44" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A44" t="s">
         <v>197</v>
       </c>
@@ -45777,7 +45784,7 @@
         <v>4.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="45" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A45" t="s">
         <v>187</v>
       </c>
@@ -45875,12 +45882,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A46" t="s">
         <v>264</v>
       </c>
     </row>
-    <row r="47" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A47" t="s">
         <v>147</v>
       </c>
@@ -45978,12 +45985,12 @@
         <v>4.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="48" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A48" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="49" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A49" t="s">
         <v>147</v>
       </c>
@@ -46081,7 +46088,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A50" t="s">
         <v>197</v>
       </c>
@@ -46179,17 +46186,17 @@
         <v>3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="51" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A51" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="52" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A52" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="53" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A53" t="s">
         <v>147</v>
       </c>
@@ -46287,12 +46294,12 @@
         <v>1.9E-2</v>
       </c>
     </row>
-    <row r="54" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A54" t="s">
         <v>270</v>
       </c>
     </row>
-    <row r="55" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A55" t="s">
         <v>147</v>
       </c>
@@ -46390,22 +46397,22 @@
         <v>4.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="56" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A56" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="57" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A57" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="58" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A58" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="59" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A59" t="s">
         <v>271</v>
       </c>
@@ -46503,7 +46510,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A60" t="s">
         <v>197</v>
       </c>
@@ -46601,7 +46608,7 @@
         <v>1.4E-2</v>
       </c>
     </row>
-    <row r="61" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A61" t="s">
         <v>238</v>
       </c>
@@ -46699,7 +46706,7 @@
         <v>4.2999999999999997E-2</v>
       </c>
     </row>
-    <row r="62" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A62" t="s">
         <v>239</v>
       </c>
@@ -46797,7 +46804,7 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="63" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A63" t="s">
         <v>259</v>
       </c>
@@ -46895,7 +46902,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A64" t="s">
         <v>191</v>
       </c>
@@ -46993,12 +47000,12 @@
         <v>4.1000000000000002E-2</v>
       </c>
     </row>
-    <row r="65" spans="1:33" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:33" s="1" customFormat="1" x14ac:dyDescent="0.75">
       <c r="A65" s="1" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="66" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A66" t="s">
         <v>271</v>
       </c>
@@ -47096,7 +47103,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A67" t="s">
         <v>197</v>
       </c>
@@ -47194,7 +47201,7 @@
         <v>1.4E-2</v>
       </c>
     </row>
-    <row r="68" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A68" t="s">
         <v>238</v>
       </c>
@@ -47292,7 +47299,7 @@
         <v>4.1000000000000002E-2</v>
       </c>
     </row>
-    <row r="69" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A69" t="s">
         <v>239</v>
       </c>
@@ -47390,7 +47397,7 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="70" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A70" t="s">
         <v>259</v>
       </c>
@@ -47488,7 +47495,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A71" t="s">
         <v>191</v>
       </c>
@@ -47586,12 +47593,12 @@
         <v>3.5999999999999997E-2</v>
       </c>
     </row>
-    <row r="72" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A72" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="73" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A73" t="s">
         <v>242</v>
       </c>
@@ -47689,7 +47696,7 @@
         <v>1.2E-2</v>
       </c>
     </row>
-    <row r="74" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A74" t="s">
         <v>243</v>
       </c>
@@ -47787,12 +47794,12 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="75" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A75" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="76" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A76" t="s">
         <v>271</v>
       </c>
@@ -47890,7 +47897,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A77" t="s">
         <v>197</v>
       </c>
@@ -47988,7 +47995,7 @@
         <v>1.4E-2</v>
       </c>
     </row>
-    <row r="78" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A78" t="s">
         <v>238</v>
       </c>
@@ -48086,7 +48093,7 @@
         <v>4.1000000000000002E-2</v>
       </c>
     </row>
-    <row r="79" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A79" t="s">
         <v>239</v>
       </c>
@@ -48184,7 +48191,7 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="80" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A80" t="s">
         <v>259</v>
       </c>
@@ -48282,7 +48289,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A81" t="s">
         <v>191</v>
       </c>
@@ -48388,19 +48395,19 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:G222"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
-    <col min="1" max="1" width="28.7109375" customWidth="1"/>
-    <col min="2" max="7" width="11.7109375" customWidth="1"/>
+    <col min="1" max="1" width="28.7265625" customWidth="1"/>
+    <col min="2" max="7" width="11.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A1" s="65" t="s">
         <v>274</v>
       </c>
       <c r="B1" s="65"/>
     </row>
-    <row r="2" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A2" s="59" t="s">
         <v>275</v>
       </c>
@@ -48411,7 +48418,7 @@
       <c r="F2" s="60"/>
       <c r="G2" s="60"/>
     </row>
-    <row r="3" spans="1:7" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.95">
       <c r="A3" s="17"/>
       <c r="B3" s="61" t="s">
         <v>61</v>
@@ -48422,7 +48429,7 @@
       <c r="F3" s="61"/>
       <c r="G3" s="62"/>
     </row>
-    <row r="4" spans="1:7" ht="23.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="23.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.8">
       <c r="A4" s="17"/>
       <c r="B4" s="19"/>
       <c r="C4" s="63" t="s">
@@ -48433,7 +48440,7 @@
       <c r="F4" s="63"/>
       <c r="G4" s="63"/>
     </row>
-    <row r="5" spans="1:7" ht="46.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="46.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.9">
       <c r="A5" s="20"/>
       <c r="B5" s="4" t="s">
         <v>276</v>
@@ -48454,7 +48461,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="24" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="24" customHeight="1" thickTop="1" x14ac:dyDescent="0.75">
       <c r="A6" s="21" t="s">
         <v>66</v>
       </c>
@@ -48477,7 +48484,7 @@
         <v>6.83</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A7" s="23" t="s">
         <v>67</v>
       </c>
@@ -48500,7 +48507,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A8" s="7" t="s">
         <v>17</v>
       </c>
@@ -48523,7 +48530,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A9" s="26" t="s">
         <v>18</v>
       </c>
@@ -48546,7 +48553,7 @@
         <v>0.14000000000000001</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A10" s="26" t="s">
         <v>19</v>
       </c>
@@ -48569,7 +48576,7 @@
         <v>0.36</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A11" s="7" t="s">
         <v>20</v>
       </c>
@@ -48592,7 +48599,7 @@
         <v>0.97</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A12" s="26" t="s">
         <v>21</v>
       </c>
@@ -48615,7 +48622,7 @@
         <v>0.63</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A13" s="26" t="s">
         <v>22</v>
       </c>
@@ -48638,7 +48645,7 @@
         <v>0.35</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A14" s="7" t="s">
         <v>23</v>
       </c>
@@ -48661,7 +48668,7 @@
         <v>3.89</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A15" s="26" t="s">
         <v>24</v>
       </c>
@@ -48684,7 +48691,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A16" s="26" t="s">
         <v>25</v>
       </c>
@@ -48707,7 +48714,7 @@
         <v>0.77</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A17" s="26" t="s">
         <v>26</v>
       </c>
@@ -48730,7 +48737,7 @@
         <v>1.1200000000000001</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A18" s="7" t="s">
         <v>27</v>
       </c>
@@ -48753,7 +48760,7 @@
         <v>1.47</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A19" s="26" t="s">
         <v>28</v>
       </c>
@@ -48776,7 +48783,7 @@
         <v>0.67</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A20" s="27" t="s">
         <v>29</v>
       </c>
@@ -48799,7 +48806,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A21" s="27" t="s">
         <v>30</v>
       </c>
@@ -48822,7 +48829,7 @@
         <v>0.43</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A22" s="26" t="s">
         <v>31</v>
       </c>
@@ -48845,7 +48852,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A23" s="23" t="s">
         <v>279</v>
       </c>
@@ -48868,7 +48875,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A24" s="7" t="s">
         <v>32</v>
       </c>
@@ -48891,7 +48898,7 @@
         <v>3.31</v>
       </c>
     </row>
-    <row r="25" spans="1:7" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" s="6" customFormat="1" x14ac:dyDescent="0.75">
       <c r="A25" s="26" t="s">
         <v>68</v>
       </c>
@@ -48914,7 +48921,7 @@
         <v>2.5299999999999998</v>
       </c>
     </row>
-    <row r="26" spans="1:7" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" s="6" customFormat="1" x14ac:dyDescent="0.75">
       <c r="A26" s="26" t="s">
         <v>69</v>
       </c>
@@ -48937,7 +48944,7 @@
         <v>0.77</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A27" s="7" t="s">
         <v>33</v>
       </c>
@@ -48960,7 +48967,7 @@
         <v>3.52</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A28" s="23" t="s">
         <v>280</v>
       </c>
@@ -48983,7 +48990,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A29" s="7" t="s">
         <v>70</v>
       </c>
@@ -49006,7 +49013,7 @@
         <v>1.52</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A30" s="7" t="s">
         <v>71</v>
       </c>
@@ -49029,7 +49036,7 @@
         <v>2.35</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A31" s="7" t="s">
         <v>72</v>
       </c>
@@ -49052,7 +49059,7 @@
         <v>0.83</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A32" s="7" t="s">
         <v>73</v>
       </c>
@@ -49075,7 +49082,7 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A33" s="7" t="s">
         <v>34</v>
       </c>
@@ -49098,7 +49105,7 @@
         <v>0.34</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A34" s="23" t="s">
         <v>74</v>
       </c>
@@ -49121,7 +49128,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A35" s="7" t="s">
         <v>75</v>
       </c>
@@ -49144,7 +49151,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A36" s="7" t="s">
         <v>36</v>
       </c>
@@ -49167,7 +49174,7 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A37" s="7" t="s">
         <v>37</v>
       </c>
@@ -49190,7 +49197,7 @@
         <v>0.37</v>
       </c>
     </row>
-    <row r="38" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A38" s="7" t="s">
         <v>38</v>
       </c>
@@ -49213,7 +49220,7 @@
         <v>1.34</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A39" s="7" t="s">
         <v>39</v>
       </c>
@@ -49236,7 +49243,7 @@
         <v>1.33</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A40" s="7" t="s">
         <v>40</v>
       </c>
@@ -49259,7 +49266,7 @@
         <v>1.92</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A41" s="7" t="s">
         <v>41</v>
       </c>
@@ -49282,7 +49289,7 @@
         <v>0.98</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A42" s="7" t="s">
         <v>76</v>
       </c>
@@ -49305,7 +49312,7 @@
         <v>0.32</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A43" s="7" t="s">
         <v>281</v>
       </c>
@@ -49328,7 +49335,7 @@
         <v>0.31</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A44" s="23" t="s">
         <v>77</v>
       </c>
@@ -49351,7 +49358,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A45" s="7" t="s">
         <v>282</v>
       </c>
@@ -49374,7 +49381,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A46" s="7" t="s">
         <v>283</v>
       </c>
@@ -49397,7 +49404,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="47" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A47" s="7" t="s">
         <v>284</v>
       </c>
@@ -49420,7 +49427,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A48" s="7" t="s">
         <v>285</v>
       </c>
@@ -49443,7 +49450,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="49" spans="1:7" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7" ht="27.25" x14ac:dyDescent="0.75">
       <c r="A49" s="7" t="s">
         <v>78</v>
       </c>
@@ -49466,7 +49473,7 @@
         <v>6.83</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A50" s="23" t="s">
         <v>79</v>
       </c>
@@ -49489,7 +49496,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:7" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:7" ht="27.25" x14ac:dyDescent="0.75">
       <c r="A51" s="7" t="s">
         <v>286</v>
       </c>
@@ -49512,7 +49519,7 @@
         <v>5.45</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A52" s="7" t="s">
         <v>43</v>
       </c>
@@ -49535,7 +49542,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="53" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A53" s="7" t="s">
         <v>44</v>
       </c>
@@ -49558,7 +49565,7 @@
         <v>0.84</v>
       </c>
     </row>
-    <row r="54" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A54" s="7" t="s">
         <v>45</v>
       </c>
@@ -49581,7 +49588,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A55" s="7" t="s">
         <v>287</v>
       </c>
@@ -49604,7 +49611,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A56" s="7" t="s">
         <v>288</v>
       </c>
@@ -49627,7 +49634,7 @@
         <v>0.11</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A57" s="7" t="s">
         <v>46</v>
       </c>
@@ -49650,7 +49657,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A58" s="7" t="s">
         <v>80</v>
       </c>
@@ -49673,7 +49680,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A59" s="23" t="s">
         <v>81</v>
       </c>
@@ -49696,7 +49703,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A60" s="7" t="s">
         <v>82</v>
       </c>
@@ -49719,7 +49726,7 @@
         <v>3.09</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A61" s="7" t="s">
         <v>47</v>
       </c>
@@ -49742,7 +49749,7 @@
         <v>3.08</v>
       </c>
     </row>
-    <row r="62" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A62" s="7" t="s">
         <v>83</v>
       </c>
@@ -49765,7 +49772,7 @@
         <v>0.35</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A63" s="7" t="s">
         <v>84</v>
       </c>
@@ -49788,7 +49795,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A64" s="7" t="s">
         <v>85</v>
       </c>
@@ -49811,7 +49818,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A65" s="7" t="s">
         <v>86</v>
       </c>
@@ -49834,7 +49841,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A66" s="7" t="s">
         <v>80</v>
       </c>
@@ -49857,7 +49864,7 @@
         <v>0.18</v>
       </c>
     </row>
-    <row r="67" spans="1:7" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:7" ht="27.25" x14ac:dyDescent="0.75">
       <c r="A67" s="7" t="s">
         <v>87</v>
       </c>
@@ -49880,7 +49887,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="68" spans="1:7" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:7" ht="27.25" x14ac:dyDescent="0.75">
       <c r="A68" s="23" t="s">
         <v>88</v>
       </c>
@@ -49903,7 +49910,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A69" s="28" t="s">
         <v>49</v>
       </c>
@@ -49926,7 +49933,7 @@
         <v>0.11</v>
       </c>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A70" s="28">
         <v>3</v>
       </c>
@@ -49949,7 +49956,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="71" spans="1:7" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:7" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A71" s="28">
         <v>4</v>
       </c>
@@ -49972,7 +49979,7 @@
         <v>1.17</v>
       </c>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A72" s="28">
         <v>5</v>
       </c>
@@ -49995,7 +50002,7 @@
         <v>1.65</v>
       </c>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A73" s="28">
         <v>6</v>
       </c>
@@ -50018,7 +50025,7 @@
         <v>1.94</v>
       </c>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A74" s="28">
         <v>7</v>
       </c>
@@ -50041,7 +50048,7 @@
         <v>0.87</v>
       </c>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A75" s="28">
         <v>8</v>
       </c>
@@ -50064,7 +50071,7 @@
         <v>0.57999999999999996</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A76" s="28" t="s">
         <v>89</v>
       </c>
@@ -50087,7 +50094,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A77" s="23" t="s">
         <v>90</v>
       </c>
@@ -50110,7 +50117,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A78" s="28">
         <v>0</v>
       </c>
@@ -50133,7 +50140,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A79" s="28">
         <v>1</v>
       </c>
@@ -50156,7 +50163,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="80" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A80" s="28">
         <v>2</v>
       </c>
@@ -50179,7 +50186,7 @@
         <v>2.36</v>
       </c>
     </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A81" s="28">
         <v>3</v>
       </c>
@@ -50202,7 +50209,7 @@
         <v>3.49</v>
       </c>
     </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A82" s="28">
         <v>4</v>
       </c>
@@ -50225,7 +50232,7 @@
         <v>0.51</v>
       </c>
     </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A83" s="28" t="s">
         <v>91</v>
       </c>
@@ -50248,7 +50255,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="84" spans="1:7" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:7" ht="27.25" x14ac:dyDescent="0.75">
       <c r="A84" s="23" t="s">
         <v>92</v>
       </c>
@@ -50271,7 +50278,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A85" s="28">
         <v>1</v>
       </c>
@@ -50294,7 +50301,7 @@
         <v>0.28000000000000003</v>
       </c>
     </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A86" s="28">
         <v>2</v>
       </c>
@@ -50317,7 +50324,7 @@
         <v>2.13</v>
       </c>
     </row>
-    <row r="87" spans="1:7" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:7" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A87" s="28">
         <v>3</v>
       </c>
@@ -50340,7 +50347,7 @@
         <v>2.36</v>
       </c>
     </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A88" s="28">
         <v>4</v>
       </c>
@@ -50363,7 +50370,7 @@
         <v>1.26</v>
       </c>
     </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A89" s="28" t="s">
         <v>91</v>
       </c>
@@ -50386,7 +50393,7 @@
         <v>0.79</v>
       </c>
     </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A90" s="23" t="s">
         <v>93</v>
       </c>
@@ -50409,7 +50416,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A91" s="28">
         <v>0</v>
       </c>
@@ -50432,7 +50439,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A92" s="28">
         <v>1</v>
       </c>
@@ -50455,7 +50462,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="93" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A93" s="28">
         <v>2</v>
       </c>
@@ -50478,7 +50485,7 @@
         <v>4.51</v>
       </c>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A94" s="28" t="s">
         <v>94</v>
       </c>
@@ -50501,7 +50508,7 @@
         <v>0.22</v>
       </c>
     </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A95" s="23" t="s">
         <v>95</v>
       </c>
@@ -50524,7 +50531,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A96" s="28">
         <v>0</v>
       </c>
@@ -50547,7 +50554,7 @@
         <v>5.98</v>
       </c>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A97" s="28">
         <v>1</v>
       </c>
@@ -50570,7 +50577,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="98" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A98" s="28" t="s">
         <v>96</v>
       </c>
@@ -50593,7 +50600,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A99" s="23" t="s">
         <v>48</v>
       </c>
@@ -50616,7 +50623,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A100" s="7" t="s">
         <v>50</v>
       </c>
@@ -50639,7 +50646,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A101" s="26" t="s">
         <v>97</v>
       </c>
@@ -50662,7 +50669,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="102" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A102" s="26" t="s">
         <v>98</v>
       </c>
@@ -50685,7 +50692,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A103" s="28" t="s">
         <v>51</v>
       </c>
@@ -50708,7 +50715,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="104" spans="1:7" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:7" ht="27.25" x14ac:dyDescent="0.75">
       <c r="A104" s="28" t="s">
         <v>78</v>
       </c>
@@ -50731,7 +50738,7 @@
         <v>6.83</v>
       </c>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A105" s="23" t="s">
         <v>99</v>
       </c>
@@ -50754,7 +50761,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A106" s="7" t="s">
         <v>50</v>
       </c>
@@ -50777,7 +50784,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A107" s="26" t="s">
         <v>100</v>
       </c>
@@ -50800,7 +50807,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="108" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A108" s="26" t="s">
         <v>101</v>
       </c>
@@ -50823,7 +50830,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A109" s="7" t="s">
         <v>51</v>
       </c>
@@ -50846,7 +50853,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="110" spans="1:7" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:7" ht="27.25" x14ac:dyDescent="0.75">
       <c r="A110" s="28" t="s">
         <v>78</v>
       </c>
@@ -50869,7 +50876,7 @@
         <v>6.83</v>
       </c>
     </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A111" s="23" t="s">
         <v>102</v>
       </c>
@@ -50892,7 +50899,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A112" s="7" t="s">
         <v>50</v>
       </c>
@@ -50915,7 +50922,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A113" s="26" t="s">
         <v>103</v>
       </c>
@@ -50938,7 +50945,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="114" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A114" s="26" t="s">
         <v>104</v>
       </c>
@@ -50961,7 +50968,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="115" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A115" s="26" t="s">
         <v>105</v>
       </c>
@@ -50984,7 +50991,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A116" s="7" t="s">
         <v>51</v>
       </c>
@@ -51007,7 +51014,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="117" spans="1:7" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:7" ht="27.25" x14ac:dyDescent="0.75">
       <c r="A117" s="28" t="s">
         <v>78</v>
       </c>
@@ -51030,7 +51037,7 @@
         <v>6.83</v>
       </c>
     </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A118" s="23" t="s">
         <v>106</v>
       </c>
@@ -51053,7 +51060,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A119" s="7" t="s">
         <v>107</v>
       </c>
@@ -51076,7 +51083,7 @@
         <v>1.39</v>
       </c>
     </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A120" s="7" t="s">
         <v>108</v>
       </c>
@@ -51099,7 +51106,7 @@
         <v>3.28</v>
       </c>
     </row>
-    <row r="121" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A121" s="7" t="s">
         <v>109</v>
       </c>
@@ -51122,7 +51129,7 @@
         <v>1.87</v>
       </c>
     </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A122" s="7" t="s">
         <v>289</v>
       </c>
@@ -51145,7 +51152,7 @@
         <v>0.28999999999999998</v>
       </c>
     </row>
-    <row r="123" spans="1:7" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:7" ht="27.25" x14ac:dyDescent="0.75">
       <c r="A123" s="23" t="s">
         <v>110</v>
       </c>
@@ -51168,7 +51175,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A124" s="7" t="s">
         <v>52</v>
       </c>
@@ -51191,7 +51198,7 @@
         <v>2.41</v>
       </c>
     </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A125" s="7" t="s">
         <v>111</v>
       </c>
@@ -51214,7 +51221,7 @@
         <v>3.19</v>
       </c>
     </row>
-    <row r="126" spans="1:7" s="6" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:7" s="6" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A126" s="7" t="s">
         <v>112</v>
       </c>
@@ -51237,7 +51244,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="127" spans="1:7" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:7" s="6" customFormat="1" x14ac:dyDescent="0.75">
       <c r="A127" s="7" t="s">
         <v>113</v>
       </c>
@@ -51260,7 +51267,7 @@
         <v>0.48</v>
       </c>
     </row>
-    <row r="128" spans="1:7" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:7" s="6" customFormat="1" x14ac:dyDescent="0.75">
       <c r="A128" s="23" t="s">
         <v>290</v>
       </c>
@@ -51283,7 +51290,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A129" s="7" t="s">
         <v>50</v>
       </c>
@@ -51306,7 +51313,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A130" s="7" t="s">
         <v>51</v>
       </c>
@@ -51329,7 +51336,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="131" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A131" s="28" t="s">
         <v>114</v>
       </c>
@@ -51352,7 +51359,7 @@
         <v>6.83</v>
       </c>
     </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A132" s="23" t="s">
         <v>115</v>
       </c>
@@ -51375,7 +51382,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A133" s="7" t="s">
         <v>116</v>
       </c>
@@ -51398,7 +51405,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A134" s="7" t="s">
         <v>117</v>
       </c>
@@ -51421,7 +51428,7 @@
         <v>0.28999999999999998</v>
       </c>
     </row>
-    <row r="135" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A135" s="7" t="s">
         <v>118</v>
       </c>
@@ -51444,7 +51451,7 @@
         <v>2.66</v>
       </c>
     </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A136" s="29" t="s">
         <v>119</v>
       </c>
@@ -51467,7 +51474,7 @@
         <v>3.23</v>
       </c>
     </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A137" s="29" t="s">
         <v>120</v>
       </c>
@@ -51490,7 +51497,7 @@
         <v>0.51</v>
       </c>
     </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A138" s="29" t="s">
         <v>121</v>
       </c>
@@ -51513,7 +51520,7 @@
         <v>0.13</v>
       </c>
     </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A139" s="29" t="s">
         <v>122</v>
       </c>
@@ -51536,7 +51543,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A140" s="23" t="s">
         <v>123</v>
       </c>
@@ -51559,7 +51566,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A141" s="7" t="s">
         <v>124</v>
       </c>
@@ -51582,7 +51589,7 @@
         <v>3.46</v>
       </c>
     </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A142" s="7" t="s">
         <v>125</v>
       </c>
@@ -51605,7 +51612,7 @@
         <v>3.29</v>
       </c>
     </row>
-    <row r="143" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A143" s="7" t="s">
         <v>126</v>
       </c>
@@ -51628,7 +51635,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A144" s="23" t="s">
         <v>127</v>
       </c>
@@ -51651,7 +51658,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A145" s="7" t="s">
         <v>128</v>
       </c>
@@ -51674,7 +51681,7 @@
         <v>3.94</v>
       </c>
     </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A146" s="7" t="s">
         <v>44</v>
       </c>
@@ -51697,7 +51704,7 @@
         <v>1.43</v>
       </c>
     </row>
-    <row r="147" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A147" s="7" t="s">
         <v>129</v>
       </c>
@@ -51720,7 +51727,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A148" s="29" t="s">
         <v>130</v>
       </c>
@@ -51743,7 +51750,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A149" s="29" t="s">
         <v>131</v>
       </c>
@@ -51766,7 +51773,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="150" spans="1:7" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:7" ht="27.25" x14ac:dyDescent="0.75">
       <c r="A150" s="23" t="s">
         <v>291</v>
       </c>
@@ -51789,7 +51796,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A151" s="28">
         <v>0</v>
       </c>
@@ -51812,7 +51819,7 @@
         <v>4.8</v>
       </c>
     </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A152" s="28">
         <v>1</v>
       </c>
@@ -51835,7 +51842,7 @@
         <v>1.27</v>
       </c>
     </row>
-    <row r="153" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A153" s="28">
         <v>2</v>
       </c>
@@ -51858,7 +51865,7 @@
         <v>0.56000000000000005</v>
       </c>
     </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A154" s="28" t="s">
         <v>94</v>
       </c>
@@ -51881,7 +51888,7 @@
         <v>0.19</v>
       </c>
     </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A155" s="23" t="s">
         <v>133</v>
       </c>
@@ -51904,7 +51911,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A156" s="7" t="s">
         <v>50</v>
       </c>
@@ -51927,7 +51934,7 @@
         <v>1.82</v>
       </c>
     </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A157" s="7" t="s">
         <v>51</v>
       </c>
@@ -51950,7 +51957,7 @@
         <v>2.35</v>
       </c>
     </row>
-    <row r="158" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A158" s="7" t="s">
         <v>132</v>
       </c>
@@ -51973,7 +51980,7 @@
         <v>2.66</v>
       </c>
     </row>
-    <row r="159" spans="1:7" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:7" ht="27.25" x14ac:dyDescent="0.75">
       <c r="A159" s="23" t="s">
         <v>134</v>
       </c>
@@ -51996,7 +52003,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A160" s="7" t="s">
         <v>50</v>
       </c>
@@ -52019,7 +52026,7 @@
         <v>3.41</v>
       </c>
     </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A161" s="7" t="s">
         <v>51</v>
       </c>
@@ -52042,7 +52049,7 @@
         <v>3.42</v>
       </c>
     </row>
-    <row r="162" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A162" s="7" t="s">
         <v>87</v>
       </c>
@@ -52065,7 +52072,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="163" spans="1:7" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:7" ht="27.25" x14ac:dyDescent="0.75">
       <c r="A163" s="23" t="s">
         <v>292</v>
       </c>
@@ -52088,7 +52095,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="164" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A164" s="7" t="s">
         <v>50</v>
       </c>
@@ -52111,7 +52118,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A165" s="26" t="s">
         <v>293</v>
       </c>
@@ -52134,7 +52141,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="166" spans="1:7" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:7" ht="33.75" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A166" s="7" t="s">
         <v>51</v>
       </c>
@@ -52157,7 +52164,7 @@
         <v>6.79</v>
       </c>
     </row>
-    <row r="167" spans="1:7" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:7" ht="27.25" x14ac:dyDescent="0.75">
       <c r="A167" s="23" t="s">
         <v>135</v>
       </c>
@@ -52180,7 +52187,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="168" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A168" s="7" t="s">
         <v>50</v>
       </c>
@@ -52203,7 +52210,7 @@
         <v>2.87</v>
       </c>
     </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A169" s="26" t="s">
         <v>294</v>
       </c>
@@ -52226,7 +52233,7 @@
         <v>1.89</v>
       </c>
     </row>
-    <row r="170" spans="1:7" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:7" ht="33.75" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A170" s="26" t="s">
         <v>295</v>
       </c>
@@ -52249,7 +52256,7 @@
         <v>0.98</v>
       </c>
     </row>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A171" s="7" t="s">
         <v>51</v>
       </c>
@@ -52272,7 +52279,7 @@
         <v>3.96</v>
       </c>
     </row>
-    <row r="172" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A172" s="23" t="s">
         <v>136</v>
       </c>
@@ -52295,7 +52302,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="173" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A173" s="7" t="s">
         <v>50</v>
       </c>
@@ -52318,7 +52325,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="174" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A174" s="7" t="s">
         <v>51</v>
       </c>
@@ -52341,7 +52348,7 @@
         <v>6.73</v>
       </c>
     </row>
-    <row r="175" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A175" s="7" t="s">
         <v>137</v>
       </c>
@@ -52364,7 +52371,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="176" spans="1:7" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:7" ht="27.25" x14ac:dyDescent="0.75">
       <c r="A176" s="23" t="s">
         <v>296</v>
       </c>
@@ -52387,7 +52394,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="177" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A177" s="7" t="s">
         <v>50</v>
       </c>
@@ -52410,7 +52417,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="178" spans="1:7" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:7" ht="27.25" x14ac:dyDescent="0.75">
       <c r="A178" s="26" t="s">
         <v>297</v>
       </c>
@@ -52433,7 +52440,7 @@
         <v>1.32</v>
       </c>
     </row>
-    <row r="179" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A179" s="26" t="s">
         <v>298</v>
       </c>
@@ -52456,7 +52463,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="180" spans="1:7" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:7" ht="27.25" x14ac:dyDescent="0.75">
       <c r="A180" s="26" t="s">
         <v>299</v>
       </c>
@@ -52479,7 +52486,7 @@
         <v>0.14000000000000001</v>
       </c>
     </row>
-    <row r="181" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A181" s="26" t="s">
         <v>259</v>
       </c>
@@ -52502,7 +52509,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="182" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A182" s="7" t="s">
         <v>51</v>
       </c>
@@ -52525,7 +52532,7 @@
         <v>5.33</v>
       </c>
     </row>
-    <row r="183" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A183" s="23" t="s">
         <v>138</v>
       </c>
@@ -52548,7 +52555,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="184" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A184" s="7" t="s">
         <v>50</v>
       </c>
@@ -52571,7 +52578,7 @@
         <v>1.02</v>
       </c>
     </row>
-    <row r="185" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A185" s="7" t="s">
         <v>51</v>
       </c>
@@ -52594,7 +52601,7 @@
         <v>5.82</v>
       </c>
     </row>
-    <row r="186" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A186" s="23" t="s">
         <v>139</v>
       </c>
@@ -52617,7 +52624,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="187" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A187" s="28" t="s">
         <v>50</v>
       </c>
@@ -52640,7 +52647,7 @@
         <v>0.23</v>
       </c>
     </row>
-    <row r="188" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A188" s="7" t="s">
         <v>51</v>
       </c>
@@ -52663,7 +52670,7 @@
         <v>6.6</v>
       </c>
     </row>
-    <row r="189" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A189" s="7" t="s">
         <v>137</v>
       </c>
@@ -52686,7 +52693,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="190" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A190" s="31" t="s">
         <v>140</v>
       </c>
@@ -52709,7 +52716,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="191" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A191" s="26" t="s">
         <v>141</v>
       </c>
@@ -52732,7 +52739,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="192" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A192" s="26" t="s">
         <v>142</v>
       </c>
@@ -52755,7 +52762,7 @@
         <v>0.14000000000000001</v>
       </c>
     </row>
-    <row r="193" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A193" s="26" t="s">
         <v>143</v>
       </c>
@@ -52778,7 +52785,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="194" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A194" s="26" t="s">
         <v>144</v>
       </c>
@@ -52801,7 +52808,7 @@
         <v>6.6</v>
       </c>
     </row>
-    <row r="195" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A195" s="26" t="s">
         <v>137</v>
       </c>
@@ -52824,7 +52831,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="196" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A196" s="31" t="s">
         <v>145</v>
       </c>
@@ -52847,7 +52854,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="197" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A197" s="26" t="s">
         <v>146</v>
       </c>
@@ -52870,7 +52877,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="198" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A198" s="27" t="s">
         <v>147</v>
       </c>
@@ -52893,7 +52900,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="199" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A199" s="27" t="s">
         <v>148</v>
       </c>
@@ -52916,7 +52923,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="200" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A200" s="27" t="s">
         <v>149</v>
       </c>
@@ -52939,7 +52946,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="201" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A201" s="27" t="s">
         <v>150</v>
       </c>
@@ -52962,7 +52969,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="202" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A202" s="26" t="s">
         <v>151</v>
       </c>
@@ -52985,7 +52992,7 @@
         <v>0.22</v>
       </c>
     </row>
-    <row r="203" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A203" s="26" t="s">
         <v>144</v>
       </c>
@@ -53008,7 +53015,7 @@
         <v>6.6</v>
       </c>
     </row>
-    <row r="204" spans="1:7" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:7" s="6" customFormat="1" x14ac:dyDescent="0.75">
       <c r="A204" s="26" t="s">
         <v>137</v>
       </c>
@@ -53031,7 +53038,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="205" spans="1:7" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:7" s="6" customFormat="1" x14ac:dyDescent="0.75">
       <c r="A205" s="23" t="s">
         <v>152</v>
       </c>
@@ -53054,7 +53061,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="206" spans="1:7" s="6" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:7" s="6" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A206" s="7" t="s">
         <v>50</v>
       </c>
@@ -53077,7 +53084,7 @@
         <v>0.28999999999999998</v>
       </c>
     </row>
-    <row r="207" spans="1:7" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:7" s="6" customFormat="1" x14ac:dyDescent="0.75">
       <c r="A207" s="7" t="s">
         <v>51</v>
       </c>
@@ -53100,7 +53107,7 @@
         <v>6.55</v>
       </c>
     </row>
-    <row r="208" spans="1:7" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:7" s="6" customFormat="1" x14ac:dyDescent="0.75">
       <c r="A208" s="31" t="s">
         <v>153</v>
       </c>
@@ -53123,7 +53130,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="209" spans="1:7" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:7" s="6" customFormat="1" x14ac:dyDescent="0.75">
       <c r="A209" s="26" t="s">
         <v>141</v>
       </c>
@@ -53146,7 +53153,7 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="210" spans="1:7" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:7" s="6" customFormat="1" x14ac:dyDescent="0.75">
       <c r="A210" s="26" t="s">
         <v>142</v>
       </c>
@@ -53169,7 +53176,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="211" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A211" s="26" t="s">
         <v>143</v>
       </c>
@@ -53192,7 +53199,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="212" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A212" s="26" t="s">
         <v>154</v>
       </c>
@@ -53215,7 +53222,7 @@
         <v>6.55</v>
       </c>
     </row>
-    <row r="213" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A213" s="31" t="s">
         <v>155</v>
       </c>
@@ -53238,7 +53245,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="214" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A214" s="26" t="s">
         <v>147</v>
       </c>
@@ -53261,7 +53268,7 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="215" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A215" s="26" t="s">
         <v>148</v>
       </c>
@@ -53284,7 +53291,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="216" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A216" s="26" t="s">
         <v>150</v>
       </c>
@@ -53307,7 +53314,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="217" spans="1:7" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:7" ht="43.5" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A217" s="26" t="s">
         <v>156</v>
       </c>
@@ -53330,7 +53337,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="218" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A218" s="26" t="s">
         <v>154</v>
       </c>
@@ -53353,7 +53360,7 @@
         <v>6.55</v>
       </c>
     </row>
-    <row r="219" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A219" s="7"/>
       <c r="B219" s="5"/>
       <c r="C219" s="5"/>
@@ -53362,7 +53369,7 @@
       <c r="F219" s="5"/>
       <c r="G219" s="5"/>
     </row>
-    <row r="220" spans="1:7" s="6" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:7" s="6" customFormat="1" ht="15.5" thickBot="1" x14ac:dyDescent="0.9">
       <c r="A220" s="26"/>
       <c r="B220" s="25"/>
       <c r="C220" s="25"/>
@@ -53371,7 +53378,7 @@
       <c r="F220" s="25"/>
       <c r="G220" s="25"/>
     </row>
-    <row r="221" spans="1:7" s="6" customFormat="1" ht="206.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:7" s="6" customFormat="1" ht="206.25" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A221" s="64" t="s">
         <v>300</v>
       </c>
@@ -53382,7 +53389,7 @@
       <c r="F221" s="64"/>
       <c r="G221" s="64"/>
     </row>
-    <row r="222" spans="1:7" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:7" s="6" customFormat="1" x14ac:dyDescent="0.75">
       <c r="A222"/>
       <c r="B222"/>
       <c r="C222"/>
@@ -53409,7 +53416,7 @@
     <tabColor theme="9"/>
   </sheetPr>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -53418,38 +53425,38 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA048DE0-AEAD-4096-B0F3-BDB0F419C9A6}">
   <dimension ref="A1:AR121"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
-    <col min="1" max="1" width="9.85546875" customWidth="1"/>
-    <col min="2" max="2" width="60.5703125" customWidth="1"/>
-    <col min="3" max="3" width="34.7109375" customWidth="1"/>
-    <col min="4" max="4" width="11.5703125" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" customWidth="1"/>
+    <col min="1" max="1" width="9.86328125" customWidth="1"/>
+    <col min="2" max="2" width="60.54296875" customWidth="1"/>
+    <col min="3" max="3" width="34.7265625" customWidth="1"/>
+    <col min="4" max="4" width="11.54296875" customWidth="1"/>
+    <col min="5" max="5" width="10.40625" customWidth="1"/>
     <col min="6" max="6" width="12" customWidth="1"/>
-    <col min="7" max="7" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.54296875" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="9.7265625" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="9.54296875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.7265625" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="9.26953125" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="13" customWidth="1"/>
-    <col min="16" max="16" width="14.140625" customWidth="1"/>
-    <col min="17" max="17" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="12.140625" customWidth="1"/>
-    <col min="21" max="21" width="13.5703125" customWidth="1"/>
-    <col min="22" max="25" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.1328125" customWidth="1"/>
+    <col min="17" max="17" width="9.26953125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9.7265625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="9.26953125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="12.1328125" customWidth="1"/>
+    <col min="21" max="21" width="13.54296875" customWidth="1"/>
+    <col min="22" max="25" width="9.26953125" bestFit="1" customWidth="1"/>
     <col min="26" max="30" width="12" bestFit="1" customWidth="1"/>
     <col min="31" max="31" width="13" customWidth="1"/>
-    <col min="45" max="45" width="11.28515625" customWidth="1"/>
+    <col min="45" max="45" width="11.26953125" customWidth="1"/>
     <col min="46" max="46" width="12" customWidth="1"/>
     <col min="47" max="47" width="11" customWidth="1"/>
-    <col min="48" max="48" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="49" max="50" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="51" max="52" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="9.54296875" bestFit="1" customWidth="1"/>
+    <col min="49" max="50" width="9.40625" bestFit="1" customWidth="1"/>
+    <col min="51" max="52" width="9.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:44" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:44" ht="18.5" x14ac:dyDescent="0.9">
       <c r="A1" s="51" t="s">
         <v>171</v>
       </c>
@@ -53499,7 +53506,7 @@
       <c r="AQ1" s="53"/>
       <c r="AR1" s="53"/>
     </row>
-    <row r="2" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:44" x14ac:dyDescent="0.75">
       <c r="A2" s="49"/>
       <c r="B2" s="49"/>
       <c r="C2" s="50" t="s">
@@ -53547,12 +53554,12 @@
       <c r="AQ2" s="49"/>
       <c r="AR2" s="49"/>
     </row>
-    <row r="3" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:44" x14ac:dyDescent="0.75">
       <c r="C3" s="1" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="4" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:44" x14ac:dyDescent="0.75">
       <c r="C4" s="1" t="s">
         <v>162</v>
       </c>
@@ -53641,7 +53648,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="5" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:44" x14ac:dyDescent="0.75">
       <c r="C5" t="s">
         <v>58</v>
       </c>
@@ -53730,7 +53737,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:44" x14ac:dyDescent="0.75">
       <c r="B6" t="s">
         <v>603</v>
       </c>
@@ -53849,7 +53856,7 @@
         <v>13474.392293370031</v>
       </c>
     </row>
-    <row r="7" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:44" x14ac:dyDescent="0.75">
       <c r="C7" t="s">
         <v>8</v>
       </c>
@@ -53938,7 +53945,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:44" x14ac:dyDescent="0.75">
       <c r="C8" t="s">
         <v>9</v>
       </c>
@@ -54027,7 +54034,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:44" x14ac:dyDescent="0.75">
       <c r="B9" t="s">
         <v>599</v>
       </c>
@@ -54147,7 +54154,7 @@
         <v>2027685.4519549906</v>
       </c>
     </row>
-    <row r="10" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:44" x14ac:dyDescent="0.75">
       <c r="B10" t="s">
         <v>601</v>
       </c>
@@ -54267,7 +54274,7 @@
         <v>240984426.03157127</v>
       </c>
     </row>
-    <row r="11" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:44" x14ac:dyDescent="0.75">
       <c r="C11" t="s">
         <v>11</v>
       </c>
@@ -54356,7 +54363,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:44" x14ac:dyDescent="0.75">
       <c r="C12" t="s">
         <v>12</v>
       </c>
@@ -54445,7 +54452,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:44" x14ac:dyDescent="0.75">
       <c r="C13" t="s">
         <v>13</v>
       </c>
@@ -54534,7 +54541,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:44" x14ac:dyDescent="0.75">
       <c r="C14" t="s">
         <v>14</v>
       </c>
@@ -54623,7 +54630,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:44" x14ac:dyDescent="0.75">
       <c r="C15" t="s">
         <v>15</v>
       </c>
@@ -54712,7 +54719,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:44" x14ac:dyDescent="0.75">
       <c r="C16" t="s">
         <v>57</v>
       </c>
@@ -54801,7 +54808,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="2:31" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:31" x14ac:dyDescent="0.75">
       <c r="C17" t="s">
         <v>60</v>
       </c>
@@ -54890,7 +54897,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="2:31" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:31" x14ac:dyDescent="0.75">
       <c r="C18" t="s">
         <v>158</v>
       </c>
@@ -54979,7 +54986,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="2:31" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:31" x14ac:dyDescent="0.75">
       <c r="C19" t="s">
         <v>159</v>
       </c>
@@ -55068,7 +55075,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="2:31" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:31" x14ac:dyDescent="0.75">
       <c r="C20" t="s">
         <v>160</v>
       </c>
@@ -55157,12 +55164,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="2:31" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:31" x14ac:dyDescent="0.75">
       <c r="C22" s="1" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="23" spans="2:31" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:31" x14ac:dyDescent="0.75">
       <c r="C23" s="1" t="s">
         <v>162</v>
       </c>
@@ -55251,7 +55258,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="24" spans="2:31" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:31" x14ac:dyDescent="0.75">
       <c r="C24" t="s">
         <v>58</v>
       </c>
@@ -55340,7 +55347,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="2:31" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:31" x14ac:dyDescent="0.75">
       <c r="B25" t="s">
         <v>603</v>
       </c>
@@ -55459,7 +55466,7 @@
         <v>3097.6077066299681</v>
       </c>
     </row>
-    <row r="26" spans="2:31" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:31" x14ac:dyDescent="0.75">
       <c r="C26" t="s">
         <v>8</v>
       </c>
@@ -55548,7 +55555,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="2:31" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:31" x14ac:dyDescent="0.75">
       <c r="C27" t="s">
         <v>9</v>
       </c>
@@ -55637,7 +55644,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="2:31" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:31" x14ac:dyDescent="0.75">
       <c r="B28" t="s">
         <v>599</v>
       </c>
@@ -55757,7 +55764,7 @@
         <v>466141.54804500932</v>
       </c>
     </row>
-    <row r="29" spans="2:31" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:31" x14ac:dyDescent="0.75">
       <c r="B29" t="s">
         <v>601</v>
       </c>
@@ -55877,7 +55884,7 @@
         <v>55399545.968428724</v>
       </c>
     </row>
-    <row r="30" spans="2:31" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:31" x14ac:dyDescent="0.75">
       <c r="C30" t="s">
         <v>11</v>
       </c>
@@ -55966,7 +55973,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="2:31" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:31" x14ac:dyDescent="0.75">
       <c r="C31" t="s">
         <v>12</v>
       </c>
@@ -56055,7 +56062,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="2:31" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:31" x14ac:dyDescent="0.75">
       <c r="C32" t="s">
         <v>13</v>
       </c>
@@ -56144,7 +56151,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:44" x14ac:dyDescent="0.75">
       <c r="C33" t="s">
         <v>14</v>
       </c>
@@ -56233,7 +56240,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:44" x14ac:dyDescent="0.75">
       <c r="C34" t="s">
         <v>15</v>
       </c>
@@ -56322,7 +56329,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:44" x14ac:dyDescent="0.75">
       <c r="C35" t="s">
         <v>57</v>
       </c>
@@ -56411,7 +56418,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:44" x14ac:dyDescent="0.75">
       <c r="C36" t="s">
         <v>60</v>
       </c>
@@ -56500,7 +56507,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:44" x14ac:dyDescent="0.75">
       <c r="C37" t="s">
         <v>158</v>
       </c>
@@ -56589,7 +56596,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:44" x14ac:dyDescent="0.75">
       <c r="C38" t="s">
         <v>159</v>
       </c>
@@ -56678,7 +56685,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:44" x14ac:dyDescent="0.75">
       <c r="C39" t="s">
         <v>160</v>
       </c>
@@ -56767,7 +56774,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:44" x14ac:dyDescent="0.75">
       <c r="A40" s="49"/>
       <c r="B40" s="49"/>
       <c r="C40" s="50" t="s">
@@ -56815,12 +56822,12 @@
       <c r="AQ40" s="49"/>
       <c r="AR40" s="49"/>
     </row>
-    <row r="41" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:44" x14ac:dyDescent="0.75">
       <c r="C41" s="1" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="42" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:44" x14ac:dyDescent="0.75">
       <c r="C42" s="1" t="s">
         <v>161</v>
       </c>
@@ -56909,7 +56916,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="43" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:44" x14ac:dyDescent="0.75">
       <c r="C43" t="s">
         <v>58</v>
       </c>
@@ -56998,7 +57005,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:44" x14ac:dyDescent="0.75">
       <c r="B44" t="s">
         <v>611</v>
       </c>
@@ -57117,7 +57124,7 @@
         <v>3.4027475107261393</v>
       </c>
     </row>
-    <row r="45" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:44" x14ac:dyDescent="0.75">
       <c r="C45" t="s">
         <v>8</v>
       </c>
@@ -57206,7 +57213,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:44" x14ac:dyDescent="0.75">
       <c r="C46" t="s">
         <v>9</v>
       </c>
@@ -57295,7 +57302,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:44" x14ac:dyDescent="0.75">
       <c r="B47" t="s">
         <v>607</v>
       </c>
@@ -57415,7 +57422,7 @@
         <v>1792.7397620011334</v>
       </c>
     </row>
-    <row r="48" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:44" x14ac:dyDescent="0.75">
       <c r="B48" t="s">
         <v>609</v>
       </c>
@@ -57535,7 +57542,7 @@
         <v>172476.23879252005</v>
       </c>
     </row>
-    <row r="49" spans="2:31" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:31" x14ac:dyDescent="0.75">
       <c r="C49" t="s">
         <v>11</v>
       </c>
@@ -57624,7 +57631,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="2:31" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:31" x14ac:dyDescent="0.75">
       <c r="C50" t="s">
         <v>12</v>
       </c>
@@ -57713,7 +57720,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="2:31" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:31" x14ac:dyDescent="0.75">
       <c r="C51" t="s">
         <v>13</v>
       </c>
@@ -57802,7 +57809,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="2:31" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:31" x14ac:dyDescent="0.75">
       <c r="C52" t="s">
         <v>14</v>
       </c>
@@ -57891,7 +57898,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="2:31" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:31" x14ac:dyDescent="0.75">
       <c r="C53" t="s">
         <v>15</v>
       </c>
@@ -57980,7 +57987,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="2:31" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:31" x14ac:dyDescent="0.75">
       <c r="C54" t="s">
         <v>57</v>
       </c>
@@ -58069,7 +58076,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="2:31" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:31" x14ac:dyDescent="0.75">
       <c r="C55" t="s">
         <v>60</v>
       </c>
@@ -58158,7 +58165,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="2:31" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:31" x14ac:dyDescent="0.75">
       <c r="C56" t="s">
         <v>158</v>
       </c>
@@ -58247,7 +58254,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="2:31" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:31" x14ac:dyDescent="0.75">
       <c r="C57" t="s">
         <v>159</v>
       </c>
@@ -58336,7 +58343,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="2:31" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:31" x14ac:dyDescent="0.75">
       <c r="C58" t="s">
         <v>160</v>
       </c>
@@ -58425,12 +58432,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="2:31" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:31" x14ac:dyDescent="0.75">
       <c r="B60" s="1" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="61" spans="2:31" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:31" x14ac:dyDescent="0.75">
       <c r="C61" s="1" t="s">
         <v>161</v>
       </c>
@@ -58519,7 +58526,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="62" spans="2:31" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:31" x14ac:dyDescent="0.75">
       <c r="C62" t="s">
         <v>58</v>
       </c>
@@ -58608,7 +58615,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="2:31" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:31" x14ac:dyDescent="0.75">
       <c r="B63" t="s">
         <v>611</v>
       </c>
@@ -58727,7 +58734,7 @@
         <v>0.78225248927386071</v>
       </c>
     </row>
-    <row r="64" spans="2:31" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:31" x14ac:dyDescent="0.75">
       <c r="C64" t="s">
         <v>8</v>
       </c>
@@ -58816,7 +58823,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:44" x14ac:dyDescent="0.75">
       <c r="C65" t="s">
         <v>9</v>
       </c>
@@ -58905,7 +58912,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:44" x14ac:dyDescent="0.75">
       <c r="B66" t="s">
         <v>607</v>
       </c>
@@ -59025,7 +59032,7 @@
         <v>412.13023799886668</v>
       </c>
     </row>
-    <row r="67" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:44" x14ac:dyDescent="0.75">
       <c r="B67" t="s">
         <v>609</v>
       </c>
@@ -59145,7 +59152,7 @@
         <v>39650.302207479966</v>
       </c>
     </row>
-    <row r="68" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:44" x14ac:dyDescent="0.75">
       <c r="C68" t="s">
         <v>11</v>
       </c>
@@ -59234,7 +59241,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:44" x14ac:dyDescent="0.75">
       <c r="C69" t="s">
         <v>12</v>
       </c>
@@ -59323,7 +59330,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:44" x14ac:dyDescent="0.75">
       <c r="C70" t="s">
         <v>13</v>
       </c>
@@ -59412,7 +59419,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:44" x14ac:dyDescent="0.75">
       <c r="C71" t="s">
         <v>14</v>
       </c>
@@ -59501,7 +59508,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:44" x14ac:dyDescent="0.75">
       <c r="C72" t="s">
         <v>15</v>
       </c>
@@ -59590,7 +59597,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:44" x14ac:dyDescent="0.75">
       <c r="C73" t="s">
         <v>57</v>
       </c>
@@ -59679,7 +59686,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:44" x14ac:dyDescent="0.75">
       <c r="C74" t="s">
         <v>60</v>
       </c>
@@ -59768,7 +59775,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:44" x14ac:dyDescent="0.75">
       <c r="C75" t="s">
         <v>158</v>
       </c>
@@ -59857,7 +59864,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:44" x14ac:dyDescent="0.75">
       <c r="C76" t="s">
         <v>159</v>
       </c>
@@ -59946,7 +59953,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:44" x14ac:dyDescent="0.75">
       <c r="C77" t="s">
         <v>160</v>
       </c>
@@ -60035,7 +60042,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:44" x14ac:dyDescent="0.75">
       <c r="D78" s="9"/>
       <c r="E78" s="9"/>
       <c r="F78" s="9"/>
@@ -60065,7 +60072,7 @@
       <c r="AD78" s="9"/>
       <c r="AE78" s="9"/>
     </row>
-    <row r="79" spans="1:44" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:44" ht="18.5" x14ac:dyDescent="0.9">
       <c r="A79" s="51" t="s">
         <v>172</v>
       </c>
@@ -60113,13 +60120,13 @@
       <c r="AQ79" s="53"/>
       <c r="AR79" s="53"/>
     </row>
-    <row r="80" spans="1:44" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:44" ht="18.5" x14ac:dyDescent="0.9">
       <c r="A80" s="14"/>
       <c r="B80" s="15" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="81" spans="2:31" x14ac:dyDescent="0.25">
+    <row r="81" spans="2:31" x14ac:dyDescent="0.75">
       <c r="B81" s="1" t="s">
         <v>170</v>
       </c>
@@ -60127,7 +60134,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="82" spans="2:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="2:31" s="1" customFormat="1" x14ac:dyDescent="0.75">
       <c r="D82" s="1">
         <v>2023</v>
       </c>
@@ -60213,7 +60220,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="83" spans="2:31" x14ac:dyDescent="0.25">
+    <row r="83" spans="2:31" x14ac:dyDescent="0.75">
       <c r="C83" t="s">
         <v>58</v>
       </c>
@@ -60302,7 +60309,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="2:31" x14ac:dyDescent="0.25">
+    <row r="84" spans="2:31" x14ac:dyDescent="0.75">
       <c r="B84" t="s">
         <v>751</v>
       </c>
@@ -60422,7 +60429,7 @@
         <v>2128.86</v>
       </c>
     </row>
-    <row r="85" spans="2:31" x14ac:dyDescent="0.25">
+    <row r="85" spans="2:31" x14ac:dyDescent="0.75">
       <c r="C85" t="s">
         <v>8</v>
       </c>
@@ -60511,7 +60518,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="2:31" x14ac:dyDescent="0.25">
+    <row r="86" spans="2:31" x14ac:dyDescent="0.75">
       <c r="C86" t="s">
         <v>9</v>
       </c>
@@ -60600,7 +60607,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="2:31" x14ac:dyDescent="0.25">
+    <row r="87" spans="2:31" x14ac:dyDescent="0.75">
       <c r="B87" t="s">
         <v>747</v>
       </c>
@@ -60720,7 +60727,7 @@
         <v>613.52099999999996</v>
       </c>
     </row>
-    <row r="88" spans="2:31" x14ac:dyDescent="0.25">
+    <row r="88" spans="2:31" x14ac:dyDescent="0.75">
       <c r="B88" t="s">
         <v>749</v>
       </c>
@@ -60840,7 +60847,7 @@
         <v>86847.686999999991</v>
       </c>
     </row>
-    <row r="89" spans="2:31" x14ac:dyDescent="0.25">
+    <row r="89" spans="2:31" x14ac:dyDescent="0.75">
       <c r="C89" t="s">
         <v>11</v>
       </c>
@@ -60929,7 +60936,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="2:31" x14ac:dyDescent="0.25">
+    <row r="90" spans="2:31" x14ac:dyDescent="0.75">
       <c r="C90" t="s">
         <v>12</v>
       </c>
@@ -61018,7 +61025,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="2:31" x14ac:dyDescent="0.25">
+    <row r="91" spans="2:31" x14ac:dyDescent="0.75">
       <c r="C91" t="s">
         <v>13</v>
       </c>
@@ -61107,7 +61114,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="2:31" x14ac:dyDescent="0.25">
+    <row r="92" spans="2:31" x14ac:dyDescent="0.75">
       <c r="B92" t="s">
         <v>753</v>
       </c>
@@ -61227,7 +61234,7 @@
         <v>20.507000000000001</v>
       </c>
     </row>
-    <row r="93" spans="2:31" x14ac:dyDescent="0.25">
+    <row r="93" spans="2:31" x14ac:dyDescent="0.75">
       <c r="C93" t="s">
         <v>15</v>
       </c>
@@ -61316,7 +61323,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="2:31" x14ac:dyDescent="0.25">
+    <row r="94" spans="2:31" x14ac:dyDescent="0.75">
       <c r="C94" t="s">
         <v>57</v>
       </c>
@@ -61405,7 +61412,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="2:31" x14ac:dyDescent="0.25">
+    <row r="95" spans="2:31" x14ac:dyDescent="0.75">
       <c r="C95" t="s">
         <v>60</v>
       </c>
@@ -61494,7 +61501,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="2:31" x14ac:dyDescent="0.25">
+    <row r="96" spans="2:31" x14ac:dyDescent="0.75">
       <c r="C96" t="s">
         <v>158</v>
       </c>
@@ -61583,7 +61590,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="2:31" x14ac:dyDescent="0.25">
+    <row r="97" spans="2:31" x14ac:dyDescent="0.75">
       <c r="C97" t="s">
         <v>159</v>
       </c>
@@ -61672,7 +61679,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="2:31" x14ac:dyDescent="0.25">
+    <row r="98" spans="2:31" x14ac:dyDescent="0.75">
       <c r="C98" t="s">
         <v>160</v>
       </c>
@@ -61761,7 +61768,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="2:31" x14ac:dyDescent="0.25">
+    <row r="99" spans="2:31" x14ac:dyDescent="0.75">
       <c r="D99" s="9"/>
       <c r="E99" s="9"/>
       <c r="F99" s="9"/>
@@ -61791,12 +61798,12 @@
       <c r="AD99" s="9"/>
       <c r="AE99" s="9"/>
     </row>
-    <row r="100" spans="2:31" x14ac:dyDescent="0.25">
+    <row r="100" spans="2:31" x14ac:dyDescent="0.75">
       <c r="B100" s="15" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="101" spans="2:31" x14ac:dyDescent="0.25">
+    <row r="101" spans="2:31" x14ac:dyDescent="0.75">
       <c r="B101" s="1" t="s">
         <v>167</v>
       </c>
@@ -61804,7 +61811,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="102" spans="2:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="2:31" s="1" customFormat="1" x14ac:dyDescent="0.75">
       <c r="D102" s="1">
         <v>2023</v>
       </c>
@@ -61890,7 +61897,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="103" spans="2:31" x14ac:dyDescent="0.25">
+    <row r="103" spans="2:31" x14ac:dyDescent="0.75">
       <c r="C103" t="s">
         <v>58</v>
       </c>
@@ -61979,7 +61986,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="2:31" x14ac:dyDescent="0.25">
+    <row r="104" spans="2:31" x14ac:dyDescent="0.75">
       <c r="B104" t="s">
         <v>739</v>
       </c>
@@ -62099,7 +62106,7 @@
         <v>12730259</v>
       </c>
     </row>
-    <row r="105" spans="2:31" x14ac:dyDescent="0.25">
+    <row r="105" spans="2:31" x14ac:dyDescent="0.75">
       <c r="C105" t="s">
         <v>8</v>
       </c>
@@ -62188,7 +62195,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="2:31" x14ac:dyDescent="0.25">
+    <row r="106" spans="2:31" x14ac:dyDescent="0.75">
       <c r="C106" t="s">
         <v>9</v>
       </c>
@@ -62277,7 +62284,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="2:31" x14ac:dyDescent="0.25">
+    <row r="107" spans="2:31" x14ac:dyDescent="0.75">
       <c r="B107" t="s">
         <v>736</v>
       </c>
@@ -62397,7 +62404,7 @@
         <v>771365</v>
       </c>
     </row>
-    <row r="108" spans="2:31" x14ac:dyDescent="0.25">
+    <row r="108" spans="2:31" x14ac:dyDescent="0.75">
       <c r="B108" t="s">
         <v>737</v>
       </c>
@@ -62517,7 +62524,7 @@
         <v>115190025</v>
       </c>
     </row>
-    <row r="109" spans="2:31" x14ac:dyDescent="0.25">
+    <row r="109" spans="2:31" x14ac:dyDescent="0.75">
       <c r="C109" t="s">
         <v>11</v>
       </c>
@@ -62606,7 +62613,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="2:31" x14ac:dyDescent="0.25">
+    <row r="110" spans="2:31" x14ac:dyDescent="0.75">
       <c r="C110" t="s">
         <v>12</v>
       </c>
@@ -62695,7 +62702,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="2:31" x14ac:dyDescent="0.25">
+    <row r="111" spans="2:31" x14ac:dyDescent="0.75">
       <c r="C111" t="s">
         <v>13</v>
       </c>
@@ -62784,7 +62791,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="2:31" x14ac:dyDescent="0.25">
+    <row r="112" spans="2:31" x14ac:dyDescent="0.75">
       <c r="B112" t="s">
         <v>741</v>
       </c>
@@ -62904,7 +62911,7 @@
         <v>81209</v>
       </c>
     </row>
-    <row r="113" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:31" x14ac:dyDescent="0.75">
       <c r="C113" t="s">
         <v>15</v>
       </c>
@@ -62993,7 +63000,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:31" x14ac:dyDescent="0.75">
       <c r="C114" t="s">
         <v>57</v>
       </c>
@@ -63082,7 +63089,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:31" x14ac:dyDescent="0.75">
       <c r="C115" t="s">
         <v>60</v>
       </c>
@@ -63171,7 +63178,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:31" x14ac:dyDescent="0.75">
       <c r="C116" t="s">
         <v>158</v>
       </c>
@@ -63260,7 +63267,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:31" x14ac:dyDescent="0.75">
       <c r="C117" t="s">
         <v>159</v>
       </c>
@@ -63349,7 +63356,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:31" x14ac:dyDescent="0.75">
       <c r="C118" t="s">
         <v>160</v>
       </c>
@@ -63438,7 +63445,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A121" t="s">
         <v>319</v>
       </c>

--- a/InputData/bldgs/BDESC/BAU Distribued Electricity Source Capacities.xlsx
+++ b/InputData/bldgs/BDESC/BAU Distribued Electricity Source Capacities.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\OliviaAshmoore\Documents\Github Repos\eps-us\InputData\bldgs\BDESC\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DanOBrien\Models\EPS\US\eps-us\InputData\bldgs\BDESC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E6E8EC5-5554-4F4F-A346-436352FFA6BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDD02FB4-E0CF-4FA4-A608-2ACFECDF4BCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" firstSheet="3" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-21030" yWindow="750" windowWidth="21600" windowHeight="12585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -12847,8 +12847,9 @@
       <c r="B1">
         <v>2024</v>
       </c>
-      <c r="C1">
-        <v>2025</v>
+      <c r="C1" s="57">
+        <f>C8-B8+'BDESC-rural-residential'!C8-'BDESC-rural-residential'!B8+'BDESC-commercial'!C8-'BDESC-commercial'!B8</f>
+        <v>7213.474999999984</v>
       </c>
       <c r="D1">
         <v>2026</v>
@@ -13504,9 +13505,9 @@
         <f>Calculations!D48+'Inflation Reduction Act'!C59</f>
         <v>33586.644085485314</v>
       </c>
-      <c r="C8" s="56">
-        <f>Calculations!E48+'Inflation Reduction Act'!D59</f>
-        <v>37908.465848613647</v>
+      <c r="C8" s="57">
+        <f>Calculations!E48</f>
+        <v>36072.861350926898</v>
       </c>
       <c r="D8" s="57">
         <f>Calculations!F48</f>
@@ -15833,9 +15834,9 @@
         <f>Calculations!D67+'Inflation Reduction Act'!C60</f>
         <v>7721.182914514693</v>
       </c>
-      <c r="C8" s="53">
-        <f>Calculations!E67+'Inflation Reduction Act'!D60</f>
-        <v>8714.7199964604661</v>
+      <c r="C8">
+        <f>Calculations!E67</f>
+        <v>8292.7356490730999</v>
       </c>
       <c r="D8">
         <f>Calculations!F67</f>

--- a/InputData/bldgs/BDESC/BAU Distribued Electricity Source Capacities.xlsx
+++ b/InputData/bldgs/BDESC/BAU Distribued Electricity Source Capacities.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DanOBrien\Models\EPS\US\eps-us\InputData\bldgs\BDESC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80E4AE99-3C8D-4BFB-A75B-0BEE50FDD424}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{804AE395-CB52-412A-8281-449A450ABD1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-26430" yWindow="3915" windowWidth="21600" windowHeight="12585" firstSheet="9" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -25,13 +25,14 @@
     <sheet name="Calcs&gt;" sheetId="8" r:id="rId10"/>
     <sheet name="Calculations" sheetId="9" r:id="rId11"/>
     <sheet name="Inflation Reduction Act" sheetId="10" r:id="rId12"/>
-    <sheet name="BDESC-urban-residential" sheetId="11" r:id="rId13"/>
-    <sheet name="BDESC-rural-residential" sheetId="12" r:id="rId14"/>
-    <sheet name="BDESC-commercial" sheetId="13" r:id="rId15"/>
+    <sheet name="Data Center Gas" sheetId="18" r:id="rId13"/>
+    <sheet name="BDESC-urban-residential" sheetId="11" r:id="rId14"/>
+    <sheet name="BDESC-rural-residential" sheetId="12" r:id="rId15"/>
+    <sheet name="BDESC-commercial" sheetId="13" r:id="rId16"/>
   </sheets>
   <definedNames>
-    <definedName name="billion_kw_to_MW">About!$B$28</definedName>
-    <definedName name="gigwatt_to_megawatt">About!$B$29</definedName>
+    <definedName name="billion_kw_to_MW">About!$B$35</definedName>
+    <definedName name="gigwatt_to_megawatt">About!$B$36</definedName>
     <definedName name="IQ_CH">110000</definedName>
     <definedName name="IQ_CQ">5000</definedName>
     <definedName name="IQ_CY">10000</definedName>
@@ -58,8 +59,8 @@
     <definedName name="IQ_WEEK">50000</definedName>
     <definedName name="IQ_YTD">3000</definedName>
     <definedName name="IQ_YTDMONTH" hidden="1">130000</definedName>
-    <definedName name="Percent_rural">About!$A$26</definedName>
-    <definedName name="Percent_Urban">About!$A$25</definedName>
+    <definedName name="Percent_rural">About!$A$33</definedName>
+    <definedName name="Percent_Urban">About!$A$32</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'EPM Table_6_02_B'!$1:$4</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -80,7 +81,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2025" uniqueCount="978">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2046" uniqueCount="996">
   <si>
     <t>BDESC BAU Distributed Electricity Source Capacity</t>
   </si>
@@ -3032,6 +3033,60 @@
   </si>
   <si>
     <t>rural</t>
+  </si>
+  <si>
+    <t>Behind-the-meter Data Center Gas Plants</t>
+  </si>
+  <si>
+    <t>Cleanview</t>
+  </si>
+  <si>
+    <t>Bypassing the Grid: How Data Center Developers Are Building Their Own Power Plants</t>
+  </si>
+  <si>
+    <t>https://cleanview.co/reports/behind-the-meter-data-centers</t>
+  </si>
+  <si>
+    <t>Cleanview's 2026 data finds 90 GW of announced capacity planned for behind-the-meter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gas capacity, with 82 GW of that announced since Q1 2025. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">"Of the roughly 90 GW of generation capacity we've identified across all projects, only </t>
+  </si>
+  <si>
+    <t xml:space="preserve">about 2 GW is actually operating today—2.5% of the total. 1.2% is under construction. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Another 36% has been permitted, and the remaining 60% exists only as announcements </t>
+  </si>
+  <si>
+    <t>or early-stage plans.</t>
+  </si>
+  <si>
+    <t>GW total</t>
+  </si>
+  <si>
+    <t>permitted</t>
+  </si>
+  <si>
+    <t>online</t>
+  </si>
+  <si>
+    <t>under construction</t>
+  </si>
+  <si>
+    <t>announced</t>
+  </si>
+  <si>
+    <t>We add the under-construction and permitted capacity to AEO forecasts, assuming that</t>
+  </si>
+  <si>
+    <t>all will come online by 2030 to meet the first wave of AI data center buildout in the U.S.</t>
+  </si>
+  <si>
+    <t>new capacity</t>
   </si>
 </sst>
 </file>
@@ -3044,8 +3099,8 @@
     <numFmt numFmtId="165" formatCode="0.0%"/>
     <numFmt numFmtId="166" formatCode="0.000E+00"/>
     <numFmt numFmtId="167" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="169" formatCode="0.00000000000"/>
-    <numFmt numFmtId="176" formatCode="#,##0.0"/>
+    <numFmt numFmtId="168" formatCode="0.00000000000"/>
+    <numFmt numFmtId="169" formatCode="#,##0.0"/>
   </numFmts>
   <fonts count="26" x14ac:knownFonts="1">
     <font>
@@ -3233,7 +3288,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="19">
+  <fills count="20">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3338,6 +3393,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFCFEAF7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3554,7 +3615,7 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="79">
+  <cellXfs count="83">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -3663,6 +3724,41 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="169" fontId="23" fillId="17" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="23" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="24" fillId="18" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="3" fontId="7" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -3683,41 +3779,10 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="23" fillId="17" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="23" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="24" fillId="18" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="20">
     <cellStyle name="60% - Accent1 2" xfId="12" xr:uid="{00000000-0005-0000-0000-00002E000000}"/>
@@ -11515,7 +11580,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F40"/>
+  <dimension ref="A1:F47"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="51.85546875" customWidth="1"/>
@@ -11625,7 +11690,7 @@
         <v>964</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B17" s="18" t="s">
         <v>9</v>
       </c>
@@ -11633,159 +11698,184 @@
         <v>963</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B20" s="3" t="s">
+        <v>978</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B21" t="s">
+        <v>979</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B22" s="2">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B23" t="s">
+        <v>980</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B24" s="18" t="s">
+        <v>981</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="8">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" s="8">
         <f>'RECS HC2.1'!B24/SUM('RECS HC2.1'!B24,'RECS HC2.1'!B27)</f>
         <v>0.81308184246741677</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B32" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="8">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="8">
         <f>'RECS HC2.1'!B27/SUM('RECS HC2.1'!B24,'RECS HC2.1'!B27)</f>
         <v>0.18691815753258317</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B33" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="28" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A28" s="10" t="s">
+    <row r="35" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A35" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="B28">
+      <c r="B35">
         <f>10^6</f>
         <v>1000000</v>
       </c>
-      <c r="C28" s="11"/>
-      <c r="D28" s="12"/>
-      <c r="E28" s="13"/>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
+      <c r="C35" s="11"/>
+      <c r="D35" s="12"/>
+      <c r="E35" s="13"/>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
         <v>19</v>
       </c>
-      <c r="B29">
+      <c r="B36">
         <v>1000</v>
       </c>
-      <c r="F29" s="13"/>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="1" t="s">
+      <c r="F36" s="13"/>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
         <v>973</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
         <v>972</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
         <v>969</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B41" t="s">
         <v>970</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A35">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42">
         <f>AEO26_Table_21._Residential!E77</f>
         <v>44.365597000000001</v>
       </c>
-      <c r="B35">
+      <c r="B42">
         <f>'STEO Feb26'!B40</f>
         <v>40.4</v>
       </c>
-      <c r="C35">
-        <f>A35-B35</f>
+      <c r="C42">
+        <f>A42-B42</f>
         <v>3.9655970000000025</v>
       </c>
-      <c r="D35" t="s">
+      <c r="D42" t="s">
         <v>975</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A36">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43">
         <f>AEO26_Table_22._Commercial!E61</f>
         <v>33.559604999999998</v>
       </c>
-      <c r="B36">
+      <c r="B43">
         <f>SUM('STEO Feb26'!B41:B42)</f>
         <v>18.8</v>
       </c>
-      <c r="C36" s="1">
-        <f>11.6-C35</f>
+      <c r="C43" s="1">
+        <f>11.6-C42</f>
         <v>7.6344029999999972</v>
       </c>
-      <c r="D36" t="s">
+      <c r="D43" t="s">
         <v>974</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B38" t="s">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B45" t="s">
         <v>971</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A39" s="55">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" s="55">
         <v>36072.861350926898</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B46" t="s">
         <v>16</v>
       </c>
-      <c r="C39" s="1">
-        <f>$C$35*A39/SUM($A$39:$A$40)</f>
+      <c r="C46" s="1">
+        <f>$C$42*A46/SUM($A$46:$A$47)</f>
         <v>3.2243549152432633</v>
       </c>
-      <c r="D39" t="s">
+      <c r="D46" t="s">
         <v>976</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A40" s="55">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" s="55">
         <v>8292.7356490730999</v>
       </c>
-      <c r="B40" t="s">
+      <c r="B47" t="s">
         <v>17</v>
       </c>
-      <c r="C40" s="1">
-        <f>$C$35*A40/SUM($A$39:$A$40)</f>
+      <c r="C47" s="1">
+        <f>$C$42*A47/SUM($A$46:$A$47)</f>
         <v>0.74124208475673992</v>
       </c>
-      <c r="D40" t="s">
+      <c r="D47" t="s">
         <v>977</v>
       </c>
     </row>
@@ -12128,111 +12218,111 @@
         <v>530</v>
       </c>
       <c r="D6">
-        <f>INDEX(AEO25_Table_21._Residential!$F$82:$AG$93,MATCH($B6,AEO25_Table_21._Residential!$B$82:$B$93,0),MATCH(D$4,AEO25_Table_21._Residential!$F$5:$AG$5,0))*About!$A$25*About!$B$28</f>
+        <f>INDEX(AEO25_Table_21._Residential!$F$82:$AG$93,MATCH($B6,AEO25_Table_21._Residential!$B$82:$B$93,0),MATCH(D$4,AEO25_Table_21._Residential!$F$5:$AG$5,0))*About!$A$32*About!$B$35</f>
         <v>5555.7882295798581</v>
       </c>
       <c r="E6">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A6,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(E$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$25*About!$B$28</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A6,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(E$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$32*About!$B$35</f>
         <v>1627.7898486197685</v>
       </c>
       <c r="F6">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A6,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(F$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$25*About!$B$28</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A6,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(F$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$32*About!$B$35</f>
         <v>3557.2330607949489</v>
       </c>
       <c r="G6">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A6,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(G$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$25*About!$B$28</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A6,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(G$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$32*About!$B$35</f>
         <v>5437.8913624220841</v>
       </c>
       <c r="H6">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A6,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(H$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$25*About!$B$28</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A6,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(H$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$32*About!$B$35</f>
         <v>5479.358536387922</v>
       </c>
       <c r="I6">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A6,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(I$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$25*About!$B$28</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A6,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(I$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$32*About!$B$35</f>
         <v>5521.6387921962278</v>
       </c>
       <c r="J6">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A6,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(J$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$25*About!$B$28</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A6,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(J$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$32*About!$B$35</f>
         <v>8143.014652311178</v>
       </c>
       <c r="K6">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A6,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(K$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$25*About!$B$28</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A6,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(K$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$32*About!$B$35</f>
         <v>11642.518902290942</v>
       </c>
       <c r="L6">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A6,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(L$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$25*About!$B$28</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A6,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(L$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$32*About!$B$35</f>
         <v>15250.976119161336</v>
       </c>
       <c r="M6">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A6,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(M$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$25*About!$B$28</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A6,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(M$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$32*About!$B$35</f>
         <v>18060.986966728731</v>
       </c>
       <c r="N6">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A6,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(N$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$25*About!$B$28</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A6,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(N$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$32*About!$B$35</f>
         <v>21580.818262770175</v>
       </c>
       <c r="O6">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A6,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(O$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$25*About!$B$28</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A6,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(O$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$32*About!$B$35</f>
         <v>21622.285436736012</v>
       </c>
       <c r="P6">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A6,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(P$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$25*About!$B$28</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A6,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(P$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$32*About!$B$35</f>
         <v>21663.752610701853</v>
       </c>
       <c r="Q6">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A6,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(Q$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$25*About!$B$28</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A6,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(Q$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$32*About!$B$35</f>
         <v>21706.032866510159</v>
       </c>
       <c r="R6">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A6,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(R$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$25*About!$B$28</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A6,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(R$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$32*About!$B$35</f>
         <v>21747.500040475996</v>
       </c>
       <c r="S6">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A6,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(S$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$25*About!$B$28</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A6,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(S$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$32*About!$B$35</f>
         <v>21789.780296284302</v>
       </c>
       <c r="T6">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A6,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(T$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$25*About!$B$28</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A6,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(T$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$32*About!$B$35</f>
         <v>21835.312879462479</v>
       </c>
       <c r="U6">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A6,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(U$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$25*About!$B$28</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A6,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(U$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$32*About!$B$35</f>
         <v>21887.350117380389</v>
       </c>
       <c r="V6">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A6,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(V$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$25*About!$B$28</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A6,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(V$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$32*About!$B$35</f>
         <v>21954.022828462723</v>
       </c>
       <c r="W6">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A6,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(W$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$25*About!$B$28</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A6,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(W$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$32*About!$B$35</f>
         <v>22048.340322188938</v>
       </c>
       <c r="X6">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A6,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(X$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$25*About!$B$28</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A6,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(X$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$32*About!$B$35</f>
         <v>22197.947381202943</v>
       </c>
       <c r="Y6">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A6,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(Y$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$25*About!$B$28</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A6,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(Y$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$32*About!$B$35</f>
         <v>22450.815834210316</v>
       </c>
       <c r="Z6">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A6,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(Z$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$25*About!$B$28</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A6,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(Z$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$32*About!$B$35</f>
         <v>22894.75852019752</v>
       </c>
       <c r="AA6">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A6,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(AA$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$25*About!$B$28</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A6,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(AA$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$32*About!$B$35</f>
         <v>23341.140451712134</v>
       </c>
       <c r="AB6">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A6,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(AB$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$25*About!$B$28</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A6,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(AB$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$32*About!$B$35</f>
         <v>23789.148546911678</v>
       </c>
       <c r="AC6">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A6,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(AC$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$25*About!$B$28</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A6,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(AC$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$32*About!$B$35</f>
         <v>24239.595887638628</v>
       </c>
       <c r="AD6">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A6,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(AD$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$25*About!$B$28</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A6,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(AD$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$32*About!$B$35</f>
         <v>24694.108637577912</v>
       </c>
     </row>
@@ -12419,111 +12509,111 @@
         <v>534</v>
       </c>
       <c r="D9">
-        <f>INDEX(AEO25_Table_21._Residential!$F$82:$AG$93,MATCH($B9,AEO25_Table_21._Residential!$B$82:$B$93,0),MATCH(D$4,AEO25_Table_21._Residential!$F$5:$AG$5,0))*About!$A$25*About!$B$28</f>
+        <f>INDEX(AEO25_Table_21._Residential!$F$82:$AG$93,MATCH($B9,AEO25_Table_21._Residential!$B$82:$B$93,0),MATCH(D$4,AEO25_Table_21._Residential!$F$5:$AG$5,0))*About!$A$32*About!$B$35</f>
         <v>300368.69424431311</v>
       </c>
       <c r="E9">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A9,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(E$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$25*About!$B$28</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A9,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(E$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$32*About!$B$35</f>
         <v>140072.86132923176</v>
       </c>
       <c r="F9">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A9,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(F$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$25*About!$B$28</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A9,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(F$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$32*About!$B$35</f>
         <v>140198.07593297173</v>
       </c>
       <c r="G9">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A9,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(G$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$25*About!$B$28</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A9,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(G$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$32*About!$B$35</f>
         <v>140350.9353193556</v>
       </c>
       <c r="H9">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A9,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(H$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$25*About!$B$28</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A9,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(H$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$32*About!$B$35</f>
         <v>140502.16854205454</v>
       </c>
       <c r="I9">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A9,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(I$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$25*About!$B$28</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A9,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(I$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$32*About!$B$35</f>
         <v>140746.90617663725</v>
       </c>
       <c r="J9">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A9,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(J$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$25*About!$B$28</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A9,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(J$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$32*About!$B$35</f>
         <v>141171.33489840524</v>
       </c>
       <c r="K9">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A9,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(K$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$25*About!$B$28</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A9,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(K$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$32*About!$B$35</f>
         <v>141941.32340322188</v>
       </c>
       <c r="L9">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A9,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(L$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$25*About!$B$28</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A9,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(L$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$32*About!$B$35</f>
         <v>143138.99295717638</v>
       </c>
       <c r="M9">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A9,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(M$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$25*About!$B$28</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A9,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(M$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$32*About!$B$35</f>
         <v>144978.99716668014</v>
       </c>
       <c r="N9">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A9,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(N$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$25*About!$B$28</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A9,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(N$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$32*About!$B$35</f>
         <v>147506.86861491136</v>
       </c>
       <c r="O9">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A9,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(O$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$25*About!$B$28</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A9,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(O$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$32*About!$B$35</f>
         <v>150522.589168623</v>
       </c>
       <c r="P9">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A9,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(P$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$25*About!$B$28</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A9,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(P$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$32*About!$B$35</f>
         <v>153902.57038776006</v>
       </c>
       <c r="Q9">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A9,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(Q$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$25*About!$B$28</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A9,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(Q$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$32*About!$B$35</f>
         <v>157645.18610863757</v>
       </c>
       <c r="R9">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A9,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(R$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$25*About!$B$28</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A9,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(R$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$32*About!$B$35</f>
         <v>161573.18448959765</v>
       </c>
       <c r="S9">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A9,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(S$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$25*About!$B$28</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A9,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(S$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$32*About!$B$35</f>
         <v>165598.75269165382</v>
       </c>
       <c r="T9">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A9,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(T$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$25*About!$B$28</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A9,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(T$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$32*About!$B$35</f>
         <v>169864.18003723791</v>
       </c>
       <c r="U9">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A9,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(U$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$25*About!$B$28</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A9,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(U$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$32*About!$B$35</f>
         <v>174618.26957014488</v>
       </c>
       <c r="V9">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A9,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(V$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$25*About!$B$28</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A9,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(V$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$32*About!$B$35</f>
         <v>179692.71334898405</v>
       </c>
       <c r="W9">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A9,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(W$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$25*About!$B$28</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A9,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(W$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$32*About!$B$35</f>
         <v>184928.14733263175</v>
       </c>
       <c r="X9">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A9,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(X$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$25*About!$B$28</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A9,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(X$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$32*About!$B$35</f>
         <v>190289.60900186186</v>
       </c>
       <c r="Y9">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A9,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(Y$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$25*About!$B$28</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A9,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(Y$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$32*About!$B$35</f>
         <v>195821.81785801018</v>
       </c>
       <c r="Z9">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A9,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(Z$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$25*About!$B$28</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A9,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(Z$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$32*About!$B$35</f>
         <v>201816.67028252245</v>
       </c>
       <c r="AA9">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A9,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(AA$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$25*About!$B$28</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A9,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(AA$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$32*About!$B$35</f>
         <v>208040.81178661055</v>
       </c>
       <c r="AB9">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A9,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(AB$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$25*About!$B$28</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A9,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(AB$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$32*About!$B$35</f>
         <v>215123.56771634417</v>
       </c>
       <c r="AC9">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A9,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(AC$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$25*About!$B$28</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A9,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(AC$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$32*About!$B$35</f>
         <v>222286.00566663966</v>
       </c>
       <c r="AD9">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A9,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(AD$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$25*About!$B$28</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A9,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(AD$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$32*About!$B$35</f>
         <v>229521.62098275719</v>
       </c>
     </row>
@@ -12538,111 +12628,111 @@
         <v>536</v>
       </c>
       <c r="D10">
-        <f>INDEX(AEO25_Table_21._Residential!$F$82:$AG$93,MATCH($B10,AEO25_Table_21._Residential!$B$82:$B$93,0),MATCH(D$4,AEO25_Table_21._Residential!$F$5:$AG$5,0))*About!$A$25*About!$B$28</f>
+        <f>INDEX(AEO25_Table_21._Residential!$F$82:$AG$93,MATCH($B10,AEO25_Table_21._Residential!$B$82:$B$93,0),MATCH(D$4,AEO25_Table_21._Residential!$F$5:$AG$5,0))*About!$A$32*About!$B$35</f>
         <v>50978364.686796732</v>
       </c>
       <c r="E10">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A10,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(E$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$25*About!$B$28</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A10,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(E$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$32*About!$B$35</f>
         <v>53470950.009228528</v>
       </c>
       <c r="F10">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A10,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(F$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$25*About!$B$28</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A10,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(F$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$32*About!$B$35</f>
         <v>56521290.774710603</v>
       </c>
       <c r="G10">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A10,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(G$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$25*About!$B$28</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A10,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(G$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$32*About!$B$35</f>
         <v>59964463.088480517</v>
       </c>
       <c r="H10">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A10,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(H$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$25*About!$B$28</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A10,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(H$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$32*About!$B$35</f>
         <v>63515989.127823189</v>
       </c>
       <c r="I10">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A10,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(I$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$25*About!$B$28</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A10,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(I$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$32*About!$B$35</f>
         <v>66825908.71075853</v>
       </c>
       <c r="J10">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A10,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(J$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$25*About!$B$28</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A10,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(J$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$32*About!$B$35</f>
         <v>70302740.173561066</v>
       </c>
       <c r="K10">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A10,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(K$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$25*About!$B$28</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A10,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(K$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$32*About!$B$35</f>
         <v>74066152.901805222</v>
       </c>
       <c r="L10">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A10,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(L$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$25*About!$B$28</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A10,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(L$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$32*About!$B$35</f>
         <v>77813083.648020715</v>
       </c>
       <c r="M10">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A10,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(M$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$25*About!$B$28</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A10,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(M$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$32*About!$B$35</f>
         <v>81739216.006152347</v>
       </c>
       <c r="N10">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A10,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(N$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$25*About!$B$28</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A10,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(N$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$32*About!$B$35</f>
         <v>85899672.046628341</v>
       </c>
       <c r="O10">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A10,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(O$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$25*About!$B$28</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A10,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(O$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$32*About!$B$35</f>
         <v>90335556.308912814</v>
       </c>
       <c r="P10">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A10,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(P$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$25*About!$B$28</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A10,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(P$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$32*About!$B$35</f>
         <v>94982501.982028648</v>
       </c>
       <c r="Q10">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A10,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(Q$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$25*About!$B$28</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A10,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(Q$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$32*About!$B$35</f>
         <v>99960122.34890309</v>
       </c>
       <c r="R10">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A10,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(R$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$25*About!$B$28</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A10,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(R$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$32*About!$B$35</f>
         <v>105171992.40767422</v>
       </c>
       <c r="S10">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A10,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(S$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$25*About!$B$28</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A10,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(S$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$32*About!$B$35</f>
         <v>110663048.75252973</v>
       </c>
       <c r="T10">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A10,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(T$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$25*About!$B$28</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A10,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(T$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$32*About!$B$35</f>
         <v>116346805.49405001</v>
       </c>
       <c r="U10">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A10,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(U$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$25*About!$B$28</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A10,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(U$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$32*About!$B$35</f>
         <v>122255072.83315793</v>
       </c>
       <c r="V10">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A10,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(V$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$25*About!$B$28</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A10,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(V$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$32*About!$B$35</f>
         <v>128329093.41050757</v>
       </c>
       <c r="W10">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A10,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(W$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$25*About!$B$28</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A10,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(W$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$32*About!$B$35</f>
         <v>134590739.12766129</v>
       </c>
       <c r="X10">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A10,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(X$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$25*About!$B$28</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A10,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(X$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$32*About!$B$35</f>
         <v>141094736.08419007</v>
       </c>
       <c r="Y10">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A10,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(Y$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$25*About!$B$28</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A10,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(Y$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$32*About!$B$35</f>
         <v>147745429.26673684</v>
       </c>
       <c r="Z10">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A10,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(Z$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$25*About!$B$28</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A10,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(Z$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$32*About!$B$35</f>
         <v>154590957.18578482</v>
       </c>
       <c r="AA10">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A10,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(AA$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$25*About!$B$28</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A10,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(AA$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$32*About!$B$35</f>
         <v>161636864.24641788</v>
       </c>
       <c r="AB10">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A10,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(AB$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$25*About!$B$28</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A10,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(AB$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$32*About!$B$35</f>
         <v>168976932.12142801</v>
       </c>
       <c r="AC10">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A10,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(AC$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$25*About!$B$28</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A10,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(AC$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$32*About!$B$35</f>
         <v>176433189.3917267</v>
       </c>
       <c r="AD10">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A10,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(AD$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$25*About!$B$28</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A10,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(AD$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$32*About!$B$35</f>
         <v>184157193.69966808</v>
       </c>
     </row>
@@ -13694,111 +13784,111 @@
         <v>530</v>
       </c>
       <c r="D25">
-        <f>INDEX(AEO25_Table_21._Residential!$F$82:$AG$93,MATCH($B25,AEO25_Table_21._Residential!$B$82:$B$93,0),MATCH(D$4,AEO25_Table_21._Residential!$F$5:$AG$5,0))*About!$A$26*About!$B$28</f>
+        <f>INDEX(AEO25_Table_21._Residential!$F$82:$AG$93,MATCH($B25,AEO25_Table_21._Residential!$B$82:$B$93,0),MATCH(D$4,AEO25_Table_21._Residential!$F$5:$AG$5,0))*About!$A$33*About!$B$35</f>
         <v>1277.2117704201407</v>
       </c>
       <c r="E25">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A25,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(E$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$26*About!$B$28</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A25,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(E$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$33*About!$B$35</f>
         <v>374.21015138023148</v>
       </c>
       <c r="F25">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A25,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(F$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$26*About!$B$28</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A25,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(F$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$33*About!$B$35</f>
         <v>817.76693920505147</v>
       </c>
       <c r="G25">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A25,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(G$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$26*About!$B$28</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A25,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(G$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$33*About!$B$35</f>
         <v>1250.1086375779162</v>
       </c>
       <c r="H25">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A25,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(H$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$26*About!$B$28</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A25,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(H$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$33*About!$B$35</f>
         <v>1259.641463612078</v>
       </c>
       <c r="I25">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A25,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(I$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$26*About!$B$28</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A25,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(I$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$33*About!$B$35</f>
         <v>1269.3612078037722</v>
       </c>
       <c r="J25">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A25,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(J$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$26*About!$B$28</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A25,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(J$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$33*About!$B$35</f>
         <v>1871.9853476888204</v>
       </c>
       <c r="K25">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A25,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(K$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$26*About!$B$28</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A25,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(K$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$33*About!$B$35</f>
         <v>2676.4810977090583</v>
       </c>
       <c r="L25">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A25,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(L$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$26*About!$B$28</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A25,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(L$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$33*About!$B$35</f>
         <v>3506.0238808386625</v>
       </c>
       <c r="M25">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A25,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(M$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$26*About!$B$28</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A25,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(M$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$33*About!$B$35</f>
         <v>4152.0130332712697</v>
       </c>
       <c r="N25">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A25,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(N$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$26*About!$B$28</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A25,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(N$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$33*About!$B$35</f>
         <v>4961.1817372298228</v>
       </c>
       <c r="O25">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A25,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(O$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$26*About!$B$28</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A25,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(O$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$33*About!$B$35</f>
         <v>4970.714563263984</v>
       </c>
       <c r="P25">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A25,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(P$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$26*About!$B$28</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A25,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(P$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$33*About!$B$35</f>
         <v>4980.2473892981461</v>
       </c>
       <c r="Q25">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A25,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(Q$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$26*About!$B$28</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A25,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(Q$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$33*About!$B$35</f>
         <v>4989.9671334898403</v>
       </c>
       <c r="R25">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A25,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(R$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$26*About!$B$28</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A25,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(R$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$33*About!$B$35</f>
         <v>4999.4999595240024</v>
       </c>
       <c r="S25">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A25,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(S$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$26*About!$B$28</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A25,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(S$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$33*About!$B$35</f>
         <v>5009.2197037156966</v>
       </c>
       <c r="T25">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A25,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(T$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$26*About!$B$28</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A25,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(T$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$33*About!$B$35</f>
         <v>5019.687120537521</v>
       </c>
       <c r="U25">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A25,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(U$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$26*About!$B$28</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A25,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(U$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$33*About!$B$35</f>
         <v>5031.6498826196057</v>
       </c>
       <c r="V25">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A25,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(V$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$26*About!$B$28</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A25,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(V$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$33*About!$B$35</f>
         <v>5046.977171537279</v>
       </c>
       <c r="W25">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A25,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(W$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$26*About!$B$28</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A25,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(W$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$33*About!$B$35</f>
         <v>5068.6596778110579</v>
       </c>
       <c r="X25">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A25,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(X$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$26*About!$B$28</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A25,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(X$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$33*About!$B$35</f>
         <v>5103.0526187970527</v>
       </c>
       <c r="Y25">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A25,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(Y$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$26*About!$B$28</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A25,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(Y$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$33*About!$B$35</f>
         <v>5161.1841657896866</v>
       </c>
       <c r="Z25">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A25,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(Z$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$26*About!$B$28</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A25,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(Z$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$33*About!$B$35</f>
         <v>5263.2414798024765</v>
       </c>
       <c r="AA25">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A25,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(AA$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$26*About!$B$28</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A25,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(AA$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$33*About!$B$35</f>
         <v>5365.8595482878654</v>
       </c>
       <c r="AB25">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A25,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(AB$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$26*About!$B$28</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A25,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(AB$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$33*About!$B$35</f>
         <v>5468.8514530883176</v>
       </c>
       <c r="AC25">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A25,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(AC$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$26*About!$B$28</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A25,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(AC$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$33*About!$B$35</f>
         <v>5572.4041123613697</v>
       </c>
       <c r="AD25">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A25,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(AD$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$26*About!$B$28</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A25,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(AD$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$33*About!$B$35</f>
         <v>5676.8913624220831</v>
       </c>
     </row>
@@ -13985,111 +14075,111 @@
         <v>534</v>
       </c>
       <c r="D28">
-        <f>INDEX(AEO25_Table_21._Residential!$F$82:$AG$93,MATCH($B28,AEO25_Table_21._Residential!$B$82:$B$93,0),MATCH(D$4,AEO25_Table_21._Residential!$F$5:$AG$5,0))*About!$A$26*About!$B$28</f>
+        <f>INDEX(AEO25_Table_21._Residential!$F$82:$AG$93,MATCH($B28,AEO25_Table_21._Residential!$B$82:$B$93,0),MATCH(D$4,AEO25_Table_21._Residential!$F$5:$AG$5,0))*About!$A$33*About!$B$35</f>
         <v>69051.305755686888</v>
       </c>
       <c r="E28">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A28,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(E$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$26*About!$B$28</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A28,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(E$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$33*About!$B$35</f>
         <v>32201.138670768236</v>
       </c>
       <c r="F28">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A28,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(F$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$26*About!$B$28</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A28,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(F$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$33*About!$B$35</f>
         <v>32229.924067028252</v>
       </c>
       <c r="G28">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A28,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(G$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$26*About!$B$28</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A28,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(G$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$33*About!$B$35</f>
         <v>32265.064680644376</v>
       </c>
       <c r="H28">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A28,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(H$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$26*About!$B$28</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A28,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(H$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$33*About!$B$35</f>
         <v>32299.831457945438</v>
       </c>
       <c r="I28">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A28,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(I$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$26*About!$B$28</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A28,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(I$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$33*About!$B$35</f>
         <v>32356.093823362749</v>
       </c>
       <c r="J28">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A28,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(J$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$26*About!$B$28</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A28,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(J$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$33*About!$B$35</f>
         <v>32453.665101594754</v>
       </c>
       <c r="K28">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A28,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(K$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$26*About!$B$28</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A28,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(K$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$33*About!$B$35</f>
         <v>32630.67659677811</v>
       </c>
       <c r="L28">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A28,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(L$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$26*About!$B$28</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A28,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(L$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$33*About!$B$35</f>
         <v>32906.007042823607</v>
       </c>
       <c r="M28">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A28,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(M$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$26*About!$B$28</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A28,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(M$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$33*About!$B$35</f>
         <v>33329.002833319842</v>
       </c>
       <c r="N28">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A28,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(N$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$26*About!$B$28</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A28,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(N$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$33*About!$B$35</f>
         <v>33910.131385088636</v>
       </c>
       <c r="O28">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A28,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(O$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$26*About!$B$28</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A28,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(O$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$33*About!$B$35</f>
         <v>34603.410831376998</v>
       </c>
       <c r="P28">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A28,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(P$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$26*About!$B$28</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A28,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(P$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$33*About!$B$35</f>
         <v>35380.429612239946</v>
       </c>
       <c r="Q28">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A28,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(Q$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$26*About!$B$28</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A28,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(Q$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$33*About!$B$35</f>
         <v>36240.813891362428</v>
       </c>
       <c r="R28">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A28,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(R$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$26*About!$B$28</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A28,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(R$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$33*About!$B$35</f>
         <v>37143.815510402332</v>
       </c>
       <c r="S28">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A28,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(S$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$26*About!$B$28</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A28,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(S$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$33*About!$B$35</f>
         <v>38069.247308346145</v>
       </c>
       <c r="T28">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A28,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(T$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$26*About!$B$28</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A28,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(T$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$33*About!$B$35</f>
         <v>39049.819962762078</v>
       </c>
       <c r="U28">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A28,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(U$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$26*About!$B$28</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A28,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(U$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$33*About!$B$35</f>
         <v>40142.730429855095</v>
       </c>
       <c r="V28">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A28,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(V$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$26*About!$B$28</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A28,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(V$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$33*About!$B$35</f>
         <v>41309.286651015951</v>
       </c>
       <c r="W28">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A28,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(W$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$26*About!$B$28</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A28,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(W$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$33*About!$B$35</f>
         <v>42512.85266736825</v>
       </c>
       <c r="X28">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A28,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(X$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$26*About!$B$28</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A28,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(X$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$33*About!$B$35</f>
         <v>43745.3909981381</v>
       </c>
       <c r="Y28">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A28,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(Y$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$26*About!$B$28</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A28,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(Y$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$33*About!$B$35</f>
         <v>45017.182141989797</v>
       </c>
       <c r="Z28">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A28,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(Z$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$26*About!$B$28</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A28,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(Z$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$33*About!$B$35</f>
         <v>46395.329717477536</v>
       </c>
       <c r="AA28">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A28,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(AA$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$26*About!$B$28</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A28,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(AA$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$33*About!$B$35</f>
         <v>47826.188213389454</v>
       </c>
       <c r="AB28">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A28,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(AB$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$26*About!$B$28</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A28,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(AB$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$33*About!$B$35</f>
         <v>49454.432283655784</v>
       </c>
       <c r="AC28">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A28,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(AC$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$26*About!$B$28</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A28,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(AC$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$33*About!$B$35</f>
         <v>51100.994333360315</v>
       </c>
       <c r="AD28">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A28,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(AD$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$26*About!$B$28</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A28,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(AD$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$33*About!$B$35</f>
         <v>52764.379017242769</v>
       </c>
     </row>
@@ -14104,111 +14194,111 @@
         <v>536</v>
       </c>
       <c r="D29">
-        <f>INDEX(AEO25_Table_21._Residential!$F$82:$AG$93,MATCH($B29,AEO25_Table_21._Residential!$B$82:$B$93,0),MATCH(D$4,AEO25_Table_21._Residential!$F$5:$AG$5,0))*About!$A$26*About!$B$28</f>
+        <f>INDEX(AEO25_Table_21._Residential!$F$82:$AG$93,MATCH($B29,AEO25_Table_21._Residential!$B$82:$B$93,0),MATCH(D$4,AEO25_Table_21._Residential!$F$5:$AG$5,0))*About!$A$33*About!$B$35</f>
         <v>11719339.313203271</v>
       </c>
       <c r="E29">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A29,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(E$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$26*About!$B$28</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A29,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(E$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$33*About!$B$35</f>
         <v>12292355.990771472</v>
       </c>
       <c r="F29">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A29,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(F$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$26*About!$B$28</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A29,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(F$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$33*About!$B$35</f>
         <v>12993594.225289404</v>
       </c>
       <c r="G29">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A29,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(G$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$26*About!$B$28</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A29,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(G$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$33*About!$B$35</f>
         <v>13785139.911519468</v>
       </c>
       <c r="H29">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A29,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(H$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$26*About!$B$28</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A29,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(H$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$33*About!$B$35</f>
         <v>14601594.872176796</v>
       </c>
       <c r="I29">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A29,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(I$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$26*About!$B$28</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A29,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(I$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$33*About!$B$35</f>
         <v>15362507.28924148</v>
       </c>
       <c r="J29">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A29,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(J$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$26*About!$B$28</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A29,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(J$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$33*About!$B$35</f>
         <v>16161790.826438921</v>
       </c>
       <c r="K29">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A29,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(K$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$26*About!$B$28</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A29,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(K$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$33*About!$B$35</f>
         <v>17026956.098194771</v>
       </c>
       <c r="L29">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A29,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(L$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$26*About!$B$28</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A29,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(L$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$33*About!$B$35</f>
         <v>17888332.351979274</v>
       </c>
       <c r="M29">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A29,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(M$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$26*About!$B$28</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A29,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(M$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$33*About!$B$35</f>
         <v>18790904.993847646</v>
       </c>
       <c r="N29">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A29,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(N$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$26*About!$B$28</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A29,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(N$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$33*About!$B$35</f>
         <v>19747345.953371648</v>
       </c>
       <c r="O29">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A29,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(O$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$26*About!$B$28</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A29,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(O$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$33*About!$B$35</f>
         <v>20767104.691087183</v>
       </c>
       <c r="P29">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A29,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(P$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$26*About!$B$28</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A29,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(P$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$33*About!$B$35</f>
         <v>21835384.017971344</v>
       </c>
       <c r="Q29">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A29,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(Q$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$26*About!$B$28</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A29,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(Q$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$33*About!$B$35</f>
         <v>22979681.651096895</v>
       </c>
       <c r="R29">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A29,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(R$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$26*About!$B$28</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A29,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(R$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$33*About!$B$35</f>
         <v>24177830.592325747</v>
       </c>
       <c r="S29">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A29,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(S$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$26*About!$B$28</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A29,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(S$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$33*About!$B$35</f>
         <v>25440161.247470248</v>
       </c>
       <c r="T29">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A29,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(T$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$26*About!$B$28</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A29,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(T$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$33*About!$B$35</f>
         <v>26746791.505949967</v>
       </c>
       <c r="U29">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A29,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(U$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$26*About!$B$28</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A29,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(U$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$33*About!$B$35</f>
         <v>28105034.166842062</v>
       </c>
       <c r="V29">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A29,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(V$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$26*About!$B$28</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A29,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(V$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$33*About!$B$35</f>
         <v>29501381.589492433</v>
       </c>
       <c r="W29">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A29,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(W$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$26*About!$B$28</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A29,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(W$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$33*About!$B$35</f>
         <v>30940861.872338701</v>
       </c>
       <c r="X29">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A29,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(X$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$26*About!$B$28</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A29,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(X$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$33*About!$B$35</f>
         <v>32436055.915809922</v>
       </c>
       <c r="Y29">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A29,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(Y$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$26*About!$B$28</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A29,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(Y$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$33*About!$B$35</f>
         <v>33964973.73326318</v>
       </c>
       <c r="Z29">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A29,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(Z$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$26*About!$B$28</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A29,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(Z$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$33*About!$B$35</f>
         <v>35538681.814215168</v>
       </c>
       <c r="AA29">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A29,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(AA$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$26*About!$B$28</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A29,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(AA$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$33*About!$B$35</f>
         <v>37158454.753582127</v>
       </c>
       <c r="AB29">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A29,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(AB$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$26*About!$B$28</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A29,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(AB$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$33*About!$B$35</f>
         <v>38845851.87857201</v>
       </c>
       <c r="AC29">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A29,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(AC$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$26*About!$B$28</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A29,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(AC$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$33*About!$B$35</f>
         <v>40559959.60827329</v>
       </c>
       <c r="AD29">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A29,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(AD$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$26*About!$B$28</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A29,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(AD$4,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$33*About!$B$35</f>
         <v>42335619.300331905</v>
       </c>
     </row>
@@ -15307,111 +15397,111 @@
         <v>530</v>
       </c>
       <c r="D44">
-        <f>INDEX(AEO25_Table_21._Residential!$F$77:$AG$80,MATCH($B44,AEO25_Table_21._Residential!$B$77:$B$80,0),MATCH(D$42,AEO25_Table_21._Residential!$F$5:$AG$5,0))*About!$A$25*About!$B$29</f>
+        <f>INDEX(AEO25_Table_21._Residential!$F$77:$AG$80,MATCH($B44,AEO25_Table_21._Residential!$B$77:$B$80,0),MATCH(D$42,AEO25_Table_21._Residential!$F$5:$AG$5,0))*About!$A$32*About!$B$36</f>
         <v>1.4025661782562939</v>
       </c>
       <c r="E44">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A44,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(E$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$25*About!$B$29</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A44,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(E$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$32*About!$B$36</f>
         <v>0.41060633044604544</v>
       </c>
       <c r="F44">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A44,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(F$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$25*About!$B$29</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A44,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(F$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$32*About!$B$36</f>
         <v>0.89845543592649557</v>
       </c>
       <c r="G44">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A44,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(G$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$25*About!$B$29</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A44,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(G$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$32*About!$B$36</f>
         <v>1.3732952319274669</v>
       </c>
       <c r="H44">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A44,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(H$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$25*About!$B$29</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A44,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(H$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$32*About!$B$36</f>
         <v>1.3838652958795432</v>
       </c>
       <c r="I44">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A44,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(I$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$25*About!$B$29</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A44,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(I$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$32*About!$B$36</f>
         <v>1.3944353598316197</v>
       </c>
       <c r="J44">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A44,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(J$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$25*About!$B$29</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A44,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(J$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$32*About!$B$36</f>
         <v>2.0562839796000971</v>
       </c>
       <c r="K44">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A44,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(K$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$25*About!$B$29</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A44,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(K$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$32*About!$B$36</f>
         <v>2.9401039423621791</v>
       </c>
       <c r="L44">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A44,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(L$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$25*About!$B$29</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A44,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(L$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$32*About!$B$36</f>
         <v>3.8515686877681534</v>
       </c>
       <c r="M44">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A44,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(M$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$25*About!$B$29</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A44,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(M$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$32*About!$B$36</f>
         <v>4.5605760543997409</v>
       </c>
       <c r="N44">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A44,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(N$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$25*About!$B$29</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A44,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(N$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$32*About!$B$36</f>
         <v>5.449274508216627</v>
       </c>
       <c r="O44">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A44,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(O$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$25*About!$B$29</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A44,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(O$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$32*About!$B$36</f>
         <v>5.459844572168703</v>
       </c>
       <c r="P44">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A44,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(P$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$25*About!$B$29</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A44,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(P$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$32*About!$B$36</f>
         <v>5.4704146361207799</v>
       </c>
       <c r="Q44">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A44,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(Q$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$25*About!$B$29</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A44,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(Q$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$32*About!$B$36</f>
         <v>5.480984700072856</v>
       </c>
       <c r="R44">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A44,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(R$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$25*About!$B$29</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A44,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(R$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$32*About!$B$36</f>
         <v>5.4915547640249329</v>
       </c>
       <c r="S44">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A44,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(S$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$25*About!$B$29</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A44,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(S$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$32*About!$B$36</f>
         <v>5.5029379098194759</v>
       </c>
       <c r="T44">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A44,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(T$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$25*About!$B$29</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A44,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(T$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$32*About!$B$36</f>
         <v>5.5143210556140208</v>
       </c>
       <c r="U44">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A44,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(U$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$25*About!$B$29</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A44,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(U$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$32*About!$B$36</f>
         <v>5.5273303650934995</v>
       </c>
       <c r="V44">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A44,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(V$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$25*About!$B$29</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A44,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(V$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$32*About!$B$36</f>
         <v>5.5444050837853149</v>
       </c>
       <c r="W44">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A44,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(W$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$25*About!$B$29</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A44,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(W$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$32*About!$B$36</f>
         <v>5.5679844572168697</v>
       </c>
       <c r="X44">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A44,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(X$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$25*About!$B$29</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A44,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(X$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$32*About!$B$36</f>
         <v>5.6053862219703712</v>
       </c>
       <c r="Y44">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A44,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(Y$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$25*About!$B$29</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A44,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(Y$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$32*About!$B$36</f>
         <v>5.6696196875252971</v>
       </c>
       <c r="Z44">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A44,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(Z$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$25*About!$B$29</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A44,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(Z$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$32*About!$B$36</f>
         <v>5.7818249817858005</v>
       </c>
       <c r="AA44">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A44,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(AA$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$25*About!$B$29</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A44,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(AA$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$32*About!$B$36</f>
         <v>5.8940302760463048</v>
       </c>
       <c r="AB44">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A44,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(AB$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$25*About!$B$29</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A44,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(AB$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$32*About!$B$36</f>
         <v>6.0070486521492752</v>
       </c>
       <c r="AC44">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A44,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(AC$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$25*About!$B$29</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A44,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(AC$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$32*About!$B$36</f>
         <v>6.1208801100947134</v>
       </c>
       <c r="AD44">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A44,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(AD$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$25*About!$B$29</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A44,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(AD$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$32*About!$B$36</f>
         <v>6.2355246498826196</v>
       </c>
     </row>
@@ -15598,111 +15688,111 @@
         <v>534</v>
       </c>
       <c r="D47">
-        <f>INDEX(AEO25_Table_21._Residential!$F$77:$AG$80,MATCH($B47,AEO25_Table_21._Residential!$B$77:$B$80,0),MATCH(D$42,AEO25_Table_21._Residential!$F$5:$AG$5,0))*About!$A$25*About!$B$29</f>
+        <f>INDEX(AEO25_Table_21._Residential!$F$77:$AG$80,MATCH($B47,AEO25_Table_21._Residential!$B$77:$B$80,0),MATCH(D$42,AEO25_Table_21._Residential!$F$5:$AG$5,0))*About!$A$32*About!$B$36</f>
         <v>250.57474912976602</v>
       </c>
       <c r="E47">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A47,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(E$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$25*About!$B$29</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A47,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(E$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$32*About!$B$36</f>
         <v>131.09481162470655</v>
       </c>
       <c r="F47">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A47,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(F$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$25*About!$B$29</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A47,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(F$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$32*About!$B$36</f>
         <v>131.20376459159718</v>
       </c>
       <c r="G47">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A47,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(G$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$25*About!$B$29</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A47,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(G$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$32*About!$B$36</f>
         <v>131.33711001376184</v>
       </c>
       <c r="H47">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A47,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(H$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$25*About!$B$29</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A47,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(H$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$32*About!$B$36</f>
         <v>131.46882927224155</v>
       </c>
       <c r="I47">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A47,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(I$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$25*About!$B$29</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A47,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(I$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$32*About!$B$36</f>
         <v>131.68185671496801</v>
       </c>
       <c r="J47">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A47,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(J$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$25*About!$B$29</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A47,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(J$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$32*About!$B$36</f>
         <v>132.05262203513317</v>
       </c>
       <c r="K47">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A47,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(K$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$25*About!$B$29</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A47,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(K$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$32*About!$B$36</f>
         <v>132.72666688253864</v>
       </c>
       <c r="L47">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A47,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(L$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$25*About!$B$29</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A47,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(L$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$32*About!$B$36</f>
         <v>133.77960786853396</v>
       </c>
       <c r="M47">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A47,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(M$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$25*About!$B$29</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A47,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(M$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$32*About!$B$36</f>
         <v>135.40658463531125</v>
       </c>
       <c r="N47">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A47,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(N$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$25*About!$B$29</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A47,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(N$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$32*About!$B$36</f>
         <v>137.65150360236379</v>
       </c>
       <c r="O47">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A47,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(O$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$25*About!$B$29</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A47,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(O$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$32*About!$B$36</f>
         <v>140.33792600987613</v>
       </c>
       <c r="P47">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A47,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(P$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$25*About!$B$29</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A47,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(P$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$32*About!$B$36</f>
         <v>143.35527272727273</v>
       </c>
       <c r="Q47">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A47,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(Q$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$25*About!$B$29</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A47,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(Q$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$32*About!$B$36</f>
         <v>146.70191759086862</v>
       </c>
       <c r="R47">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A47,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(R$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$25*About!$B$29</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A47,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(R$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$32*About!$B$36</f>
         <v>150.2176834776977</v>
       </c>
       <c r="S47">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A47,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(S$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$25*About!$B$29</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A47,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(S$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$32*About!$B$36</f>
         <v>153.8212622035133</v>
       </c>
       <c r="T47">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A47,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(T$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$25*About!$B$29</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A47,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(T$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$32*About!$B$36</f>
         <v>157.64274686311018</v>
       </c>
       <c r="U47">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A47,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(U$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$25*About!$B$29</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A47,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(U$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$32*About!$B$36</f>
         <v>161.90654804500929</v>
       </c>
       <c r="V47">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A47,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(V$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$25*About!$B$29</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A47,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(V$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$32*About!$B$36</f>
         <v>166.46143252651177</v>
       </c>
       <c r="W47">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A47,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(W$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$25*About!$B$29</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A47,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(W$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$32*About!$B$36</f>
         <v>171.16429790334331</v>
       </c>
       <c r="X47">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A47,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(X$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$25*About!$B$29</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A47,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(X$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$32*About!$B$36</f>
         <v>175.98343398364767</v>
       </c>
       <c r="Y47">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A47,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(Y$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$25*About!$B$29</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A47,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(Y$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$32*About!$B$36</f>
         <v>180.96112102323323</v>
       </c>
       <c r="Z47">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A47,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(Z$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$25*About!$B$29</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A47,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(Z$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$32*About!$B$36</f>
         <v>186.38193766696349</v>
       </c>
       <c r="AA47">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A47,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(AA$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$25*About!$B$29</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A47,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(AA$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$32*About!$B$36</f>
         <v>192.00683785315306</v>
       </c>
       <c r="AB47">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A47,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(AB$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$25*About!$B$29</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A47,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(AB$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$32*About!$B$36</f>
         <v>198.43587598154292</v>
       </c>
       <c r="AC47">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A47,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(AC$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$25*About!$B$29</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A47,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(AC$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$32*About!$B$36</f>
         <v>204.93646531206994</v>
       </c>
       <c r="AD47">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A47,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(AD$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$25*About!$B$29</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A47,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(AD$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$32*About!$B$36</f>
         <v>211.50616659920667</v>
       </c>
     </row>
@@ -15717,111 +15807,111 @@
         <v>536</v>
       </c>
       <c r="D48">
-        <f>INDEX(AEO25_Table_21._Residential!$F$77:$AG$80,MATCH($B48,AEO25_Table_21._Residential!$B$77:$B$80,0),MATCH(D$42,AEO25_Table_21._Residential!$F$5:$AG$5,0))*About!$A$25*About!$B$29</f>
+        <f>INDEX(AEO25_Table_21._Residential!$F$77:$AG$80,MATCH($B48,AEO25_Table_21._Residential!$B$77:$B$80,0),MATCH(D$42,AEO25_Table_21._Residential!$F$5:$AG$5,0))*About!$A$32*About!$B$36</f>
         <v>33586.644085485314</v>
       </c>
       <c r="E48">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A48,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(E$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$25*About!$B$29</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A48,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(E$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$32*About!$B$36</f>
         <v>36072.861350926898</v>
       </c>
       <c r="F48">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A48,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(F$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$25*About!$B$29</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A48,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(F$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$32*About!$B$36</f>
         <v>38259.984834453164</v>
       </c>
       <c r="G48">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A48,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(G$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$25*About!$B$29</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A48,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(G$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$32*About!$B$36</f>
         <v>40727.440236379822</v>
       </c>
       <c r="H48">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A48,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(H$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$25*About!$B$29</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A48,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(H$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$32*About!$B$36</f>
         <v>43279.974083056746</v>
       </c>
       <c r="I48">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A48,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(I$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$25*About!$B$29</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A48,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(I$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$32*About!$B$36</f>
         <v>45677.105223346553</v>
       </c>
       <c r="J48">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A48,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(J$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$25*About!$B$29</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A48,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(J$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$32*About!$B$36</f>
         <v>48200.653515421349</v>
       </c>
       <c r="K48">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A48,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(K$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$25*About!$B$29</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A48,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(K$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$32*About!$B$36</f>
         <v>50934.882696025255</v>
       </c>
       <c r="L48">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A48,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(L$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$25*About!$B$29</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A48,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(L$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$32*About!$B$36</f>
         <v>53663.724396340971</v>
       </c>
       <c r="M48">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A48,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(M$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$25*About!$B$29</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A48,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(M$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$32*About!$B$36</f>
         <v>56531.886044199789</v>
       </c>
       <c r="N48">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A48,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(N$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$25*About!$B$29</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A48,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(N$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$32*About!$B$36</f>
         <v>59575.347324212737</v>
       </c>
       <c r="O48">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A48,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(O$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$25*About!$B$29</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A48,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(O$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$32*About!$B$36</f>
         <v>62828.816260989224</v>
       </c>
       <c r="P48">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A48,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(P$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$25*About!$B$29</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A48,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(P$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$32*About!$B$36</f>
         <v>66242.132209503761</v>
       </c>
       <c r="Q48">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A48,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(Q$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$25*About!$B$29</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A48,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(Q$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$32*About!$B$36</f>
         <v>69907.185614182774</v>
       </c>
       <c r="R48">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A48,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(R$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$25*About!$B$29</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A48,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(R$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$32*About!$B$36</f>
         <v>73746.942662025409</v>
       </c>
       <c r="S48">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A48,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(S$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$25*About!$B$29</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A48,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(S$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$32*About!$B$36</f>
         <v>77794.55432591273</v>
       </c>
       <c r="T48">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A48,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(T$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$25*About!$B$29</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A48,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(T$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$32*About!$B$36</f>
         <v>81990.716855500679</v>
       </c>
       <c r="U48">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A48,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(U$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$25*About!$B$29</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A48,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(U$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$32*About!$B$36</f>
         <v>86364.605253460701</v>
       </c>
       <c r="V48">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A48,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(V$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$25*About!$B$29</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A48,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(V$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$32*About!$B$36</f>
         <v>90868.614390998133</v>
       </c>
       <c r="W48">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A48,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(W$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$25*About!$B$29</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A48,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(W$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$32*About!$B$36</f>
         <v>95514.394104751875</v>
       </c>
       <c r="X48">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A48,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(X$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$25*About!$B$29</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A48,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(X$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$32*About!$B$36</f>
         <v>100341.03086505302</v>
       </c>
       <c r="Y48">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A48,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(Y$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$25*About!$B$29</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A48,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(Y$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$32*About!$B$36</f>
         <v>105287.69639310289</v>
       </c>
       <c r="Z48">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A48,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(Z$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$25*About!$B$29</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A48,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(Z$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$32*About!$B$36</f>
         <v>110385.40081729133</v>
       </c>
       <c r="AA48">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A48,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(AA$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$25*About!$B$29</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A48,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(AA$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$32*About!$B$36</f>
         <v>115640.48292366226</v>
       </c>
       <c r="AB48">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A48,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(AB$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$25*About!$B$29</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A48,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(AB$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$32*About!$B$36</f>
         <v>121126.73883331985</v>
       </c>
       <c r="AC48">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A48,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(AC$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$25*About!$B$29</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A48,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(AC$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$32*About!$B$36</f>
         <v>126714.16976896301</v>
       </c>
       <c r="AD48">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A48,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(AD$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$25*About!$B$29</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A48,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(AD$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$32*About!$B$36</f>
         <v>132502.56445203593</v>
       </c>
     </row>
@@ -16873,111 +16963,111 @@
         <v>530</v>
       </c>
       <c r="D63">
-        <f>INDEX(AEO25_Table_21._Residential!$F$77:$AG$80,MATCH($B63,AEO25_Table_21._Residential!$B$77:$B$80,0),MATCH(D$42,AEO25_Table_21._Residential!$F$5:$AG$5,0))*About!$A$26*About!$B$29</f>
+        <f>INDEX(AEO25_Table_21._Residential!$F$77:$AG$80,MATCH($B63,AEO25_Table_21._Residential!$B$77:$B$80,0),MATCH(D$42,AEO25_Table_21._Residential!$F$5:$AG$5,0))*About!$A$33*About!$B$36</f>
         <v>0.32243382174370594</v>
       </c>
       <c r="E63">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A63,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(E$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$26*About!$B$29</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A63,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(E$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$33*About!$B$36</f>
         <v>9.4393669553954507E-2</v>
       </c>
       <c r="F63">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A63,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(F$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$26*About!$B$29</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A63,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(F$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$33*About!$B$36</f>
         <v>0.20654456407350441</v>
       </c>
       <c r="G63">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A63,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(G$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$26*About!$B$29</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A63,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(G$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$33*About!$B$36</f>
         <v>0.31570476807253295</v>
       </c>
       <c r="H63">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A63,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(H$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$26*About!$B$29</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A63,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(H$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$33*About!$B$36</f>
         <v>0.31813470412045658</v>
       </c>
       <c r="I63">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A63,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(I$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$26*About!$B$29</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A63,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(I$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$33*About!$B$36</f>
         <v>0.32056464016838015</v>
       </c>
       <c r="J63">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A63,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(J$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$26*About!$B$29</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A63,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(J$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$33*About!$B$36</f>
         <v>0.47271602039990285</v>
       </c>
       <c r="K63">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A63,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(K$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$26*About!$B$29</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A63,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(K$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$33*About!$B$36</f>
         <v>0.67589605763782079</v>
       </c>
       <c r="L63">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A63,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(L$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$26*About!$B$29</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A63,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(L$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$33*About!$B$36</f>
         <v>0.88543131223184646</v>
       </c>
       <c r="M63">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A63,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(M$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$26*About!$B$29</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A63,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(M$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$33*About!$B$36</f>
         <v>1.0484239456002591</v>
       </c>
       <c r="N63">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A63,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(N$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$26*About!$B$29</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A63,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(N$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$33*About!$B$36</f>
         <v>1.2527254917833723</v>
       </c>
       <c r="O63">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A63,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(O$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$26*About!$B$29</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A63,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(O$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$33*About!$B$36</f>
         <v>1.255155427831296</v>
       </c>
       <c r="P63">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A63,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(P$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$26*About!$B$29</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A63,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(P$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$33*About!$B$36</f>
         <v>1.2575853638792196</v>
       </c>
       <c r="Q63">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A63,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(Q$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$26*About!$B$29</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A63,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(Q$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$33*About!$B$36</f>
         <v>1.2600152999271432</v>
       </c>
       <c r="R63">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A63,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(R$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$26*About!$B$29</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A63,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(R$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$33*About!$B$36</f>
         <v>1.2624452359750666</v>
       </c>
       <c r="S63">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A63,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(S$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$26*About!$B$29</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A63,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(S$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$33*About!$B$36</f>
         <v>1.265062090180523</v>
       </c>
       <c r="T63">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A63,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(T$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$26*About!$B$29</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A63,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(T$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$33*About!$B$36</f>
         <v>1.2676789443859791</v>
       </c>
       <c r="U63">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A63,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(U$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$26*About!$B$29</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A63,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(U$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$33*About!$B$36</f>
         <v>1.2706696349065005</v>
       </c>
       <c r="V63">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A63,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(V$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$26*About!$B$29</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A63,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(V$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$33*About!$B$36</f>
         <v>1.2745949162146848</v>
       </c>
       <c r="W63">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A63,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(W$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$26*About!$B$29</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A63,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(W$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$33*About!$B$36</f>
         <v>1.2800155427831297</v>
       </c>
       <c r="X63">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A63,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(X$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$26*About!$B$29</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A63,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(X$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$33*About!$B$36</f>
         <v>1.2886137780296285</v>
       </c>
       <c r="Y63">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A63,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(Y$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$26*About!$B$29</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A63,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(Y$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$33*About!$B$36</f>
         <v>1.3033803124747023</v>
       </c>
       <c r="Z63">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A63,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(Z$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$26*About!$B$29</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A63,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(Z$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$33*About!$B$36</f>
         <v>1.329175018214199</v>
       </c>
       <c r="AA63">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A63,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(AA$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$26*About!$B$29</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A63,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(AA$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$33*About!$B$36</f>
         <v>1.3549697239536955</v>
       </c>
       <c r="AB63">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A63,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(AB$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$26*About!$B$29</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A63,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(AB$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$33*About!$B$36</f>
         <v>1.3809513478507245</v>
       </c>
       <c r="AC63">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A63,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(AC$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$26*About!$B$29</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A63,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(AC$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$33*About!$B$36</f>
         <v>1.4071198899052861</v>
       </c>
       <c r="AD63">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A63,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(AD$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$26*About!$B$29</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A63,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(AD$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$33*About!$B$36</f>
         <v>1.4334753501173803</v>
       </c>
     </row>
@@ -17164,111 +17254,111 @@
         <v>534</v>
       </c>
       <c r="D66">
-        <f>INDEX(AEO25_Table_21._Residential!$F$77:$AG$80,MATCH($B66,AEO25_Table_21._Residential!$B$77:$B$80,0),MATCH(D$42,AEO25_Table_21._Residential!$F$5:$AG$5,0))*About!$A$26*About!$B$29</f>
+        <f>INDEX(AEO25_Table_21._Residential!$F$77:$AG$80,MATCH($B66,AEO25_Table_21._Residential!$B$77:$B$80,0),MATCH(D$42,AEO25_Table_21._Residential!$F$5:$AG$5,0))*About!$A$33*About!$B$36</f>
         <v>57.60425087023394</v>
       </c>
       <c r="E66">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A66,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(E$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$26*About!$B$29</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A66,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(E$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$33*About!$B$36</f>
         <v>30.137188375293448</v>
       </c>
       <c r="F66">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A66,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(F$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$26*About!$B$29</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A66,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(F$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$33*About!$B$36</f>
         <v>30.162235408402818</v>
       </c>
       <c r="G66">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A66,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(G$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$26*About!$B$29</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A66,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(G$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$33*About!$B$36</f>
         <v>30.192889986238161</v>
       </c>
       <c r="H66">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A66,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(H$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$26*About!$B$29</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A66,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(H$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$33*About!$B$36</f>
         <v>30.223170727758436</v>
       </c>
       <c r="I66">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A66,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(I$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$26*About!$B$29</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A66,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(I$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$33*About!$B$36</f>
         <v>30.272143285031973</v>
       </c>
       <c r="J66">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A66,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(J$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$26*About!$B$29</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A66,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(J$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$33*About!$B$36</f>
         <v>30.357377964866835</v>
       </c>
       <c r="K66">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A66,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(K$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$26*About!$B$29</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A66,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(K$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$33*About!$B$36</f>
         <v>30.512333117461345</v>
       </c>
       <c r="L66">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A66,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(L$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$26*About!$B$29</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A66,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(L$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$33*About!$B$36</f>
         <v>30.754392131466041</v>
       </c>
       <c r="M66">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A66,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(M$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$26*About!$B$29</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A66,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(M$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$33*About!$B$36</f>
         <v>31.128415364688738</v>
       </c>
       <c r="N66">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A66,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(N$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$26*About!$B$29</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A66,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(N$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$33*About!$B$36</f>
         <v>31.644496397636203</v>
       </c>
       <c r="O66">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A66,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(O$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$26*About!$B$29</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A66,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(O$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$33*About!$B$36</f>
         <v>32.262073990123852</v>
       </c>
       <c r="P66">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A66,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(P$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$26*About!$B$29</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A66,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(P$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$33*About!$B$36</f>
         <v>32.955727272727266</v>
       </c>
       <c r="Q66">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A66,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(Q$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$26*About!$B$29</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A66,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(Q$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$33*About!$B$36</f>
         <v>33.725082409131382</v>
       </c>
       <c r="R66">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A66,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(R$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$26*About!$B$29</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A66,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(R$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$33*About!$B$36</f>
         <v>34.533316522302272</v>
       </c>
       <c r="S66">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A66,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(S$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$26*About!$B$29</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A66,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(S$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$33*About!$B$36</f>
         <v>35.361737796486679</v>
       </c>
       <c r="T66">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A66,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(T$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$26*About!$B$29</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A66,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(T$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$33*About!$B$36</f>
         <v>36.240253136889827</v>
       </c>
       <c r="U66">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A66,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(U$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$26*About!$B$29</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A66,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(U$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$33*About!$B$36</f>
         <v>37.220451954990693</v>
       </c>
       <c r="V66">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A66,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(V$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$26*About!$B$29</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A66,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(V$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$33*About!$B$36</f>
         <v>38.267567473488214</v>
       </c>
       <c r="W66">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A66,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(W$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$26*About!$B$29</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A66,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(W$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$33*About!$B$36</f>
         <v>39.34870209665668</v>
       </c>
       <c r="X66">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A66,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(X$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$26*About!$B$29</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A66,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(X$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$33*About!$B$36</f>
         <v>40.456566016352298</v>
       </c>
       <c r="Y66">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A66,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(Y$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$26*About!$B$29</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A66,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(Y$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$33*About!$B$36</f>
         <v>41.600878976766779</v>
       </c>
       <c r="Z66">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A66,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(Z$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$26*About!$B$29</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A66,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(Z$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$33*About!$B$36</f>
         <v>42.847062333036504</v>
       </c>
       <c r="AA66">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A66,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(AA$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$26*About!$B$29</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A66,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(AA$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$33*About!$B$36</f>
         <v>44.140162146846919</v>
       </c>
       <c r="AB66">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A66,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(AB$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$26*About!$B$29</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A66,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(AB$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$33*About!$B$36</f>
         <v>45.618124018457053</v>
       </c>
       <c r="AC66">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A66,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(AC$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$26*About!$B$29</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A66,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(AC$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$33*About!$B$36</f>
         <v>47.112534687930058</v>
       </c>
       <c r="AD66">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A66,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(AD$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$26*About!$B$29</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A66,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(AD$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$33*About!$B$36</f>
         <v>48.622833400793326</v>
       </c>
     </row>
@@ -17283,111 +17373,111 @@
         <v>536</v>
       </c>
       <c r="D67">
-        <f>INDEX(AEO25_Table_21._Residential!$F$77:$AG$80,MATCH($B67,AEO25_Table_21._Residential!$B$77:$B$80,0),MATCH(D$42,AEO25_Table_21._Residential!$F$5:$AG$5,0))*About!$A$26*About!$B$29</f>
+        <f>INDEX(AEO25_Table_21._Residential!$F$77:$AG$80,MATCH($B67,AEO25_Table_21._Residential!$B$77:$B$80,0),MATCH(D$42,AEO25_Table_21._Residential!$F$5:$AG$5,0))*About!$A$33*About!$B$36</f>
         <v>7721.182914514693</v>
       </c>
       <c r="E67">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A67,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(E$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$26*About!$B$29</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A67,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(E$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$33*About!$B$36</f>
         <v>8292.7356490730999</v>
       </c>
       <c r="F67">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A67,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(F$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$26*About!$B$29</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A67,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(F$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$33*About!$B$36</f>
         <v>8795.5301655468302</v>
       </c>
       <c r="G67">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A67,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(G$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$26*About!$B$29</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A67,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(G$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$33*About!$B$36</f>
         <v>9362.7697636201738</v>
       </c>
       <c r="H67">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A67,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(H$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$26*About!$B$29</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A67,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(H$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$33*About!$B$36</f>
         <v>9949.5679169432515</v>
       </c>
       <c r="I67">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A67,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(I$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$26*About!$B$29</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A67,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(I$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$33*About!$B$36</f>
         <v>10500.640776653445</v>
       </c>
       <c r="J67">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A67,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(J$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$26*About!$B$29</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A67,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(J$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$33*About!$B$36</f>
         <v>11080.775484578644</v>
       </c>
       <c r="K67">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A67,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(K$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$26*About!$B$29</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A67,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(K$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$33*About!$B$36</f>
         <v>11709.343303974743</v>
       </c>
       <c r="L67">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A67,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(L$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$26*About!$B$29</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A67,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(L$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$33*About!$B$36</f>
         <v>12336.67260365903</v>
       </c>
       <c r="M67">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A67,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(M$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$26*About!$B$29</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A67,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(M$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$33*About!$B$36</f>
         <v>12996.02995580021</v>
       </c>
       <c r="N67">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A67,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(N$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$26*About!$B$29</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A67,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(N$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$33*About!$B$36</f>
         <v>13695.686675787258</v>
       </c>
       <c r="O67">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A67,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(O$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$26*About!$B$29</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A67,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(O$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$33*About!$B$36</f>
         <v>14443.621739010765</v>
       </c>
       <c r="P67">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A67,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(P$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$26*About!$B$29</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A67,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(P$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$33*About!$B$36</f>
         <v>15228.303790496237</v>
       </c>
       <c r="Q67">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A67,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(Q$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$26*About!$B$29</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A67,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(Q$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$33*About!$B$36</f>
         <v>16070.857385817209</v>
       </c>
       <c r="R67">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A67,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(R$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$26*About!$B$29</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A67,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(R$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$33*About!$B$36</f>
         <v>16953.57333797458</v>
       </c>
       <c r="S67">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A67,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(S$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$26*About!$B$29</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A67,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(S$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$33*About!$B$36</f>
         <v>17884.072674087267</v>
       </c>
       <c r="T67">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A67,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(T$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$26*About!$B$29</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A67,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(T$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$33*About!$B$36</f>
         <v>18848.722144499312</v>
       </c>
       <c r="U67">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A67,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(U$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$26*About!$B$29</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A67,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(U$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$33*About!$B$36</f>
         <v>19854.228746539302</v>
       </c>
       <c r="V67">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A67,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(V$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$26*About!$B$29</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A67,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(V$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$33*About!$B$36</f>
         <v>20889.648609001859</v>
       </c>
       <c r="W67">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A67,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(W$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$26*About!$B$29</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A67,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(W$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$33*About!$B$36</f>
         <v>21957.659895248118</v>
       </c>
       <c r="X67">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A67,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(X$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$26*About!$B$29</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A67,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(X$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$33*About!$B$36</f>
         <v>23067.248134946974</v>
       </c>
       <c r="Y67">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A67,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(Y$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$26*About!$B$29</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A67,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(Y$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$33*About!$B$36</f>
         <v>24204.429606897113</v>
       </c>
       <c r="Z67">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A67,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(Z$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$26*About!$B$29</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A67,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(Z$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$33*About!$B$36</f>
         <v>25376.333182708651</v>
       </c>
       <c r="AA67">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A67,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(AA$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$26*About!$B$29</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A67,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(AA$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$33*About!$B$36</f>
         <v>26584.416076337729</v>
       </c>
       <c r="AB67">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A67,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(AB$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$26*About!$B$29</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A67,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(AB$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$33*About!$B$36</f>
         <v>27845.643166680158</v>
       </c>
       <c r="AC67">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A67,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(AC$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$26*About!$B$29</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A67,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(AC$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$33*About!$B$36</f>
         <v>29130.129231036997</v>
       </c>
       <c r="AD67">
-        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A67,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(AD$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$26*About!$B$29</f>
+        <f>INDEX(AEO26_Table_21._Residential!$E$6:$AD$92,MATCH($A67,AEO26_Table_21._Residential!$B$6:$B$92,0),MATCH(AD$42,AEO26_Table_21._Residential!$E$5:$AD$5,0))*About!$A$33*About!$B$36</f>
         <v>30460.814547964055</v>
       </c>
     </row>
@@ -23344,6 +23434,694 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{858104B2-5734-4794-B2D1-CAE7717AD060}">
+  <dimension ref="B2:AB26"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="30" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B2" s="79" t="s">
+        <v>982</v>
+      </c>
+    </row>
+    <row r="3" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B3" t="s">
+        <v>983</v>
+      </c>
+    </row>
+    <row r="5" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B5" t="s">
+        <v>984</v>
+      </c>
+    </row>
+    <row r="6" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
+        <v>985</v>
+      </c>
+    </row>
+    <row r="7" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B7" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="8" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B8" t="s">
+        <v>987</v>
+      </c>
+    </row>
+    <row r="10" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B10">
+        <v>90</v>
+      </c>
+      <c r="C10" t="s">
+        <v>988</v>
+      </c>
+    </row>
+    <row r="11" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B11" s="81">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="C11" t="s">
+        <v>990</v>
+      </c>
+    </row>
+    <row r="12" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B12" s="16">
+        <v>1.2E-2</v>
+      </c>
+      <c r="C12" t="s">
+        <v>991</v>
+      </c>
+    </row>
+    <row r="13" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B13" s="80">
+        <v>0.36</v>
+      </c>
+      <c r="C13" t="s">
+        <v>989</v>
+      </c>
+    </row>
+    <row r="14" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B14" s="80">
+        <v>0.6</v>
+      </c>
+      <c r="C14" t="s">
+        <v>992</v>
+      </c>
+    </row>
+    <row r="16" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B16" t="s">
+        <v>993</v>
+      </c>
+    </row>
+    <row r="17" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B17" t="s">
+        <v>994</v>
+      </c>
+    </row>
+    <row r="19" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="C19">
+        <v>2025</v>
+      </c>
+      <c r="D19">
+        <v>2026</v>
+      </c>
+      <c r="E19">
+        <v>2027</v>
+      </c>
+      <c r="F19">
+        <v>2028</v>
+      </c>
+      <c r="G19">
+        <v>2029</v>
+      </c>
+      <c r="H19">
+        <v>2030</v>
+      </c>
+      <c r="I19">
+        <v>2031</v>
+      </c>
+      <c r="J19">
+        <v>2032</v>
+      </c>
+      <c r="K19">
+        <v>2033</v>
+      </c>
+      <c r="L19">
+        <v>2034</v>
+      </c>
+      <c r="M19">
+        <v>2035</v>
+      </c>
+      <c r="N19">
+        <v>2036</v>
+      </c>
+      <c r="O19">
+        <v>2037</v>
+      </c>
+      <c r="P19">
+        <v>2038</v>
+      </c>
+      <c r="Q19">
+        <v>2039</v>
+      </c>
+      <c r="R19">
+        <v>2040</v>
+      </c>
+      <c r="S19">
+        <v>2041</v>
+      </c>
+      <c r="T19">
+        <v>2042</v>
+      </c>
+      <c r="U19">
+        <v>2043</v>
+      </c>
+      <c r="V19">
+        <v>2044</v>
+      </c>
+      <c r="W19">
+        <v>2045</v>
+      </c>
+      <c r="X19">
+        <v>2046</v>
+      </c>
+      <c r="Y19">
+        <v>2047</v>
+      </c>
+      <c r="Z19">
+        <v>2048</v>
+      </c>
+      <c r="AA19">
+        <v>2049</v>
+      </c>
+      <c r="AB19">
+        <v>2050</v>
+      </c>
+    </row>
+    <row r="20" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B20" t="s">
+        <v>995</v>
+      </c>
+      <c r="C20">
+        <v>0</v>
+      </c>
+      <c r="D20">
+        <f>$B$10*$B$13/5+C20</f>
+        <v>6.4799999999999995</v>
+      </c>
+      <c r="E20">
+        <f>$B$10*$B$13/5+D20</f>
+        <v>12.959999999999999</v>
+      </c>
+      <c r="F20">
+        <f t="shared" ref="F20:H20" si="0">$B$10*$B$13/5+E20</f>
+        <v>19.439999999999998</v>
+      </c>
+      <c r="G20">
+        <f t="shared" si="0"/>
+        <v>25.919999999999998</v>
+      </c>
+      <c r="H20">
+        <f t="shared" si="0"/>
+        <v>32.4</v>
+      </c>
+      <c r="I20">
+        <f>H20</f>
+        <v>32.4</v>
+      </c>
+      <c r="J20">
+        <f t="shared" ref="J20:AB20" si="1">I20</f>
+        <v>32.4</v>
+      </c>
+      <c r="K20">
+        <f t="shared" si="1"/>
+        <v>32.4</v>
+      </c>
+      <c r="L20">
+        <f t="shared" si="1"/>
+        <v>32.4</v>
+      </c>
+      <c r="M20">
+        <f t="shared" si="1"/>
+        <v>32.4</v>
+      </c>
+      <c r="N20">
+        <f t="shared" si="1"/>
+        <v>32.4</v>
+      </c>
+      <c r="O20">
+        <f t="shared" si="1"/>
+        <v>32.4</v>
+      </c>
+      <c r="P20">
+        <f t="shared" si="1"/>
+        <v>32.4</v>
+      </c>
+      <c r="Q20">
+        <f t="shared" si="1"/>
+        <v>32.4</v>
+      </c>
+      <c r="R20">
+        <f t="shared" si="1"/>
+        <v>32.4</v>
+      </c>
+      <c r="S20">
+        <f t="shared" si="1"/>
+        <v>32.4</v>
+      </c>
+      <c r="T20">
+        <f t="shared" si="1"/>
+        <v>32.4</v>
+      </c>
+      <c r="U20">
+        <f t="shared" si="1"/>
+        <v>32.4</v>
+      </c>
+      <c r="V20">
+        <f t="shared" si="1"/>
+        <v>32.4</v>
+      </c>
+      <c r="W20">
+        <f t="shared" si="1"/>
+        <v>32.4</v>
+      </c>
+      <c r="X20">
+        <f t="shared" si="1"/>
+        <v>32.4</v>
+      </c>
+      <c r="Y20">
+        <f t="shared" si="1"/>
+        <v>32.4</v>
+      </c>
+      <c r="Z20">
+        <f t="shared" si="1"/>
+        <v>32.4</v>
+      </c>
+      <c r="AA20">
+        <f t="shared" si="1"/>
+        <v>32.4</v>
+      </c>
+      <c r="AB20">
+        <f t="shared" si="1"/>
+        <v>32.4</v>
+      </c>
+    </row>
+    <row r="23" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="C23">
+        <v>2025</v>
+      </c>
+      <c r="D23">
+        <v>2026</v>
+      </c>
+      <c r="E23">
+        <v>2027</v>
+      </c>
+      <c r="F23">
+        <v>2028</v>
+      </c>
+      <c r="G23">
+        <v>2029</v>
+      </c>
+      <c r="H23">
+        <v>2030</v>
+      </c>
+      <c r="I23">
+        <v>2031</v>
+      </c>
+      <c r="J23">
+        <v>2032</v>
+      </c>
+      <c r="K23">
+        <v>2033</v>
+      </c>
+      <c r="L23">
+        <v>2034</v>
+      </c>
+      <c r="M23">
+        <v>2035</v>
+      </c>
+      <c r="N23">
+        <v>2036</v>
+      </c>
+      <c r="O23">
+        <v>2037</v>
+      </c>
+      <c r="P23">
+        <v>2038</v>
+      </c>
+      <c r="Q23">
+        <v>2039</v>
+      </c>
+      <c r="R23">
+        <v>2040</v>
+      </c>
+      <c r="S23">
+        <v>2041</v>
+      </c>
+      <c r="T23">
+        <v>2042</v>
+      </c>
+      <c r="U23">
+        <v>2043</v>
+      </c>
+      <c r="V23">
+        <v>2044</v>
+      </c>
+      <c r="W23">
+        <v>2045</v>
+      </c>
+      <c r="X23">
+        <v>2046</v>
+      </c>
+      <c r="Y23">
+        <v>2047</v>
+      </c>
+      <c r="Z23">
+        <v>2048</v>
+      </c>
+      <c r="AA23">
+        <v>2049</v>
+      </c>
+      <c r="AB23">
+        <v>2050</v>
+      </c>
+    </row>
+    <row r="24" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B24" s="1" t="s">
+        <v>548</v>
+      </c>
+      <c r="C24">
+        <f>Calculations!E44</f>
+        <v>0.41060633044604544</v>
+      </c>
+      <c r="D24">
+        <f>Calculations!F44</f>
+        <v>0.89845543592649557</v>
+      </c>
+      <c r="E24">
+        <f>Calculations!G44</f>
+        <v>1.3732952319274669</v>
+      </c>
+      <c r="F24">
+        <f>Calculations!H44</f>
+        <v>1.3838652958795432</v>
+      </c>
+      <c r="G24">
+        <f>Calculations!I44</f>
+        <v>1.3944353598316197</v>
+      </c>
+      <c r="H24">
+        <f>Calculations!J44</f>
+        <v>2.0562839796000971</v>
+      </c>
+      <c r="I24">
+        <f>Calculations!K44</f>
+        <v>2.9401039423621791</v>
+      </c>
+      <c r="J24">
+        <f>Calculations!L44</f>
+        <v>3.8515686877681534</v>
+      </c>
+      <c r="K24">
+        <f>Calculations!M44</f>
+        <v>4.5605760543997409</v>
+      </c>
+      <c r="L24">
+        <f>Calculations!N44</f>
+        <v>5.449274508216627</v>
+      </c>
+      <c r="M24">
+        <f>Calculations!O44</f>
+        <v>5.459844572168703</v>
+      </c>
+      <c r="N24">
+        <f>Calculations!P44</f>
+        <v>5.4704146361207799</v>
+      </c>
+      <c r="O24">
+        <f>Calculations!Q44</f>
+        <v>5.480984700072856</v>
+      </c>
+      <c r="P24">
+        <f>Calculations!R44</f>
+        <v>5.4915547640249329</v>
+      </c>
+      <c r="Q24">
+        <f>Calculations!S44</f>
+        <v>5.5029379098194759</v>
+      </c>
+      <c r="R24">
+        <f>Calculations!T44</f>
+        <v>5.5143210556140208</v>
+      </c>
+      <c r="S24">
+        <f>Calculations!U44</f>
+        <v>5.5273303650934995</v>
+      </c>
+      <c r="T24">
+        <f>Calculations!V44</f>
+        <v>5.5444050837853149</v>
+      </c>
+      <c r="U24">
+        <f>Calculations!W44</f>
+        <v>5.5679844572168697</v>
+      </c>
+      <c r="V24">
+        <f>Calculations!X44</f>
+        <v>5.6053862219703712</v>
+      </c>
+      <c r="W24">
+        <f>Calculations!Y44</f>
+        <v>5.6696196875252971</v>
+      </c>
+      <c r="X24">
+        <f>Calculations!Z44</f>
+        <v>5.7818249817858005</v>
+      </c>
+      <c r="Y24">
+        <f>Calculations!AA44</f>
+        <v>5.8940302760463048</v>
+      </c>
+      <c r="Z24">
+        <f>Calculations!AB44</f>
+        <v>6.0070486521492752</v>
+      </c>
+      <c r="AA24">
+        <f>Calculations!AC44</f>
+        <v>6.1208801100947134</v>
+      </c>
+      <c r="AB24">
+        <f>Calculations!AD44</f>
+        <v>6.2355246498826196</v>
+      </c>
+    </row>
+    <row r="25" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B25" s="1" t="s">
+        <v>553</v>
+      </c>
+      <c r="C25">
+        <f>Calculations!E63</f>
+        <v>9.4393669553954507E-2</v>
+      </c>
+      <c r="D25">
+        <f>Calculations!F63</f>
+        <v>0.20654456407350441</v>
+      </c>
+      <c r="E25">
+        <f>Calculations!G63</f>
+        <v>0.31570476807253295</v>
+      </c>
+      <c r="F25">
+        <f>Calculations!H63</f>
+        <v>0.31813470412045658</v>
+      </c>
+      <c r="G25">
+        <f>Calculations!I63</f>
+        <v>0.32056464016838015</v>
+      </c>
+      <c r="H25">
+        <f>Calculations!J63</f>
+        <v>0.47271602039990285</v>
+      </c>
+      <c r="I25">
+        <f>Calculations!K63</f>
+        <v>0.67589605763782079</v>
+      </c>
+      <c r="J25">
+        <f>Calculations!L63</f>
+        <v>0.88543131223184646</v>
+      </c>
+      <c r="K25">
+        <f>Calculations!M63</f>
+        <v>1.0484239456002591</v>
+      </c>
+      <c r="L25">
+        <f>Calculations!N63</f>
+        <v>1.2527254917833723</v>
+      </c>
+      <c r="M25">
+        <f>Calculations!O63</f>
+        <v>1.255155427831296</v>
+      </c>
+      <c r="N25">
+        <f>Calculations!P63</f>
+        <v>1.2575853638792196</v>
+      </c>
+      <c r="O25">
+        <f>Calculations!Q63</f>
+        <v>1.2600152999271432</v>
+      </c>
+      <c r="P25">
+        <f>Calculations!R63</f>
+        <v>1.2624452359750666</v>
+      </c>
+      <c r="Q25">
+        <f>Calculations!S63</f>
+        <v>1.265062090180523</v>
+      </c>
+      <c r="R25">
+        <f>Calculations!T63</f>
+        <v>1.2676789443859791</v>
+      </c>
+      <c r="S25">
+        <f>Calculations!U63</f>
+        <v>1.2706696349065005</v>
+      </c>
+      <c r="T25">
+        <f>Calculations!V63</f>
+        <v>1.2745949162146848</v>
+      </c>
+      <c r="U25">
+        <f>Calculations!W63</f>
+        <v>1.2800155427831297</v>
+      </c>
+      <c r="V25">
+        <f>Calculations!X63</f>
+        <v>1.2886137780296285</v>
+      </c>
+      <c r="W25">
+        <f>Calculations!Y63</f>
+        <v>1.3033803124747023</v>
+      </c>
+      <c r="X25">
+        <f>Calculations!Z63</f>
+        <v>1.329175018214199</v>
+      </c>
+      <c r="Y25">
+        <f>Calculations!AA63</f>
+        <v>1.3549697239536955</v>
+      </c>
+      <c r="Z25">
+        <f>Calculations!AB63</f>
+        <v>1.3809513478507245</v>
+      </c>
+      <c r="AA25">
+        <f>Calculations!AC63</f>
+        <v>1.4071198899052861</v>
+      </c>
+      <c r="AB25">
+        <f>Calculations!AD63</f>
+        <v>1.4334753501173803</v>
+      </c>
+    </row>
+    <row r="26" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B26" s="1" t="s">
+        <v>555</v>
+      </c>
+      <c r="C26">
+        <f>Calculations!E84</f>
+        <v>1508.008</v>
+      </c>
+      <c r="D26">
+        <f>Calculations!F84+D20*1000</f>
+        <v>8020.9689999999991</v>
+      </c>
+      <c r="E26">
+        <f>Calculations!G84+E20*1000</f>
+        <v>14519.124999999998</v>
+      </c>
+      <c r="F26">
+        <f>Calculations!H84+F20*1000</f>
+        <v>21016.868999999995</v>
+      </c>
+      <c r="G26">
+        <f>Calculations!I84+G20*1000</f>
+        <v>27515.394999999997</v>
+      </c>
+      <c r="H26">
+        <f>Calculations!J84+H20*1000</f>
+        <v>34015.290999999997</v>
+      </c>
+      <c r="I26">
+        <f>Calculations!K84+I20*1000</f>
+        <v>34034.760999999999</v>
+      </c>
+      <c r="J26">
+        <f>Calculations!L84+J20*1000</f>
+        <v>34055.343999999997</v>
+      </c>
+      <c r="K26">
+        <f>Calculations!M84+K20*1000</f>
+        <v>34076.552000000003</v>
+      </c>
+      <c r="L26">
+        <f>Calculations!N84+L20*1000</f>
+        <v>34100.095000000001</v>
+      </c>
+      <c r="M26">
+        <f>Calculations!O84+M20*1000</f>
+        <v>34122.014000000003</v>
+      </c>
+      <c r="N26">
+        <f>Calculations!P84+N20*1000</f>
+        <v>34144.811999999998</v>
+      </c>
+      <c r="O26">
+        <f>Calculations!Q84+O20*1000</f>
+        <v>34169.997000000003</v>
+      </c>
+      <c r="P26">
+        <f>Calculations!R84+P20*1000</f>
+        <v>34193.459000000003</v>
+      </c>
+      <c r="Q26">
+        <f>Calculations!S84+Q20*1000</f>
+        <v>34216.315999999999</v>
+      </c>
+      <c r="R26">
+        <f>Calculations!T84+R20*1000</f>
+        <v>34238.228000000003</v>
+      </c>
+      <c r="S26">
+        <f>Calculations!U84+S20*1000</f>
+        <v>34258.498999999996</v>
+      </c>
+      <c r="T26">
+        <f>Calculations!V84+T20*1000</f>
+        <v>34281.084999999999</v>
+      </c>
+      <c r="U26">
+        <f>Calculations!W84+U20*1000</f>
+        <v>34301.161999999997</v>
+      </c>
+      <c r="V26">
+        <f>Calculations!X84+V20*1000</f>
+        <v>34321.178</v>
+      </c>
+      <c r="W26">
+        <f>Calculations!Y84+W20*1000</f>
+        <v>34340.084000000003</v>
+      </c>
+      <c r="X26">
+        <f>Calculations!Z84+X20*1000</f>
+        <v>34359.432999999997</v>
+      </c>
+      <c r="Y26">
+        <f>Calculations!AA84+Y20*1000</f>
+        <v>34379.940999999999</v>
+      </c>
+      <c r="Z26">
+        <f>Calculations!AB84+Z20*1000</f>
+        <v>34400.097000000002</v>
+      </c>
+      <c r="AA26">
+        <f>Calculations!AC84+AA20*1000</f>
+        <v>34419.017999999996</v>
+      </c>
+      <c r="AB26">
+        <f>Calculations!AD84+AB20*1000</f>
+        <v>34439.06</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <sheetPr>
     <tabColor theme="3"/>
@@ -24018,111 +24796,111 @@
         <v>536</v>
       </c>
       <c r="B8" s="55">
-        <f>Calculations!D48-About!$C$39*1000</f>
+        <f>Calculations!D48-About!$C$46*1000</f>
         <v>30362.289170242049</v>
       </c>
       <c r="C8" s="55">
-        <f>Calculations!E48-About!$C$39*1000</f>
+        <f>Calculations!E48-About!$C$46*1000</f>
         <v>32848.506435683637</v>
       </c>
       <c r="D8" s="55">
-        <f>Calculations!F48-About!$C$39*1000</f>
+        <f>Calculations!F48-About!$C$46*1000</f>
         <v>35035.629919209903</v>
       </c>
       <c r="E8" s="55">
-        <f>Calculations!G48-About!$C$39*1000</f>
+        <f>Calculations!G48-About!$C$46*1000</f>
         <v>37503.085321136561</v>
       </c>
       <c r="F8" s="55">
-        <f>Calculations!H48-About!$C$39*1000</f>
+        <f>Calculations!H48-About!$C$46*1000</f>
         <v>40055.619167813486</v>
       </c>
       <c r="G8" s="55">
-        <f>Calculations!I48-About!$C$39*1000</f>
+        <f>Calculations!I48-About!$C$46*1000</f>
         <v>42452.750308103292</v>
       </c>
       <c r="H8" s="55">
-        <f>Calculations!J48-About!$C$39*1000</f>
+        <f>Calculations!J48-About!$C$46*1000</f>
         <v>44976.298600178088</v>
       </c>
       <c r="I8" s="55">
-        <f>Calculations!K48-About!$C$39*1000</f>
+        <f>Calculations!K48-About!$C$46*1000</f>
         <v>47710.527780781995</v>
       </c>
       <c r="J8" s="55">
-        <f>Calculations!L48-About!$C$39*1000</f>
+        <f>Calculations!L48-About!$C$46*1000</f>
         <v>50439.36948109771</v>
       </c>
       <c r="K8" s="55">
-        <f>Calculations!M48-About!$C$39*1000</f>
+        <f>Calculations!M48-About!$C$46*1000</f>
         <v>53307.531128956529</v>
       </c>
       <c r="L8" s="55">
-        <f>Calculations!N48-About!$C$39*1000</f>
+        <f>Calculations!N48-About!$C$46*1000</f>
         <v>56350.992408969476</v>
       </c>
       <c r="M8" s="55">
-        <f>Calculations!O48-About!$C$39*1000</f>
+        <f>Calculations!O48-About!$C$46*1000</f>
         <v>59604.461345745964</v>
       </c>
       <c r="N8" s="55">
-        <f>Calculations!P48-About!$C$39*1000</f>
+        <f>Calculations!P48-About!$C$46*1000</f>
         <v>63017.777294260501</v>
       </c>
       <c r="O8" s="55">
-        <f>Calculations!Q48-About!$C$39*1000</f>
+        <f>Calculations!Q48-About!$C$46*1000</f>
         <v>66682.830698939506</v>
       </c>
       <c r="P8" s="55">
-        <f>Calculations!R48-About!$C$39*1000</f>
+        <f>Calculations!R48-About!$C$46*1000</f>
         <v>70522.587746782141</v>
       </c>
       <c r="Q8" s="55">
-        <f>Calculations!S48-About!$C$39*1000</f>
+        <f>Calculations!S48-About!$C$46*1000</f>
         <v>74570.199410669462</v>
       </c>
       <c r="R8" s="55">
-        <f>Calculations!T48-About!$C$39*1000</f>
+        <f>Calculations!T48-About!$C$46*1000</f>
         <v>78766.361940257411</v>
       </c>
       <c r="S8" s="55">
-        <f>Calculations!U48-About!$C$39*1000</f>
+        <f>Calculations!U48-About!$C$46*1000</f>
         <v>83140.250338217433</v>
       </c>
       <c r="T8" s="55">
-        <f>Calculations!V48-About!$C$39*1000</f>
+        <f>Calculations!V48-About!$C$46*1000</f>
         <v>87644.259475754865</v>
       </c>
       <c r="U8" s="55">
-        <f>Calculations!W48-About!$C$39*1000</f>
+        <f>Calculations!W48-About!$C$46*1000</f>
         <v>92290.039189508607</v>
       </c>
       <c r="V8" s="55">
-        <f>Calculations!X48-About!$C$39*1000</f>
+        <f>Calculations!X48-About!$C$46*1000</f>
         <v>97116.675949809753</v>
       </c>
       <c r="W8" s="55">
-        <f>Calculations!Y48-About!$C$39*1000</f>
+        <f>Calculations!Y48-About!$C$46*1000</f>
         <v>102063.34147785962</v>
       </c>
       <c r="X8" s="55">
-        <f>Calculations!Z48-About!$C$39*1000</f>
+        <f>Calculations!Z48-About!$C$46*1000</f>
         <v>107161.04590204806</v>
       </c>
       <c r="Y8" s="55">
-        <f>Calculations!AA48-About!$C$39*1000</f>
+        <f>Calculations!AA48-About!$C$46*1000</f>
         <v>112416.12800841899</v>
       </c>
       <c r="Z8" s="55">
-        <f>Calculations!AB48-About!$C$39*1000</f>
+        <f>Calculations!AB48-About!$C$46*1000</f>
         <v>117902.38391807658</v>
       </c>
       <c r="AA8" s="55">
-        <f>Calculations!AC48-About!$C$39*1000</f>
+        <f>Calculations!AC48-About!$C$46*1000</f>
         <v>123489.81485371974</v>
       </c>
       <c r="AB8" s="55">
-        <f>Calculations!AD48-About!$C$39*1000</f>
+        <f>Calculations!AD48-About!$C$46*1000</f>
         <v>129278.20953679267</v>
       </c>
     </row>
@@ -25589,17 +26367,17 @@
       </c>
     </row>
     <row r="27" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="C27" s="66"/>
+      <c r="C27" s="56"/>
     </row>
     <row r="28" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="C28" s="66"/>
+      <c r="C28" s="56"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <sheetPr>
     <tabColor theme="3"/>
@@ -26353,111 +27131,111 @@
         <v>536</v>
       </c>
       <c r="B8">
-        <f>Calculations!D67-About!$C$40*1000</f>
+        <f>Calculations!D67-About!$C$47*1000</f>
         <v>6979.940829757953</v>
       </c>
       <c r="C8">
-        <f>Calculations!E67-About!$C$40*1000</f>
+        <f>Calculations!E67-About!$C$47*1000</f>
         <v>7551.4935643163599</v>
       </c>
       <c r="D8">
-        <f>Calculations!F67-About!$C$40*1000</f>
+        <f>Calculations!F67-About!$C$47*1000</f>
         <v>8054.2880807900901</v>
       </c>
       <c r="E8">
-        <f>Calculations!G67-About!$C$40*1000</f>
+        <f>Calculations!G67-About!$C$47*1000</f>
         <v>8621.5276788634346</v>
       </c>
       <c r="F8">
-        <f>Calculations!H67-About!$C$40*1000</f>
+        <f>Calculations!H67-About!$C$47*1000</f>
         <v>9208.3258321865123</v>
       </c>
       <c r="G8">
-        <f>Calculations!I67-About!$C$40*1000</f>
+        <f>Calculations!I67-About!$C$47*1000</f>
         <v>9759.3986918967057</v>
       </c>
       <c r="H8">
-        <f>Calculations!J67-About!$C$40*1000</f>
+        <f>Calculations!J67-About!$C$47*1000</f>
         <v>10339.533399821905</v>
       </c>
       <c r="I8">
-        <f>Calculations!K67-About!$C$40*1000</f>
+        <f>Calculations!K67-About!$C$47*1000</f>
         <v>10968.101219218004</v>
       </c>
       <c r="J8">
-        <f>Calculations!L67-About!$C$40*1000</f>
+        <f>Calculations!L67-About!$C$47*1000</f>
         <v>11595.430518902291</v>
       </c>
       <c r="K8">
-        <f>Calculations!M67-About!$C$40*1000</f>
+        <f>Calculations!M67-About!$C$47*1000</f>
         <v>12254.787871043471</v>
       </c>
       <c r="L8">
-        <f>Calculations!N67-About!$C$40*1000</f>
+        <f>Calculations!N67-About!$C$47*1000</f>
         <v>12954.444591030518</v>
       </c>
       <c r="M8">
-        <f>Calculations!O67-About!$C$40*1000</f>
+        <f>Calculations!O67-About!$C$47*1000</f>
         <v>13702.379654254026</v>
       </c>
       <c r="N8">
-        <f>Calculations!P67-About!$C$40*1000</f>
+        <f>Calculations!P67-About!$C$47*1000</f>
         <v>14487.061705739497</v>
       </c>
       <c r="O8">
-        <f>Calculations!Q67-About!$C$40*1000</f>
+        <f>Calculations!Q67-About!$C$47*1000</f>
         <v>15329.61530106047</v>
       </c>
       <c r="P8">
-        <f>Calculations!R67-About!$C$40*1000</f>
+        <f>Calculations!R67-About!$C$47*1000</f>
         <v>16212.331253217841</v>
       </c>
       <c r="Q8">
-        <f>Calculations!S67-About!$C$40*1000</f>
+        <f>Calculations!S67-About!$C$47*1000</f>
         <v>17142.830589330526</v>
       </c>
       <c r="R8">
-        <f>Calculations!T67-About!$C$40*1000</f>
+        <f>Calculations!T67-About!$C$47*1000</f>
         <v>18107.480059742571</v>
       </c>
       <c r="S8">
-        <f>Calculations!U67-About!$C$40*1000</f>
+        <f>Calculations!U67-About!$C$47*1000</f>
         <v>19112.986661782561</v>
       </c>
       <c r="T8">
-        <f>Calculations!V67-About!$C$40*1000</f>
+        <f>Calculations!V67-About!$C$47*1000</f>
         <v>20148.406524245118</v>
       </c>
       <c r="U8">
-        <f>Calculations!W67-About!$C$40*1000</f>
+        <f>Calculations!W67-About!$C$47*1000</f>
         <v>21216.417810491377</v>
       </c>
       <c r="V8">
-        <f>Calculations!X67-About!$C$40*1000</f>
+        <f>Calculations!X67-About!$C$47*1000</f>
         <v>22326.006050190234</v>
       </c>
       <c r="W8">
-        <f>Calculations!Y67-About!$C$40*1000</f>
+        <f>Calculations!Y67-About!$C$47*1000</f>
         <v>23463.187522140372</v>
       </c>
       <c r="X8">
-        <f>Calculations!Z67-About!$C$40*1000</f>
+        <f>Calculations!Z67-About!$C$47*1000</f>
         <v>24635.09109795191</v>
       </c>
       <c r="Y8">
-        <f>Calculations!AA67-About!$C$40*1000</f>
+        <f>Calculations!AA67-About!$C$47*1000</f>
         <v>25843.173991580989</v>
       </c>
       <c r="Z8">
-        <f>Calculations!AB67-About!$C$40*1000</f>
+        <f>Calculations!AB67-About!$C$47*1000</f>
         <v>27104.401081923417</v>
       </c>
       <c r="AA8">
-        <f>Calculations!AC67-About!$C$40*1000</f>
+        <f>Calculations!AC67-About!$C$47*1000</f>
         <v>28388.887146280256</v>
       </c>
       <c r="AB8">
-        <f>Calculations!AD67-About!$C$40*1000</f>
+        <f>Calculations!AD67-About!$C$47*1000</f>
         <v>29719.572463207314</v>
       </c>
     </row>
@@ -28204,7 +28982,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <sheetPr>
     <tabColor theme="3"/>
@@ -28509,109 +29287,109 @@
         <f>Calculations!D84</f>
         <v>1468.7250000000001</v>
       </c>
-      <c r="C4">
-        <f>Calculations!E84</f>
+      <c r="C4" s="82">
+        <f>'Data Center Gas'!C26</f>
         <v>1508.008</v>
       </c>
-      <c r="D4">
-        <f>Calculations!F84</f>
-        <v>1540.9690000000001</v>
-      </c>
-      <c r="E4">
-        <f>Calculations!G84</f>
-        <v>1559.125</v>
-      </c>
-      <c r="F4">
-        <f>Calculations!H84</f>
-        <v>1576.8690000000001</v>
-      </c>
-      <c r="G4">
-        <f>Calculations!I84</f>
-        <v>1595.395</v>
-      </c>
-      <c r="H4">
-        <f>Calculations!J84</f>
-        <v>1615.2909999999999</v>
-      </c>
-      <c r="I4">
-        <f>Calculations!K84</f>
-        <v>1634.761</v>
-      </c>
-      <c r="J4">
-        <f>Calculations!L84</f>
-        <v>1655.3439999999998</v>
-      </c>
-      <c r="K4">
-        <f>Calculations!M84</f>
-        <v>1676.5520000000001</v>
-      </c>
-      <c r="L4">
-        <f>Calculations!N84</f>
-        <v>1700.0949999999998</v>
-      </c>
-      <c r="M4">
-        <f>Calculations!O84</f>
-        <v>1722.0139999999999</v>
-      </c>
-      <c r="N4">
-        <f>Calculations!P84</f>
-        <v>1744.8120000000001</v>
-      </c>
-      <c r="O4">
-        <f>Calculations!Q84</f>
-        <v>1769.9970000000001</v>
-      </c>
-      <c r="P4">
-        <f>Calculations!R84</f>
-        <v>1793.4589999999998</v>
-      </c>
-      <c r="Q4">
-        <f>Calculations!S84</f>
-        <v>1816.316</v>
-      </c>
-      <c r="R4">
-        <f>Calculations!T84</f>
-        <v>1838.2280000000001</v>
-      </c>
-      <c r="S4">
-        <f>Calculations!U84</f>
-        <v>1858.4989999999998</v>
-      </c>
-      <c r="T4">
-        <f>Calculations!V84</f>
-        <v>1881.0849999999998</v>
-      </c>
-      <c r="U4">
-        <f>Calculations!W84</f>
-        <v>1901.162</v>
-      </c>
-      <c r="V4">
-        <f>Calculations!X84</f>
-        <v>1921.1780000000001</v>
-      </c>
-      <c r="W4">
-        <f>Calculations!Y84</f>
-        <v>1940.0839999999998</v>
-      </c>
-      <c r="X4">
-        <f>Calculations!Z84</f>
-        <v>1959.433</v>
-      </c>
-      <c r="Y4">
-        <f>Calculations!AA84</f>
-        <v>1979.941</v>
-      </c>
-      <c r="Z4">
-        <f>Calculations!AB84</f>
-        <v>2000.0969999999998</v>
-      </c>
-      <c r="AA4">
-        <f>Calculations!AC84</f>
-        <v>2019.018</v>
-      </c>
-      <c r="AB4">
-        <f>Calculations!AD84</f>
-        <v>2039.0600000000002</v>
+      <c r="D4" s="82">
+        <f>'Data Center Gas'!D26</f>
+        <v>8020.9689999999991</v>
+      </c>
+      <c r="E4" s="82">
+        <f>'Data Center Gas'!E26</f>
+        <v>14519.124999999998</v>
+      </c>
+      <c r="F4" s="82">
+        <f>'Data Center Gas'!F26</f>
+        <v>21016.868999999995</v>
+      </c>
+      <c r="G4" s="82">
+        <f>'Data Center Gas'!G26</f>
+        <v>27515.394999999997</v>
+      </c>
+      <c r="H4" s="82">
+        <f>'Data Center Gas'!H26</f>
+        <v>34015.290999999997</v>
+      </c>
+      <c r="I4" s="82">
+        <f>'Data Center Gas'!I26</f>
+        <v>34034.760999999999</v>
+      </c>
+      <c r="J4" s="82">
+        <f>'Data Center Gas'!J26</f>
+        <v>34055.343999999997</v>
+      </c>
+      <c r="K4" s="82">
+        <f>'Data Center Gas'!K26</f>
+        <v>34076.552000000003</v>
+      </c>
+      <c r="L4" s="82">
+        <f>'Data Center Gas'!L26</f>
+        <v>34100.095000000001</v>
+      </c>
+      <c r="M4" s="82">
+        <f>'Data Center Gas'!M26</f>
+        <v>34122.014000000003</v>
+      </c>
+      <c r="N4" s="82">
+        <f>'Data Center Gas'!N26</f>
+        <v>34144.811999999998</v>
+      </c>
+      <c r="O4" s="82">
+        <f>'Data Center Gas'!O26</f>
+        <v>34169.997000000003</v>
+      </c>
+      <c r="P4" s="82">
+        <f>'Data Center Gas'!P26</f>
+        <v>34193.459000000003</v>
+      </c>
+      <c r="Q4" s="82">
+        <f>'Data Center Gas'!Q26</f>
+        <v>34216.315999999999</v>
+      </c>
+      <c r="R4" s="82">
+        <f>'Data Center Gas'!R26</f>
+        <v>34238.228000000003</v>
+      </c>
+      <c r="S4" s="82">
+        <f>'Data Center Gas'!S26</f>
+        <v>34258.498999999996</v>
+      </c>
+      <c r="T4" s="82">
+        <f>'Data Center Gas'!T26</f>
+        <v>34281.084999999999</v>
+      </c>
+      <c r="U4" s="82">
+        <f>'Data Center Gas'!U26</f>
+        <v>34301.161999999997</v>
+      </c>
+      <c r="V4" s="82">
+        <f>'Data Center Gas'!V26</f>
+        <v>34321.178</v>
+      </c>
+      <c r="W4" s="82">
+        <f>'Data Center Gas'!W26</f>
+        <v>34340.084000000003</v>
+      </c>
+      <c r="X4" s="82">
+        <f>'Data Center Gas'!X26</f>
+        <v>34359.432999999997</v>
+      </c>
+      <c r="Y4" s="82">
+        <f>'Data Center Gas'!Y26</f>
+        <v>34379.940999999999</v>
+      </c>
+      <c r="Z4" s="82">
+        <f>'Data Center Gas'!Z26</f>
+        <v>34400.097000000002</v>
+      </c>
+      <c r="AA4" s="82">
+        <f>'Data Center Gas'!AA26</f>
+        <v>34419.017999999996</v>
+      </c>
+      <c r="AB4" s="82">
+        <f>'Data Center Gas'!AB26</f>
+        <v>34439.06</v>
       </c>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.25">
@@ -28958,111 +29736,111 @@
         <v>536</v>
       </c>
       <c r="B8">
-        <f>Calculations!D88-About!$C$36*1000</f>
+        <f>Calculations!D88-About!$C$43*1000</f>
         <v>21769.497000000003</v>
       </c>
       <c r="C8">
-        <f>Calculations!E88-About!$C$36*1000</f>
+        <f>Calculations!E88-About!$C$43*1000</f>
         <v>25925.201999999997</v>
       </c>
       <c r="D8">
-        <f>Calculations!F88-About!$C$36*1000</f>
+        <f>Calculations!F88-About!$C$43*1000</f>
         <v>30160.527000000002</v>
       </c>
       <c r="E8">
-        <f>Calculations!G88-About!$C$36*1000</f>
+        <f>Calculations!G88-About!$C$43*1000</f>
         <v>33771.183000000005</v>
       </c>
       <c r="F8">
-        <f>Calculations!H88-About!$C$36*1000</f>
+        <f>Calculations!H88-About!$C$43*1000</f>
         <v>35511.208000000006</v>
       </c>
       <c r="G8">
-        <f>Calculations!I88-About!$C$36*1000</f>
+        <f>Calculations!I88-About!$C$43*1000</f>
         <v>36631.794000000002</v>
       </c>
       <c r="H8">
-        <f>Calculations!J88-About!$C$36*1000</f>
+        <f>Calculations!J88-About!$C$43*1000</f>
         <v>37899.681000000004</v>
       </c>
       <c r="I8">
-        <f>Calculations!K88-About!$C$36*1000</f>
+        <f>Calculations!K88-About!$C$43*1000</f>
         <v>38829.173999999999</v>
       </c>
       <c r="J8">
-        <f>Calculations!L88-About!$C$36*1000</f>
+        <f>Calculations!L88-About!$C$43*1000</f>
         <v>39576.554000000004</v>
       </c>
       <c r="K8">
-        <f>Calculations!M88-About!$C$36*1000</f>
+        <f>Calculations!M88-About!$C$43*1000</f>
         <v>40414.337000000007</v>
       </c>
       <c r="L8">
-        <f>Calculations!N88-About!$C$36*1000</f>
+        <f>Calculations!N88-About!$C$43*1000</f>
         <v>41719.628000000004</v>
       </c>
       <c r="M8">
-        <f>Calculations!O88-About!$C$36*1000</f>
+        <f>Calculations!O88-About!$C$43*1000</f>
         <v>42791.535000000003</v>
       </c>
       <c r="N8">
-        <f>Calculations!P88-About!$C$36*1000</f>
+        <f>Calculations!P88-About!$C$43*1000</f>
         <v>43690.09</v>
       </c>
       <c r="O8">
-        <f>Calculations!Q88-About!$C$36*1000</f>
+        <f>Calculations!Q88-About!$C$43*1000</f>
         <v>45293.167000000001</v>
       </c>
       <c r="P8">
-        <f>Calculations!R88-About!$C$36*1000</f>
+        <f>Calculations!R88-About!$C$43*1000</f>
         <v>46843.823000000004</v>
       </c>
       <c r="Q8">
-        <f>Calculations!S88-About!$C$36*1000</f>
+        <f>Calculations!S88-About!$C$43*1000</f>
         <v>48761.62</v>
       </c>
       <c r="R8">
-        <f>Calculations!T88-About!$C$36*1000</f>
+        <f>Calculations!T88-About!$C$43*1000</f>
         <v>50386.563000000002</v>
       </c>
       <c r="S8">
-        <f>Calculations!U88-About!$C$36*1000</f>
+        <f>Calculations!U88-About!$C$43*1000</f>
         <v>51249.068999999996</v>
       </c>
       <c r="T8">
-        <f>Calculations!V88-About!$C$36*1000</f>
+        <f>Calculations!V88-About!$C$43*1000</f>
         <v>52600.880000000005</v>
       </c>
       <c r="U8">
-        <f>Calculations!W88-About!$C$36*1000</f>
+        <f>Calculations!W88-About!$C$43*1000</f>
         <v>53315.83</v>
       </c>
       <c r="V8">
-        <f>Calculations!X88-About!$C$36*1000</f>
+        <f>Calculations!X88-About!$C$43*1000</f>
         <v>54131.939000000006</v>
       </c>
       <c r="W8">
-        <f>Calculations!Y88-About!$C$36*1000</f>
+        <f>Calculations!Y88-About!$C$43*1000</f>
         <v>54786.152000000002</v>
       </c>
       <c r="X8">
-        <f>Calculations!Z88-About!$C$36*1000</f>
+        <f>Calculations!Z88-About!$C$43*1000</f>
         <v>55810.433000000005</v>
       </c>
       <c r="Y8">
-        <f>Calculations!AA88-About!$C$36*1000</f>
+        <f>Calculations!AA88-About!$C$43*1000</f>
         <v>57088.451999999997</v>
       </c>
       <c r="Z8">
-        <f>Calculations!AB88-About!$C$36*1000</f>
+        <f>Calculations!AB88-About!$C$43*1000</f>
         <v>58391.651000000005</v>
       </c>
       <c r="AA8">
-        <f>Calculations!AC88-About!$C$36*1000</f>
+        <f>Calculations!AC88-About!$C$43*1000</f>
         <v>59345.417000000009</v>
       </c>
       <c r="AB8">
-        <f>Calculations!AD88-About!$C$36*1000</f>
+        <f>Calculations!AD88-About!$C$43*1000</f>
         <v>60616.367999999995</v>
       </c>
     </row>
@@ -30811,4239 +31589,4234 @@
   <dimension ref="A1:U67"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.5703125" style="67" bestFit="1" customWidth="1"/>
-    <col min="2" max="21" width="12" style="67" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="9.140625" style="67"/>
+    <col min="1" max="1" width="20.5703125" style="57" bestFit="1" customWidth="1"/>
+    <col min="2" max="21" width="12" style="57" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="9.140625" style="57"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:21" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="78" t="s">
+      <c r="A1" s="67" t="s">
         <v>959</v>
       </c>
-      <c r="B1" s="78"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
-      <c r="F1" s="78"/>
-      <c r="G1" s="78"/>
-      <c r="H1" s="78"/>
-      <c r="I1" s="78"/>
-      <c r="J1" s="78"/>
-      <c r="K1" s="78"/>
-      <c r="L1" s="78"/>
-      <c r="M1" s="78"/>
-      <c r="N1" s="78"/>
-      <c r="O1" s="78"/>
-      <c r="P1" s="78"/>
-      <c r="Q1" s="78"/>
-      <c r="R1" s="78"/>
-      <c r="S1" s="78"/>
-      <c r="T1" s="78"/>
-      <c r="U1" s="78"/>
+      <c r="B1" s="67"/>
+      <c r="C1" s="67"/>
+      <c r="D1" s="67"/>
+      <c r="E1" s="67"/>
+      <c r="F1" s="67"/>
+      <c r="G1" s="67"/>
+      <c r="H1" s="67"/>
+      <c r="I1" s="67"/>
+      <c r="J1" s="67"/>
+      <c r="K1" s="67"/>
+      <c r="L1" s="67"/>
+      <c r="M1" s="67"/>
+      <c r="N1" s="67"/>
+      <c r="O1" s="67"/>
+      <c r="P1" s="67"/>
+      <c r="Q1" s="67"/>
+      <c r="R1" s="67"/>
+      <c r="S1" s="67"/>
+      <c r="T1" s="67"/>
+      <c r="U1" s="67"/>
     </row>
     <row r="2" spans="1:21" ht="39" x14ac:dyDescent="0.25">
-      <c r="A2" s="74" t="s">
+      <c r="A2" s="63" t="s">
         <v>958</v>
       </c>
-      <c r="B2" s="76" t="s">
+      <c r="B2" s="64" t="s">
         <v>957</v>
       </c>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
-      <c r="F2" s="77"/>
-      <c r="G2" s="77"/>
-      <c r="H2" s="77"/>
-      <c r="I2" s="77"/>
-      <c r="J2" s="77"/>
-      <c r="K2" s="77"/>
-      <c r="L2" s="77"/>
-      <c r="M2" s="77"/>
-      <c r="N2" s="77"/>
-      <c r="O2" s="75"/>
-      <c r="P2" s="76" t="s">
+      <c r="C2" s="68"/>
+      <c r="D2" s="68"/>
+      <c r="E2" s="68"/>
+      <c r="F2" s="68"/>
+      <c r="G2" s="68"/>
+      <c r="H2" s="68"/>
+      <c r="I2" s="68"/>
+      <c r="J2" s="68"/>
+      <c r="K2" s="68"/>
+      <c r="L2" s="68"/>
+      <c r="M2" s="68"/>
+      <c r="N2" s="68"/>
+      <c r="O2" s="65"/>
+      <c r="P2" s="64" t="s">
         <v>956</v>
       </c>
-      <c r="Q2" s="75"/>
-      <c r="R2" s="76" t="s">
+      <c r="Q2" s="65"/>
+      <c r="R2" s="64" t="s">
         <v>955</v>
       </c>
-      <c r="S2" s="77"/>
-      <c r="T2" s="77"/>
-      <c r="U2" s="75"/>
+      <c r="S2" s="68"/>
+      <c r="T2" s="68"/>
+      <c r="U2" s="65"/>
     </row>
     <row r="3" spans="1:21" ht="39" x14ac:dyDescent="0.25">
-      <c r="A3" s="74" t="s">
+      <c r="A3" s="63" t="s">
         <v>954</v>
       </c>
-      <c r="B3" s="76" t="s">
+      <c r="B3" s="64" t="s">
         <v>86</v>
       </c>
-      <c r="C3" s="75"/>
-      <c r="D3" s="76" t="s">
+      <c r="C3" s="65"/>
+      <c r="D3" s="64" t="s">
         <v>953</v>
       </c>
-      <c r="E3" s="75"/>
-      <c r="F3" s="76" t="s">
+      <c r="E3" s="65"/>
+      <c r="F3" s="64" t="s">
         <v>44</v>
       </c>
-      <c r="G3" s="75"/>
-      <c r="H3" s="76" t="s">
+      <c r="G3" s="65"/>
+      <c r="H3" s="64" t="s">
         <v>952</v>
       </c>
-      <c r="I3" s="75"/>
-      <c r="J3" s="76" t="s">
+      <c r="I3" s="65"/>
+      <c r="J3" s="64" t="s">
         <v>951</v>
       </c>
-      <c r="K3" s="75"/>
-      <c r="L3" s="76" t="s">
+      <c r="K3" s="65"/>
+      <c r="L3" s="64" t="s">
         <v>950</v>
       </c>
-      <c r="M3" s="75"/>
-      <c r="N3" s="76" t="s">
+      <c r="M3" s="65"/>
+      <c r="N3" s="64" t="s">
         <v>949</v>
       </c>
-      <c r="O3" s="75"/>
-      <c r="P3" s="76" t="s">
+      <c r="O3" s="65"/>
+      <c r="P3" s="64" t="s">
         <v>948</v>
       </c>
-      <c r="Q3" s="75"/>
-      <c r="R3" s="76" t="s">
+      <c r="Q3" s="65"/>
+      <c r="R3" s="64" t="s">
         <v>947</v>
       </c>
-      <c r="S3" s="75"/>
-      <c r="T3" s="76" t="s">
+      <c r="S3" s="65"/>
+      <c r="T3" s="64" t="s">
         <v>946</v>
       </c>
-      <c r="U3" s="75"/>
+      <c r="U3" s="65"/>
     </row>
     <row r="4" spans="1:21" ht="26.25" x14ac:dyDescent="0.25">
-      <c r="A4" s="74" t="s">
+      <c r="A4" s="63" t="s">
         <v>945</v>
       </c>
-      <c r="B4" s="73" t="s">
+      <c r="B4" s="62" t="s">
         <v>944</v>
       </c>
-      <c r="C4" s="73" t="s">
+      <c r="C4" s="62" t="s">
         <v>943</v>
       </c>
-      <c r="D4" s="73" t="s">
+      <c r="D4" s="62" t="s">
         <v>944</v>
       </c>
-      <c r="E4" s="73" t="s">
+      <c r="E4" s="62" t="s">
         <v>943</v>
       </c>
-      <c r="F4" s="73" t="s">
+      <c r="F4" s="62" t="s">
         <v>944</v>
       </c>
-      <c r="G4" s="73" t="s">
+      <c r="G4" s="62" t="s">
         <v>943</v>
       </c>
-      <c r="H4" s="73" t="s">
+      <c r="H4" s="62" t="s">
         <v>944</v>
       </c>
-      <c r="I4" s="73" t="s">
+      <c r="I4" s="62" t="s">
         <v>943</v>
       </c>
-      <c r="J4" s="73" t="s">
+      <c r="J4" s="62" t="s">
         <v>944</v>
       </c>
-      <c r="K4" s="73" t="s">
+      <c r="K4" s="62" t="s">
         <v>943</v>
       </c>
-      <c r="L4" s="73" t="s">
+      <c r="L4" s="62" t="s">
         <v>944</v>
       </c>
-      <c r="M4" s="73" t="s">
+      <c r="M4" s="62" t="s">
         <v>943</v>
       </c>
-      <c r="N4" s="73" t="s">
+      <c r="N4" s="62" t="s">
         <v>944</v>
       </c>
-      <c r="O4" s="73" t="s">
+      <c r="O4" s="62" t="s">
         <v>943</v>
       </c>
-      <c r="P4" s="73" t="s">
+      <c r="P4" s="62" t="s">
         <v>944</v>
       </c>
-      <c r="Q4" s="73" t="s">
+      <c r="Q4" s="62" t="s">
         <v>943</v>
       </c>
-      <c r="R4" s="73" t="s">
+      <c r="R4" s="62" t="s">
         <v>944</v>
       </c>
-      <c r="S4" s="73" t="s">
+      <c r="S4" s="62" t="s">
         <v>943</v>
       </c>
-      <c r="T4" s="73" t="s">
+      <c r="T4" s="62" t="s">
         <v>944</v>
       </c>
-      <c r="U4" s="73" t="s">
+      <c r="U4" s="62" t="s">
         <v>943</v>
       </c>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A5" s="70" t="s">
+      <c r="A5" s="59" t="s">
         <v>382</v>
       </c>
-      <c r="B5" s="69">
+      <c r="B5" s="58">
         <v>1760.5</v>
       </c>
-      <c r="C5" s="69">
+      <c r="C5" s="58">
         <v>1575.7</v>
       </c>
-      <c r="D5" s="69">
+      <c r="D5" s="58">
         <v>3439.2</v>
       </c>
-      <c r="E5" s="69">
+      <c r="E5" s="58">
         <v>3158.1</v>
       </c>
-      <c r="F5" s="69">
-        <v>0</v>
-      </c>
-      <c r="G5" s="69">
-        <v>0</v>
-      </c>
-      <c r="H5" s="69">
+      <c r="F5" s="58">
+        <v>0</v>
+      </c>
+      <c r="G5" s="58">
+        <v>0</v>
+      </c>
+      <c r="H5" s="58">
         <v>1951.7</v>
       </c>
-      <c r="I5" s="69">
+      <c r="I5" s="58">
         <v>1951.7</v>
       </c>
-      <c r="J5" s="69">
+      <c r="J5" s="58">
         <v>1247.4000000000001</v>
       </c>
-      <c r="K5" s="69">
+      <c r="K5" s="58">
         <v>1247.4000000000001</v>
       </c>
-      <c r="L5" s="69">
-        <v>0</v>
-      </c>
-      <c r="M5" s="69">
-        <v>0</v>
-      </c>
-      <c r="N5" s="69">
+      <c r="L5" s="58">
+        <v>0</v>
+      </c>
+      <c r="M5" s="58">
+        <v>0</v>
+      </c>
+      <c r="N5" s="58">
         <v>8398.7999999999993</v>
       </c>
-      <c r="O5" s="69">
+      <c r="O5" s="58">
         <v>7932.9</v>
       </c>
-      <c r="P5" s="69">
+      <c r="P5" s="58">
         <v>6175.5</v>
       </c>
-      <c r="Q5" s="69">
+      <c r="Q5" s="58">
         <v>5628.8</v>
       </c>
-      <c r="R5" s="69">
+      <c r="R5" s="58">
         <v>9614.7000000000007</v>
       </c>
-      <c r="S5" s="69">
+      <c r="S5" s="58">
         <v>8786.9</v>
       </c>
-      <c r="T5" s="69">
+      <c r="T5" s="58">
         <v>9614.7000000000007</v>
       </c>
-      <c r="U5" s="69">
+      <c r="U5" s="58">
         <v>8786.9</v>
       </c>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A6" s="72" t="s">
+      <c r="A6" s="61" t="s">
         <v>942</v>
       </c>
-      <c r="B6" s="71">
+      <c r="B6" s="60">
         <v>5</v>
       </c>
-      <c r="C6" s="71">
+      <c r="C6" s="60">
         <v>5</v>
       </c>
-      <c r="D6" s="71">
+      <c r="D6" s="60">
         <v>491</v>
       </c>
-      <c r="E6" s="71">
+      <c r="E6" s="60">
         <v>322.3</v>
       </c>
-      <c r="F6" s="71">
-        <v>0</v>
-      </c>
-      <c r="G6" s="71">
-        <v>0</v>
-      </c>
-      <c r="H6" s="71">
+      <c r="F6" s="60">
+        <v>0</v>
+      </c>
+      <c r="G6" s="60">
+        <v>0</v>
+      </c>
+      <c r="H6" s="60">
         <v>119.2</v>
       </c>
-      <c r="I6" s="71">
+      <c r="I6" s="60">
         <v>119.2</v>
       </c>
-      <c r="J6" s="71">
+      <c r="J6" s="60">
         <v>139.6</v>
       </c>
-      <c r="K6" s="71">
+      <c r="K6" s="60">
         <v>139.6</v>
       </c>
-      <c r="L6" s="71">
-        <v>0</v>
-      </c>
-      <c r="M6" s="71">
-        <v>0</v>
-      </c>
-      <c r="N6" s="71">
+      <c r="L6" s="60">
+        <v>0</v>
+      </c>
+      <c r="M6" s="60">
+        <v>0</v>
+      </c>
+      <c r="N6" s="60">
         <v>754.8</v>
       </c>
-      <c r="O6" s="71">
+      <c r="O6" s="60">
         <v>586.1</v>
       </c>
-      <c r="P6" s="71">
+      <c r="P6" s="60">
         <v>1385.9</v>
       </c>
-      <c r="Q6" s="71">
+      <c r="Q6" s="60">
         <v>1132.3</v>
       </c>
-      <c r="R6" s="71">
+      <c r="R6" s="60">
         <v>1876.9</v>
       </c>
-      <c r="S6" s="71">
+      <c r="S6" s="60">
         <v>1454.6</v>
       </c>
-      <c r="T6" s="71">
+      <c r="T6" s="60">
         <v>1876.9</v>
       </c>
-      <c r="U6" s="71">
+      <c r="U6" s="60">
         <v>1454.6</v>
       </c>
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A7" s="72" t="s">
+      <c r="A7" s="61" t="s">
         <v>941</v>
       </c>
-      <c r="B7" s="71">
+      <c r="B7" s="60">
         <v>1214.3</v>
       </c>
-      <c r="C7" s="71">
+      <c r="C7" s="60">
         <v>1029.5</v>
       </c>
-      <c r="D7" s="71">
+      <c r="D7" s="60">
         <v>871.1</v>
       </c>
-      <c r="E7" s="71">
+      <c r="E7" s="60">
         <v>829.2</v>
       </c>
-      <c r="F7" s="71">
-        <v>0</v>
-      </c>
-      <c r="G7" s="71">
-        <v>0</v>
-      </c>
-      <c r="H7" s="71">
+      <c r="F7" s="60">
+        <v>0</v>
+      </c>
+      <c r="G7" s="60">
+        <v>0</v>
+      </c>
+      <c r="H7" s="60">
         <v>725.8</v>
       </c>
-      <c r="I7" s="71">
+      <c r="I7" s="60">
         <v>725.8</v>
       </c>
-      <c r="J7" s="71">
+      <c r="J7" s="60">
         <v>488.6</v>
       </c>
-      <c r="K7" s="71">
+      <c r="K7" s="60">
         <v>488.6</v>
       </c>
-      <c r="L7" s="71">
-        <v>0</v>
-      </c>
-      <c r="M7" s="71">
-        <v>0</v>
-      </c>
-      <c r="N7" s="71">
+      <c r="L7" s="60">
+        <v>0</v>
+      </c>
+      <c r="M7" s="60">
+        <v>0</v>
+      </c>
+      <c r="N7" s="60">
         <v>3299.8</v>
       </c>
-      <c r="O7" s="71">
+      <c r="O7" s="60">
         <v>3073.1</v>
       </c>
-      <c r="P7" s="71">
+      <c r="P7" s="60">
         <v>965.2</v>
       </c>
-      <c r="Q7" s="71">
+      <c r="Q7" s="60">
         <v>849.4</v>
       </c>
-      <c r="R7" s="71">
+      <c r="R7" s="60">
         <v>1836.3</v>
       </c>
-      <c r="S7" s="71">
+      <c r="S7" s="60">
         <v>1678.6</v>
       </c>
-      <c r="T7" s="71">
+      <c r="T7" s="60">
         <v>1836.3</v>
       </c>
-      <c r="U7" s="71">
+      <c r="U7" s="60">
         <v>1678.6</v>
       </c>
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A8" s="72" t="s">
+      <c r="A8" s="61" t="s">
         <v>940</v>
       </c>
-      <c r="B8" s="71">
+      <c r="B8" s="60">
         <v>101.8</v>
       </c>
-      <c r="C8" s="71">
+      <c r="C8" s="60">
         <v>101.8</v>
       </c>
-      <c r="D8" s="71">
+      <c r="D8" s="60">
         <v>1479.7</v>
       </c>
-      <c r="E8" s="71">
+      <c r="E8" s="60">
         <v>1430.5</v>
       </c>
-      <c r="F8" s="71">
-        <v>0</v>
-      </c>
-      <c r="G8" s="71">
-        <v>0</v>
-      </c>
-      <c r="H8" s="71">
+      <c r="F8" s="60">
+        <v>0</v>
+      </c>
+      <c r="G8" s="60">
+        <v>0</v>
+      </c>
+      <c r="H8" s="60">
         <v>267.2</v>
       </c>
-      <c r="I8" s="71">
+      <c r="I8" s="60">
         <v>267.2</v>
       </c>
-      <c r="J8" s="71">
+      <c r="J8" s="60">
         <v>273.10000000000002</v>
       </c>
-      <c r="K8" s="71">
+      <c r="K8" s="60">
         <v>273.10000000000002</v>
       </c>
-      <c r="L8" s="71">
-        <v>0</v>
-      </c>
-      <c r="M8" s="71">
-        <v>0</v>
-      </c>
-      <c r="N8" s="71">
+      <c r="L8" s="60">
+        <v>0</v>
+      </c>
+      <c r="M8" s="60">
+        <v>0</v>
+      </c>
+      <c r="N8" s="60">
         <v>2121.8000000000002</v>
       </c>
-      <c r="O8" s="71">
+      <c r="O8" s="60">
         <v>2072.6</v>
       </c>
-      <c r="P8" s="71">
+      <c r="P8" s="60">
         <v>3113.9</v>
       </c>
-      <c r="Q8" s="71">
+      <c r="Q8" s="60">
         <v>2966.5</v>
       </c>
-      <c r="R8" s="71">
+      <c r="R8" s="60">
         <v>4593.6000000000004</v>
       </c>
-      <c r="S8" s="71">
+      <c r="S8" s="60">
         <v>4397</v>
       </c>
-      <c r="T8" s="71">
+      <c r="T8" s="60">
         <v>4593.6000000000004</v>
       </c>
-      <c r="U8" s="71">
+      <c r="U8" s="60">
         <v>4397</v>
       </c>
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A9" s="72" t="s">
+      <c r="A9" s="61" t="s">
         <v>939</v>
       </c>
-      <c r="B9" s="71">
+      <c r="B9" s="60">
         <v>211.9</v>
       </c>
-      <c r="C9" s="71">
+      <c r="C9" s="60">
         <v>211.9</v>
       </c>
-      <c r="D9" s="71">
+      <c r="D9" s="60">
         <v>2.4</v>
       </c>
-      <c r="E9" s="71">
+      <c r="E9" s="60">
         <v>2.4</v>
       </c>
-      <c r="F9" s="71">
-        <v>0</v>
-      </c>
-      <c r="G9" s="71">
-        <v>0</v>
-      </c>
-      <c r="H9" s="71">
+      <c r="F9" s="60">
+        <v>0</v>
+      </c>
+      <c r="G9" s="60">
+        <v>0</v>
+      </c>
+      <c r="H9" s="60">
         <v>505.8</v>
       </c>
-      <c r="I9" s="71">
+      <c r="I9" s="60">
         <v>505.8</v>
       </c>
-      <c r="J9" s="71">
+      <c r="J9" s="60">
         <v>225.8</v>
       </c>
-      <c r="K9" s="71">
+      <c r="K9" s="60">
         <v>225.8</v>
       </c>
-      <c r="L9" s="71">
-        <v>0</v>
-      </c>
-      <c r="M9" s="71">
-        <v>0</v>
-      </c>
-      <c r="N9" s="71">
+      <c r="L9" s="60">
+        <v>0</v>
+      </c>
+      <c r="M9" s="60">
+        <v>0</v>
+      </c>
+      <c r="N9" s="60">
         <v>945.9</v>
       </c>
-      <c r="O9" s="71">
+      <c r="O9" s="60">
         <v>945.9</v>
       </c>
-      <c r="P9" s="71">
+      <c r="P9" s="60">
         <v>313.60000000000002</v>
       </c>
-      <c r="Q9" s="71">
+      <c r="Q9" s="60">
         <v>270.39999999999998</v>
       </c>
-      <c r="R9" s="71">
+      <c r="R9" s="60">
         <v>316</v>
       </c>
-      <c r="S9" s="71">
+      <c r="S9" s="60">
         <v>272.8</v>
       </c>
-      <c r="T9" s="71">
+      <c r="T9" s="60">
         <v>316</v>
       </c>
-      <c r="U9" s="71">
+      <c r="U9" s="60">
         <v>272.8</v>
       </c>
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A10" s="72" t="s">
+      <c r="A10" s="61" t="s">
         <v>938</v>
       </c>
-      <c r="B10" s="71">
+      <c r="B10" s="60">
         <v>77.3</v>
       </c>
-      <c r="C10" s="71">
+      <c r="C10" s="60">
         <v>77.3</v>
       </c>
-      <c r="D10" s="71">
+      <c r="D10" s="60">
         <v>439.3</v>
       </c>
-      <c r="E10" s="71">
+      <c r="E10" s="60">
         <v>418.5</v>
       </c>
-      <c r="F10" s="71">
-        <v>0</v>
-      </c>
-      <c r="G10" s="71">
-        <v>0</v>
-      </c>
-      <c r="H10" s="71">
+      <c r="F10" s="60">
+        <v>0</v>
+      </c>
+      <c r="G10" s="60">
+        <v>0</v>
+      </c>
+      <c r="H10" s="60">
         <v>2.7</v>
       </c>
-      <c r="I10" s="71">
+      <c r="I10" s="60">
         <v>2.7</v>
       </c>
-      <c r="J10" s="71">
+      <c r="J10" s="60">
         <v>40.1</v>
       </c>
-      <c r="K10" s="71">
+      <c r="K10" s="60">
         <v>40.1</v>
       </c>
-      <c r="L10" s="71">
-        <v>0</v>
-      </c>
-      <c r="M10" s="71">
-        <v>0</v>
-      </c>
-      <c r="N10" s="71">
+      <c r="L10" s="60">
+        <v>0</v>
+      </c>
+      <c r="M10" s="60">
+        <v>0</v>
+      </c>
+      <c r="N10" s="60">
         <v>559.4</v>
       </c>
-      <c r="O10" s="71">
+      <c r="O10" s="60">
         <v>538.6</v>
       </c>
-      <c r="P10" s="71">
+      <c r="P10" s="60">
         <v>207.9</v>
       </c>
-      <c r="Q10" s="71">
+      <c r="Q10" s="60">
         <v>224.4</v>
       </c>
-      <c r="R10" s="71">
+      <c r="R10" s="60">
         <v>647.20000000000005</v>
       </c>
-      <c r="S10" s="71">
+      <c r="S10" s="60">
         <v>642.9</v>
       </c>
-      <c r="T10" s="71">
+      <c r="T10" s="60">
         <v>647.20000000000005</v>
       </c>
-      <c r="U10" s="71">
+      <c r="U10" s="60">
         <v>642.9</v>
       </c>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A11" s="72" t="s">
+      <c r="A11" s="61" t="s">
         <v>937</v>
       </c>
-      <c r="B11" s="71">
+      <c r="B11" s="60">
         <v>150.19999999999999</v>
       </c>
-      <c r="C11" s="71">
+      <c r="C11" s="60">
         <v>150.19999999999999</v>
       </c>
-      <c r="D11" s="71">
+      <c r="D11" s="60">
         <v>155.69999999999999</v>
       </c>
-      <c r="E11" s="71">
+      <c r="E11" s="60">
         <v>155.19999999999999</v>
       </c>
-      <c r="F11" s="71">
-        <v>0</v>
-      </c>
-      <c r="G11" s="71">
-        <v>0</v>
-      </c>
-      <c r="H11" s="71">
+      <c r="F11" s="60">
+        <v>0</v>
+      </c>
+      <c r="G11" s="60">
+        <v>0</v>
+      </c>
+      <c r="H11" s="60">
         <v>331</v>
       </c>
-      <c r="I11" s="71">
+      <c r="I11" s="60">
         <v>331</v>
       </c>
-      <c r="J11" s="71">
+      <c r="J11" s="60">
         <v>80.2</v>
       </c>
-      <c r="K11" s="71">
+      <c r="K11" s="60">
         <v>80.2</v>
       </c>
-      <c r="L11" s="71">
-        <v>0</v>
-      </c>
-      <c r="M11" s="71">
-        <v>0</v>
-      </c>
-      <c r="N11" s="71">
+      <c r="L11" s="60">
+        <v>0</v>
+      </c>
+      <c r="M11" s="60">
+        <v>0</v>
+      </c>
+      <c r="N11" s="60">
         <v>717.1</v>
       </c>
-      <c r="O11" s="71">
+      <c r="O11" s="60">
         <v>716.6</v>
       </c>
-      <c r="P11" s="71">
+      <c r="P11" s="60">
         <v>189</v>
       </c>
-      <c r="Q11" s="71">
+      <c r="Q11" s="60">
         <v>185.7</v>
       </c>
-      <c r="R11" s="71">
+      <c r="R11" s="60">
         <v>344.7</v>
       </c>
-      <c r="S11" s="71">
+      <c r="S11" s="60">
         <v>340.9</v>
       </c>
-      <c r="T11" s="71">
+      <c r="T11" s="60">
         <v>344.7</v>
       </c>
-      <c r="U11" s="71">
+      <c r="U11" s="60">
         <v>340.9</v>
       </c>
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A12" s="70" t="s">
+      <c r="A12" s="59" t="s">
         <v>383</v>
       </c>
-      <c r="B12" s="69">
+      <c r="B12" s="58">
         <v>4429.8999999999996</v>
       </c>
-      <c r="C12" s="69">
+      <c r="C12" s="58">
         <v>4429.8999999999996</v>
       </c>
-      <c r="D12" s="69">
+      <c r="D12" s="58">
         <v>5419.6</v>
       </c>
-      <c r="E12" s="69">
+      <c r="E12" s="58">
         <v>4722.2</v>
       </c>
-      <c r="F12" s="69">
-        <v>0</v>
-      </c>
-      <c r="G12" s="69">
-        <v>0</v>
-      </c>
-      <c r="H12" s="69">
+      <c r="F12" s="58">
+        <v>0</v>
+      </c>
+      <c r="G12" s="58">
+        <v>0</v>
+      </c>
+      <c r="H12" s="58">
         <v>5505.2</v>
       </c>
-      <c r="I12" s="69">
+      <c r="I12" s="58">
         <v>5505.2</v>
       </c>
-      <c r="J12" s="69">
+      <c r="J12" s="58">
         <v>1016</v>
       </c>
-      <c r="K12" s="69">
+      <c r="K12" s="58">
         <v>1020.8</v>
       </c>
-      <c r="L12" s="69">
-        <v>0</v>
-      </c>
-      <c r="M12" s="69">
-        <v>0</v>
-      </c>
-      <c r="N12" s="69">
+      <c r="L12" s="58">
+        <v>0</v>
+      </c>
+      <c r="M12" s="58">
+        <v>0</v>
+      </c>
+      <c r="N12" s="58">
         <v>16370.7</v>
       </c>
-      <c r="O12" s="69">
+      <c r="O12" s="58">
         <v>15678.1</v>
       </c>
-      <c r="P12" s="69">
+      <c r="P12" s="58">
         <v>8116.2</v>
       </c>
-      <c r="Q12" s="69">
+      <c r="Q12" s="58">
         <v>6867.6</v>
       </c>
-      <c r="R12" s="69">
+      <c r="R12" s="58">
         <v>13535.8</v>
       </c>
-      <c r="S12" s="69">
+      <c r="S12" s="58">
         <v>11589.8</v>
       </c>
-      <c r="T12" s="69">
+      <c r="T12" s="58">
         <v>13535.8</v>
       </c>
-      <c r="U12" s="69">
+      <c r="U12" s="58">
         <v>11589.8</v>
       </c>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A13" s="72" t="s">
+      <c r="A13" s="61" t="s">
         <v>936</v>
       </c>
-      <c r="B13" s="71">
+      <c r="B13" s="60">
         <v>7.6</v>
       </c>
-      <c r="C13" s="71">
+      <c r="C13" s="60">
         <v>7.6</v>
       </c>
-      <c r="D13" s="71">
+      <c r="D13" s="60">
         <v>1240.7</v>
       </c>
-      <c r="E13" s="71">
+      <c r="E13" s="60">
         <v>1179.7</v>
       </c>
-      <c r="F13" s="71">
-        <v>0</v>
-      </c>
-      <c r="G13" s="71">
-        <v>0</v>
-      </c>
-      <c r="H13" s="71">
+      <c r="F13" s="60">
+        <v>0</v>
+      </c>
+      <c r="G13" s="60">
+        <v>0</v>
+      </c>
+      <c r="H13" s="60">
         <v>12.3</v>
       </c>
-      <c r="I13" s="71">
+      <c r="I13" s="60">
         <v>12.3</v>
       </c>
-      <c r="J13" s="71">
+      <c r="J13" s="60">
         <v>188.7</v>
       </c>
-      <c r="K13" s="71">
+      <c r="K13" s="60">
         <v>188.7</v>
       </c>
-      <c r="L13" s="71">
-        <v>0</v>
-      </c>
-      <c r="M13" s="71">
-        <v>0</v>
-      </c>
-      <c r="N13" s="71">
+      <c r="L13" s="60">
+        <v>0</v>
+      </c>
+      <c r="M13" s="60">
+        <v>0</v>
+      </c>
+      <c r="N13" s="60">
         <v>1449.3</v>
       </c>
-      <c r="O13" s="71">
+      <c r="O13" s="60">
         <v>1388.3</v>
       </c>
-      <c r="P13" s="71">
+      <c r="P13" s="60">
         <v>2975</v>
       </c>
-      <c r="Q13" s="71">
+      <c r="Q13" s="60">
         <v>2489.6</v>
       </c>
-      <c r="R13" s="71">
+      <c r="R13" s="60">
         <v>4215.7</v>
       </c>
-      <c r="S13" s="71">
+      <c r="S13" s="60">
         <v>3669.3</v>
       </c>
-      <c r="T13" s="71">
+      <c r="T13" s="60">
         <v>4215.7</v>
       </c>
-      <c r="U13" s="71">
+      <c r="U13" s="60">
         <v>3669.3</v>
       </c>
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A14" s="72" t="s">
+      <c r="A14" s="61" t="s">
         <v>935</v>
       </c>
-      <c r="B14" s="71">
+      <c r="B14" s="60">
         <v>2869.7</v>
       </c>
-      <c r="C14" s="71">
+      <c r="C14" s="60">
         <v>2869.7</v>
       </c>
-      <c r="D14" s="71">
+      <c r="D14" s="60">
         <v>3052.3</v>
       </c>
-      <c r="E14" s="71">
+      <c r="E14" s="60">
         <v>2668.6</v>
       </c>
-      <c r="F14" s="71">
-        <v>0</v>
-      </c>
-      <c r="G14" s="71">
-        <v>0</v>
-      </c>
-      <c r="H14" s="71">
+      <c r="F14" s="60">
+        <v>0</v>
+      </c>
+      <c r="G14" s="60">
+        <v>0</v>
+      </c>
+      <c r="H14" s="60">
         <v>4563.3999999999996</v>
       </c>
-      <c r="I14" s="71">
+      <c r="I14" s="60">
         <v>4563.3999999999996</v>
       </c>
-      <c r="J14" s="71">
+      <c r="J14" s="60">
         <v>395.5</v>
       </c>
-      <c r="K14" s="71">
+      <c r="K14" s="60">
         <v>400.3</v>
       </c>
-      <c r="L14" s="71">
-        <v>0</v>
-      </c>
-      <c r="M14" s="71">
-        <v>0</v>
-      </c>
-      <c r="N14" s="71">
+      <c r="L14" s="60">
+        <v>0</v>
+      </c>
+      <c r="M14" s="60">
+        <v>0</v>
+      </c>
+      <c r="N14" s="60">
         <v>10880.9</v>
       </c>
-      <c r="O14" s="71">
+      <c r="O14" s="60">
         <v>10502</v>
       </c>
-      <c r="P14" s="71">
+      <c r="P14" s="60">
         <v>3933.7</v>
       </c>
-      <c r="Q14" s="71">
+      <c r="Q14" s="60">
         <v>3394</v>
       </c>
-      <c r="R14" s="71">
+      <c r="R14" s="60">
         <v>6986</v>
       </c>
-      <c r="S14" s="71">
+      <c r="S14" s="60">
         <v>6062.6</v>
       </c>
-      <c r="T14" s="71">
+      <c r="T14" s="60">
         <v>6986</v>
       </c>
-      <c r="U14" s="71">
+      <c r="U14" s="60">
         <v>6062.6</v>
       </c>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A15" s="72" t="s">
+      <c r="A15" s="61" t="s">
         <v>934</v>
       </c>
-      <c r="B15" s="71">
+      <c r="B15" s="60">
         <v>1552.6</v>
       </c>
-      <c r="C15" s="71">
+      <c r="C15" s="60">
         <v>1552.6</v>
       </c>
-      <c r="D15" s="71">
+      <c r="D15" s="60">
         <v>1126.5999999999999</v>
       </c>
-      <c r="E15" s="71">
+      <c r="E15" s="60">
         <v>873.9</v>
       </c>
-      <c r="F15" s="71">
-        <v>0</v>
-      </c>
-      <c r="G15" s="71">
-        <v>0</v>
-      </c>
-      <c r="H15" s="71">
+      <c r="F15" s="60">
+        <v>0</v>
+      </c>
+      <c r="G15" s="60">
+        <v>0</v>
+      </c>
+      <c r="H15" s="60">
         <v>929.5</v>
       </c>
-      <c r="I15" s="71">
+      <c r="I15" s="60">
         <v>929.5</v>
       </c>
-      <c r="J15" s="71">
+      <c r="J15" s="60">
         <v>431.8</v>
       </c>
-      <c r="K15" s="71">
+      <c r="K15" s="60">
         <v>431.8</v>
       </c>
-      <c r="L15" s="71">
-        <v>0</v>
-      </c>
-      <c r="M15" s="71">
-        <v>0</v>
-      </c>
-      <c r="N15" s="71">
+      <c r="L15" s="60">
+        <v>0</v>
+      </c>
+      <c r="M15" s="60">
+        <v>0</v>
+      </c>
+      <c r="N15" s="60">
         <v>4040.5</v>
       </c>
-      <c r="O15" s="71">
+      <c r="O15" s="60">
         <v>3787.8</v>
       </c>
-      <c r="P15" s="71">
+      <c r="P15" s="60">
         <v>1207.5</v>
       </c>
-      <c r="Q15" s="71">
+      <c r="Q15" s="60">
         <v>984</v>
       </c>
-      <c r="R15" s="71">
+      <c r="R15" s="60">
         <v>2334.1</v>
       </c>
-      <c r="S15" s="71">
+      <c r="S15" s="60">
         <v>1857.9</v>
       </c>
-      <c r="T15" s="71">
+      <c r="T15" s="60">
         <v>2334.1</v>
       </c>
-      <c r="U15" s="71">
+      <c r="U15" s="60">
         <v>1857.9</v>
       </c>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A16" s="70" t="s">
+      <c r="A16" s="59" t="s">
         <v>385</v>
       </c>
-      <c r="B16" s="69">
+      <c r="B16" s="58">
         <v>17986.2</v>
       </c>
-      <c r="C16" s="69">
+      <c r="C16" s="58">
         <v>17215.099999999999</v>
       </c>
-      <c r="D16" s="69">
+      <c r="D16" s="58">
         <v>17278.900000000001</v>
       </c>
-      <c r="E16" s="69">
+      <c r="E16" s="58">
         <v>11949.2</v>
       </c>
-      <c r="F16" s="69">
-        <v>0</v>
-      </c>
-      <c r="G16" s="69">
-        <v>0</v>
-      </c>
-      <c r="H16" s="69">
+      <c r="F16" s="58">
+        <v>0</v>
+      </c>
+      <c r="G16" s="58">
+        <v>0</v>
+      </c>
+      <c r="H16" s="58">
         <v>875.3</v>
       </c>
-      <c r="I16" s="69">
+      <c r="I16" s="58">
         <v>880.5</v>
       </c>
-      <c r="J16" s="69">
+      <c r="J16" s="58">
         <v>921.9</v>
       </c>
-      <c r="K16" s="69">
+      <c r="K16" s="58">
         <v>925.9</v>
       </c>
-      <c r="L16" s="69">
-        <v>0</v>
-      </c>
-      <c r="M16" s="69">
-        <v>0</v>
-      </c>
-      <c r="N16" s="69">
+      <c r="L16" s="58">
+        <v>0</v>
+      </c>
+      <c r="M16" s="58">
+        <v>0</v>
+      </c>
+      <c r="N16" s="58">
         <v>37062.300000000003</v>
       </c>
-      <c r="O16" s="69">
+      <c r="O16" s="58">
         <v>30970.7</v>
       </c>
-      <c r="P16" s="69">
+      <c r="P16" s="58">
         <v>3163.5</v>
       </c>
-      <c r="Q16" s="69">
+      <c r="Q16" s="58">
         <v>2596.1999999999998</v>
       </c>
-      <c r="R16" s="69">
+      <c r="R16" s="58">
         <v>20442.400000000001</v>
       </c>
-      <c r="S16" s="69">
+      <c r="S16" s="58">
         <v>14545.4</v>
       </c>
-      <c r="T16" s="69">
+      <c r="T16" s="58">
         <v>20442.400000000001</v>
       </c>
-      <c r="U16" s="69">
+      <c r="U16" s="58">
         <v>14545.4</v>
       </c>
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A17" s="72" t="s">
+      <c r="A17" s="61" t="s">
         <v>933</v>
       </c>
-      <c r="B17" s="71">
+      <c r="B17" s="60">
         <v>8432.1</v>
       </c>
-      <c r="C17" s="71">
+      <c r="C17" s="60">
         <v>7873.7</v>
       </c>
-      <c r="D17" s="71">
+      <c r="D17" s="60">
         <v>3901.6</v>
       </c>
-      <c r="E17" s="71">
+      <c r="E17" s="60">
         <v>2958.7</v>
       </c>
-      <c r="F17" s="71">
-        <v>0</v>
-      </c>
-      <c r="G17" s="71">
-        <v>0</v>
-      </c>
-      <c r="H17" s="71">
+      <c r="F17" s="60">
+        <v>0</v>
+      </c>
+      <c r="G17" s="60">
+        <v>0</v>
+      </c>
+      <c r="H17" s="60">
         <v>32.9</v>
       </c>
-      <c r="I17" s="71">
+      <c r="I17" s="60">
         <v>32.9</v>
       </c>
-      <c r="J17" s="71">
+      <c r="J17" s="60">
         <v>55.2</v>
       </c>
-      <c r="K17" s="71">
+      <c r="K17" s="60">
         <v>55.2</v>
       </c>
-      <c r="L17" s="71">
-        <v>0</v>
-      </c>
-      <c r="M17" s="71">
-        <v>0</v>
-      </c>
-      <c r="N17" s="71">
+      <c r="L17" s="60">
+        <v>0</v>
+      </c>
+      <c r="M17" s="60">
+        <v>0</v>
+      </c>
+      <c r="N17" s="60">
         <v>12421.8</v>
       </c>
-      <c r="O17" s="71">
+      <c r="O17" s="60">
         <v>10920.5</v>
       </c>
-      <c r="P17" s="71">
+      <c r="P17" s="60">
         <v>1742.9</v>
       </c>
-      <c r="Q17" s="71">
+      <c r="Q17" s="60">
         <v>1372.4</v>
       </c>
-      <c r="R17" s="71">
+      <c r="R17" s="60">
         <v>5644.5</v>
       </c>
-      <c r="S17" s="71">
+      <c r="S17" s="60">
         <v>4331.1000000000004</v>
       </c>
-      <c r="T17" s="71">
+      <c r="T17" s="60">
         <v>5644.5</v>
       </c>
-      <c r="U17" s="71">
+      <c r="U17" s="60">
         <v>4331.1000000000004</v>
       </c>
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A18" s="72" t="s">
+      <c r="A18" s="61" t="s">
         <v>932</v>
       </c>
-      <c r="B18" s="71">
+      <c r="B18" s="60">
         <v>3851.8</v>
       </c>
-      <c r="C18" s="71">
+      <c r="C18" s="60">
         <v>3639.1</v>
       </c>
-      <c r="D18" s="71">
+      <c r="D18" s="60">
         <v>4514.5</v>
       </c>
-      <c r="E18" s="71">
+      <c r="E18" s="60">
         <v>2490</v>
       </c>
-      <c r="F18" s="71">
-        <v>0</v>
-      </c>
-      <c r="G18" s="71">
-        <v>0</v>
-      </c>
-      <c r="H18" s="71">
+      <c r="F18" s="60">
+        <v>0</v>
+      </c>
+      <c r="G18" s="60">
+        <v>0</v>
+      </c>
+      <c r="H18" s="60">
         <v>71.599999999999994</v>
       </c>
-      <c r="I18" s="71">
+      <c r="I18" s="60">
         <v>71.599999999999994</v>
       </c>
-      <c r="J18" s="71">
+      <c r="J18" s="60">
         <v>48.6</v>
       </c>
-      <c r="K18" s="71">
+      <c r="K18" s="60">
         <v>48.6</v>
       </c>
-      <c r="L18" s="71">
-        <v>0</v>
-      </c>
-      <c r="M18" s="71">
-        <v>0</v>
-      </c>
-      <c r="N18" s="71">
+      <c r="L18" s="60">
+        <v>0</v>
+      </c>
+      <c r="M18" s="60">
+        <v>0</v>
+      </c>
+      <c r="N18" s="60">
         <v>8486.5</v>
       </c>
-      <c r="O18" s="71">
+      <c r="O18" s="60">
         <v>6249.3</v>
       </c>
-      <c r="P18" s="71">
+      <c r="P18" s="60">
         <v>296.2</v>
       </c>
-      <c r="Q18" s="71">
+      <c r="Q18" s="60">
         <v>270.3</v>
       </c>
-      <c r="R18" s="71">
+      <c r="R18" s="60">
         <v>4810.7</v>
       </c>
-      <c r="S18" s="71">
+      <c r="S18" s="60">
         <v>2760.3</v>
       </c>
-      <c r="T18" s="71">
+      <c r="T18" s="60">
         <v>4810.7</v>
       </c>
-      <c r="U18" s="71">
+      <c r="U18" s="60">
         <v>2760.3</v>
       </c>
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A19" s="72" t="s">
+      <c r="A19" s="61" t="s">
         <v>931</v>
       </c>
-      <c r="B19" s="71">
+      <c r="B19" s="60">
         <v>3774.3</v>
       </c>
-      <c r="C19" s="71">
+      <c r="C19" s="60">
         <v>3774.3</v>
       </c>
-      <c r="D19" s="71">
+      <c r="D19" s="60">
         <v>1965.8</v>
       </c>
-      <c r="E19" s="71">
+      <c r="E19" s="60">
         <v>1158</v>
       </c>
-      <c r="F19" s="71">
-        <v>0</v>
-      </c>
-      <c r="G19" s="71">
-        <v>0</v>
-      </c>
-      <c r="H19" s="71">
+      <c r="F19" s="60">
+        <v>0</v>
+      </c>
+      <c r="G19" s="60">
+        <v>0</v>
+      </c>
+      <c r="H19" s="60">
         <v>263.5</v>
       </c>
-      <c r="I19" s="71">
+      <c r="I19" s="60">
         <v>263.5</v>
       </c>
-      <c r="J19" s="71">
+      <c r="J19" s="60">
         <v>478.3</v>
       </c>
-      <c r="K19" s="71">
+      <c r="K19" s="60">
         <v>478.3</v>
       </c>
-      <c r="L19" s="71">
-        <v>0</v>
-      </c>
-      <c r="M19" s="71">
-        <v>0</v>
-      </c>
-      <c r="N19" s="71">
+      <c r="L19" s="60">
+        <v>0</v>
+      </c>
+      <c r="M19" s="60">
+        <v>0</v>
+      </c>
+      <c r="N19" s="60">
         <v>6481.9</v>
       </c>
-      <c r="O19" s="71">
+      <c r="O19" s="60">
         <v>5674.1</v>
       </c>
-      <c r="P19" s="71">
+      <c r="P19" s="60">
         <v>323.7</v>
       </c>
-      <c r="Q19" s="71">
+      <c r="Q19" s="60">
         <v>270</v>
       </c>
-      <c r="R19" s="71">
+      <c r="R19" s="60">
         <v>2289.5</v>
       </c>
-      <c r="S19" s="71">
+      <c r="S19" s="60">
         <v>1428</v>
       </c>
-      <c r="T19" s="71">
+      <c r="T19" s="60">
         <v>2289.5</v>
       </c>
-      <c r="U19" s="71">
+      <c r="U19" s="60">
         <v>1428</v>
       </c>
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A20" s="72" t="s">
+      <c r="A20" s="61" t="s">
         <v>930</v>
       </c>
-      <c r="B20" s="71">
+      <c r="B20" s="60">
         <v>1101.8</v>
       </c>
-      <c r="C20" s="71">
+      <c r="C20" s="60">
         <v>1101.8</v>
       </c>
-      <c r="D20" s="71">
+      <c r="D20" s="60">
         <v>4359.6000000000004</v>
       </c>
-      <c r="E20" s="71">
+      <c r="E20" s="60">
         <v>3236.5</v>
       </c>
-      <c r="F20" s="71">
-        <v>0</v>
-      </c>
-      <c r="G20" s="71">
-        <v>0</v>
-      </c>
-      <c r="H20" s="71">
+      <c r="F20" s="60">
+        <v>0</v>
+      </c>
+      <c r="G20" s="60">
+        <v>0</v>
+      </c>
+      <c r="H20" s="60">
         <v>96.7</v>
       </c>
-      <c r="I20" s="71">
+      <c r="I20" s="60">
         <v>101.9</v>
       </c>
-      <c r="J20" s="71">
+      <c r="J20" s="60">
         <v>60.3</v>
       </c>
-      <c r="K20" s="71">
+      <c r="K20" s="60">
         <v>64.3</v>
       </c>
-      <c r="L20" s="71">
-        <v>0</v>
-      </c>
-      <c r="M20" s="71">
-        <v>0</v>
-      </c>
-      <c r="N20" s="71">
+      <c r="L20" s="60">
+        <v>0</v>
+      </c>
+      <c r="M20" s="60">
+        <v>0</v>
+      </c>
+      <c r="N20" s="60">
         <v>5618.4</v>
       </c>
-      <c r="O20" s="71">
+      <c r="O20" s="60">
         <v>4504.5</v>
       </c>
-      <c r="P20" s="71">
+      <c r="P20" s="60">
         <v>494.9</v>
       </c>
-      <c r="Q20" s="71">
+      <c r="Q20" s="60">
         <v>411.9</v>
       </c>
-      <c r="R20" s="71">
+      <c r="R20" s="60">
         <v>4854.5</v>
       </c>
-      <c r="S20" s="71">
+      <c r="S20" s="60">
         <v>3648.4</v>
       </c>
-      <c r="T20" s="71">
+      <c r="T20" s="60">
         <v>4854.5</v>
       </c>
-      <c r="U20" s="71">
+      <c r="U20" s="60">
         <v>3648.4</v>
       </c>
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A21" s="72" t="s">
+      <c r="A21" s="61" t="s">
         <v>929</v>
       </c>
-      <c r="B21" s="71">
+      <c r="B21" s="60">
         <v>826.2</v>
       </c>
-      <c r="C21" s="71">
+      <c r="C21" s="60">
         <v>826.2</v>
       </c>
-      <c r="D21" s="71">
+      <c r="D21" s="60">
         <v>2537.4</v>
       </c>
-      <c r="E21" s="71">
+      <c r="E21" s="60">
         <v>2106</v>
       </c>
-      <c r="F21" s="71">
-        <v>0</v>
-      </c>
-      <c r="G21" s="71">
-        <v>0</v>
-      </c>
-      <c r="H21" s="71">
+      <c r="F21" s="60">
+        <v>0</v>
+      </c>
+      <c r="G21" s="60">
+        <v>0</v>
+      </c>
+      <c r="H21" s="60">
         <v>410.6</v>
       </c>
-      <c r="I21" s="71">
+      <c r="I21" s="60">
         <v>410.6</v>
       </c>
-      <c r="J21" s="71">
+      <c r="J21" s="60">
         <v>279.5</v>
       </c>
-      <c r="K21" s="71">
+      <c r="K21" s="60">
         <v>279.5</v>
       </c>
-      <c r="L21" s="71">
-        <v>0</v>
-      </c>
-      <c r="M21" s="71">
-        <v>0</v>
-      </c>
-      <c r="N21" s="71">
+      <c r="L21" s="60">
+        <v>0</v>
+      </c>
+      <c r="M21" s="60">
+        <v>0</v>
+      </c>
+      <c r="N21" s="60">
         <v>4053.7</v>
       </c>
-      <c r="O21" s="71">
+      <c r="O21" s="60">
         <v>3622.3</v>
       </c>
-      <c r="P21" s="71">
+      <c r="P21" s="60">
         <v>305.8</v>
       </c>
-      <c r="Q21" s="71">
+      <c r="Q21" s="60">
         <v>271.7</v>
       </c>
-      <c r="R21" s="71">
+      <c r="R21" s="60">
         <v>2843.2</v>
       </c>
-      <c r="S21" s="71">
+      <c r="S21" s="60">
         <v>2377.6999999999998</v>
       </c>
-      <c r="T21" s="71">
+      <c r="T21" s="60">
         <v>2843.2</v>
       </c>
-      <c r="U21" s="71">
+      <c r="U21" s="60">
         <v>2377.6999999999998</v>
       </c>
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A22" s="70" t="s">
+      <c r="A22" s="59" t="s">
         <v>386</v>
       </c>
-      <c r="B22" s="69">
+      <c r="B22" s="58">
         <v>41872.800000000003</v>
       </c>
-      <c r="C22" s="69">
+      <c r="C22" s="58">
         <v>40683.699999999997</v>
       </c>
-      <c r="D22" s="69">
+      <c r="D22" s="58">
         <v>4560.3999999999996</v>
       </c>
-      <c r="E22" s="69">
+      <c r="E22" s="58">
         <v>3198.9</v>
       </c>
-      <c r="F22" s="69">
-        <v>0</v>
-      </c>
-      <c r="G22" s="69">
-        <v>0</v>
-      </c>
-      <c r="H22" s="69">
+      <c r="F22" s="58">
+        <v>0</v>
+      </c>
+      <c r="G22" s="58">
+        <v>0</v>
+      </c>
+      <c r="H22" s="58">
         <v>3363.7</v>
       </c>
-      <c r="I22" s="69">
+      <c r="I22" s="58">
         <v>3363.7</v>
       </c>
-      <c r="J22" s="69">
+      <c r="J22" s="58">
         <v>384.7</v>
       </c>
-      <c r="K22" s="69">
+      <c r="K22" s="58">
         <v>389.4</v>
       </c>
-      <c r="L22" s="69">
-        <v>0</v>
-      </c>
-      <c r="M22" s="69">
-        <v>0</v>
-      </c>
-      <c r="N22" s="69">
+      <c r="L22" s="58">
+        <v>0</v>
+      </c>
+      <c r="M22" s="58">
+        <v>0</v>
+      </c>
+      <c r="N22" s="58">
         <v>50181.599999999999</v>
       </c>
-      <c r="O22" s="69">
+      <c r="O22" s="58">
         <v>47635.7</v>
       </c>
-      <c r="P22" s="69">
+      <c r="P22" s="58">
         <v>1449</v>
       </c>
-      <c r="Q22" s="69">
+      <c r="Q22" s="58">
         <v>1220.9000000000001</v>
       </c>
-      <c r="R22" s="69">
+      <c r="R22" s="58">
         <v>6009.4</v>
       </c>
-      <c r="S22" s="69">
+      <c r="S22" s="58">
         <v>4419.8</v>
       </c>
-      <c r="T22" s="69">
+      <c r="T22" s="58">
         <v>6009.4</v>
       </c>
-      <c r="U22" s="69">
+      <c r="U22" s="58">
         <v>4419.8</v>
       </c>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A23" s="72" t="s">
+      <c r="A23" s="61" t="s">
         <v>928</v>
       </c>
-      <c r="B23" s="71">
+      <c r="B23" s="60">
         <v>13242.2</v>
       </c>
-      <c r="C23" s="71">
+      <c r="C23" s="60">
         <v>12865.5</v>
       </c>
-      <c r="D23" s="71">
+      <c r="D23" s="60">
         <v>691.4</v>
       </c>
-      <c r="E23" s="71">
+      <c r="E23" s="60">
         <v>676.1</v>
       </c>
-      <c r="F23" s="71">
-        <v>0</v>
-      </c>
-      <c r="G23" s="71">
-        <v>0</v>
-      </c>
-      <c r="H23" s="71">
+      <c r="F23" s="60">
+        <v>0</v>
+      </c>
+      <c r="G23" s="60">
+        <v>0</v>
+      </c>
+      <c r="H23" s="60">
         <v>209.4</v>
       </c>
-      <c r="I23" s="71">
+      <c r="I23" s="60">
         <v>209.4</v>
       </c>
-      <c r="J23" s="71">
+      <c r="J23" s="60">
         <v>20.6</v>
       </c>
-      <c r="K23" s="71">
+      <c r="K23" s="60">
         <v>20.6</v>
       </c>
-      <c r="L23" s="71">
-        <v>0</v>
-      </c>
-      <c r="M23" s="71">
-        <v>0</v>
-      </c>
-      <c r="N23" s="71">
+      <c r="L23" s="60">
+        <v>0</v>
+      </c>
+      <c r="M23" s="60">
+        <v>0</v>
+      </c>
+      <c r="N23" s="60">
         <v>14163.6</v>
       </c>
-      <c r="O23" s="71">
+      <c r="O23" s="60">
         <v>13771.6</v>
       </c>
-      <c r="P23" s="71">
+      <c r="P23" s="60">
         <v>388.5</v>
       </c>
-      <c r="Q23" s="71">
+      <c r="Q23" s="60">
         <v>332.8</v>
       </c>
-      <c r="R23" s="71">
+      <c r="R23" s="60">
         <v>1079.9000000000001</v>
       </c>
-      <c r="S23" s="71">
+      <c r="S23" s="60">
         <v>1008.9</v>
       </c>
-      <c r="T23" s="71">
+      <c r="T23" s="60">
         <v>1079.9000000000001</v>
       </c>
-      <c r="U23" s="71">
+      <c r="U23" s="60">
         <v>1008.9</v>
       </c>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A24" s="72" t="s">
+      <c r="A24" s="61" t="s">
         <v>927</v>
       </c>
-      <c r="B24" s="71">
+      <c r="B24" s="60">
         <v>9651.1</v>
       </c>
-      <c r="C24" s="71">
+      <c r="C24" s="60">
         <v>9042.7000000000007</v>
       </c>
-      <c r="D24" s="71">
+      <c r="D24" s="60">
         <v>277.89999999999998</v>
       </c>
-      <c r="E24" s="71">
+      <c r="E24" s="60">
         <v>65.8</v>
       </c>
-      <c r="F24" s="71">
-        <v>0</v>
-      </c>
-      <c r="G24" s="71">
-        <v>0</v>
-      </c>
-      <c r="H24" s="71">
+      <c r="F24" s="60">
+        <v>0</v>
+      </c>
+      <c r="G24" s="60">
+        <v>0</v>
+      </c>
+      <c r="H24" s="60">
         <v>7</v>
       </c>
-      <c r="I24" s="71">
+      <c r="I24" s="60">
         <v>7</v>
       </c>
-      <c r="J24" s="71">
+      <c r="J24" s="60">
         <v>9</v>
       </c>
-      <c r="K24" s="71">
+      <c r="K24" s="60">
         <v>9</v>
       </c>
-      <c r="L24" s="71">
-        <v>0</v>
-      </c>
-      <c r="M24" s="71">
-        <v>0</v>
-      </c>
-      <c r="N24" s="71">
+      <c r="L24" s="60">
+        <v>0</v>
+      </c>
+      <c r="M24" s="60">
+        <v>0</v>
+      </c>
+      <c r="N24" s="60">
         <v>9945</v>
       </c>
-      <c r="O24" s="71">
+      <c r="O24" s="60">
         <v>9124.5</v>
       </c>
-      <c r="P24" s="71">
+      <c r="P24" s="60">
         <v>128.9</v>
       </c>
-      <c r="Q24" s="71">
+      <c r="Q24" s="60">
         <v>108.6</v>
       </c>
-      <c r="R24" s="71">
+      <c r="R24" s="60">
         <v>406.8</v>
       </c>
-      <c r="S24" s="71">
+      <c r="S24" s="60">
         <v>174.4</v>
       </c>
-      <c r="T24" s="71">
+      <c r="T24" s="60">
         <v>406.8</v>
       </c>
-      <c r="U24" s="71">
+      <c r="U24" s="60">
         <v>174.4</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A25" s="72" t="s">
+      <c r="A25" s="61" t="s">
         <v>926</v>
       </c>
-      <c r="B25" s="71">
+      <c r="B25" s="60">
         <v>4901.3999999999996</v>
       </c>
-      <c r="C25" s="71">
+      <c r="C25" s="60">
         <v>4901.3999999999996</v>
       </c>
-      <c r="D25" s="71">
+      <c r="D25" s="60">
         <v>1910.8</v>
       </c>
-      <c r="E25" s="71">
+      <c r="E25" s="60">
         <v>1641.7</v>
       </c>
-      <c r="F25" s="71">
-        <v>0</v>
-      </c>
-      <c r="G25" s="71">
-        <v>0</v>
-      </c>
-      <c r="H25" s="71">
+      <c r="F25" s="60">
+        <v>0</v>
+      </c>
+      <c r="G25" s="60">
+        <v>0</v>
+      </c>
+      <c r="H25" s="60">
         <v>212</v>
       </c>
-      <c r="I25" s="71">
+      <c r="I25" s="60">
         <v>212</v>
       </c>
-      <c r="J25" s="71">
+      <c r="J25" s="60">
         <v>316.60000000000002</v>
       </c>
-      <c r="K25" s="71">
+      <c r="K25" s="60">
         <v>316.60000000000002</v>
       </c>
-      <c r="L25" s="71">
-        <v>0</v>
-      </c>
-      <c r="M25" s="71">
-        <v>0</v>
-      </c>
-      <c r="N25" s="71">
+      <c r="L25" s="60">
+        <v>0</v>
+      </c>
+      <c r="M25" s="60">
+        <v>0</v>
+      </c>
+      <c r="N25" s="60">
         <v>7340.8</v>
       </c>
-      <c r="O25" s="71">
+      <c r="O25" s="60">
         <v>7071.7</v>
       </c>
-      <c r="P25" s="71">
+      <c r="P25" s="60">
         <v>362.7</v>
       </c>
-      <c r="Q25" s="71">
+      <c r="Q25" s="60">
         <v>296.10000000000002</v>
       </c>
-      <c r="R25" s="71">
+      <c r="R25" s="60">
         <v>2273.5</v>
       </c>
-      <c r="S25" s="71">
+      <c r="S25" s="60">
         <v>1937.8</v>
       </c>
-      <c r="T25" s="71">
+      <c r="T25" s="60">
         <v>2273.5</v>
       </c>
-      <c r="U25" s="71">
+      <c r="U25" s="60">
         <v>1937.8</v>
       </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A26" s="72" t="s">
+      <c r="A26" s="61" t="s">
         <v>925</v>
       </c>
-      <c r="B26" s="71">
+      <c r="B26" s="60">
         <v>2392.9</v>
       </c>
-      <c r="C26" s="71">
+      <c r="C26" s="60">
         <v>2392.9</v>
       </c>
-      <c r="D26" s="71">
+      <c r="D26" s="60">
         <v>1331.8</v>
       </c>
-      <c r="E26" s="71">
+      <c r="E26" s="60">
         <v>469.8</v>
       </c>
-      <c r="F26" s="71">
-        <v>0</v>
-      </c>
-      <c r="G26" s="71">
-        <v>0</v>
-      </c>
-      <c r="H26" s="71">
+      <c r="F26" s="60">
+        <v>0</v>
+      </c>
+      <c r="G26" s="60">
+        <v>0</v>
+      </c>
+      <c r="H26" s="60">
         <v>548.5</v>
       </c>
-      <c r="I26" s="71">
+      <c r="I26" s="60">
         <v>548.5</v>
       </c>
-      <c r="J26" s="71">
+      <c r="J26" s="60">
         <v>14</v>
       </c>
-      <c r="K26" s="71">
+      <c r="K26" s="60">
         <v>14</v>
       </c>
-      <c r="L26" s="71">
-        <v>0</v>
-      </c>
-      <c r="M26" s="71">
-        <v>0</v>
-      </c>
-      <c r="N26" s="71">
+      <c r="L26" s="60">
+        <v>0</v>
+      </c>
+      <c r="M26" s="60">
+        <v>0</v>
+      </c>
+      <c r="N26" s="60">
         <v>4287.2</v>
       </c>
-      <c r="O26" s="71">
+      <c r="O26" s="60">
         <v>3425.2</v>
       </c>
-      <c r="P26" s="71">
+      <c r="P26" s="60">
         <v>519.79999999999995</v>
       </c>
-      <c r="Q26" s="71">
+      <c r="Q26" s="60">
         <v>439.8</v>
       </c>
-      <c r="R26" s="71">
+      <c r="R26" s="60">
         <v>1851.6</v>
       </c>
-      <c r="S26" s="71">
+      <c r="S26" s="60">
         <v>909.6</v>
       </c>
-      <c r="T26" s="71">
+      <c r="T26" s="60">
         <v>1851.6</v>
       </c>
-      <c r="U26" s="71">
+      <c r="U26" s="60">
         <v>909.6</v>
       </c>
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A27" s="72" t="s">
+      <c r="A27" s="61" t="s">
         <v>924</v>
       </c>
-      <c r="B27" s="71">
+      <c r="B27" s="60">
         <v>3520.9</v>
       </c>
-      <c r="C27" s="71">
+      <c r="C27" s="60">
         <v>3516.9</v>
       </c>
-      <c r="D27" s="71">
+      <c r="D27" s="60">
         <v>139.5</v>
       </c>
-      <c r="E27" s="71">
+      <c r="E27" s="60">
         <v>136.5</v>
       </c>
-      <c r="F27" s="71">
-        <v>0</v>
-      </c>
-      <c r="G27" s="71">
-        <v>0</v>
-      </c>
-      <c r="H27" s="71">
+      <c r="F27" s="60">
+        <v>0</v>
+      </c>
+      <c r="G27" s="60">
+        <v>0</v>
+      </c>
+      <c r="H27" s="60">
         <v>278.8</v>
       </c>
-      <c r="I27" s="71">
+      <c r="I27" s="60">
         <v>278.8</v>
       </c>
-      <c r="J27" s="71">
+      <c r="J27" s="60">
         <v>9.3000000000000007</v>
       </c>
-      <c r="K27" s="71">
+      <c r="K27" s="60">
         <v>14</v>
       </c>
-      <c r="L27" s="71">
-        <v>0</v>
-      </c>
-      <c r="M27" s="71">
-        <v>0</v>
-      </c>
-      <c r="N27" s="71">
+      <c r="L27" s="60">
+        <v>0</v>
+      </c>
+      <c r="M27" s="60">
+        <v>0</v>
+      </c>
+      <c r="N27" s="60">
         <v>3948.5</v>
       </c>
-      <c r="O27" s="71">
+      <c r="O27" s="60">
         <v>3946.2</v>
       </c>
-      <c r="P27" s="71">
+      <c r="P27" s="60">
         <v>40.200000000000003</v>
       </c>
-      <c r="Q27" s="71">
+      <c r="Q27" s="60">
         <v>36</v>
       </c>
-      <c r="R27" s="71">
+      <c r="R27" s="60">
         <v>179.7</v>
       </c>
-      <c r="S27" s="71">
+      <c r="S27" s="60">
         <v>172.5</v>
       </c>
-      <c r="T27" s="71">
+      <c r="T27" s="60">
         <v>179.7</v>
       </c>
-      <c r="U27" s="71">
+      <c r="U27" s="60">
         <v>172.5</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A28" s="72" t="s">
+      <c r="A28" s="61" t="s">
         <v>923</v>
       </c>
-      <c r="B28" s="71">
+      <c r="B28" s="60">
         <v>4714</v>
       </c>
-      <c r="C28" s="71">
+      <c r="C28" s="60">
         <v>4514</v>
       </c>
-      <c r="D28" s="71">
-        <v>0</v>
-      </c>
-      <c r="E28" s="71">
-        <v>0</v>
-      </c>
-      <c r="F28" s="71">
-        <v>0</v>
-      </c>
-      <c r="G28" s="71">
-        <v>0</v>
-      </c>
-      <c r="H28" s="71">
+      <c r="D28" s="60">
+        <v>0</v>
+      </c>
+      <c r="E28" s="60">
+        <v>0</v>
+      </c>
+      <c r="F28" s="60">
+        <v>0</v>
+      </c>
+      <c r="G28" s="60">
+        <v>0</v>
+      </c>
+      <c r="H28" s="60">
         <v>510</v>
       </c>
-      <c r="I28" s="71">
+      <c r="I28" s="60">
         <v>510</v>
       </c>
-      <c r="J28" s="71">
+      <c r="J28" s="60">
         <v>9.8000000000000007</v>
       </c>
-      <c r="K28" s="71">
+      <c r="K28" s="60">
         <v>9.8000000000000007</v>
       </c>
-      <c r="L28" s="71">
-        <v>0</v>
-      </c>
-      <c r="M28" s="71">
-        <v>0</v>
-      </c>
-      <c r="N28" s="71">
+      <c r="L28" s="60">
+        <v>0</v>
+      </c>
+      <c r="M28" s="60">
+        <v>0</v>
+      </c>
+      <c r="N28" s="60">
         <v>5233.8</v>
       </c>
-      <c r="O28" s="71">
+      <c r="O28" s="60">
         <v>5033.8</v>
       </c>
-      <c r="P28" s="71">
+      <c r="P28" s="60">
         <v>3</v>
       </c>
-      <c r="Q28" s="71">
+      <c r="Q28" s="60">
         <v>2.2000000000000002</v>
       </c>
-      <c r="R28" s="71">
+      <c r="R28" s="60">
         <v>3</v>
       </c>
-      <c r="S28" s="71">
+      <c r="S28" s="60">
         <v>2.2000000000000002</v>
       </c>
-      <c r="T28" s="71">
+      <c r="T28" s="60">
         <v>3</v>
       </c>
-      <c r="U28" s="71">
+      <c r="U28" s="60">
         <v>2.2000000000000002</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A29" s="72" t="s">
+      <c r="A29" s="61" t="s">
         <v>922</v>
       </c>
-      <c r="B29" s="71">
+      <c r="B29" s="60">
         <v>3450.3</v>
       </c>
-      <c r="C29" s="71">
+      <c r="C29" s="60">
         <v>3450.3</v>
       </c>
-      <c r="D29" s="71">
+      <c r="D29" s="60">
         <v>209</v>
       </c>
-      <c r="E29" s="71">
+      <c r="E29" s="60">
         <v>209</v>
       </c>
-      <c r="F29" s="71">
-        <v>0</v>
-      </c>
-      <c r="G29" s="71">
-        <v>0</v>
-      </c>
-      <c r="H29" s="71">
+      <c r="F29" s="60">
+        <v>0</v>
+      </c>
+      <c r="G29" s="60">
+        <v>0</v>
+      </c>
+      <c r="H29" s="60">
         <v>1598</v>
       </c>
-      <c r="I29" s="71">
+      <c r="I29" s="60">
         <v>1598</v>
       </c>
-      <c r="J29" s="71">
+      <c r="J29" s="60">
         <v>5.4</v>
       </c>
-      <c r="K29" s="71">
+      <c r="K29" s="60">
         <v>5.4</v>
       </c>
-      <c r="L29" s="71">
-        <v>0</v>
-      </c>
-      <c r="M29" s="71">
-        <v>0</v>
-      </c>
-      <c r="N29" s="71">
+      <c r="L29" s="60">
+        <v>0</v>
+      </c>
+      <c r="M29" s="60">
+        <v>0</v>
+      </c>
+      <c r="N29" s="60">
         <v>5262.7</v>
       </c>
-      <c r="O29" s="71">
+      <c r="O29" s="60">
         <v>5262.7</v>
       </c>
-      <c r="P29" s="71">
+      <c r="P29" s="60">
         <v>5.9</v>
       </c>
-      <c r="Q29" s="71">
+      <c r="Q29" s="60">
         <v>5.4</v>
       </c>
-      <c r="R29" s="71">
+      <c r="R29" s="60">
         <v>214.9</v>
       </c>
-      <c r="S29" s="71">
+      <c r="S29" s="60">
         <v>214.4</v>
       </c>
-      <c r="T29" s="71">
+      <c r="T29" s="60">
         <v>214.9</v>
       </c>
-      <c r="U29" s="71">
+      <c r="U29" s="60">
         <v>214.4</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A30" s="70" t="s">
+      <c r="A30" s="59" t="s">
         <v>388</v>
       </c>
-      <c r="B30" s="69">
+      <c r="B30" s="58">
         <v>1511.1</v>
       </c>
-      <c r="C30" s="69">
+      <c r="C30" s="58">
         <v>1456.2</v>
       </c>
-      <c r="D30" s="69">
+      <c r="D30" s="58">
         <v>33149.5</v>
       </c>
-      <c r="E30" s="69">
+      <c r="E30" s="58">
         <v>29987.3</v>
       </c>
-      <c r="F30" s="69">
-        <v>0</v>
-      </c>
-      <c r="G30" s="69">
-        <v>0</v>
-      </c>
-      <c r="H30" s="69">
+      <c r="F30" s="58">
+        <v>0</v>
+      </c>
+      <c r="G30" s="58">
+        <v>0</v>
+      </c>
+      <c r="H30" s="58">
         <v>7054.2</v>
       </c>
-      <c r="I30" s="69">
+      <c r="I30" s="58">
         <v>7054.2</v>
       </c>
-      <c r="J30" s="69">
+      <c r="J30" s="58">
         <v>3701.9</v>
       </c>
-      <c r="K30" s="69">
+      <c r="K30" s="58">
         <v>3812.8</v>
       </c>
-      <c r="L30" s="69">
-        <v>0</v>
-      </c>
-      <c r="M30" s="69">
-        <v>0</v>
-      </c>
-      <c r="N30" s="69">
+      <c r="L30" s="58">
+        <v>0</v>
+      </c>
+      <c r="M30" s="58">
+        <v>0</v>
+      </c>
+      <c r="N30" s="58">
         <v>45416.7</v>
       </c>
-      <c r="O30" s="69">
+      <c r="O30" s="58">
         <v>42310.5</v>
       </c>
-      <c r="P30" s="69">
+      <c r="P30" s="58">
         <v>7116.8</v>
       </c>
-      <c r="Q30" s="69">
+      <c r="Q30" s="58">
         <v>6328.6</v>
       </c>
-      <c r="R30" s="69">
+      <c r="R30" s="58">
         <v>40266.300000000003</v>
       </c>
-      <c r="S30" s="69">
+      <c r="S30" s="58">
         <v>36315.9</v>
       </c>
-      <c r="T30" s="69">
+      <c r="T30" s="58">
         <v>40266.300000000003</v>
       </c>
-      <c r="U30" s="69">
+      <c r="U30" s="58">
         <v>36315.9</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A31" s="72" t="s">
+      <c r="A31" s="61" t="s">
         <v>921</v>
       </c>
-      <c r="B31" s="71">
+      <c r="B31" s="60">
         <v>2</v>
       </c>
-      <c r="C31" s="71">
+      <c r="C31" s="60">
         <v>2</v>
       </c>
-      <c r="D31" s="71">
+      <c r="D31" s="60">
         <v>107.9</v>
       </c>
-      <c r="E31" s="71">
+      <c r="E31" s="60">
         <v>96.9</v>
       </c>
-      <c r="F31" s="71">
-        <v>0</v>
-      </c>
-      <c r="G31" s="71">
-        <v>0</v>
-      </c>
-      <c r="H31" s="71">
-        <v>0</v>
-      </c>
-      <c r="I31" s="71">
-        <v>0</v>
-      </c>
-      <c r="J31" s="71">
+      <c r="F31" s="60">
+        <v>0</v>
+      </c>
+      <c r="G31" s="60">
+        <v>0</v>
+      </c>
+      <c r="H31" s="60">
+        <v>0</v>
+      </c>
+      <c r="I31" s="60">
+        <v>0</v>
+      </c>
+      <c r="J31" s="60">
         <v>14.2</v>
       </c>
-      <c r="K31" s="71">
+      <c r="K31" s="60">
         <v>14.2</v>
       </c>
-      <c r="L31" s="71">
-        <v>0</v>
-      </c>
-      <c r="M31" s="71">
-        <v>0</v>
-      </c>
-      <c r="N31" s="71">
+      <c r="L31" s="60">
+        <v>0</v>
+      </c>
+      <c r="M31" s="60">
+        <v>0</v>
+      </c>
+      <c r="N31" s="60">
         <v>124.1</v>
       </c>
-      <c r="O31" s="71">
+      <c r="O31" s="60">
         <v>113.1</v>
       </c>
-      <c r="P31" s="71">
+      <c r="P31" s="60">
         <v>159.5</v>
       </c>
-      <c r="Q31" s="71">
+      <c r="Q31" s="60">
         <v>143.5</v>
       </c>
-      <c r="R31" s="71">
+      <c r="R31" s="60">
         <v>267.39999999999998</v>
       </c>
-      <c r="S31" s="71">
+      <c r="S31" s="60">
         <v>240.4</v>
       </c>
-      <c r="T31" s="71">
+      <c r="T31" s="60">
         <v>267.39999999999998</v>
       </c>
-      <c r="U31" s="71">
+      <c r="U31" s="60">
         <v>240.4</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A32" s="72" t="s">
+      <c r="A32" s="61" t="s">
         <v>920</v>
       </c>
-      <c r="B32" s="71">
-        <v>0</v>
-      </c>
-      <c r="C32" s="71">
-        <v>0</v>
-      </c>
-      <c r="D32" s="71">
+      <c r="B32" s="60">
+        <v>0</v>
+      </c>
+      <c r="C32" s="60">
+        <v>0</v>
+      </c>
+      <c r="D32" s="60">
         <v>35.200000000000003</v>
       </c>
-      <c r="E32" s="71">
+      <c r="E32" s="60">
         <v>29.2</v>
       </c>
-      <c r="F32" s="71">
-        <v>0</v>
-      </c>
-      <c r="G32" s="71">
-        <v>0</v>
-      </c>
-      <c r="H32" s="71">
-        <v>0</v>
-      </c>
-      <c r="I32" s="71">
-        <v>0</v>
-      </c>
-      <c r="J32" s="71">
+      <c r="F32" s="60">
+        <v>0</v>
+      </c>
+      <c r="G32" s="60">
+        <v>0</v>
+      </c>
+      <c r="H32" s="60">
+        <v>0</v>
+      </c>
+      <c r="I32" s="60">
+        <v>0</v>
+      </c>
+      <c r="J32" s="60">
         <v>12</v>
       </c>
-      <c r="K32" s="71">
+      <c r="K32" s="60">
         <v>12</v>
       </c>
-      <c r="L32" s="71">
-        <v>0</v>
-      </c>
-      <c r="M32" s="71">
-        <v>0</v>
-      </c>
-      <c r="N32" s="71">
+      <c r="L32" s="60">
+        <v>0</v>
+      </c>
+      <c r="M32" s="60">
+        <v>0</v>
+      </c>
+      <c r="N32" s="60">
         <v>47.2</v>
       </c>
-      <c r="O32" s="71">
+      <c r="O32" s="60">
         <v>41.2</v>
       </c>
-      <c r="P32" s="71">
+      <c r="P32" s="60">
         <v>261.7</v>
       </c>
-      <c r="Q32" s="71">
+      <c r="Q32" s="60">
         <v>176.1</v>
       </c>
-      <c r="R32" s="71">
+      <c r="R32" s="60">
         <v>296.89999999999998</v>
       </c>
-      <c r="S32" s="71">
+      <c r="S32" s="60">
         <v>205.3</v>
       </c>
-      <c r="T32" s="71">
+      <c r="T32" s="60">
         <v>296.89999999999998</v>
       </c>
-      <c r="U32" s="71">
+      <c r="U32" s="60">
         <v>205.3</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A33" s="72" t="s">
+      <c r="A33" s="61" t="s">
         <v>919</v>
       </c>
-      <c r="B33" s="71">
-        <v>0</v>
-      </c>
-      <c r="C33" s="71">
-        <v>0</v>
-      </c>
-      <c r="D33" s="71">
+      <c r="B33" s="60">
+        <v>0</v>
+      </c>
+      <c r="C33" s="60">
+        <v>0</v>
+      </c>
+      <c r="D33" s="60">
         <v>12293.5</v>
       </c>
-      <c r="E33" s="71">
+      <c r="E33" s="60">
         <v>10950.8</v>
       </c>
-      <c r="F33" s="71">
-        <v>0</v>
-      </c>
-      <c r="G33" s="71">
-        <v>0</v>
-      </c>
-      <c r="H33" s="71">
+      <c r="F33" s="60">
+        <v>0</v>
+      </c>
+      <c r="G33" s="60">
+        <v>0</v>
+      </c>
+      <c r="H33" s="60">
         <v>43.5</v>
       </c>
-      <c r="I33" s="71">
+      <c r="I33" s="60">
         <v>43.5</v>
       </c>
-      <c r="J33" s="71">
+      <c r="J33" s="60">
         <v>990.4</v>
       </c>
-      <c r="K33" s="71">
+      <c r="K33" s="60">
         <v>992</v>
       </c>
-      <c r="L33" s="71">
-        <v>0</v>
-      </c>
-      <c r="M33" s="71">
-        <v>0</v>
-      </c>
-      <c r="N33" s="71">
+      <c r="L33" s="60">
+        <v>0</v>
+      </c>
+      <c r="M33" s="60">
+        <v>0</v>
+      </c>
+      <c r="N33" s="60">
         <v>13327.4</v>
       </c>
-      <c r="O33" s="71">
+      <c r="O33" s="60">
         <v>11986.3</v>
       </c>
-      <c r="P33" s="71">
+      <c r="P33" s="60">
         <v>3175.6</v>
       </c>
-      <c r="Q33" s="71">
+      <c r="Q33" s="60">
         <v>2819.9</v>
       </c>
-      <c r="R33" s="71">
+      <c r="R33" s="60">
         <v>15469.1</v>
       </c>
-      <c r="S33" s="71">
+      <c r="S33" s="60">
         <v>13770.7</v>
       </c>
-      <c r="T33" s="71">
+      <c r="T33" s="60">
         <v>15469.1</v>
       </c>
-      <c r="U33" s="71">
+      <c r="U33" s="60">
         <v>13770.7</v>
       </c>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A34" s="72" t="s">
+      <c r="A34" s="61" t="s">
         <v>918</v>
       </c>
-      <c r="B34" s="71">
-        <v>0</v>
-      </c>
-      <c r="C34" s="71">
-        <v>0</v>
-      </c>
-      <c r="D34" s="71">
+      <c r="B34" s="60">
+        <v>0</v>
+      </c>
+      <c r="C34" s="60">
+        <v>0</v>
+      </c>
+      <c r="D34" s="60">
         <v>5402.8</v>
       </c>
-      <c r="E34" s="71">
+      <c r="E34" s="60">
         <v>5002.8</v>
       </c>
-      <c r="F34" s="71">
-        <v>0</v>
-      </c>
-      <c r="G34" s="71">
-        <v>0</v>
-      </c>
-      <c r="H34" s="71">
+      <c r="F34" s="60">
+        <v>0</v>
+      </c>
+      <c r="G34" s="60">
+        <v>0</v>
+      </c>
+      <c r="H34" s="60">
         <v>1985</v>
       </c>
-      <c r="I34" s="71">
+      <c r="I34" s="60">
         <v>1985</v>
       </c>
-      <c r="J34" s="71">
+      <c r="J34" s="60">
         <v>959.1</v>
       </c>
-      <c r="K34" s="71">
+      <c r="K34" s="60">
         <v>1067.0999999999999</v>
       </c>
-      <c r="L34" s="71">
-        <v>0</v>
-      </c>
-      <c r="M34" s="71">
-        <v>0</v>
-      </c>
-      <c r="N34" s="71">
+      <c r="L34" s="60">
+        <v>0</v>
+      </c>
+      <c r="M34" s="60">
+        <v>0</v>
+      </c>
+      <c r="N34" s="60">
         <v>8346.9</v>
       </c>
-      <c r="O34" s="71">
+      <c r="O34" s="60">
         <v>8054.9</v>
       </c>
-      <c r="P34" s="71">
+      <c r="P34" s="60">
         <v>375.1</v>
       </c>
-      <c r="Q34" s="71">
+      <c r="Q34" s="60">
         <v>342.4</v>
       </c>
-      <c r="R34" s="71">
+      <c r="R34" s="60">
         <v>5777.9</v>
       </c>
-      <c r="S34" s="71">
+      <c r="S34" s="60">
         <v>5345.2</v>
       </c>
-      <c r="T34" s="71">
+      <c r="T34" s="60">
         <v>5777.9</v>
       </c>
-      <c r="U34" s="71">
+      <c r="U34" s="60">
         <v>5345.2</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A35" s="72" t="s">
+      <c r="A35" s="61" t="s">
         <v>917</v>
       </c>
-      <c r="B35" s="71">
+      <c r="B35" s="60">
         <v>244.9</v>
       </c>
-      <c r="C35" s="71">
+      <c r="C35" s="60">
         <v>190</v>
       </c>
-      <c r="D35" s="71">
+      <c r="D35" s="60">
         <v>1061.0999999999999</v>
       </c>
-      <c r="E35" s="71">
+      <c r="E35" s="60">
         <v>671.4</v>
       </c>
-      <c r="F35" s="71">
-        <v>0</v>
-      </c>
-      <c r="G35" s="71">
-        <v>0</v>
-      </c>
-      <c r="H35" s="71">
+      <c r="F35" s="60">
+        <v>0</v>
+      </c>
+      <c r="G35" s="60">
+        <v>0</v>
+      </c>
+      <c r="H35" s="60">
         <v>514.9</v>
       </c>
-      <c r="I35" s="71">
+      <c r="I35" s="60">
         <v>514.9</v>
       </c>
-      <c r="J35" s="71">
+      <c r="J35" s="60">
         <v>137.30000000000001</v>
       </c>
-      <c r="K35" s="71">
+      <c r="K35" s="60">
         <v>138.6</v>
       </c>
-      <c r="L35" s="71">
-        <v>0</v>
-      </c>
-      <c r="M35" s="71">
-        <v>0</v>
-      </c>
-      <c r="N35" s="71">
+      <c r="L35" s="60">
+        <v>0</v>
+      </c>
+      <c r="M35" s="60">
+        <v>0</v>
+      </c>
+      <c r="N35" s="60">
         <v>1958.2</v>
       </c>
-      <c r="O35" s="71">
+      <c r="O35" s="60">
         <v>1514.9</v>
       </c>
-      <c r="P35" s="71">
+      <c r="P35" s="60">
         <v>1351.8</v>
       </c>
-      <c r="Q35" s="71">
+      <c r="Q35" s="60">
         <v>1132.4000000000001</v>
       </c>
-      <c r="R35" s="71">
+      <c r="R35" s="60">
         <v>2412.9</v>
       </c>
-      <c r="S35" s="71">
+      <c r="S35" s="60">
         <v>1803.8</v>
       </c>
-      <c r="T35" s="71">
+      <c r="T35" s="60">
         <v>2412.9</v>
       </c>
-      <c r="U35" s="71">
+      <c r="U35" s="60">
         <v>1803.8</v>
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A36" s="72" t="s">
+      <c r="A36" s="61" t="s">
         <v>916</v>
       </c>
-      <c r="B36" s="71">
+      <c r="B36" s="60">
         <v>397</v>
       </c>
-      <c r="C36" s="71">
+      <c r="C36" s="60">
         <v>397</v>
       </c>
-      <c r="D36" s="71">
+      <c r="D36" s="60">
         <v>7032.1</v>
       </c>
-      <c r="E36" s="71">
+      <c r="E36" s="60">
         <v>6786.7</v>
       </c>
-      <c r="F36" s="71">
-        <v>0</v>
-      </c>
-      <c r="G36" s="71">
-        <v>0</v>
-      </c>
-      <c r="H36" s="71">
+      <c r="F36" s="60">
+        <v>0</v>
+      </c>
+      <c r="G36" s="60">
+        <v>0</v>
+      </c>
+      <c r="H36" s="60">
         <v>2009.4</v>
       </c>
-      <c r="I36" s="71">
+      <c r="I36" s="60">
         <v>2009.4</v>
       </c>
-      <c r="J36" s="71">
+      <c r="J36" s="60">
         <v>409.9</v>
       </c>
-      <c r="K36" s="71">
+      <c r="K36" s="60">
         <v>409.9</v>
       </c>
-      <c r="L36" s="71">
-        <v>0</v>
-      </c>
-      <c r="M36" s="71">
-        <v>0</v>
-      </c>
-      <c r="N36" s="71">
+      <c r="L36" s="60">
+        <v>0</v>
+      </c>
+      <c r="M36" s="60">
+        <v>0</v>
+      </c>
+      <c r="N36" s="60">
         <v>9848.4</v>
       </c>
-      <c r="O36" s="71">
+      <c r="O36" s="60">
         <v>9603</v>
       </c>
-      <c r="P36" s="71">
+      <c r="P36" s="60">
         <v>636.70000000000005</v>
       </c>
-      <c r="Q36" s="71">
+      <c r="Q36" s="60">
         <v>579.20000000000005</v>
       </c>
-      <c r="R36" s="71">
+      <c r="R36" s="60">
         <v>7668.8</v>
       </c>
-      <c r="S36" s="71">
+      <c r="S36" s="60">
         <v>7365.9</v>
       </c>
-      <c r="T36" s="71">
+      <c r="T36" s="60">
         <v>7668.8</v>
       </c>
-      <c r="U36" s="71">
+      <c r="U36" s="60">
         <v>7365.9</v>
       </c>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A37" s="72" t="s">
+      <c r="A37" s="61" t="s">
         <v>915</v>
       </c>
-      <c r="B37" s="71">
-        <v>0</v>
-      </c>
-      <c r="C37" s="71">
-        <v>0</v>
-      </c>
-      <c r="D37" s="71">
+      <c r="B37" s="60">
+        <v>0</v>
+      </c>
+      <c r="C37" s="60">
+        <v>0</v>
+      </c>
+      <c r="D37" s="60">
         <v>1923.7</v>
       </c>
-      <c r="E37" s="71">
+      <c r="E37" s="60">
         <v>1646.7</v>
       </c>
-      <c r="F37" s="71">
-        <v>0</v>
-      </c>
-      <c r="G37" s="71">
-        <v>0</v>
-      </c>
-      <c r="H37" s="71">
+      <c r="F37" s="60">
+        <v>0</v>
+      </c>
+      <c r="G37" s="60">
+        <v>0</v>
+      </c>
+      <c r="H37" s="60">
         <v>1294</v>
       </c>
-      <c r="I37" s="71">
+      <c r="I37" s="60">
         <v>1294</v>
       </c>
-      <c r="J37" s="71">
+      <c r="J37" s="60">
         <v>462.5</v>
       </c>
-      <c r="K37" s="71">
+      <c r="K37" s="60">
         <v>462.5</v>
       </c>
-      <c r="L37" s="71">
-        <v>0</v>
-      </c>
-      <c r="M37" s="71">
-        <v>0</v>
-      </c>
-      <c r="N37" s="71">
+      <c r="L37" s="60">
+        <v>0</v>
+      </c>
+      <c r="M37" s="60">
+        <v>0</v>
+      </c>
+      <c r="N37" s="60">
         <v>3680.2</v>
       </c>
-      <c r="O37" s="71">
+      <c r="O37" s="60">
         <v>3403.2</v>
       </c>
-      <c r="P37" s="71">
+      <c r="P37" s="60">
         <v>415.3</v>
       </c>
-      <c r="Q37" s="71">
+      <c r="Q37" s="60">
         <v>400.2</v>
       </c>
-      <c r="R37" s="71">
+      <c r="R37" s="60">
         <v>2339</v>
       </c>
-      <c r="S37" s="71">
+      <c r="S37" s="60">
         <v>2046.9</v>
       </c>
-      <c r="T37" s="71">
+      <c r="T37" s="60">
         <v>2339</v>
       </c>
-      <c r="U37" s="71">
+      <c r="U37" s="60">
         <v>2046.9</v>
       </c>
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A38" s="72" t="s">
+      <c r="A38" s="61" t="s">
         <v>914</v>
       </c>
-      <c r="B38" s="71">
+      <c r="B38" s="60">
         <v>12</v>
       </c>
-      <c r="C38" s="71">
+      <c r="C38" s="60">
         <v>12</v>
       </c>
-      <c r="D38" s="71">
+      <c r="D38" s="60">
         <v>5163</v>
       </c>
-      <c r="E38" s="71">
+      <c r="E38" s="60">
         <v>4678.3999999999996</v>
       </c>
-      <c r="F38" s="71">
-        <v>0</v>
-      </c>
-      <c r="G38" s="71">
-        <v>0</v>
-      </c>
-      <c r="H38" s="71">
+      <c r="F38" s="60">
+        <v>0</v>
+      </c>
+      <c r="G38" s="60">
+        <v>0</v>
+      </c>
+      <c r="H38" s="60">
         <v>866.6</v>
       </c>
-      <c r="I38" s="71">
+      <c r="I38" s="60">
         <v>866.6</v>
       </c>
-      <c r="J38" s="71">
+      <c r="J38" s="60">
         <v>713.3</v>
       </c>
-      <c r="K38" s="71">
+      <c r="K38" s="60">
         <v>713.3</v>
       </c>
-      <c r="L38" s="71">
-        <v>0</v>
-      </c>
-      <c r="M38" s="71">
-        <v>0</v>
-      </c>
-      <c r="N38" s="71">
+      <c r="L38" s="60">
+        <v>0</v>
+      </c>
+      <c r="M38" s="60">
+        <v>0</v>
+      </c>
+      <c r="N38" s="60">
         <v>6754.9</v>
       </c>
-      <c r="O38" s="71">
+      <c r="O38" s="60">
         <v>6270.3</v>
       </c>
-      <c r="P38" s="71">
+      <c r="P38" s="60">
         <v>678.7</v>
       </c>
-      <c r="Q38" s="71">
+      <c r="Q38" s="60">
         <v>690.1</v>
       </c>
-      <c r="R38" s="71">
+      <c r="R38" s="60">
         <v>5841.7</v>
       </c>
-      <c r="S38" s="71">
+      <c r="S38" s="60">
         <v>5368.5</v>
       </c>
-      <c r="T38" s="71">
+      <c r="T38" s="60">
         <v>5841.7</v>
       </c>
-      <c r="U38" s="71">
+      <c r="U38" s="60">
         <v>5368.5</v>
       </c>
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A39" s="72" t="s">
+      <c r="A39" s="61" t="s">
         <v>913</v>
       </c>
-      <c r="B39" s="71">
+      <c r="B39" s="60">
         <v>855.2</v>
       </c>
-      <c r="C39" s="71">
+      <c r="C39" s="60">
         <v>855.2</v>
       </c>
-      <c r="D39" s="71">
+      <c r="D39" s="60">
         <v>130.19999999999999</v>
       </c>
-      <c r="E39" s="71">
+      <c r="E39" s="60">
         <v>124.4</v>
       </c>
-      <c r="F39" s="71">
-        <v>0</v>
-      </c>
-      <c r="G39" s="71">
-        <v>0</v>
-      </c>
-      <c r="H39" s="71">
+      <c r="F39" s="60">
+        <v>0</v>
+      </c>
+      <c r="G39" s="60">
+        <v>0</v>
+      </c>
+      <c r="H39" s="60">
         <v>340.8</v>
       </c>
-      <c r="I39" s="71">
+      <c r="I39" s="60">
         <v>340.8</v>
       </c>
-      <c r="J39" s="71">
+      <c r="J39" s="60">
         <v>3.2</v>
       </c>
-      <c r="K39" s="71">
+      <c r="K39" s="60">
         <v>3.2</v>
       </c>
-      <c r="L39" s="71">
-        <v>0</v>
-      </c>
-      <c r="M39" s="71">
-        <v>0</v>
-      </c>
-      <c r="N39" s="71">
+      <c r="L39" s="60">
+        <v>0</v>
+      </c>
+      <c r="M39" s="60">
+        <v>0</v>
+      </c>
+      <c r="N39" s="60">
         <v>1329.4</v>
       </c>
-      <c r="O39" s="71">
+      <c r="O39" s="60">
         <v>1323.6</v>
       </c>
-      <c r="P39" s="71">
+      <c r="P39" s="60">
         <v>62.3</v>
       </c>
-      <c r="Q39" s="71">
+      <c r="Q39" s="60">
         <v>44.8</v>
       </c>
-      <c r="R39" s="71">
+      <c r="R39" s="60">
         <v>192.5</v>
       </c>
-      <c r="S39" s="71">
+      <c r="S39" s="60">
         <v>169.2</v>
       </c>
-      <c r="T39" s="71">
+      <c r="T39" s="60">
         <v>192.5</v>
       </c>
-      <c r="U39" s="71">
+      <c r="U39" s="60">
         <v>169.2</v>
       </c>
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A40" s="70" t="s">
+      <c r="A40" s="59" t="s">
         <v>389</v>
       </c>
-      <c r="B40" s="69">
+      <c r="B40" s="58">
         <v>186.6</v>
       </c>
-      <c r="C40" s="69">
+      <c r="C40" s="58">
         <v>186.6</v>
       </c>
-      <c r="D40" s="69">
+      <c r="D40" s="58">
         <v>4307.8999999999996</v>
       </c>
-      <c r="E40" s="69">
+      <c r="E40" s="58">
         <v>2910.3</v>
       </c>
-      <c r="F40" s="69">
-        <v>0</v>
-      </c>
-      <c r="G40" s="69">
-        <v>0</v>
-      </c>
-      <c r="H40" s="69">
+      <c r="F40" s="58">
+        <v>0</v>
+      </c>
+      <c r="G40" s="58">
+        <v>0</v>
+      </c>
+      <c r="H40" s="58">
         <v>7036.6</v>
       </c>
-      <c r="I40" s="69">
+      <c r="I40" s="58">
         <v>7036.6</v>
       </c>
-      <c r="J40" s="69">
+      <c r="J40" s="58">
         <v>1073.5</v>
       </c>
-      <c r="K40" s="69">
+      <c r="K40" s="58">
         <v>1073.5</v>
       </c>
-      <c r="L40" s="69">
-        <v>0</v>
-      </c>
-      <c r="M40" s="69">
-        <v>0</v>
-      </c>
-      <c r="N40" s="69">
+      <c r="L40" s="58">
+        <v>0</v>
+      </c>
+      <c r="M40" s="58">
+        <v>0</v>
+      </c>
+      <c r="N40" s="58">
         <v>12604.6</v>
       </c>
-      <c r="O40" s="69">
+      <c r="O40" s="58">
         <v>11207</v>
       </c>
-      <c r="P40" s="69">
+      <c r="P40" s="58">
         <v>217.8</v>
       </c>
-      <c r="Q40" s="69">
+      <c r="Q40" s="58">
         <v>204.4</v>
       </c>
-      <c r="R40" s="69">
+      <c r="R40" s="58">
         <v>4525.7</v>
       </c>
-      <c r="S40" s="69">
+      <c r="S40" s="58">
         <v>3114.7</v>
       </c>
-      <c r="T40" s="69">
+      <c r="T40" s="58">
         <v>4525.7</v>
       </c>
-      <c r="U40" s="69">
+      <c r="U40" s="58">
         <v>3114.7</v>
       </c>
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A41" s="72" t="s">
+      <c r="A41" s="61" t="s">
         <v>912</v>
       </c>
-      <c r="B41" s="71">
-        <v>0</v>
-      </c>
-      <c r="C41" s="71">
-        <v>0</v>
-      </c>
-      <c r="D41" s="71">
+      <c r="B41" s="60">
+        <v>0</v>
+      </c>
+      <c r="C41" s="60">
+        <v>0</v>
+      </c>
+      <c r="D41" s="60">
         <v>743.5</v>
       </c>
-      <c r="E41" s="71">
+      <c r="E41" s="60">
         <v>663.5</v>
       </c>
-      <c r="F41" s="71">
-        <v>0</v>
-      </c>
-      <c r="G41" s="71">
-        <v>0</v>
-      </c>
-      <c r="H41" s="71">
+      <c r="F41" s="60">
+        <v>0</v>
+      </c>
+      <c r="G41" s="60">
+        <v>0</v>
+      </c>
+      <c r="H41" s="60">
         <v>3290.6</v>
       </c>
-      <c r="I41" s="71">
+      <c r="I41" s="60">
         <v>3290.6</v>
       </c>
-      <c r="J41" s="71">
+      <c r="J41" s="60">
         <v>613.9</v>
       </c>
-      <c r="K41" s="71">
+      <c r="K41" s="60">
         <v>613.9</v>
       </c>
-      <c r="L41" s="71">
-        <v>0</v>
-      </c>
-      <c r="M41" s="71">
-        <v>0</v>
-      </c>
-      <c r="N41" s="71">
+      <c r="L41" s="60">
+        <v>0</v>
+      </c>
+      <c r="M41" s="60">
+        <v>0</v>
+      </c>
+      <c r="N41" s="60">
         <v>4648</v>
       </c>
-      <c r="O41" s="71">
+      <c r="O41" s="60">
         <v>4568</v>
       </c>
-      <c r="P41" s="71" t="s">
+      <c r="P41" s="60" t="s">
         <v>911</v>
       </c>
-      <c r="Q41" s="71">
+      <c r="Q41" s="60">
         <v>17</v>
       </c>
-      <c r="R41" s="71" t="s">
+      <c r="R41" s="60" t="s">
         <v>911</v>
       </c>
-      <c r="S41" s="71">
+      <c r="S41" s="60">
         <v>680.5</v>
       </c>
-      <c r="T41" s="71" t="s">
+      <c r="T41" s="60" t="s">
         <v>911</v>
       </c>
-      <c r="U41" s="71">
+      <c r="U41" s="60">
         <v>680.5</v>
       </c>
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A42" s="72" t="s">
+      <c r="A42" s="61" t="s">
         <v>910</v>
       </c>
-      <c r="B42" s="71">
-        <v>0</v>
-      </c>
-      <c r="C42" s="71">
-        <v>0</v>
-      </c>
-      <c r="D42" s="71">
+      <c r="B42" s="60">
+        <v>0</v>
+      </c>
+      <c r="C42" s="60">
+        <v>0</v>
+      </c>
+      <c r="D42" s="60">
         <v>1136.0999999999999</v>
       </c>
-      <c r="E42" s="71">
+      <c r="E42" s="60">
         <v>426.1</v>
       </c>
-      <c r="F42" s="71">
-        <v>0</v>
-      </c>
-      <c r="G42" s="71">
-        <v>0</v>
-      </c>
-      <c r="H42" s="71">
+      <c r="F42" s="60">
+        <v>0</v>
+      </c>
+      <c r="G42" s="60">
+        <v>0</v>
+      </c>
+      <c r="H42" s="60">
         <v>1137.4000000000001</v>
       </c>
-      <c r="I42" s="71">
+      <c r="I42" s="60">
         <v>1137.4000000000001</v>
       </c>
-      <c r="J42" s="71">
+      <c r="J42" s="60">
         <v>70.5</v>
       </c>
-      <c r="K42" s="71">
+      <c r="K42" s="60">
         <v>70.5</v>
       </c>
-      <c r="L42" s="71">
-        <v>0</v>
-      </c>
-      <c r="M42" s="71">
-        <v>0</v>
-      </c>
-      <c r="N42" s="71">
+      <c r="L42" s="60">
+        <v>0</v>
+      </c>
+      <c r="M42" s="60">
+        <v>0</v>
+      </c>
+      <c r="N42" s="60">
         <v>2344</v>
       </c>
-      <c r="O42" s="71">
+      <c r="O42" s="60">
         <v>1634</v>
       </c>
-      <c r="P42" s="71">
+      <c r="P42" s="60">
         <v>123.4</v>
       </c>
-      <c r="Q42" s="71">
+      <c r="Q42" s="60">
         <v>110.4</v>
       </c>
-      <c r="R42" s="71">
+      <c r="R42" s="60">
         <v>1259.5</v>
       </c>
-      <c r="S42" s="71">
+      <c r="S42" s="60">
         <v>536.5</v>
       </c>
-      <c r="T42" s="71">
+      <c r="T42" s="60">
         <v>1259.5</v>
       </c>
-      <c r="U42" s="71">
+      <c r="U42" s="60">
         <v>536.5</v>
       </c>
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A43" s="72" t="s">
+      <c r="A43" s="61" t="s">
         <v>909</v>
       </c>
-      <c r="B43" s="71">
+      <c r="B43" s="60">
         <v>184.5</v>
       </c>
-      <c r="C43" s="71">
+      <c r="C43" s="60">
         <v>184.5</v>
       </c>
-      <c r="D43" s="71">
+      <c r="D43" s="60">
         <v>1524.5</v>
       </c>
-      <c r="E43" s="71">
+      <c r="E43" s="60">
         <v>1219.7</v>
       </c>
-      <c r="F43" s="71">
-        <v>0</v>
-      </c>
-      <c r="G43" s="71">
-        <v>0</v>
-      </c>
-      <c r="H43" s="71">
-        <v>0</v>
-      </c>
-      <c r="I43" s="71">
-        <v>0</v>
-      </c>
-      <c r="J43" s="71">
+      <c r="F43" s="60">
+        <v>0</v>
+      </c>
+      <c r="G43" s="60">
+        <v>0</v>
+      </c>
+      <c r="H43" s="60">
+        <v>0</v>
+      </c>
+      <c r="I43" s="60">
+        <v>0</v>
+      </c>
+      <c r="J43" s="60">
         <v>302.39999999999998</v>
       </c>
-      <c r="K43" s="71">
+      <c r="K43" s="60">
         <v>302.39999999999998</v>
       </c>
-      <c r="L43" s="71">
-        <v>0</v>
-      </c>
-      <c r="M43" s="71">
-        <v>0</v>
-      </c>
-      <c r="N43" s="71">
+      <c r="L43" s="60">
+        <v>0</v>
+      </c>
+      <c r="M43" s="60">
+        <v>0</v>
+      </c>
+      <c r="N43" s="60">
         <v>2011.4</v>
       </c>
-      <c r="O43" s="71">
+      <c r="O43" s="60">
         <v>1706.6</v>
       </c>
-      <c r="P43" s="71">
+      <c r="P43" s="60">
         <v>20.7</v>
       </c>
-      <c r="Q43" s="71">
+      <c r="Q43" s="60">
         <v>18.399999999999999</v>
       </c>
-      <c r="R43" s="71">
+      <c r="R43" s="60">
         <v>1545.2</v>
       </c>
-      <c r="S43" s="71">
+      <c r="S43" s="60">
         <v>1238.0999999999999</v>
       </c>
-      <c r="T43" s="71">
+      <c r="T43" s="60">
         <v>1545.2</v>
       </c>
-      <c r="U43" s="71">
+      <c r="U43" s="60">
         <v>1238.0999999999999</v>
       </c>
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A44" s="72" t="s">
+      <c r="A44" s="61" t="s">
         <v>908</v>
       </c>
-      <c r="B44" s="71">
+      <c r="B44" s="60">
         <v>2.1</v>
       </c>
-      <c r="C44" s="71">
+      <c r="C44" s="60">
         <v>2.1</v>
       </c>
-      <c r="D44" s="71">
+      <c r="D44" s="60">
         <v>903.8</v>
       </c>
-      <c r="E44" s="71">
+      <c r="E44" s="60">
         <v>601</v>
       </c>
-      <c r="F44" s="71">
-        <v>0</v>
-      </c>
-      <c r="G44" s="71">
-        <v>0</v>
-      </c>
-      <c r="H44" s="71">
+      <c r="F44" s="60">
+        <v>0</v>
+      </c>
+      <c r="G44" s="60">
+        <v>0</v>
+      </c>
+      <c r="H44" s="60">
         <v>2608.6</v>
       </c>
-      <c r="I44" s="71">
+      <c r="I44" s="60">
         <v>2608.6</v>
       </c>
-      <c r="J44" s="71">
+      <c r="J44" s="60">
         <v>86.7</v>
       </c>
-      <c r="K44" s="71">
+      <c r="K44" s="60">
         <v>86.7</v>
       </c>
-      <c r="L44" s="71">
-        <v>0</v>
-      </c>
-      <c r="M44" s="71">
-        <v>0</v>
-      </c>
-      <c r="N44" s="71">
+      <c r="L44" s="60">
+        <v>0</v>
+      </c>
+      <c r="M44" s="60">
+        <v>0</v>
+      </c>
+      <c r="N44" s="60">
         <v>3601.2</v>
       </c>
-      <c r="O44" s="71">
+      <c r="O44" s="60">
         <v>3298.4</v>
       </c>
-      <c r="P44" s="71">
+      <c r="P44" s="60">
         <v>54.1</v>
       </c>
-      <c r="Q44" s="71">
+      <c r="Q44" s="60">
         <v>58.6</v>
       </c>
-      <c r="R44" s="71">
+      <c r="R44" s="60">
         <v>957.9</v>
       </c>
-      <c r="S44" s="71">
+      <c r="S44" s="60">
         <v>659.6</v>
       </c>
-      <c r="T44" s="71">
+      <c r="T44" s="60">
         <v>957.9</v>
       </c>
-      <c r="U44" s="71">
+      <c r="U44" s="60">
         <v>659.6</v>
       </c>
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A45" s="70" t="s">
+      <c r="A45" s="59" t="s">
         <v>390</v>
       </c>
-      <c r="B45" s="69">
+      <c r="B45" s="58">
         <v>57406.1</v>
       </c>
-      <c r="C45" s="69">
+      <c r="C45" s="58">
         <v>54726.1</v>
       </c>
-      <c r="D45" s="69">
+      <c r="D45" s="58">
         <v>34790.1</v>
       </c>
-      <c r="E45" s="69">
+      <c r="E45" s="58">
         <v>25383.8</v>
       </c>
-      <c r="F45" s="69">
-        <v>0</v>
-      </c>
-      <c r="G45" s="69">
-        <v>0</v>
-      </c>
-      <c r="H45" s="69">
+      <c r="F45" s="58">
+        <v>0</v>
+      </c>
+      <c r="G45" s="58">
+        <v>0</v>
+      </c>
+      <c r="H45" s="58">
         <v>3001</v>
       </c>
-      <c r="I45" s="69">
+      <c r="I45" s="58">
         <v>3002.3</v>
       </c>
-      <c r="J45" s="69">
+      <c r="J45" s="58">
         <v>1057.5999999999999</v>
       </c>
-      <c r="K45" s="69">
+      <c r="K45" s="58">
         <v>1057.5999999999999</v>
       </c>
-      <c r="L45" s="69">
-        <v>0</v>
-      </c>
-      <c r="M45" s="69">
-        <v>0</v>
-      </c>
-      <c r="N45" s="69">
+      <c r="L45" s="58">
+        <v>0</v>
+      </c>
+      <c r="M45" s="58">
+        <v>0</v>
+      </c>
+      <c r="N45" s="58">
         <v>96254.8</v>
       </c>
-      <c r="O45" s="69">
+      <c r="O45" s="58">
         <v>84169.8</v>
       </c>
-      <c r="P45" s="69">
+      <c r="P45" s="58">
         <v>4015.8</v>
       </c>
-      <c r="Q45" s="69">
+      <c r="Q45" s="58">
         <v>3753.6</v>
       </c>
-      <c r="R45" s="69">
+      <c r="R45" s="58">
         <v>38805.9</v>
       </c>
-      <c r="S45" s="69">
+      <c r="S45" s="58">
         <v>29137.4</v>
       </c>
-      <c r="T45" s="69">
+      <c r="T45" s="58">
         <v>38805.9</v>
       </c>
-      <c r="U45" s="69">
+      <c r="U45" s="58">
         <v>29137.4</v>
       </c>
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A46" s="72" t="s">
+      <c r="A46" s="61" t="s">
         <v>907</v>
       </c>
-      <c r="B46" s="71">
+      <c r="B46" s="60">
         <v>135</v>
       </c>
-      <c r="C46" s="71">
-        <v>0</v>
-      </c>
-      <c r="D46" s="71">
+      <c r="C46" s="60">
+        <v>0</v>
+      </c>
+      <c r="D46" s="60">
         <v>2537.5</v>
       </c>
-      <c r="E46" s="71">
+      <c r="E46" s="60">
         <v>1784.5</v>
       </c>
-      <c r="F46" s="71">
-        <v>0</v>
-      </c>
-      <c r="G46" s="71">
-        <v>0</v>
-      </c>
-      <c r="H46" s="71">
+      <c r="F46" s="60">
+        <v>0</v>
+      </c>
+      <c r="G46" s="60">
+        <v>0</v>
+      </c>
+      <c r="H46" s="60">
         <v>1264.5</v>
       </c>
-      <c r="I46" s="71">
+      <c r="I46" s="60">
         <v>1264.5</v>
       </c>
-      <c r="J46" s="71">
+      <c r="J46" s="60">
         <v>225.7</v>
       </c>
-      <c r="K46" s="71">
+      <c r="K46" s="60">
         <v>225.7</v>
       </c>
-      <c r="L46" s="71">
-        <v>0</v>
-      </c>
-      <c r="M46" s="71">
-        <v>0</v>
-      </c>
-      <c r="N46" s="71">
+      <c r="L46" s="60">
+        <v>0</v>
+      </c>
+      <c r="M46" s="60">
+        <v>0</v>
+      </c>
+      <c r="N46" s="60">
         <v>4162.7</v>
       </c>
-      <c r="O46" s="71">
+      <c r="O46" s="60">
         <v>3274.7</v>
       </c>
-      <c r="P46" s="71">
+      <c r="P46" s="60">
         <v>355.6</v>
       </c>
-      <c r="Q46" s="71">
+      <c r="Q46" s="60">
         <v>333.9</v>
       </c>
-      <c r="R46" s="71">
+      <c r="R46" s="60">
         <v>2893.1</v>
       </c>
-      <c r="S46" s="71">
+      <c r="S46" s="60">
         <v>2118.4</v>
       </c>
-      <c r="T46" s="71">
+      <c r="T46" s="60">
         <v>2893.1</v>
       </c>
-      <c r="U46" s="71">
+      <c r="U46" s="60">
         <v>2118.4</v>
       </c>
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A47" s="72" t="s">
+      <c r="A47" s="61" t="s">
         <v>906</v>
       </c>
-      <c r="B47" s="71">
-        <v>0</v>
-      </c>
-      <c r="C47" s="71">
-        <v>0</v>
-      </c>
-      <c r="D47" s="71">
+      <c r="B47" s="60">
+        <v>0</v>
+      </c>
+      <c r="C47" s="60">
+        <v>0</v>
+      </c>
+      <c r="D47" s="60">
         <v>1225.0999999999999</v>
       </c>
-      <c r="E47" s="71">
+      <c r="E47" s="60">
         <v>1052.5999999999999</v>
       </c>
-      <c r="F47" s="71">
-        <v>0</v>
-      </c>
-      <c r="G47" s="71">
-        <v>0</v>
-      </c>
-      <c r="H47" s="71">
+      <c r="F47" s="60">
+        <v>0</v>
+      </c>
+      <c r="G47" s="60">
+        <v>0</v>
+      </c>
+      <c r="H47" s="60">
         <v>192</v>
       </c>
-      <c r="I47" s="71">
+      <c r="I47" s="60">
         <v>192</v>
       </c>
-      <c r="J47" s="71">
+      <c r="J47" s="60">
         <v>420.1</v>
       </c>
-      <c r="K47" s="71">
+      <c r="K47" s="60">
         <v>420.1</v>
       </c>
-      <c r="L47" s="71">
-        <v>0</v>
-      </c>
-      <c r="M47" s="71">
-        <v>0</v>
-      </c>
-      <c r="N47" s="71">
+      <c r="L47" s="60">
+        <v>0</v>
+      </c>
+      <c r="M47" s="60">
+        <v>0</v>
+      </c>
+      <c r="N47" s="60">
         <v>1837.2</v>
       </c>
-      <c r="O47" s="71">
+      <c r="O47" s="60">
         <v>1664.7</v>
       </c>
-      <c r="P47" s="71">
+      <c r="P47" s="60">
         <v>238.7</v>
       </c>
-      <c r="Q47" s="71">
+      <c r="Q47" s="60">
         <v>202.6</v>
       </c>
-      <c r="R47" s="71">
+      <c r="R47" s="60">
         <v>1463.8</v>
       </c>
-      <c r="S47" s="71">
+      <c r="S47" s="60">
         <v>1255.2</v>
       </c>
-      <c r="T47" s="71">
+      <c r="T47" s="60">
         <v>1463.8</v>
       </c>
-      <c r="U47" s="71">
+      <c r="U47" s="60">
         <v>1255.2</v>
       </c>
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A48" s="72" t="s">
+      <c r="A48" s="61" t="s">
         <v>905</v>
       </c>
-      <c r="B48" s="71">
+      <c r="B48" s="60">
         <v>13593.7</v>
       </c>
-      <c r="C48" s="71">
+      <c r="C48" s="60">
         <v>12748.2</v>
       </c>
-      <c r="D48" s="71">
+      <c r="D48" s="60">
         <v>523.5</v>
       </c>
-      <c r="E48" s="71">
+      <c r="E48" s="60">
         <v>173.5</v>
       </c>
-      <c r="F48" s="71">
-        <v>0</v>
-      </c>
-      <c r="G48" s="71">
-        <v>0</v>
-      </c>
-      <c r="H48" s="71">
+      <c r="F48" s="60">
+        <v>0</v>
+      </c>
+      <c r="G48" s="60">
+        <v>0</v>
+      </c>
+      <c r="H48" s="60">
         <v>832.4</v>
       </c>
-      <c r="I48" s="71">
+      <c r="I48" s="60">
         <v>832.4</v>
       </c>
-      <c r="J48" s="71">
+      <c r="J48" s="60">
         <v>76.2</v>
       </c>
-      <c r="K48" s="71">
+      <c r="K48" s="60">
         <v>76.2</v>
       </c>
-      <c r="L48" s="71">
-        <v>0</v>
-      </c>
-      <c r="M48" s="71">
-        <v>0</v>
-      </c>
-      <c r="N48" s="71">
+      <c r="L48" s="60">
+        <v>0</v>
+      </c>
+      <c r="M48" s="60">
+        <v>0</v>
+      </c>
+      <c r="N48" s="60">
         <v>15025.8</v>
       </c>
-      <c r="O48" s="71">
+      <c r="O48" s="60">
         <v>13830.3</v>
       </c>
-      <c r="P48" s="71">
+      <c r="P48" s="60">
         <v>164.3</v>
       </c>
-      <c r="Q48" s="71">
+      <c r="Q48" s="60">
         <v>145.1</v>
       </c>
-      <c r="R48" s="71">
+      <c r="R48" s="60">
         <v>687.8</v>
       </c>
-      <c r="S48" s="71">
+      <c r="S48" s="60">
         <v>318.60000000000002</v>
       </c>
-      <c r="T48" s="71">
+      <c r="T48" s="60">
         <v>687.8</v>
       </c>
-      <c r="U48" s="71">
+      <c r="U48" s="60">
         <v>318.60000000000002</v>
       </c>
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A49" s="72" t="s">
+      <c r="A49" s="61" t="s">
         <v>904</v>
       </c>
-      <c r="B49" s="71">
+      <c r="B49" s="60">
         <v>43677.4</v>
       </c>
-      <c r="C49" s="71">
+      <c r="C49" s="60">
         <v>41977.9</v>
       </c>
-      <c r="D49" s="71">
+      <c r="D49" s="60">
         <v>30504</v>
       </c>
-      <c r="E49" s="71">
+      <c r="E49" s="60">
         <v>22373.200000000001</v>
       </c>
-      <c r="F49" s="71">
-        <v>0</v>
-      </c>
-      <c r="G49" s="71">
-        <v>0</v>
-      </c>
-      <c r="H49" s="71">
+      <c r="F49" s="60">
+        <v>0</v>
+      </c>
+      <c r="G49" s="60">
+        <v>0</v>
+      </c>
+      <c r="H49" s="60">
         <v>712.1</v>
       </c>
-      <c r="I49" s="71">
+      <c r="I49" s="60">
         <v>713.4</v>
       </c>
-      <c r="J49" s="71">
+      <c r="J49" s="60">
         <v>335.6</v>
       </c>
-      <c r="K49" s="71">
+      <c r="K49" s="60">
         <v>335.6</v>
       </c>
-      <c r="L49" s="71">
-        <v>0</v>
-      </c>
-      <c r="M49" s="71">
-        <v>0</v>
-      </c>
-      <c r="N49" s="71">
+      <c r="L49" s="60">
+        <v>0</v>
+      </c>
+      <c r="M49" s="60">
+        <v>0</v>
+      </c>
+      <c r="N49" s="60">
         <v>75229.100000000006</v>
       </c>
-      <c r="O49" s="71">
+      <c r="O49" s="60">
         <v>65400.1</v>
       </c>
-      <c r="P49" s="71">
+      <c r="P49" s="60">
         <v>3257.3</v>
       </c>
-      <c r="Q49" s="71">
+      <c r="Q49" s="60">
         <v>3072</v>
       </c>
-      <c r="R49" s="71">
+      <c r="R49" s="60">
         <v>33761.300000000003</v>
       </c>
-      <c r="S49" s="71">
+      <c r="S49" s="60">
         <v>25445.200000000001</v>
       </c>
-      <c r="T49" s="71">
+      <c r="T49" s="60">
         <v>33761.300000000003</v>
       </c>
-      <c r="U49" s="71">
+      <c r="U49" s="60">
         <v>25445.200000000001</v>
       </c>
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A50" s="70" t="s">
+      <c r="A50" s="59" t="s">
         <v>392</v>
       </c>
-      <c r="B50" s="69">
+      <c r="B50" s="58">
         <v>18777.3</v>
       </c>
-      <c r="C50" s="69">
+      <c r="C50" s="58">
         <v>17729.7</v>
       </c>
-      <c r="D50" s="69">
+      <c r="D50" s="58">
         <v>21301.3</v>
       </c>
-      <c r="E50" s="69">
+      <c r="E50" s="58">
         <v>17591.900000000001</v>
       </c>
-      <c r="F50" s="69">
+      <c r="F50" s="58">
         <v>474.2</v>
       </c>
-      <c r="G50" s="69">
+      <c r="G50" s="58">
         <v>474.2</v>
       </c>
-      <c r="H50" s="69">
+      <c r="H50" s="58">
         <v>10604.9</v>
       </c>
-      <c r="I50" s="69">
+      <c r="I50" s="58">
         <v>10602.9</v>
       </c>
-      <c r="J50" s="69">
+      <c r="J50" s="58">
         <v>174</v>
       </c>
-      <c r="K50" s="69">
+      <c r="K50" s="58">
         <v>179.4</v>
       </c>
-      <c r="L50" s="69">
+      <c r="L50" s="58">
         <v>751.8</v>
       </c>
-      <c r="M50" s="69">
+      <c r="M50" s="58">
         <v>751.8</v>
       </c>
-      <c r="N50" s="69">
+      <c r="N50" s="58">
         <v>52083.5</v>
       </c>
-      <c r="O50" s="69">
+      <c r="O50" s="58">
         <v>47329.9</v>
       </c>
-      <c r="P50" s="69">
+      <c r="P50" s="58">
         <v>6997.6</v>
       </c>
-      <c r="Q50" s="69">
+      <c r="Q50" s="58">
         <v>6500.9</v>
       </c>
-      <c r="R50" s="69">
+      <c r="R50" s="58">
         <v>28298.9</v>
       </c>
-      <c r="S50" s="69">
+      <c r="S50" s="58">
         <v>24092.799999999999</v>
       </c>
-      <c r="T50" s="69">
+      <c r="T50" s="58">
         <v>28773.1</v>
       </c>
-      <c r="U50" s="69">
+      <c r="U50" s="58">
         <v>24567</v>
       </c>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A51" s="72" t="s">
+      <c r="A51" s="61" t="s">
         <v>903</v>
       </c>
-      <c r="B51" s="71">
+      <c r="B51" s="60">
         <v>1234.5</v>
       </c>
-      <c r="C51" s="71">
+      <c r="C51" s="60">
         <v>1234.5</v>
       </c>
-      <c r="D51" s="71">
+      <c r="D51" s="60">
         <v>6280.3</v>
       </c>
-      <c r="E51" s="71">
+      <c r="E51" s="60">
         <v>4755.2</v>
       </c>
-      <c r="F51" s="71">
+      <c r="F51" s="60">
         <v>295.60000000000002</v>
       </c>
-      <c r="G51" s="71">
+      <c r="G51" s="60">
         <v>295.60000000000002</v>
       </c>
-      <c r="H51" s="71">
+      <c r="H51" s="60">
         <v>2720.6</v>
       </c>
-      <c r="I51" s="71">
+      <c r="I51" s="60">
         <v>2720.6</v>
       </c>
-      <c r="J51" s="71">
+      <c r="J51" s="60">
         <v>27.9</v>
       </c>
-      <c r="K51" s="71">
+      <c r="K51" s="60">
         <v>27.9</v>
       </c>
-      <c r="L51" s="71">
-        <v>0</v>
-      </c>
-      <c r="M51" s="71">
-        <v>0</v>
-      </c>
-      <c r="N51" s="71">
+      <c r="L51" s="60">
+        <v>0</v>
+      </c>
+      <c r="M51" s="60">
+        <v>0</v>
+      </c>
+      <c r="N51" s="60">
         <v>10558.9</v>
       </c>
-      <c r="O51" s="71">
+      <c r="O51" s="60">
         <v>9033.7999999999993</v>
       </c>
-      <c r="P51" s="71">
+      <c r="P51" s="60">
         <v>3100.5</v>
       </c>
-      <c r="Q51" s="71">
+      <c r="Q51" s="60">
         <v>2896.3</v>
       </c>
-      <c r="R51" s="71">
+      <c r="R51" s="60">
         <v>9380.7999999999993</v>
       </c>
-      <c r="S51" s="71">
+      <c r="S51" s="60">
         <v>7651.5</v>
       </c>
-      <c r="T51" s="71">
+      <c r="T51" s="60">
         <v>9676.4</v>
       </c>
-      <c r="U51" s="71">
+      <c r="U51" s="60">
         <v>7947.1</v>
       </c>
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A52" s="72" t="s">
+      <c r="A52" s="61" t="s">
         <v>902</v>
       </c>
-      <c r="B52" s="71">
+      <c r="B52" s="60">
         <v>5336.7</v>
       </c>
-      <c r="C52" s="71">
+      <c r="C52" s="60">
         <v>5336.7</v>
       </c>
-      <c r="D52" s="71">
+      <c r="D52" s="60">
         <v>3244.8</v>
       </c>
-      <c r="E52" s="71">
+      <c r="E52" s="60">
         <v>2366.6999999999998</v>
       </c>
-      <c r="F52" s="71">
-        <v>0</v>
-      </c>
-      <c r="G52" s="71">
-        <v>0</v>
-      </c>
-      <c r="H52" s="71">
+      <c r="F52" s="60">
+        <v>0</v>
+      </c>
+      <c r="G52" s="60">
+        <v>0</v>
+      </c>
+      <c r="H52" s="60">
         <v>693.2</v>
       </c>
-      <c r="I52" s="71">
+      <c r="I52" s="60">
         <v>693.2</v>
       </c>
-      <c r="J52" s="71">
+      <c r="J52" s="60">
         <v>28.7</v>
       </c>
-      <c r="K52" s="71">
+      <c r="K52" s="60">
         <v>28.7</v>
       </c>
-      <c r="L52" s="71">
-        <v>0</v>
-      </c>
-      <c r="M52" s="71">
-        <v>0</v>
-      </c>
-      <c r="N52" s="71">
+      <c r="L52" s="60">
+        <v>0</v>
+      </c>
+      <c r="M52" s="60">
+        <v>0</v>
+      </c>
+      <c r="N52" s="60">
         <v>9303.4</v>
       </c>
-      <c r="O52" s="71">
+      <c r="O52" s="60">
         <v>8425.2999999999993</v>
       </c>
-      <c r="P52" s="71">
+      <c r="P52" s="60">
         <v>1305.4000000000001</v>
       </c>
-      <c r="Q52" s="71">
+      <c r="Q52" s="60">
         <v>1201.2</v>
       </c>
-      <c r="R52" s="71">
+      <c r="R52" s="60">
         <v>4550.2</v>
       </c>
-      <c r="S52" s="71">
+      <c r="S52" s="60">
         <v>3567.9</v>
       </c>
-      <c r="T52" s="71">
+      <c r="T52" s="60">
         <v>4550.2</v>
       </c>
-      <c r="U52" s="71">
+      <c r="U52" s="60">
         <v>3567.9</v>
       </c>
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A53" s="72" t="s">
+      <c r="A53" s="61" t="s">
         <v>901</v>
       </c>
-      <c r="B53" s="71">
+      <c r="B53" s="60">
         <v>1128.3</v>
       </c>
-      <c r="C53" s="71">
+      <c r="C53" s="60">
         <v>1128.3</v>
       </c>
-      <c r="D53" s="71">
+      <c r="D53" s="60">
         <v>701.6</v>
       </c>
-      <c r="E53" s="71">
+      <c r="E53" s="60">
         <v>501.6</v>
       </c>
-      <c r="F53" s="71">
-        <v>0</v>
-      </c>
-      <c r="G53" s="71">
-        <v>0</v>
-      </c>
-      <c r="H53" s="71">
+      <c r="F53" s="60">
+        <v>0</v>
+      </c>
+      <c r="G53" s="60">
+        <v>0</v>
+      </c>
+      <c r="H53" s="60">
         <v>2656.7</v>
       </c>
-      <c r="I53" s="71">
+      <c r="I53" s="60">
         <v>2653.8</v>
       </c>
-      <c r="J53" s="71">
+      <c r="J53" s="60">
         <v>87.6</v>
       </c>
-      <c r="K53" s="71">
+      <c r="K53" s="60">
         <v>87.6</v>
       </c>
-      <c r="L53" s="71">
+      <c r="L53" s="60">
         <v>10</v>
       </c>
-      <c r="M53" s="71">
+      <c r="M53" s="60">
         <v>10</v>
       </c>
-      <c r="N53" s="71">
+      <c r="N53" s="60">
         <v>4584.2</v>
       </c>
-      <c r="O53" s="71">
+      <c r="O53" s="60">
         <v>4381.3</v>
       </c>
-      <c r="P53" s="71">
+      <c r="P53" s="60">
         <v>197.9</v>
       </c>
-      <c r="Q53" s="71">
+      <c r="Q53" s="60">
         <v>177.6</v>
       </c>
-      <c r="R53" s="71">
+      <c r="R53" s="60">
         <v>899.5</v>
       </c>
-      <c r="S53" s="71">
+      <c r="S53" s="60">
         <v>679.2</v>
       </c>
-      <c r="T53" s="71">
+      <c r="T53" s="60">
         <v>899.5</v>
       </c>
-      <c r="U53" s="71">
+      <c r="U53" s="60">
         <v>679.2</v>
       </c>
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A54" s="72" t="s">
+      <c r="A54" s="61" t="s">
         <v>900</v>
       </c>
-      <c r="B54" s="71">
+      <c r="B54" s="60">
         <v>1956.8</v>
       </c>
-      <c r="C54" s="71">
+      <c r="C54" s="60">
         <v>1889.6</v>
       </c>
-      <c r="D54" s="71">
+      <c r="D54" s="60">
         <v>181</v>
       </c>
-      <c r="E54" s="71">
+      <c r="E54" s="60">
         <v>179</v>
       </c>
-      <c r="F54" s="71">
-        <v>0</v>
-      </c>
-      <c r="G54" s="71">
-        <v>0</v>
-      </c>
-      <c r="H54" s="71">
+      <c r="F54" s="60">
+        <v>0</v>
+      </c>
+      <c r="G54" s="60">
+        <v>0</v>
+      </c>
+      <c r="H54" s="60">
         <v>2833.6</v>
       </c>
-      <c r="I54" s="71">
+      <c r="I54" s="60">
         <v>2834.1</v>
       </c>
-      <c r="J54" s="71">
+      <c r="J54" s="60">
         <v>6.2</v>
       </c>
-      <c r="K54" s="71">
+      <c r="K54" s="60">
         <v>6.2</v>
       </c>
-      <c r="L54" s="71">
-        <v>0</v>
-      </c>
-      <c r="M54" s="71">
-        <v>0</v>
-      </c>
-      <c r="N54" s="71">
+      <c r="L54" s="60">
+        <v>0</v>
+      </c>
+      <c r="M54" s="60">
+        <v>0</v>
+      </c>
+      <c r="N54" s="60">
         <v>4977.6000000000004</v>
       </c>
-      <c r="O54" s="71">
+      <c r="O54" s="60">
         <v>4908.8999999999996</v>
       </c>
-      <c r="P54" s="71">
+      <c r="P54" s="60">
         <v>111.1</v>
       </c>
-      <c r="Q54" s="71">
+      <c r="Q54" s="60">
         <v>81.8</v>
       </c>
-      <c r="R54" s="71">
+      <c r="R54" s="60">
         <v>292.10000000000002</v>
       </c>
-      <c r="S54" s="71">
+      <c r="S54" s="60">
         <v>260.8</v>
       </c>
-      <c r="T54" s="71">
+      <c r="T54" s="60">
         <v>292.10000000000002</v>
       </c>
-      <c r="U54" s="71">
+      <c r="U54" s="60">
         <v>260.8</v>
       </c>
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A55" s="72" t="s">
+      <c r="A55" s="61" t="s">
         <v>899</v>
       </c>
-      <c r="B55" s="71">
+      <c r="B55" s="60">
         <v>150</v>
       </c>
-      <c r="C55" s="71">
+      <c r="C55" s="60">
         <v>150</v>
       </c>
-      <c r="D55" s="71">
+      <c r="D55" s="60">
         <v>5222.6000000000004</v>
       </c>
-      <c r="E55" s="71">
+      <c r="E55" s="60">
         <v>5028.3999999999996</v>
       </c>
-      <c r="F55" s="71">
+      <c r="F55" s="60">
         <v>178.5</v>
       </c>
-      <c r="G55" s="71">
+      <c r="G55" s="60">
         <v>178.5</v>
       </c>
-      <c r="H55" s="71">
+      <c r="H55" s="60">
         <v>1051.7</v>
       </c>
-      <c r="I55" s="71">
+      <c r="I55" s="60">
         <v>1051.7</v>
       </c>
-      <c r="J55" s="71">
+      <c r="J55" s="60">
         <v>9.8000000000000007</v>
       </c>
-      <c r="K55" s="71">
+      <c r="K55" s="60">
         <v>9.8000000000000007</v>
       </c>
-      <c r="L55" s="71">
+      <c r="L55" s="60">
         <v>662.5</v>
       </c>
-      <c r="M55" s="71">
+      <c r="M55" s="60">
         <v>662.5</v>
       </c>
-      <c r="N55" s="71">
+      <c r="N55" s="60">
         <v>7275.1</v>
       </c>
-      <c r="O55" s="71">
+      <c r="O55" s="60">
         <v>7080.9</v>
       </c>
-      <c r="P55" s="71">
+      <c r="P55" s="60">
         <v>1222.9000000000001</v>
       </c>
-      <c r="Q55" s="71">
+      <c r="Q55" s="60">
         <v>1124.3</v>
       </c>
-      <c r="R55" s="71">
+      <c r="R55" s="60">
         <v>6445.5</v>
       </c>
-      <c r="S55" s="71">
+      <c r="S55" s="60">
         <v>6152.7</v>
       </c>
-      <c r="T55" s="71">
+      <c r="T55" s="60">
         <v>6624</v>
       </c>
-      <c r="U55" s="71">
+      <c r="U55" s="60">
         <v>6331.2</v>
       </c>
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A56" s="72" t="s">
+      <c r="A56" s="61" t="s">
         <v>898</v>
       </c>
-      <c r="B56" s="71">
+      <c r="B56" s="60">
         <v>3997</v>
       </c>
-      <c r="C56" s="71">
+      <c r="C56" s="60">
         <v>3997</v>
       </c>
-      <c r="D56" s="71">
+      <c r="D56" s="60">
         <v>2905.7</v>
       </c>
-      <c r="E56" s="71">
+      <c r="E56" s="60">
         <v>2321.9</v>
       </c>
-      <c r="F56" s="71">
-        <v>0</v>
-      </c>
-      <c r="G56" s="71">
-        <v>0</v>
-      </c>
-      <c r="H56" s="71">
+      <c r="F56" s="60">
+        <v>0</v>
+      </c>
+      <c r="G56" s="60">
+        <v>0</v>
+      </c>
+      <c r="H56" s="60">
         <v>82.7</v>
       </c>
-      <c r="I56" s="71">
+      <c r="I56" s="60">
         <v>82.7</v>
       </c>
-      <c r="J56" s="71">
+      <c r="J56" s="60">
         <v>3.2</v>
       </c>
-      <c r="K56" s="71">
+      <c r="K56" s="60">
         <v>6.4</v>
       </c>
-      <c r="L56" s="71">
+      <c r="L56" s="60">
         <v>8.6</v>
       </c>
-      <c r="M56" s="71">
+      <c r="M56" s="60">
         <v>8.6</v>
       </c>
-      <c r="N56" s="71">
+      <c r="N56" s="60">
         <v>6997.2</v>
       </c>
-      <c r="O56" s="71">
+      <c r="O56" s="60">
         <v>6416.6</v>
       </c>
-      <c r="P56" s="71">
+      <c r="P56" s="60">
         <v>406.2</v>
       </c>
-      <c r="Q56" s="71">
+      <c r="Q56" s="60">
         <v>411.6</v>
       </c>
-      <c r="R56" s="71">
+      <c r="R56" s="60">
         <v>3311.9</v>
       </c>
-      <c r="S56" s="71">
+      <c r="S56" s="60">
         <v>2733.5</v>
       </c>
-      <c r="T56" s="71">
+      <c r="T56" s="60">
         <v>3311.9</v>
       </c>
-      <c r="U56" s="71">
+      <c r="U56" s="60">
         <v>2733.5</v>
       </c>
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A57" s="72" t="s">
+      <c r="A57" s="61" t="s">
         <v>897</v>
       </c>
-      <c r="B57" s="71">
+      <c r="B57" s="60">
         <v>389.7</v>
       </c>
-      <c r="C57" s="71">
+      <c r="C57" s="60">
         <v>389.7</v>
       </c>
-      <c r="D57" s="71">
+      <c r="D57" s="60">
         <v>2523.3000000000002</v>
       </c>
-      <c r="E57" s="71">
+      <c r="E57" s="60">
         <v>2197.1</v>
       </c>
-      <c r="F57" s="71">
+      <c r="F57" s="60">
         <v>0.1</v>
       </c>
-      <c r="G57" s="71">
+      <c r="G57" s="60">
         <v>0.1</v>
       </c>
-      <c r="H57" s="71">
+      <c r="H57" s="60">
         <v>259.3</v>
       </c>
-      <c r="I57" s="71">
+      <c r="I57" s="60">
         <v>259.7</v>
       </c>
-      <c r="J57" s="71">
+      <c r="J57" s="60">
         <v>10.6</v>
       </c>
-      <c r="K57" s="71">
+      <c r="K57" s="60">
         <v>12.8</v>
       </c>
-      <c r="L57" s="71">
+      <c r="L57" s="60">
         <v>70.7</v>
       </c>
-      <c r="M57" s="71">
+      <c r="M57" s="60">
         <v>70.7</v>
       </c>
-      <c r="N57" s="71">
+      <c r="N57" s="60">
         <v>3253.7</v>
       </c>
-      <c r="O57" s="71">
+      <c r="O57" s="60">
         <v>2930.1</v>
       </c>
-      <c r="P57" s="71">
+      <c r="P57" s="60">
         <v>627.20000000000005</v>
       </c>
-      <c r="Q57" s="71">
+      <c r="Q57" s="60">
         <v>586.29999999999995</v>
       </c>
-      <c r="R57" s="71">
+      <c r="R57" s="60">
         <v>3150.5</v>
       </c>
-      <c r="S57" s="71">
+      <c r="S57" s="60">
         <v>2783.4</v>
       </c>
-      <c r="T57" s="71">
+      <c r="T57" s="60">
         <v>3150.6</v>
       </c>
-      <c r="U57" s="71">
+      <c r="U57" s="60">
         <v>2783.5</v>
       </c>
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A58" s="72" t="s">
+      <c r="A58" s="61" t="s">
         <v>896</v>
       </c>
-      <c r="B58" s="71">
+      <c r="B58" s="60">
         <v>4584.3</v>
       </c>
-      <c r="C58" s="71">
+      <c r="C58" s="60">
         <v>3603.9</v>
       </c>
-      <c r="D58" s="71">
+      <c r="D58" s="60">
         <v>242</v>
       </c>
-      <c r="E58" s="71">
+      <c r="E58" s="60">
         <v>242</v>
       </c>
-      <c r="F58" s="71">
-        <v>0</v>
-      </c>
-      <c r="G58" s="71">
-        <v>0</v>
-      </c>
-      <c r="H58" s="71">
+      <c r="F58" s="60">
+        <v>0</v>
+      </c>
+      <c r="G58" s="60">
+        <v>0</v>
+      </c>
+      <c r="H58" s="60">
         <v>307.10000000000002</v>
       </c>
-      <c r="I58" s="71">
+      <c r="I58" s="60">
         <v>307.10000000000002</v>
       </c>
-      <c r="J58" s="71">
-        <v>0</v>
-      </c>
-      <c r="K58" s="71">
-        <v>0</v>
-      </c>
-      <c r="L58" s="71">
-        <v>0</v>
-      </c>
-      <c r="M58" s="71">
-        <v>0</v>
-      </c>
-      <c r="N58" s="71">
+      <c r="J58" s="60">
+        <v>0</v>
+      </c>
+      <c r="K58" s="60">
+        <v>0</v>
+      </c>
+      <c r="L58" s="60">
+        <v>0</v>
+      </c>
+      <c r="M58" s="60">
+        <v>0</v>
+      </c>
+      <c r="N58" s="60">
         <v>5133.3999999999996</v>
       </c>
-      <c r="O58" s="71">
+      <c r="O58" s="60">
         <v>4153</v>
       </c>
-      <c r="P58" s="71">
+      <c r="P58" s="60">
         <v>26.5</v>
       </c>
-      <c r="Q58" s="71">
+      <c r="Q58" s="60">
         <v>21.7</v>
       </c>
-      <c r="R58" s="71">
+      <c r="R58" s="60">
         <v>268.5</v>
       </c>
-      <c r="S58" s="71">
+      <c r="S58" s="60">
         <v>263.7</v>
       </c>
-      <c r="T58" s="71">
+      <c r="T58" s="60">
         <v>268.5</v>
       </c>
-      <c r="U58" s="71">
+      <c r="U58" s="60">
         <v>263.7</v>
       </c>
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A59" s="70" t="s">
+      <c r="A59" s="59" t="s">
         <v>895</v>
       </c>
-      <c r="B59" s="69">
+      <c r="B59" s="58">
         <v>14048.2</v>
       </c>
-      <c r="C59" s="69">
+      <c r="C59" s="58">
         <v>13802.1</v>
       </c>
-      <c r="D59" s="69">
+      <c r="D59" s="58">
         <v>24986.3</v>
       </c>
-      <c r="E59" s="69">
+      <c r="E59" s="58">
         <v>22685.200000000001</v>
       </c>
-      <c r="F59" s="69">
+      <c r="F59" s="58">
         <v>917.8</v>
       </c>
-      <c r="G59" s="69">
+      <c r="G59" s="58">
         <v>917.8</v>
       </c>
-      <c r="H59" s="69">
+      <c r="H59" s="58">
         <v>39991.5</v>
       </c>
-      <c r="I59" s="69">
+      <c r="I59" s="58">
         <v>39991.1</v>
       </c>
-      <c r="J59" s="69">
+      <c r="J59" s="58">
         <v>1522.4</v>
       </c>
-      <c r="K59" s="69">
+      <c r="K59" s="58">
         <v>1544.1</v>
       </c>
-      <c r="L59" s="69">
+      <c r="L59" s="58">
         <v>1900.7</v>
       </c>
-      <c r="M59" s="69">
+      <c r="M59" s="58">
         <v>1900.7</v>
       </c>
-      <c r="N59" s="69">
+      <c r="N59" s="58">
         <v>83366.899999999994</v>
       </c>
-      <c r="O59" s="69">
+      <c r="O59" s="58">
         <v>80841</v>
       </c>
-      <c r="P59" s="69">
+      <c r="P59" s="58">
         <v>21249</v>
       </c>
-      <c r="Q59" s="69">
+      <c r="Q59" s="58">
         <v>19189.599999999999</v>
       </c>
-      <c r="R59" s="69">
+      <c r="R59" s="58">
         <v>46235.3</v>
       </c>
-      <c r="S59" s="69">
+      <c r="S59" s="58">
         <v>41874.800000000003</v>
       </c>
-      <c r="T59" s="69">
+      <c r="T59" s="58">
         <v>47153.1</v>
       </c>
-      <c r="U59" s="69">
+      <c r="U59" s="58">
         <v>42792.6</v>
       </c>
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A60" s="72" t="s">
+      <c r="A60" s="61" t="s">
         <v>894</v>
       </c>
-      <c r="B60" s="71">
+      <c r="B60" s="60">
         <v>6502.9</v>
       </c>
-      <c r="C60" s="71">
+      <c r="C60" s="60">
         <v>6456.8</v>
       </c>
-      <c r="D60" s="71">
+      <c r="D60" s="60">
         <v>23428</v>
       </c>
-      <c r="E60" s="71">
+      <c r="E60" s="60">
         <v>21365.200000000001</v>
       </c>
-      <c r="F60" s="71">
+      <c r="F60" s="60">
         <v>917.8</v>
       </c>
-      <c r="G60" s="71">
+      <c r="G60" s="60">
         <v>917.8</v>
       </c>
-      <c r="H60" s="71">
+      <c r="H60" s="60">
         <v>10209.1</v>
       </c>
-      <c r="I60" s="71">
+      <c r="I60" s="60">
         <v>10213.6</v>
       </c>
-      <c r="J60" s="71">
+      <c r="J60" s="60">
         <v>957.7</v>
       </c>
-      <c r="K60" s="71">
+      <c r="K60" s="60">
         <v>979.4</v>
       </c>
-      <c r="L60" s="71">
+      <c r="L60" s="60">
         <v>1881.2</v>
       </c>
-      <c r="M60" s="71">
+      <c r="M60" s="60">
         <v>1881.2</v>
       </c>
-      <c r="N60" s="71">
+      <c r="N60" s="60">
         <v>43896.7</v>
       </c>
-      <c r="O60" s="71">
+      <c r="O60" s="60">
         <v>41814</v>
       </c>
-      <c r="P60" s="71">
+      <c r="P60" s="60">
         <v>20107.8</v>
       </c>
-      <c r="Q60" s="71">
+      <c r="Q60" s="60">
         <v>18209.2</v>
       </c>
-      <c r="R60" s="71">
+      <c r="R60" s="60">
         <v>43535.8</v>
       </c>
-      <c r="S60" s="71">
+      <c r="S60" s="60">
         <v>39574.400000000001</v>
       </c>
-      <c r="T60" s="71">
+      <c r="T60" s="60">
         <v>44453.599999999999</v>
       </c>
-      <c r="U60" s="71">
+      <c r="U60" s="60">
         <v>40492.199999999997</v>
       </c>
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A61" s="72" t="s">
+      <c r="A61" s="61" t="s">
         <v>893</v>
       </c>
-      <c r="B61" s="71">
+      <c r="B61" s="60">
         <v>4170.3999999999996</v>
       </c>
-      <c r="C61" s="71">
+      <c r="C61" s="60">
         <v>3970.4</v>
       </c>
-      <c r="D61" s="71">
+      <c r="D61" s="60">
         <v>1290</v>
       </c>
-      <c r="E61" s="71">
+      <c r="E61" s="60">
         <v>1051.7</v>
       </c>
-      <c r="F61" s="71">
-        <v>0</v>
-      </c>
-      <c r="G61" s="71">
-        <v>0</v>
-      </c>
-      <c r="H61" s="71">
+      <c r="F61" s="60">
+        <v>0</v>
+      </c>
+      <c r="G61" s="60">
+        <v>0</v>
+      </c>
+      <c r="H61" s="60">
         <v>8264.2000000000007</v>
       </c>
-      <c r="I61" s="71">
+      <c r="I61" s="60">
         <v>8264.2000000000007</v>
       </c>
-      <c r="J61" s="71">
+      <c r="J61" s="60">
         <v>294.89999999999998</v>
       </c>
-      <c r="K61" s="71">
+      <c r="K61" s="60">
         <v>294.89999999999998</v>
       </c>
-      <c r="L61" s="71">
+      <c r="L61" s="60">
         <v>19.5</v>
       </c>
-      <c r="M61" s="71">
+      <c r="M61" s="60">
         <v>19.5</v>
       </c>
-      <c r="N61" s="71">
+      <c r="N61" s="60">
         <v>14039</v>
       </c>
-      <c r="O61" s="71">
+      <c r="O61" s="60">
         <v>13600.7</v>
       </c>
-      <c r="P61" s="71">
+      <c r="P61" s="60">
         <v>556.29999999999995</v>
       </c>
-      <c r="Q61" s="71">
+      <c r="Q61" s="60">
         <v>476.8</v>
       </c>
-      <c r="R61" s="71">
+      <c r="R61" s="60">
         <v>1846.3</v>
       </c>
-      <c r="S61" s="71">
+      <c r="S61" s="60">
         <v>1528.5</v>
       </c>
-      <c r="T61" s="71">
+      <c r="T61" s="60">
         <v>1846.3</v>
       </c>
-      <c r="U61" s="71">
+      <c r="U61" s="60">
         <v>1528.5</v>
       </c>
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A62" s="72" t="s">
+      <c r="A62" s="61" t="s">
         <v>892</v>
       </c>
-      <c r="B62" s="71">
+      <c r="B62" s="60">
         <v>3374.9</v>
       </c>
-      <c r="C62" s="71">
+      <c r="C62" s="60">
         <v>3374.9</v>
       </c>
-      <c r="D62" s="71">
+      <c r="D62" s="60">
         <v>268.3</v>
       </c>
-      <c r="E62" s="71">
+      <c r="E62" s="60">
         <v>268.3</v>
       </c>
-      <c r="F62" s="71">
-        <v>0</v>
-      </c>
-      <c r="G62" s="71">
-        <v>0</v>
-      </c>
-      <c r="H62" s="71">
+      <c r="F62" s="60">
+        <v>0</v>
+      </c>
+      <c r="G62" s="60">
+        <v>0</v>
+      </c>
+      <c r="H62" s="60">
         <v>21518.2</v>
       </c>
-      <c r="I62" s="71">
+      <c r="I62" s="60">
         <v>21513.3</v>
       </c>
-      <c r="J62" s="71">
+      <c r="J62" s="60">
         <v>269.8</v>
       </c>
-      <c r="K62" s="71">
+      <c r="K62" s="60">
         <v>269.8</v>
       </c>
-      <c r="L62" s="71">
-        <v>0</v>
-      </c>
-      <c r="M62" s="71">
-        <v>0</v>
-      </c>
-      <c r="N62" s="71">
+      <c r="L62" s="60">
+        <v>0</v>
+      </c>
+      <c r="M62" s="60">
+        <v>0</v>
+      </c>
+      <c r="N62" s="60">
         <v>25431.200000000001</v>
       </c>
-      <c r="O62" s="71">
+      <c r="O62" s="60">
         <v>25426.3</v>
       </c>
-      <c r="P62" s="71">
+      <c r="P62" s="60">
         <v>584.9</v>
       </c>
-      <c r="Q62" s="71">
+      <c r="Q62" s="60">
         <v>503.6</v>
       </c>
-      <c r="R62" s="71">
+      <c r="R62" s="60">
         <v>853.2</v>
       </c>
-      <c r="S62" s="71">
+      <c r="S62" s="60">
         <v>771.9</v>
       </c>
-      <c r="T62" s="71">
+      <c r="T62" s="60">
         <v>853.2</v>
       </c>
-      <c r="U62" s="71">
+      <c r="U62" s="60">
         <v>771.9</v>
       </c>
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A63" s="70" t="s">
+      <c r="A63" s="59" t="s">
         <v>891</v>
       </c>
-      <c r="B63" s="69">
+      <c r="B63" s="58">
         <v>292.2</v>
       </c>
-      <c r="C63" s="69">
+      <c r="C63" s="58">
         <v>292.2</v>
       </c>
-      <c r="D63" s="69">
+      <c r="D63" s="58">
         <v>565.29999999999995</v>
       </c>
-      <c r="E63" s="69">
+      <c r="E63" s="58">
         <v>473.2</v>
       </c>
-      <c r="F63" s="69">
-        <v>0</v>
-      </c>
-      <c r="G63" s="69">
-        <v>0</v>
-      </c>
-      <c r="H63" s="69">
+      <c r="F63" s="58">
+        <v>0</v>
+      </c>
+      <c r="G63" s="58">
+        <v>0</v>
+      </c>
+      <c r="H63" s="58">
         <v>508.6</v>
       </c>
-      <c r="I63" s="69">
+      <c r="I63" s="58">
         <v>508.7</v>
       </c>
-      <c r="J63" s="69">
+      <c r="J63" s="58">
         <v>160.9</v>
       </c>
-      <c r="K63" s="69">
+      <c r="K63" s="58">
         <v>160.9</v>
       </c>
-      <c r="L63" s="69">
+      <c r="L63" s="58">
         <v>43</v>
       </c>
-      <c r="M63" s="69">
+      <c r="M63" s="58">
         <v>43</v>
       </c>
-      <c r="N63" s="69">
+      <c r="N63" s="58">
         <v>1570</v>
       </c>
-      <c r="O63" s="69">
+      <c r="O63" s="58">
         <v>1478</v>
       </c>
-      <c r="P63" s="69">
+      <c r="P63" s="58">
         <v>1004.4</v>
       </c>
-      <c r="Q63" s="69">
+      <c r="Q63" s="58">
         <v>937.4</v>
       </c>
-      <c r="R63" s="69">
+      <c r="R63" s="58">
         <v>1569.7</v>
       </c>
-      <c r="S63" s="69">
+      <c r="S63" s="58">
         <v>1410.6</v>
       </c>
-      <c r="T63" s="69">
+      <c r="T63" s="58">
         <v>1569.7</v>
       </c>
-      <c r="U63" s="69">
+      <c r="U63" s="58">
         <v>1410.6</v>
       </c>
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A64" s="72" t="s">
+      <c r="A64" s="61" t="s">
         <v>890</v>
       </c>
-      <c r="B64" s="71">
+      <c r="B64" s="60">
         <v>59</v>
       </c>
-      <c r="C64" s="71">
+      <c r="C64" s="60">
         <v>59</v>
       </c>
-      <c r="D64" s="71">
+      <c r="D64" s="60">
         <v>7.7</v>
       </c>
-      <c r="E64" s="71">
+      <c r="E64" s="60">
         <v>7.7</v>
       </c>
-      <c r="F64" s="71">
-        <v>0</v>
-      </c>
-      <c r="G64" s="71">
-        <v>0</v>
-      </c>
-      <c r="H64" s="71">
+      <c r="F64" s="60">
+        <v>0</v>
+      </c>
+      <c r="G64" s="60">
+        <v>0</v>
+      </c>
+      <c r="H64" s="60">
         <v>476.2</v>
       </c>
-      <c r="I64" s="71">
+      <c r="I64" s="60">
         <v>476.3</v>
       </c>
-      <c r="J64" s="71">
+      <c r="J64" s="60">
         <v>7</v>
       </c>
-      <c r="K64" s="71">
+      <c r="K64" s="60">
         <v>7</v>
       </c>
-      <c r="L64" s="71">
-        <v>0</v>
-      </c>
-      <c r="M64" s="71">
-        <v>0</v>
-      </c>
-      <c r="N64" s="71">
+      <c r="L64" s="60">
+        <v>0</v>
+      </c>
+      <c r="M64" s="60">
+        <v>0</v>
+      </c>
+      <c r="N64" s="60">
         <v>549.9</v>
       </c>
-      <c r="O64" s="71">
+      <c r="O64" s="60">
         <v>550</v>
       </c>
-      <c r="P64" s="71">
+      <c r="P64" s="60">
         <v>23</v>
       </c>
-      <c r="Q64" s="71">
+      <c r="Q64" s="60">
         <v>19.2</v>
       </c>
-      <c r="R64" s="71">
+      <c r="R64" s="60">
         <v>30.7</v>
       </c>
-      <c r="S64" s="71">
+      <c r="S64" s="60">
         <v>26.9</v>
       </c>
-      <c r="T64" s="71">
+      <c r="T64" s="60">
         <v>30.7</v>
       </c>
-      <c r="U64" s="71">
+      <c r="U64" s="60">
         <v>26.9</v>
       </c>
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A65" s="72" t="s">
+      <c r="A65" s="61" t="s">
         <v>889</v>
       </c>
-      <c r="B65" s="71">
+      <c r="B65" s="60">
         <v>233.2</v>
       </c>
-      <c r="C65" s="71">
+      <c r="C65" s="60">
         <v>233.2</v>
       </c>
-      <c r="D65" s="71">
+      <c r="D65" s="60">
         <v>557.6</v>
       </c>
-      <c r="E65" s="71">
+      <c r="E65" s="60">
         <v>465.5</v>
       </c>
-      <c r="F65" s="71">
-        <v>0</v>
-      </c>
-      <c r="G65" s="71">
-        <v>0</v>
-      </c>
-      <c r="H65" s="71">
+      <c r="F65" s="60">
+        <v>0</v>
+      </c>
+      <c r="G65" s="60">
+        <v>0</v>
+      </c>
+      <c r="H65" s="60">
         <v>32.4</v>
       </c>
-      <c r="I65" s="71">
+      <c r="I65" s="60">
         <v>32.4</v>
       </c>
-      <c r="J65" s="71">
+      <c r="J65" s="60">
         <v>153.9</v>
       </c>
-      <c r="K65" s="71">
+      <c r="K65" s="60">
         <v>153.9</v>
       </c>
-      <c r="L65" s="71">
+      <c r="L65" s="60">
         <v>43</v>
       </c>
-      <c r="M65" s="71">
+      <c r="M65" s="60">
         <v>43</v>
       </c>
-      <c r="N65" s="71">
+      <c r="N65" s="60">
         <v>1020.1</v>
       </c>
-      <c r="O65" s="71">
+      <c r="O65" s="60">
         <v>928</v>
       </c>
-      <c r="P65" s="71">
+      <c r="P65" s="60">
         <v>981.3</v>
       </c>
-      <c r="Q65" s="71">
+      <c r="Q65" s="60">
         <v>918.1</v>
       </c>
-      <c r="R65" s="71">
+      <c r="R65" s="60">
         <v>1538.9</v>
       </c>
-      <c r="S65" s="71">
+      <c r="S65" s="60">
         <v>1383.6</v>
       </c>
-      <c r="T65" s="71">
+      <c r="T65" s="60">
         <v>1538.9</v>
       </c>
-      <c r="U65" s="71">
+      <c r="U65" s="60">
         <v>1383.6</v>
       </c>
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A66" s="70" t="s">
+      <c r="A66" s="59" t="s">
         <v>888</v>
       </c>
-      <c r="B66" s="69">
+      <c r="B66" s="58">
         <v>158270.9</v>
       </c>
-      <c r="C66" s="69">
+      <c r="C66" s="58">
         <v>152097.29999999999</v>
       </c>
-      <c r="D66" s="69">
+      <c r="D66" s="58">
         <v>149798.5</v>
       </c>
-      <c r="E66" s="69">
+      <c r="E66" s="58">
         <v>122060.1</v>
       </c>
-      <c r="F66" s="69">
+      <c r="F66" s="58">
         <v>1392</v>
       </c>
-      <c r="G66" s="69">
+      <c r="G66" s="58">
         <v>1392</v>
       </c>
-      <c r="H66" s="69">
+      <c r="H66" s="58">
         <v>79892.7</v>
       </c>
-      <c r="I66" s="69">
+      <c r="I66" s="58">
         <v>79896.899999999994</v>
       </c>
-      <c r="J66" s="69">
+      <c r="J66" s="58">
         <v>11260.3</v>
       </c>
-      <c r="K66" s="69">
+      <c r="K66" s="58">
         <v>11411.8</v>
       </c>
-      <c r="L66" s="69">
+      <c r="L66" s="58">
         <v>2695.5</v>
       </c>
-      <c r="M66" s="69">
+      <c r="M66" s="58">
         <v>2695.5</v>
       </c>
-      <c r="N66" s="69">
+      <c r="N66" s="58">
         <v>403309.9</v>
       </c>
-      <c r="O66" s="69">
+      <c r="O66" s="58">
         <v>369553.6</v>
       </c>
-      <c r="P66" s="69">
+      <c r="P66" s="58">
         <v>59505.5</v>
       </c>
-      <c r="Q66" s="69">
+      <c r="Q66" s="58">
         <v>53228.1</v>
       </c>
-      <c r="R66" s="69">
+      <c r="R66" s="58">
         <v>209304</v>
       </c>
-      <c r="S66" s="69">
+      <c r="S66" s="58">
         <v>175288.2</v>
       </c>
-      <c r="T66" s="69">
+      <c r="T66" s="58">
         <v>210696</v>
       </c>
-      <c r="U66" s="69">
+      <c r="U66" s="58">
         <v>176680.2</v>
       </c>
     </row>
     <row r="67" spans="1:21" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="68" t="s">
+      <c r="A67" s="66" t="s">
         <v>887</v>
       </c>
-      <c r="B67" s="68"/>
-      <c r="C67" s="68"/>
-      <c r="D67" s="68"/>
-      <c r="E67" s="68"/>
-      <c r="F67" s="68"/>
-      <c r="G67" s="68"/>
-      <c r="H67" s="68"/>
-      <c r="I67" s="68"/>
-      <c r="J67" s="68"/>
-      <c r="K67" s="68"/>
-      <c r="L67" s="68"/>
-      <c r="M67" s="68"/>
-      <c r="N67" s="68"/>
-      <c r="O67" s="68"/>
-      <c r="P67" s="68"/>
-      <c r="Q67" s="68"/>
-      <c r="R67" s="68"/>
-      <c r="S67" s="68"/>
-      <c r="T67" s="68"/>
-      <c r="U67" s="68"/>
+      <c r="B67" s="66"/>
+      <c r="C67" s="66"/>
+      <c r="D67" s="66"/>
+      <c r="E67" s="66"/>
+      <c r="F67" s="66"/>
+      <c r="G67" s="66"/>
+      <c r="H67" s="66"/>
+      <c r="I67" s="66"/>
+      <c r="J67" s="66"/>
+      <c r="K67" s="66"/>
+      <c r="L67" s="66"/>
+      <c r="M67" s="66"/>
+      <c r="N67" s="66"/>
+      <c r="O67" s="66"/>
+      <c r="P67" s="66"/>
+      <c r="Q67" s="66"/>
+      <c r="R67" s="66"/>
+      <c r="S67" s="66"/>
+      <c r="T67" s="66"/>
+      <c r="U67" s="66"/>
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="N3:O3"/>
-    <mergeCell ref="P3:Q3"/>
-    <mergeCell ref="R3:S3"/>
-    <mergeCell ref="T3:U3"/>
-    <mergeCell ref="A67:U67"/>
     <mergeCell ref="A1:U1"/>
     <mergeCell ref="B2:O2"/>
     <mergeCell ref="P2:Q2"/>
@@ -35054,6 +35827,11 @@
     <mergeCell ref="H3:I3"/>
     <mergeCell ref="J3:K3"/>
     <mergeCell ref="L3:M3"/>
+    <mergeCell ref="N3:O3"/>
+    <mergeCell ref="P3:Q3"/>
+    <mergeCell ref="R3:S3"/>
+    <mergeCell ref="T3:U3"/>
+    <mergeCell ref="A67:U67"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup scale="37" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -47750,43 +48528,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="78" t="s">
         <v>369</v>
       </c>
-      <c r="B1" s="62"/>
+      <c r="B1" s="75"/>
     </row>
     <row r="2" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="61" t="s">
+      <c r="A2" s="74" t="s">
         <v>370</v>
       </c>
-      <c r="B2" s="62"/>
-      <c r="C2" s="62"/>
-      <c r="D2" s="62"/>
-      <c r="E2" s="62"/>
-      <c r="F2" s="62"/>
-      <c r="G2" s="62"/>
+      <c r="B2" s="75"/>
+      <c r="C2" s="75"/>
+      <c r="D2" s="75"/>
+      <c r="E2" s="75"/>
+      <c r="F2" s="75"/>
+      <c r="G2" s="75"/>
     </row>
     <row r="3" spans="1:7" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="17"/>
-      <c r="B3" s="56" t="s">
+      <c r="B3" s="69" t="s">
         <v>371</v>
       </c>
-      <c r="C3" s="57"/>
-      <c r="D3" s="57"/>
-      <c r="E3" s="57"/>
-      <c r="F3" s="57"/>
-      <c r="G3" s="57"/>
+      <c r="C3" s="70"/>
+      <c r="D3" s="70"/>
+      <c r="E3" s="70"/>
+      <c r="F3" s="70"/>
+      <c r="G3" s="70"/>
     </row>
     <row r="4" spans="1:7" ht="23.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A4" s="17"/>
       <c r="B4" s="19"/>
-      <c r="C4" s="58" t="s">
+      <c r="C4" s="71" t="s">
         <v>372</v>
       </c>
-      <c r="D4" s="59"/>
-      <c r="E4" s="59"/>
-      <c r="F4" s="59"/>
-      <c r="G4" s="60"/>
+      <c r="D4" s="72"/>
+      <c r="E4" s="72"/>
+      <c r="F4" s="72"/>
+      <c r="G4" s="73"/>
     </row>
     <row r="5" spans="1:7" ht="46.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="20"/>
@@ -52307,15 +53085,15 @@
       <c r="G220" s="25"/>
     </row>
     <row r="221" spans="1:7" s="6" customFormat="1" ht="206.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A221" s="63" t="s">
+      <c r="A221" s="76" t="s">
         <v>523</v>
       </c>
-      <c r="B221" s="64"/>
-      <c r="C221" s="64"/>
-      <c r="D221" s="64"/>
-      <c r="E221" s="64"/>
-      <c r="F221" s="64"/>
-      <c r="G221" s="64"/>
+      <c r="B221" s="77"/>
+      <c r="C221" s="77"/>
+      <c r="D221" s="77"/>
+      <c r="E221" s="77"/>
+      <c r="F221" s="77"/>
+      <c r="G221" s="77"/>
     </row>
     <row r="222" spans="1:7" s="6" customFormat="1" x14ac:dyDescent="0.25"/>
   </sheetData>

--- a/InputData/bldgs/BDESC/BAU Distribued Electricity Source Capacities.xlsx
+++ b/InputData/bldgs/BDESC/BAU Distribued Electricity Source Capacities.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DanOBrien\Models\EPS\US\eps-us\InputData\bldgs\BDESC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{804AE395-CB52-412A-8281-449A450ABD1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E568A12B-05DA-4807-A2BF-B044209A26FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -81,7 +81,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2046" uniqueCount="996">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2050" uniqueCount="999">
   <si>
     <t>BDESC BAU Distributed Electricity Source Capacity</t>
   </si>
@@ -3038,55 +3038,75 @@
     <t>Behind-the-meter Data Center Gas Plants</t>
   </si>
   <si>
-    <t>Cleanview</t>
-  </si>
-  <si>
-    <t>Bypassing the Grid: How Data Center Developers Are Building Their Own Power Plants</t>
-  </si>
-  <si>
-    <t>https://cleanview.co/reports/behind-the-meter-data-centers</t>
-  </si>
-  <si>
-    <t>Cleanview's 2026 data finds 90 GW of announced capacity planned for behind-the-meter</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gas capacity, with 82 GW of that announced since Q1 2025. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">"Of the roughly 90 GW of generation capacity we've identified across all projects, only </t>
-  </si>
-  <si>
-    <t xml:space="preserve">about 2 GW is actually operating today—2.5% of the total. 1.2% is under construction. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Another 36% has been permitted, and the remaining 60% exists only as announcements </t>
-  </si>
-  <si>
-    <t>or early-stage plans.</t>
-  </si>
-  <si>
-    <t>GW total</t>
-  </si>
-  <si>
-    <t>permitted</t>
-  </si>
-  <si>
-    <t>online</t>
-  </si>
-  <si>
-    <t>under construction</t>
-  </si>
-  <si>
-    <t>announced</t>
-  </si>
-  <si>
-    <t>We add the under-construction and permitted capacity to AEO forecasts, assuming that</t>
-  </si>
-  <si>
-    <t>all will come online by 2030 to meet the first wave of AI data center buildout in the U.S.</t>
-  </si>
-  <si>
-    <t>new capacity</t>
+    <r>
+      <t>Table 3.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13.5"/>
+        <color rgb="FF161400"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t> Overall Behind-the-Meter Effective Capacity Growth by Region Out to 2030 (GW)</t>
+    </r>
+  </si>
+  <si>
+    <t>Actual</t>
+  </si>
+  <si>
+    <t>Forecast</t>
+  </si>
+  <si>
+    <t>ISO regions</t>
+  </si>
+  <si>
+    <t>CAISO</t>
+  </si>
+  <si>
+    <t>ERCOT</t>
+  </si>
+  <si>
+    <t>NE-ISO</t>
+  </si>
+  <si>
+    <t>MISO</t>
+  </si>
+  <si>
+    <t>NY-ISO</t>
+  </si>
+  <si>
+    <t>PJM</t>
+  </si>
+  <si>
+    <t>SPP</t>
+  </si>
+  <si>
+    <t>Non-ISO regions</t>
+  </si>
+  <si>
+    <t>Annual incremental</t>
+  </si>
+  <si>
+    <t>—</t>
+  </si>
+  <si>
+    <t>RAND has estimated the behind the meter capacity to support data centers through 2030.</t>
+  </si>
+  <si>
+    <t>We assume 100% of this gas.</t>
+  </si>
+  <si>
+    <t>We add this forecasted capacity to AEO forecasts, which isn't capturing this trend</t>
+  </si>
+  <si>
+    <t>RAND</t>
+  </si>
+  <si>
+    <t>https://www.rand.org/pubs/research_briefs/RBA3845-1.html</t>
+  </si>
+  <si>
+    <t>How Much More Power Can the U.S. Grid Provide for AI?</t>
   </si>
 </sst>
 </file>
@@ -3102,7 +3122,7 @@
     <numFmt numFmtId="168" formatCode="0.00000000000"/>
     <numFmt numFmtId="169" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="26" x14ac:knownFonts="1">
+  <fonts count="30" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3287,6 +3307,32 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="13.5"/>
+      <color rgb="FF161400"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13.5"/>
+      <color rgb="FF2D2B19"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF2D2B19"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF2D2B19"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="20">
     <fill>
@@ -3403,7 +3449,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="16">
+  <borders count="24">
     <border>
       <left/>
       <right/>
@@ -3580,6 +3626,94 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color rgb="FF2D2B19"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FFD0D0CC"/>
+      </right>
+      <top/>
+      <bottom style="thick">
+        <color rgb="FF2D2B19"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FFD0D0CC"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FFD0D0CC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FFD0D0CC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFD0D0CC"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color rgb="FF2D2B19"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thick">
+        <color rgb="FF2D2B19"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFD0D0CC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FFD0D0CC"/>
+      </right>
+      <top style="thick">
+        <color rgb="FF2D2B19"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFD0D0CC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFD0D0CC"/>
+      </left>
+      <right/>
+      <top style="thick">
+        <color rgb="FF2D2B19"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFD0D0CC"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -3615,7 +3749,7 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="83">
+  <cellXfs count="96">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -3744,11 +3878,27 @@
     <xf numFmtId="0" fontId="24" fillId="18" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="28" fillId="16" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="16" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="16" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="16" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="16" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="16" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -3756,7 +3906,13 @@
     <xf numFmtId="0" fontId="25" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="24" fillId="18" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="7" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3779,10 +3935,33 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="28" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="16" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="16" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="16" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="16" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="16" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="16" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="16" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="16" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="20">
     <cellStyle name="60% - Accent1 2" xfId="12" xr:uid="{00000000-0005-0000-0000-00002E000000}"/>
@@ -11710,7 +11889,7 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
-        <v>979</v>
+        <v>996</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -11720,12 +11899,12 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
-        <v>980</v>
+        <v>998</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B24" s="18" t="s">
-        <v>981</v>
+        <v>997</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -23435,689 +23614,774 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{858104B2-5734-4794-B2D1-CAE7717AD060}">
-  <dimension ref="B2:AB26"/>
+  <dimension ref="B2:AC27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B2" s="79" t="s">
+    <row r="2" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B2" t="s">
+        <v>993</v>
+      </c>
+    </row>
+    <row r="3" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B3" t="s">
+        <v>994</v>
+      </c>
+    </row>
+    <row r="5" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B5" t="s">
+        <v>995</v>
+      </c>
+    </row>
+    <row r="7" spans="2:9" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="B7" s="65" t="s">
+        <v>979</v>
+      </c>
+    </row>
+    <row r="9" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="87"/>
+      <c r="C9" s="89" t="s">
+        <v>980</v>
+      </c>
+      <c r="D9" s="89"/>
+      <c r="E9" s="90"/>
+      <c r="F9" s="91" t="s">
+        <v>981</v>
+      </c>
+      <c r="G9" s="89"/>
+      <c r="H9" s="89"/>
+      <c r="I9" s="89"/>
+    </row>
+    <row r="10" spans="2:9" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B10" s="88"/>
+      <c r="C10" s="66">
+        <v>2024</v>
+      </c>
+      <c r="D10" s="66">
+        <v>2025</v>
+      </c>
+      <c r="E10" s="67">
+        <v>2026</v>
+      </c>
+      <c r="F10" s="66">
+        <v>2027</v>
+      </c>
+      <c r="G10" s="66">
+        <v>2028</v>
+      </c>
+      <c r="H10" s="66">
+        <v>2029</v>
+      </c>
+      <c r="I10" s="66">
+        <v>2030</v>
+      </c>
+    </row>
+    <row r="11" spans="2:9" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B11" s="92" t="s">
         <v>982</v>
       </c>
-    </row>
-    <row r="3" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B3" t="s">
+      <c r="C11" s="92"/>
+      <c r="D11" s="92"/>
+      <c r="E11" s="93"/>
+      <c r="F11" s="94"/>
+      <c r="G11" s="95"/>
+      <c r="H11" s="95"/>
+      <c r="I11" s="95"/>
+    </row>
+    <row r="12" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B12" s="68" t="s">
         <v>983</v>
       </c>
-    </row>
-    <row r="5" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B5" t="s">
+      <c r="C12" s="69">
+        <v>3</v>
+      </c>
+      <c r="D12" s="69">
+        <v>3.1</v>
+      </c>
+      <c r="E12" s="70">
+        <v>3.2</v>
+      </c>
+      <c r="F12" s="69">
+        <v>3.3</v>
+      </c>
+      <c r="G12" s="69">
+        <v>3.4</v>
+      </c>
+      <c r="H12" s="69">
+        <v>3.5</v>
+      </c>
+      <c r="I12" s="69">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="13" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="68" t="s">
         <v>984</v>
       </c>
-    </row>
-    <row r="6" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B6" t="s">
+      <c r="C13" s="69">
+        <v>2</v>
+      </c>
+      <c r="D13" s="69">
+        <v>3.3</v>
+      </c>
+      <c r="E13" s="70">
+        <v>4.7</v>
+      </c>
+      <c r="F13" s="69">
+        <v>4.8</v>
+      </c>
+      <c r="G13" s="69">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="H13" s="69">
+        <v>6.9</v>
+      </c>
+      <c r="I13" s="69">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B14" s="68" t="s">
         <v>985</v>
       </c>
-    </row>
-    <row r="7" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B7" t="s">
+      <c r="C14" s="69">
+        <v>0.2</v>
+      </c>
+      <c r="D14" s="69">
+        <v>0.2</v>
+      </c>
+      <c r="E14" s="70">
+        <v>0.2</v>
+      </c>
+      <c r="F14" s="69">
+        <v>0.4</v>
+      </c>
+      <c r="G14" s="69">
+        <v>0.6</v>
+      </c>
+      <c r="H14" s="69">
+        <v>0.8</v>
+      </c>
+      <c r="I14" s="69">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B15" s="68" t="s">
         <v>986</v>
       </c>
-    </row>
-    <row r="8" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B8" t="s">
+      <c r="C15" s="69">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="D15" s="69">
+        <v>2.5</v>
+      </c>
+      <c r="E15" s="70">
+        <v>2.9</v>
+      </c>
+      <c r="F15" s="69">
+        <v>3.9</v>
+      </c>
+      <c r="G15" s="69">
+        <v>5</v>
+      </c>
+      <c r="H15" s="69">
+        <v>8.1</v>
+      </c>
+      <c r="I15" s="69">
+        <v>11.2</v>
+      </c>
+    </row>
+    <row r="16" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B16" s="68" t="s">
         <v>987</v>
       </c>
-    </row>
-    <row r="10" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B10">
-        <v>90</v>
-      </c>
-      <c r="C10" t="s">
+      <c r="C16" s="69">
+        <v>0.8</v>
+      </c>
+      <c r="D16" s="69">
+        <v>1.6</v>
+      </c>
+      <c r="E16" s="70">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="F16" s="69">
+        <v>2.6</v>
+      </c>
+      <c r="G16" s="69">
+        <v>2.8</v>
+      </c>
+      <c r="H16" s="69">
+        <v>3</v>
+      </c>
+      <c r="I16" s="69">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="17" spans="2:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B17" s="68" t="s">
         <v>988</v>
       </c>
-    </row>
-    <row r="11" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B11" s="81">
-        <v>2.5000000000000001E-2</v>
-      </c>
-      <c r="C11" t="s">
+      <c r="C17" s="69">
+        <v>0.9</v>
+      </c>
+      <c r="D17" s="69">
+        <v>1.8</v>
+      </c>
+      <c r="E17" s="70">
+        <v>2.6</v>
+      </c>
+      <c r="F17" s="69">
+        <v>2.9</v>
+      </c>
+      <c r="G17" s="69">
+        <v>3.2</v>
+      </c>
+      <c r="H17" s="69">
+        <v>3.9</v>
+      </c>
+      <c r="I17" s="69">
+        <v>4.7</v>
+      </c>
+    </row>
+    <row r="18" spans="2:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B18" s="68" t="s">
+        <v>989</v>
+      </c>
+      <c r="C18" s="69">
+        <v>0.5</v>
+      </c>
+      <c r="D18" s="69">
+        <v>0.6</v>
+      </c>
+      <c r="E18" s="70">
+        <v>0.7</v>
+      </c>
+      <c r="F18" s="69">
+        <v>0.9</v>
+      </c>
+      <c r="G18" s="69">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="H18" s="69">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="I18" s="69">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="19" spans="2:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B19" s="68" t="s">
         <v>990</v>
       </c>
-    </row>
-    <row r="12" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B12" s="16">
-        <v>1.2E-2</v>
-      </c>
-      <c r="C12" t="s">
+      <c r="C19" s="69">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="D19" s="69">
+        <v>3.5</v>
+      </c>
+      <c r="E19" s="70">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="F19" s="69">
+        <v>6</v>
+      </c>
+      <c r="G19" s="69">
+        <v>7.3</v>
+      </c>
+      <c r="H19" s="69">
+        <v>9.6999999999999993</v>
+      </c>
+      <c r="I19" s="69">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="20" spans="2:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B20" s="68" t="s">
         <v>991</v>
       </c>
-    </row>
-    <row r="13" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B13" s="80">
-        <v>0.36</v>
-      </c>
-      <c r="C13" t="s">
-        <v>989</v>
-      </c>
-    </row>
-    <row r="14" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B14" s="80">
-        <v>0.6</v>
-      </c>
-      <c r="C14" t="s">
+      <c r="C20" s="69" t="s">
         <v>992</v>
       </c>
-    </row>
-    <row r="16" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B16" t="s">
-        <v>993</v>
-      </c>
-    </row>
-    <row r="17" spans="2:28" x14ac:dyDescent="0.25">
-      <c r="B17" t="s">
-        <v>994</v>
-      </c>
-    </row>
-    <row r="19" spans="2:28" x14ac:dyDescent="0.25">
-      <c r="C19">
+      <c r="D20" s="69">
+        <v>4.7</v>
+      </c>
+      <c r="E20" s="70">
+        <v>4.7</v>
+      </c>
+      <c r="F20" s="69">
+        <v>3.5</v>
+      </c>
+      <c r="G20" s="69">
+        <v>3.5</v>
+      </c>
+      <c r="H20" s="69">
+        <v>10</v>
+      </c>
+      <c r="I20" s="69">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="21" spans="2:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B21" s="71" t="s">
+        <v>37</v>
+      </c>
+      <c r="C21" s="69">
+        <v>12</v>
+      </c>
+      <c r="D21" s="69">
+        <v>17</v>
+      </c>
+      <c r="E21" s="70">
+        <v>21</v>
+      </c>
+      <c r="F21" s="69">
+        <v>25</v>
+      </c>
+      <c r="G21" s="69">
+        <v>29</v>
+      </c>
+      <c r="H21" s="69">
+        <v>39</v>
+      </c>
+      <c r="I21" s="69">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="24" spans="2:29" x14ac:dyDescent="0.25">
+      <c r="C24">
+        <v>2024</v>
+      </c>
+      <c r="D24">
         <v>2025</v>
       </c>
-      <c r="D19">
+      <c r="E24">
         <v>2026</v>
       </c>
-      <c r="E19">
+      <c r="F24">
         <v>2027</v>
       </c>
-      <c r="F19">
+      <c r="G24">
         <v>2028</v>
       </c>
-      <c r="G19">
+      <c r="H24">
         <v>2029</v>
       </c>
-      <c r="H19">
+      <c r="I24">
         <v>2030</v>
       </c>
-      <c r="I19">
+      <c r="J24">
         <v>2031</v>
       </c>
-      <c r="J19">
+      <c r="K24">
         <v>2032</v>
       </c>
-      <c r="K19">
+      <c r="L24">
         <v>2033</v>
       </c>
-      <c r="L19">
+      <c r="M24">
         <v>2034</v>
       </c>
-      <c r="M19">
+      <c r="N24">
         <v>2035</v>
       </c>
-      <c r="N19">
+      <c r="O24">
         <v>2036</v>
       </c>
-      <c r="O19">
+      <c r="P24">
         <v>2037</v>
       </c>
-      <c r="P19">
+      <c r="Q24">
         <v>2038</v>
       </c>
-      <c r="Q19">
+      <c r="R24">
         <v>2039</v>
       </c>
-      <c r="R19">
+      <c r="S24">
         <v>2040</v>
       </c>
-      <c r="S19">
+      <c r="T24">
         <v>2041</v>
       </c>
-      <c r="T19">
+      <c r="U24">
         <v>2042</v>
       </c>
-      <c r="U19">
+      <c r="V24">
         <v>2043</v>
       </c>
-      <c r="V19">
+      <c r="W24">
         <v>2044</v>
       </c>
-      <c r="W19">
+      <c r="X24">
         <v>2045</v>
       </c>
-      <c r="X19">
+      <c r="Y24">
         <v>2046</v>
       </c>
-      <c r="Y19">
+      <c r="Z24">
         <v>2047</v>
       </c>
-      <c r="Z19">
+      <c r="AA24">
         <v>2048</v>
       </c>
-      <c r="AA19">
+      <c r="AB24">
         <v>2049</v>
       </c>
-      <c r="AB19">
+      <c r="AC24">
         <v>2050</v>
       </c>
     </row>
-    <row r="20" spans="2:28" x14ac:dyDescent="0.25">
-      <c r="B20" t="s">
-        <v>995</v>
-      </c>
-      <c r="C20">
-        <v>0</v>
-      </c>
-      <c r="D20">
-        <f>$B$10*$B$13/5+C20</f>
-        <v>6.4799999999999995</v>
-      </c>
-      <c r="E20">
-        <f>$B$10*$B$13/5+D20</f>
-        <v>12.959999999999999</v>
-      </c>
-      <c r="F20">
-        <f t="shared" ref="F20:H20" si="0">$B$10*$B$13/5+E20</f>
-        <v>19.439999999999998</v>
-      </c>
-      <c r="G20">
-        <f t="shared" si="0"/>
-        <v>25.919999999999998</v>
-      </c>
-      <c r="H20">
-        <f t="shared" si="0"/>
-        <v>32.4</v>
-      </c>
-      <c r="I20">
-        <f>H20</f>
-        <v>32.4</v>
-      </c>
-      <c r="J20">
-        <f t="shared" ref="J20:AB20" si="1">I20</f>
-        <v>32.4</v>
-      </c>
-      <c r="K20">
-        <f t="shared" si="1"/>
-        <v>32.4</v>
-      </c>
-      <c r="L20">
-        <f t="shared" si="1"/>
-        <v>32.4</v>
-      </c>
-      <c r="M20">
-        <f t="shared" si="1"/>
-        <v>32.4</v>
-      </c>
-      <c r="N20">
-        <f t="shared" si="1"/>
-        <v>32.4</v>
-      </c>
-      <c r="O20">
-        <f t="shared" si="1"/>
-        <v>32.4</v>
-      </c>
-      <c r="P20">
-        <f t="shared" si="1"/>
-        <v>32.4</v>
-      </c>
-      <c r="Q20">
-        <f t="shared" si="1"/>
-        <v>32.4</v>
-      </c>
-      <c r="R20">
-        <f t="shared" si="1"/>
-        <v>32.4</v>
-      </c>
-      <c r="S20">
-        <f t="shared" si="1"/>
-        <v>32.4</v>
-      </c>
-      <c r="T20">
-        <f t="shared" si="1"/>
-        <v>32.4</v>
-      </c>
-      <c r="U20">
-        <f t="shared" si="1"/>
-        <v>32.4</v>
-      </c>
-      <c r="V20">
-        <f t="shared" si="1"/>
-        <v>32.4</v>
-      </c>
-      <c r="W20">
-        <f t="shared" si="1"/>
-        <v>32.4</v>
-      </c>
-      <c r="X20">
-        <f t="shared" si="1"/>
-        <v>32.4</v>
-      </c>
-      <c r="Y20">
-        <f t="shared" si="1"/>
-        <v>32.4</v>
-      </c>
-      <c r="Z20">
-        <f t="shared" si="1"/>
-        <v>32.4</v>
-      </c>
-      <c r="AA20">
-        <f t="shared" si="1"/>
-        <v>32.4</v>
-      </c>
-      <c r="AB20">
-        <f t="shared" si="1"/>
-        <v>32.4</v>
-      </c>
-    </row>
-    <row r="23" spans="2:28" x14ac:dyDescent="0.25">
-      <c r="C23">
-        <v>2025</v>
-      </c>
-      <c r="D23">
-        <v>2026</v>
-      </c>
-      <c r="E23">
-        <v>2027</v>
-      </c>
-      <c r="F23">
-        <v>2028</v>
-      </c>
-      <c r="G23">
-        <v>2029</v>
-      </c>
-      <c r="H23">
-        <v>2030</v>
-      </c>
-      <c r="I23">
-        <v>2031</v>
-      </c>
-      <c r="J23">
-        <v>2032</v>
-      </c>
-      <c r="K23">
-        <v>2033</v>
-      </c>
-      <c r="L23">
-        <v>2034</v>
-      </c>
-      <c r="M23">
-        <v>2035</v>
-      </c>
-      <c r="N23">
-        <v>2036</v>
-      </c>
-      <c r="O23">
-        <v>2037</v>
-      </c>
-      <c r="P23">
-        <v>2038</v>
-      </c>
-      <c r="Q23">
-        <v>2039</v>
-      </c>
-      <c r="R23">
-        <v>2040</v>
-      </c>
-      <c r="S23">
-        <v>2041</v>
-      </c>
-      <c r="T23">
-        <v>2042</v>
-      </c>
-      <c r="U23">
-        <v>2043</v>
-      </c>
-      <c r="V23">
-        <v>2044</v>
-      </c>
-      <c r="W23">
-        <v>2045</v>
-      </c>
-      <c r="X23">
-        <v>2046</v>
-      </c>
-      <c r="Y23">
-        <v>2047</v>
-      </c>
-      <c r="Z23">
-        <v>2048</v>
-      </c>
-      <c r="AA23">
-        <v>2049</v>
-      </c>
-      <c r="AB23">
-        <v>2050</v>
-      </c>
-    </row>
-    <row r="24" spans="2:28" x14ac:dyDescent="0.25">
-      <c r="B24" s="1" t="s">
+    <row r="25" spans="2:29" x14ac:dyDescent="0.25">
+      <c r="B25" s="1" t="s">
         <v>548</v>
       </c>
-      <c r="C24">
+      <c r="C25">
+        <f>Calculations!D44</f>
+        <v>1.4025661782562939</v>
+      </c>
+      <c r="D25">
         <f>Calculations!E44</f>
         <v>0.41060633044604544</v>
       </c>
-      <c r="D24">
+      <c r="E25">
         <f>Calculations!F44</f>
         <v>0.89845543592649557</v>
       </c>
-      <c r="E24">
+      <c r="F25">
         <f>Calculations!G44</f>
         <v>1.3732952319274669</v>
       </c>
-      <c r="F24">
+      <c r="G25">
         <f>Calculations!H44</f>
         <v>1.3838652958795432</v>
       </c>
-      <c r="G24">
+      <c r="H25">
         <f>Calculations!I44</f>
         <v>1.3944353598316197</v>
       </c>
-      <c r="H24">
+      <c r="I25">
         <f>Calculations!J44</f>
         <v>2.0562839796000971</v>
       </c>
-      <c r="I24">
+      <c r="J25">
         <f>Calculations!K44</f>
         <v>2.9401039423621791</v>
       </c>
-      <c r="J24">
+      <c r="K25">
         <f>Calculations!L44</f>
         <v>3.8515686877681534</v>
       </c>
-      <c r="K24">
+      <c r="L25">
         <f>Calculations!M44</f>
         <v>4.5605760543997409</v>
       </c>
-      <c r="L24">
+      <c r="M25">
         <f>Calculations!N44</f>
         <v>5.449274508216627</v>
       </c>
-      <c r="M24">
+      <c r="N25">
         <f>Calculations!O44</f>
         <v>5.459844572168703</v>
       </c>
-      <c r="N24">
+      <c r="O25">
         <f>Calculations!P44</f>
         <v>5.4704146361207799</v>
       </c>
-      <c r="O24">
+      <c r="P25">
         <f>Calculations!Q44</f>
         <v>5.480984700072856</v>
       </c>
-      <c r="P24">
+      <c r="Q25">
         <f>Calculations!R44</f>
         <v>5.4915547640249329</v>
       </c>
-      <c r="Q24">
+      <c r="R25">
         <f>Calculations!S44</f>
         <v>5.5029379098194759</v>
       </c>
-      <c r="R24">
+      <c r="S25">
         <f>Calculations!T44</f>
         <v>5.5143210556140208</v>
       </c>
-      <c r="S24">
+      <c r="T25">
         <f>Calculations!U44</f>
         <v>5.5273303650934995</v>
       </c>
-      <c r="T24">
+      <c r="U25">
         <f>Calculations!V44</f>
         <v>5.5444050837853149</v>
       </c>
-      <c r="U24">
+      <c r="V25">
         <f>Calculations!W44</f>
         <v>5.5679844572168697</v>
       </c>
-      <c r="V24">
+      <c r="W25">
         <f>Calculations!X44</f>
         <v>5.6053862219703712</v>
       </c>
-      <c r="W24">
+      <c r="X25">
         <f>Calculations!Y44</f>
         <v>5.6696196875252971</v>
       </c>
-      <c r="X24">
+      <c r="Y25">
         <f>Calculations!Z44</f>
         <v>5.7818249817858005</v>
       </c>
-      <c r="Y24">
+      <c r="Z25">
         <f>Calculations!AA44</f>
         <v>5.8940302760463048</v>
       </c>
-      <c r="Z24">
+      <c r="AA25">
         <f>Calculations!AB44</f>
         <v>6.0070486521492752</v>
       </c>
-      <c r="AA24">
+      <c r="AB25">
         <f>Calculations!AC44</f>
         <v>6.1208801100947134</v>
       </c>
-      <c r="AB24">
+      <c r="AC25">
         <f>Calculations!AD44</f>
         <v>6.2355246498826196</v>
       </c>
     </row>
-    <row r="25" spans="2:28" x14ac:dyDescent="0.25">
-      <c r="B25" s="1" t="s">
+    <row r="26" spans="2:29" x14ac:dyDescent="0.25">
+      <c r="B26" s="1" t="s">
         <v>553</v>
       </c>
-      <c r="C25">
+      <c r="C26">
+        <f>Calculations!D63</f>
+        <v>0.32243382174370594</v>
+      </c>
+      <c r="D26">
         <f>Calculations!E63</f>
         <v>9.4393669553954507E-2</v>
       </c>
-      <c r="D25">
+      <c r="E26">
         <f>Calculations!F63</f>
         <v>0.20654456407350441</v>
       </c>
-      <c r="E25">
+      <c r="F26">
         <f>Calculations!G63</f>
         <v>0.31570476807253295</v>
       </c>
-      <c r="F25">
+      <c r="G26">
         <f>Calculations!H63</f>
         <v>0.31813470412045658</v>
       </c>
-      <c r="G25">
+      <c r="H26">
         <f>Calculations!I63</f>
         <v>0.32056464016838015</v>
       </c>
-      <c r="H25">
+      <c r="I26">
         <f>Calculations!J63</f>
         <v>0.47271602039990285</v>
       </c>
-      <c r="I25">
+      <c r="J26">
         <f>Calculations!K63</f>
         <v>0.67589605763782079</v>
       </c>
-      <c r="J25">
+      <c r="K26">
         <f>Calculations!L63</f>
         <v>0.88543131223184646</v>
       </c>
-      <c r="K25">
+      <c r="L26">
         <f>Calculations!M63</f>
         <v>1.0484239456002591</v>
       </c>
-      <c r="L25">
+      <c r="M26">
         <f>Calculations!N63</f>
         <v>1.2527254917833723</v>
       </c>
-      <c r="M25">
+      <c r="N26">
         <f>Calculations!O63</f>
         <v>1.255155427831296</v>
       </c>
-      <c r="N25">
+      <c r="O26">
         <f>Calculations!P63</f>
         <v>1.2575853638792196</v>
       </c>
-      <c r="O25">
+      <c r="P26">
         <f>Calculations!Q63</f>
         <v>1.2600152999271432</v>
       </c>
-      <c r="P25">
+      <c r="Q26">
         <f>Calculations!R63</f>
         <v>1.2624452359750666</v>
       </c>
-      <c r="Q25">
+      <c r="R26">
         <f>Calculations!S63</f>
         <v>1.265062090180523</v>
       </c>
-      <c r="R25">
+      <c r="S26">
         <f>Calculations!T63</f>
         <v>1.2676789443859791</v>
       </c>
-      <c r="S25">
+      <c r="T26">
         <f>Calculations!U63</f>
         <v>1.2706696349065005</v>
       </c>
-      <c r="T25">
+      <c r="U26">
         <f>Calculations!V63</f>
         <v>1.2745949162146848</v>
       </c>
-      <c r="U25">
+      <c r="V26">
         <f>Calculations!W63</f>
         <v>1.2800155427831297</v>
       </c>
-      <c r="V25">
+      <c r="W26">
         <f>Calculations!X63</f>
         <v>1.2886137780296285</v>
       </c>
-      <c r="W25">
+      <c r="X26">
         <f>Calculations!Y63</f>
         <v>1.3033803124747023</v>
       </c>
-      <c r="X25">
+      <c r="Y26">
         <f>Calculations!Z63</f>
         <v>1.329175018214199</v>
       </c>
-      <c r="Y25">
+      <c r="Z26">
         <f>Calculations!AA63</f>
         <v>1.3549697239536955</v>
       </c>
-      <c r="Z25">
+      <c r="AA26">
         <f>Calculations!AB63</f>
         <v>1.3809513478507245</v>
       </c>
-      <c r="AA25">
+      <c r="AB26">
         <f>Calculations!AC63</f>
         <v>1.4071198899052861</v>
       </c>
-      <c r="AB25">
+      <c r="AC26">
         <f>Calculations!AD63</f>
         <v>1.4334753501173803</v>
       </c>
     </row>
-    <row r="26" spans="2:28" x14ac:dyDescent="0.25">
-      <c r="B26" s="1" t="s">
+    <row r="27" spans="2:29" x14ac:dyDescent="0.25">
+      <c r="B27" s="1" t="s">
         <v>555</v>
       </c>
-      <c r="C26">
-        <f>Calculations!E84</f>
-        <v>1508.008</v>
-      </c>
-      <c r="D26">
-        <f>Calculations!F84+D20*1000</f>
-        <v>8020.9689999999991</v>
-      </c>
-      <c r="E26">
-        <f>Calculations!G84+E20*1000</f>
-        <v>14519.124999999998</v>
-      </c>
-      <c r="F26">
-        <f>Calculations!H84+F20*1000</f>
-        <v>21016.868999999995</v>
-      </c>
-      <c r="G26">
-        <f>Calculations!I84+G20*1000</f>
-        <v>27515.394999999997</v>
-      </c>
-      <c r="H26">
-        <f>Calculations!J84+H20*1000</f>
-        <v>34015.290999999997</v>
-      </c>
-      <c r="I26">
-        <f>Calculations!K84+I20*1000</f>
-        <v>34034.760999999999</v>
-      </c>
-      <c r="J26">
-        <f>Calculations!L84+J20*1000</f>
-        <v>34055.343999999997</v>
-      </c>
-      <c r="K26">
-        <f>Calculations!M84+K20*1000</f>
-        <v>34076.552000000003</v>
-      </c>
-      <c r="L26">
-        <f>Calculations!N84+L20*1000</f>
-        <v>34100.095000000001</v>
-      </c>
-      <c r="M26">
-        <f>Calculations!O84+M20*1000</f>
-        <v>34122.014000000003</v>
-      </c>
-      <c r="N26">
-        <f>Calculations!P84+N20*1000</f>
-        <v>34144.811999999998</v>
-      </c>
-      <c r="O26">
-        <f>Calculations!Q84+O20*1000</f>
-        <v>34169.997000000003</v>
-      </c>
-      <c r="P26">
-        <f>Calculations!R84+P20*1000</f>
-        <v>34193.459000000003</v>
-      </c>
-      <c r="Q26">
-        <f>Calculations!S84+Q20*1000</f>
-        <v>34216.315999999999</v>
-      </c>
-      <c r="R26">
-        <f>Calculations!T84+R20*1000</f>
-        <v>34238.228000000003</v>
-      </c>
-      <c r="S26">
-        <f>Calculations!U84+S20*1000</f>
-        <v>34258.498999999996</v>
-      </c>
-      <c r="T26">
-        <f>Calculations!V84+T20*1000</f>
-        <v>34281.084999999999</v>
-      </c>
-      <c r="U26">
-        <f>Calculations!W84+U20*1000</f>
-        <v>34301.161999999997</v>
-      </c>
-      <c r="V26">
-        <f>Calculations!X84+V20*1000</f>
-        <v>34321.178</v>
-      </c>
-      <c r="W26">
-        <f>Calculations!Y84+W20*1000</f>
-        <v>34340.084000000003</v>
-      </c>
-      <c r="X26">
-        <f>Calculations!Z84+X20*1000</f>
-        <v>34359.432999999997</v>
-      </c>
-      <c r="Y26">
-        <f>Calculations!AA84+Y20*1000</f>
-        <v>34379.940999999999</v>
-      </c>
-      <c r="Z26">
-        <f>Calculations!AB84+Z20*1000</f>
-        <v>34400.097000000002</v>
-      </c>
-      <c r="AA26">
-        <f>Calculations!AC84+AA20*1000</f>
-        <v>34419.017999999996</v>
-      </c>
-      <c r="AB26">
-        <f>Calculations!AD84+AB20*1000</f>
-        <v>34439.06</v>
+      <c r="C27">
+        <f>Calculations!D84+C21*1000</f>
+        <v>13468.725</v>
+      </c>
+      <c r="D27">
+        <f>Calculations!E84+D21*1000</f>
+        <v>18508.008000000002</v>
+      </c>
+      <c r="E27">
+        <f>Calculations!F84+E21*1000</f>
+        <v>22540.969000000001</v>
+      </c>
+      <c r="F27">
+        <f>Calculations!G84+F21*1000</f>
+        <v>26559.125</v>
+      </c>
+      <c r="G27">
+        <f>Calculations!H84+G21*1000</f>
+        <v>30576.868999999999</v>
+      </c>
+      <c r="H27">
+        <f>Calculations!I84+H21*1000</f>
+        <v>40595.394999999997</v>
+      </c>
+      <c r="I27">
+        <f>Calculations!J84+I21*1000</f>
+        <v>50615.290999999997</v>
+      </c>
+      <c r="J27">
+        <f>Calculations!K84+$I$21*1000</f>
+        <v>50634.760999999999</v>
+      </c>
+      <c r="K27">
+        <f>Calculations!L84+$I$21*1000</f>
+        <v>50655.343999999997</v>
+      </c>
+      <c r="L27">
+        <f>Calculations!M84+$I$21*1000</f>
+        <v>50676.552000000003</v>
+      </c>
+      <c r="M27">
+        <f>Calculations!N84+$I$21*1000</f>
+        <v>50700.095000000001</v>
+      </c>
+      <c r="N27">
+        <f>Calculations!O84+$I$21*1000</f>
+        <v>50722.014000000003</v>
+      </c>
+      <c r="O27">
+        <f>Calculations!P84+$I$21*1000</f>
+        <v>50744.811999999998</v>
+      </c>
+      <c r="P27">
+        <f>Calculations!Q84+$I$21*1000</f>
+        <v>50769.997000000003</v>
+      </c>
+      <c r="Q27">
+        <f>Calculations!R84+$I$21*1000</f>
+        <v>50793.459000000003</v>
+      </c>
+      <c r="R27">
+        <f>Calculations!S84+$I$21*1000</f>
+        <v>50816.315999999999</v>
+      </c>
+      <c r="S27">
+        <f>Calculations!T84+$I$21*1000</f>
+        <v>50838.228000000003</v>
+      </c>
+      <c r="T27">
+        <f>Calculations!U84+$I$21*1000</f>
+        <v>50858.498999999996</v>
+      </c>
+      <c r="U27">
+        <f>Calculations!V84+$I$21*1000</f>
+        <v>50881.084999999999</v>
+      </c>
+      <c r="V27">
+        <f>Calculations!W84+$I$21*1000</f>
+        <v>50901.161999999997</v>
+      </c>
+      <c r="W27">
+        <f>Calculations!X84+$I$21*1000</f>
+        <v>50921.178</v>
+      </c>
+      <c r="X27">
+        <f>Calculations!Y84+$I$21*1000</f>
+        <v>50940.084000000003</v>
+      </c>
+      <c r="Y27">
+        <f>Calculations!Z84+$I$21*1000</f>
+        <v>50959.432999999997</v>
+      </c>
+      <c r="Z27">
+        <f>Calculations!AA84+$I$21*1000</f>
+        <v>50979.940999999999</v>
+      </c>
+      <c r="AA27">
+        <f>Calculations!AB84+$I$21*1000</f>
+        <v>51000.097000000002</v>
+      </c>
+      <c r="AB27">
+        <f>Calculations!AC84+$I$21*1000</f>
+        <v>51019.017999999996</v>
+      </c>
+      <c r="AC27">
+        <f>Calculations!AD84+$I$21*1000</f>
+        <v>51039.06</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="C9:E9"/>
+    <mergeCell ref="F9:I9"/>
+    <mergeCell ref="B11:E11"/>
+    <mergeCell ref="F11:I11"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -29287,109 +29551,109 @@
         <f>Calculations!D84</f>
         <v>1468.7250000000001</v>
       </c>
-      <c r="C4" s="82">
-        <f>'Data Center Gas'!C26</f>
-        <v>1508.008</v>
-      </c>
-      <c r="D4" s="82">
-        <f>'Data Center Gas'!D26</f>
-        <v>8020.9689999999991</v>
-      </c>
-      <c r="E4" s="82">
-        <f>'Data Center Gas'!E26</f>
-        <v>14519.124999999998</v>
-      </c>
-      <c r="F4" s="82">
-        <f>'Data Center Gas'!F26</f>
-        <v>21016.868999999995</v>
-      </c>
-      <c r="G4" s="82">
-        <f>'Data Center Gas'!G26</f>
-        <v>27515.394999999997</v>
-      </c>
-      <c r="H4" s="82">
-        <f>'Data Center Gas'!H26</f>
-        <v>34015.290999999997</v>
-      </c>
-      <c r="I4" s="82">
-        <f>'Data Center Gas'!I26</f>
-        <v>34034.760999999999</v>
-      </c>
-      <c r="J4" s="82">
-        <f>'Data Center Gas'!J26</f>
-        <v>34055.343999999997</v>
-      </c>
-      <c r="K4" s="82">
-        <f>'Data Center Gas'!K26</f>
-        <v>34076.552000000003</v>
-      </c>
-      <c r="L4" s="82">
-        <f>'Data Center Gas'!L26</f>
-        <v>34100.095000000001</v>
-      </c>
-      <c r="M4" s="82">
-        <f>'Data Center Gas'!M26</f>
-        <v>34122.014000000003</v>
-      </c>
-      <c r="N4" s="82">
-        <f>'Data Center Gas'!N26</f>
-        <v>34144.811999999998</v>
-      </c>
-      <c r="O4" s="82">
-        <f>'Data Center Gas'!O26</f>
-        <v>34169.997000000003</v>
-      </c>
-      <c r="P4" s="82">
-        <f>'Data Center Gas'!P26</f>
-        <v>34193.459000000003</v>
-      </c>
-      <c r="Q4" s="82">
-        <f>'Data Center Gas'!Q26</f>
-        <v>34216.315999999999</v>
-      </c>
-      <c r="R4" s="82">
-        <f>'Data Center Gas'!R26</f>
-        <v>34238.228000000003</v>
-      </c>
-      <c r="S4" s="82">
-        <f>'Data Center Gas'!S26</f>
-        <v>34258.498999999996</v>
-      </c>
-      <c r="T4" s="82">
-        <f>'Data Center Gas'!T26</f>
-        <v>34281.084999999999</v>
-      </c>
-      <c r="U4" s="82">
-        <f>'Data Center Gas'!U26</f>
-        <v>34301.161999999997</v>
-      </c>
-      <c r="V4" s="82">
-        <f>'Data Center Gas'!V26</f>
-        <v>34321.178</v>
-      </c>
-      <c r="W4" s="82">
-        <f>'Data Center Gas'!W26</f>
-        <v>34340.084000000003</v>
-      </c>
-      <c r="X4" s="82">
-        <f>'Data Center Gas'!X26</f>
-        <v>34359.432999999997</v>
-      </c>
-      <c r="Y4" s="82">
-        <f>'Data Center Gas'!Y26</f>
-        <v>34379.940999999999</v>
-      </c>
-      <c r="Z4" s="82">
-        <f>'Data Center Gas'!Z26</f>
-        <v>34400.097000000002</v>
-      </c>
-      <c r="AA4" s="82">
-        <f>'Data Center Gas'!AA26</f>
-        <v>34419.017999999996</v>
-      </c>
-      <c r="AB4" s="82">
-        <f>'Data Center Gas'!AB26</f>
-        <v>34439.06</v>
+      <c r="C4" s="64">
+        <f>'Data Center Gas'!D27</f>
+        <v>18508.008000000002</v>
+      </c>
+      <c r="D4" s="64">
+        <f>'Data Center Gas'!E27</f>
+        <v>22540.969000000001</v>
+      </c>
+      <c r="E4" s="64">
+        <f>'Data Center Gas'!F27</f>
+        <v>26559.125</v>
+      </c>
+      <c r="F4" s="64">
+        <f>'Data Center Gas'!G27</f>
+        <v>30576.868999999999</v>
+      </c>
+      <c r="G4" s="64">
+        <f>'Data Center Gas'!H27</f>
+        <v>40595.394999999997</v>
+      </c>
+      <c r="H4" s="64">
+        <f>'Data Center Gas'!I27</f>
+        <v>50615.290999999997</v>
+      </c>
+      <c r="I4" s="64">
+        <f>'Data Center Gas'!J27</f>
+        <v>50634.760999999999</v>
+      </c>
+      <c r="J4" s="64">
+        <f>'Data Center Gas'!K27</f>
+        <v>50655.343999999997</v>
+      </c>
+      <c r="K4" s="64">
+        <f>'Data Center Gas'!L27</f>
+        <v>50676.552000000003</v>
+      </c>
+      <c r="L4" s="64">
+        <f>'Data Center Gas'!M27</f>
+        <v>50700.095000000001</v>
+      </c>
+      <c r="M4" s="64">
+        <f>'Data Center Gas'!N27</f>
+        <v>50722.014000000003</v>
+      </c>
+      <c r="N4" s="64">
+        <f>'Data Center Gas'!O27</f>
+        <v>50744.811999999998</v>
+      </c>
+      <c r="O4" s="64">
+        <f>'Data Center Gas'!P27</f>
+        <v>50769.997000000003</v>
+      </c>
+      <c r="P4" s="64">
+        <f>'Data Center Gas'!Q27</f>
+        <v>50793.459000000003</v>
+      </c>
+      <c r="Q4" s="64">
+        <f>'Data Center Gas'!R27</f>
+        <v>50816.315999999999</v>
+      </c>
+      <c r="R4" s="64">
+        <f>'Data Center Gas'!S27</f>
+        <v>50838.228000000003</v>
+      </c>
+      <c r="S4" s="64">
+        <f>'Data Center Gas'!T27</f>
+        <v>50858.498999999996</v>
+      </c>
+      <c r="T4" s="64">
+        <f>'Data Center Gas'!U27</f>
+        <v>50881.084999999999</v>
+      </c>
+      <c r="U4" s="64">
+        <f>'Data Center Gas'!V27</f>
+        <v>50901.161999999997</v>
+      </c>
+      <c r="V4" s="64">
+        <f>'Data Center Gas'!W27</f>
+        <v>50921.178</v>
+      </c>
+      <c r="W4" s="64">
+        <f>'Data Center Gas'!X27</f>
+        <v>50940.084000000003</v>
+      </c>
+      <c r="X4" s="64">
+        <f>'Data Center Gas'!Y27</f>
+        <v>50959.432999999997</v>
+      </c>
+      <c r="Y4" s="64">
+        <f>'Data Center Gas'!Z27</f>
+        <v>50979.940999999999</v>
+      </c>
+      <c r="Z4" s="64">
+        <f>'Data Center Gas'!AA27</f>
+        <v>51000.097000000002</v>
+      </c>
+      <c r="AA4" s="64">
+        <f>'Data Center Gas'!AB27</f>
+        <v>51019.017999999996</v>
+      </c>
+      <c r="AB4" s="64">
+        <f>'Data Center Gas'!AC27</f>
+        <v>51039.06</v>
       </c>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.25">
@@ -31595,105 +31859,105 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="67" t="s">
+      <c r="A1" s="73" t="s">
         <v>959</v>
       </c>
-      <c r="B1" s="67"/>
-      <c r="C1" s="67"/>
-      <c r="D1" s="67"/>
-      <c r="E1" s="67"/>
-      <c r="F1" s="67"/>
-      <c r="G1" s="67"/>
-      <c r="H1" s="67"/>
-      <c r="I1" s="67"/>
-      <c r="J1" s="67"/>
-      <c r="K1" s="67"/>
-      <c r="L1" s="67"/>
-      <c r="M1" s="67"/>
-      <c r="N1" s="67"/>
-      <c r="O1" s="67"/>
-      <c r="P1" s="67"/>
-      <c r="Q1" s="67"/>
-      <c r="R1" s="67"/>
-      <c r="S1" s="67"/>
-      <c r="T1" s="67"/>
-      <c r="U1" s="67"/>
+      <c r="B1" s="73"/>
+      <c r="C1" s="73"/>
+      <c r="D1" s="73"/>
+      <c r="E1" s="73"/>
+      <c r="F1" s="73"/>
+      <c r="G1" s="73"/>
+      <c r="H1" s="73"/>
+      <c r="I1" s="73"/>
+      <c r="J1" s="73"/>
+      <c r="K1" s="73"/>
+      <c r="L1" s="73"/>
+      <c r="M1" s="73"/>
+      <c r="N1" s="73"/>
+      <c r="O1" s="73"/>
+      <c r="P1" s="73"/>
+      <c r="Q1" s="73"/>
+      <c r="R1" s="73"/>
+      <c r="S1" s="73"/>
+      <c r="T1" s="73"/>
+      <c r="U1" s="73"/>
     </row>
     <row r="2" spans="1:21" ht="39" x14ac:dyDescent="0.25">
       <c r="A2" s="63" t="s">
         <v>958</v>
       </c>
-      <c r="B2" s="64" t="s">
+      <c r="B2" s="74" t="s">
         <v>957</v>
       </c>
-      <c r="C2" s="68"/>
-      <c r="D2" s="68"/>
-      <c r="E2" s="68"/>
-      <c r="F2" s="68"/>
-      <c r="G2" s="68"/>
-      <c r="H2" s="68"/>
-      <c r="I2" s="68"/>
-      <c r="J2" s="68"/>
-      <c r="K2" s="68"/>
-      <c r="L2" s="68"/>
-      <c r="M2" s="68"/>
-      <c r="N2" s="68"/>
-      <c r="O2" s="65"/>
-      <c r="P2" s="64" t="s">
+      <c r="C2" s="75"/>
+      <c r="D2" s="75"/>
+      <c r="E2" s="75"/>
+      <c r="F2" s="75"/>
+      <c r="G2" s="75"/>
+      <c r="H2" s="75"/>
+      <c r="I2" s="75"/>
+      <c r="J2" s="75"/>
+      <c r="K2" s="75"/>
+      <c r="L2" s="75"/>
+      <c r="M2" s="75"/>
+      <c r="N2" s="75"/>
+      <c r="O2" s="76"/>
+      <c r="P2" s="74" t="s">
         <v>956</v>
       </c>
-      <c r="Q2" s="65"/>
-      <c r="R2" s="64" t="s">
+      <c r="Q2" s="76"/>
+      <c r="R2" s="74" t="s">
         <v>955</v>
       </c>
-      <c r="S2" s="68"/>
-      <c r="T2" s="68"/>
-      <c r="U2" s="65"/>
+      <c r="S2" s="75"/>
+      <c r="T2" s="75"/>
+      <c r="U2" s="76"/>
     </row>
     <row r="3" spans="1:21" ht="39" x14ac:dyDescent="0.25">
       <c r="A3" s="63" t="s">
         <v>954</v>
       </c>
-      <c r="B3" s="64" t="s">
+      <c r="B3" s="74" t="s">
         <v>86</v>
       </c>
-      <c r="C3" s="65"/>
-      <c r="D3" s="64" t="s">
+      <c r="C3" s="76"/>
+      <c r="D3" s="74" t="s">
         <v>953</v>
       </c>
-      <c r="E3" s="65"/>
-      <c r="F3" s="64" t="s">
+      <c r="E3" s="76"/>
+      <c r="F3" s="74" t="s">
         <v>44</v>
       </c>
-      <c r="G3" s="65"/>
-      <c r="H3" s="64" t="s">
+      <c r="G3" s="76"/>
+      <c r="H3" s="74" t="s">
         <v>952</v>
       </c>
-      <c r="I3" s="65"/>
-      <c r="J3" s="64" t="s">
+      <c r="I3" s="76"/>
+      <c r="J3" s="74" t="s">
         <v>951</v>
       </c>
-      <c r="K3" s="65"/>
-      <c r="L3" s="64" t="s">
+      <c r="K3" s="76"/>
+      <c r="L3" s="74" t="s">
         <v>950</v>
       </c>
-      <c r="M3" s="65"/>
-      <c r="N3" s="64" t="s">
+      <c r="M3" s="76"/>
+      <c r="N3" s="74" t="s">
         <v>949</v>
       </c>
-      <c r="O3" s="65"/>
-      <c r="P3" s="64" t="s">
+      <c r="O3" s="76"/>
+      <c r="P3" s="74" t="s">
         <v>948</v>
       </c>
-      <c r="Q3" s="65"/>
-      <c r="R3" s="64" t="s">
+      <c r="Q3" s="76"/>
+      <c r="R3" s="74" t="s">
         <v>947</v>
       </c>
-      <c r="S3" s="65"/>
-      <c r="T3" s="64" t="s">
+      <c r="S3" s="76"/>
+      <c r="T3" s="74" t="s">
         <v>946</v>
       </c>
-      <c r="U3" s="65"/>
+      <c r="U3" s="76"/>
     </row>
     <row r="4" spans="1:21" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A4" s="63" t="s">
@@ -35791,32 +36055,33 @@
       </c>
     </row>
     <row r="67" spans="1:21" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="66" t="s">
+      <c r="A67" s="72" t="s">
         <v>887</v>
       </c>
-      <c r="B67" s="66"/>
-      <c r="C67" s="66"/>
-      <c r="D67" s="66"/>
-      <c r="E67" s="66"/>
-      <c r="F67" s="66"/>
-      <c r="G67" s="66"/>
-      <c r="H67" s="66"/>
-      <c r="I67" s="66"/>
-      <c r="J67" s="66"/>
-      <c r="K67" s="66"/>
-      <c r="L67" s="66"/>
-      <c r="M67" s="66"/>
-      <c r="N67" s="66"/>
-      <c r="O67" s="66"/>
-      <c r="P67" s="66"/>
-      <c r="Q67" s="66"/>
-      <c r="R67" s="66"/>
-      <c r="S67" s="66"/>
-      <c r="T67" s="66"/>
-      <c r="U67" s="66"/>
+      <c r="B67" s="72"/>
+      <c r="C67" s="72"/>
+      <c r="D67" s="72"/>
+      <c r="E67" s="72"/>
+      <c r="F67" s="72"/>
+      <c r="G67" s="72"/>
+      <c r="H67" s="72"/>
+      <c r="I67" s="72"/>
+      <c r="J67" s="72"/>
+      <c r="K67" s="72"/>
+      <c r="L67" s="72"/>
+      <c r="M67" s="72"/>
+      <c r="N67" s="72"/>
+      <c r="O67" s="72"/>
+      <c r="P67" s="72"/>
+      <c r="Q67" s="72"/>
+      <c r="R67" s="72"/>
+      <c r="S67" s="72"/>
+      <c r="T67" s="72"/>
+      <c r="U67" s="72"/>
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="A67:U67"/>
     <mergeCell ref="A1:U1"/>
     <mergeCell ref="B2:O2"/>
     <mergeCell ref="P2:Q2"/>
@@ -35831,7 +36096,6 @@
     <mergeCell ref="P3:Q3"/>
     <mergeCell ref="R3:S3"/>
     <mergeCell ref="T3:U3"/>
-    <mergeCell ref="A67:U67"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup scale="37" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -48528,43 +48792,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="78" t="s">
+      <c r="A1" s="86" t="s">
         <v>369</v>
       </c>
-      <c r="B1" s="75"/>
+      <c r="B1" s="83"/>
     </row>
     <row r="2" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="74" t="s">
+      <c r="A2" s="82" t="s">
         <v>370</v>
       </c>
-      <c r="B2" s="75"/>
-      <c r="C2" s="75"/>
-      <c r="D2" s="75"/>
-      <c r="E2" s="75"/>
-      <c r="F2" s="75"/>
-      <c r="G2" s="75"/>
+      <c r="B2" s="83"/>
+      <c r="C2" s="83"/>
+      <c r="D2" s="83"/>
+      <c r="E2" s="83"/>
+      <c r="F2" s="83"/>
+      <c r="G2" s="83"/>
     </row>
     <row r="3" spans="1:7" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="17"/>
-      <c r="B3" s="69" t="s">
+      <c r="B3" s="77" t="s">
         <v>371</v>
       </c>
-      <c r="C3" s="70"/>
-      <c r="D3" s="70"/>
-      <c r="E3" s="70"/>
-      <c r="F3" s="70"/>
-      <c r="G3" s="70"/>
+      <c r="C3" s="78"/>
+      <c r="D3" s="78"/>
+      <c r="E3" s="78"/>
+      <c r="F3" s="78"/>
+      <c r="G3" s="78"/>
     </row>
     <row r="4" spans="1:7" ht="23.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A4" s="17"/>
       <c r="B4" s="19"/>
-      <c r="C4" s="71" t="s">
+      <c r="C4" s="79" t="s">
         <v>372</v>
       </c>
-      <c r="D4" s="72"/>
-      <c r="E4" s="72"/>
-      <c r="F4" s="72"/>
-      <c r="G4" s="73"/>
+      <c r="D4" s="80"/>
+      <c r="E4" s="80"/>
+      <c r="F4" s="80"/>
+      <c r="G4" s="81"/>
     </row>
     <row r="5" spans="1:7" ht="46.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="20"/>
@@ -53085,15 +53349,15 @@
       <c r="G220" s="25"/>
     </row>
     <row r="221" spans="1:7" s="6" customFormat="1" ht="206.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A221" s="76" t="s">
+      <c r="A221" s="84" t="s">
         <v>523</v>
       </c>
-      <c r="B221" s="77"/>
-      <c r="C221" s="77"/>
-      <c r="D221" s="77"/>
-      <c r="E221" s="77"/>
-      <c r="F221" s="77"/>
-      <c r="G221" s="77"/>
+      <c r="B221" s="85"/>
+      <c r="C221" s="85"/>
+      <c r="D221" s="85"/>
+      <c r="E221" s="85"/>
+      <c r="F221" s="85"/>
+      <c r="G221" s="85"/>
     </row>
     <row r="222" spans="1:7" s="6" customFormat="1" x14ac:dyDescent="0.25"/>
   </sheetData>
